--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1830,13 +1830,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.0019957176</v>
+        <v>46149.168662384254</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70624586806</v>
+        <v>46175.87291253472</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706257777776</v>
+        <v>46175.87292444444</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1883,13 +1883,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.00206601852</v>
+        <v>46149.16873268518</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.706218611114</v>
+        <v>46175.87288527778</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70624668981</v>
+        <v>46175.87291335648</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1946,13 +1946,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.00206940972</v>
+        <v>46149.16873607639</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70621924769</v>
+        <v>46175.87288591435</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.706246608795</v>
+        <v>46175.87291327547</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2009,13 +2009,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.002072152776</v>
+        <v>46149.16873881944</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.70621967592</v>
+        <v>46175.87288634259</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.706247800925</v>
+        <v>46175.87291446759</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2072,13 +2072,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.00207495371</v>
+        <v>46149.16874162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70622006945</v>
+        <v>46175.872886736106</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70624652778</v>
+        <v>46175.87291319444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2135,13 +2135,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.002078136575</v>
+        <v>46149.16874480324</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70622064815</v>
+        <v>46175.872887314814</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70624614583</v>
+        <v>46175.8729128125</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2198,11 +2198,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.00200085648</v>
+        <v>46149.16866752315</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46183.704021944446</v>
+        <v>46183.87068861111</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2245,13 +2245,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.00208121528</v>
+        <v>46149.168747881944</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.7040040625</v>
+        <v>46183.87067072917</v>
       </c>
       <c r="D11" s="9">
-        <v>46183.70402252315</v>
+        <v>46183.87068918982</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>51</v>
@@ -2310,13 +2310,13 @@
         <v>56</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.00208630787</v>
+        <v>46149.16875297454</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.70401074074</v>
+        <v>46183.87067740741</v>
       </c>
       <c r="D12" s="5">
-        <v>46183.70402590278</v>
+        <v>46183.87069256944</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>57</v>
@@ -2375,13 +2375,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.002091331015</v>
+        <v>46149.168757997686</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.70401635417</v>
+        <v>46183.87068302083</v>
       </c>
       <c r="D13" s="9">
-        <v>46183.70403271991</v>
+        <v>46183.87069938658</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>61</v>
@@ -2440,11 +2440,11 @@
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.00209608796</v>
+        <v>46149.168762754634</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46183.70403209491</v>
+        <v>46183.87069876157</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2503,11 +2503,11 @@
         <v>68</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.00200555555</v>
+        <v>46149.16867222222</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46155.38555898148</v>
+        <v>46155.55222564815</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>69</v>
@@ -2550,11 +2550,11 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.00210356481</v>
+        <v>46149.16877023148</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46183.704032118054</v>
+        <v>46183.870698784725</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2613,11 +2613,11 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.00210846065</v>
+        <v>46149.16877512731</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46183.70402885417</v>
+        <v>46183.87069552083</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2676,11 +2676,11 @@
         <v>77</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.00211332176</v>
+        <v>46149.168779988424</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46183.70402866898</v>
+        <v>46183.870695335645</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>78</v>
@@ -2739,11 +2739,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.002118171295</v>
+        <v>46149.168784837966</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46181.01144054398</v>
+        <v>46181.17810721065</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2802,11 +2802,11 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.00212268518</v>
+        <v>46149.168789351854</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46181.01144054398</v>
+        <v>46181.17810721065</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2865,11 +2865,11 @@
         <v>92</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.00212619213</v>
+        <v>46149.16879285879</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46181.01144111111</v>
+        <v>46181.17810777778</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>93</v>
@@ -2928,11 +2928,11 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.00212975695</v>
+        <v>46149.16879642361</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46181.01144061342</v>
+        <v>46181.178107280095</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2991,11 +2991,11 @@
         <v>98</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.002010208336</v>
+        <v>46149.168676875</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46155.386767407406</v>
+        <v>46155.55343407407</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>99</v>
@@ -3038,11 +3038,11 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.00213346065</v>
+        <v>46149.168800127314</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.693065011576</v>
+        <v>46169.85973167824</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3101,11 +3101,11 @@
         <v>106</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.00213748842</v>
+        <v>46149.168804155095</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.6935390625</v>
+        <v>46169.86020572917</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>107</v>
@@ -3160,11 +3160,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.002141944446</v>
+        <v>46149.16880861111</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.693560740736</v>
+        <v>46169.86022740741</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3219,11 +3219,11 @@
         <v>113</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.00214671296</v>
+        <v>46149.16881337963</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46179.010007881945</v>
+        <v>46179.17667454861</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>114</v>
@@ -3282,11 +3282,11 @@
         <v>116</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.00215085648</v>
+        <v>46149.16881752315</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.69348751157</v>
+        <v>46169.86015417824</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>117</v>
@@ -3341,11 +3341,11 @@
         <v>119</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.00215518518</v>
+        <v>46149.168821851854</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46178.00393269676</v>
+        <v>46178.170599363424</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>120</v>
@@ -3400,11 +3400,11 @@
         <v>122</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.00215962963</v>
+        <v>46149.1688262963</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.69309373843</v>
+        <v>46169.85976040509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>123</v>
@@ -3463,11 +3463,11 @@
         <v>125</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.00216386574</v>
+        <v>46149.168830532406</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46169.693425115736</v>
+        <v>46169.86009178241</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>126</v>
@@ -3522,11 +3522,11 @@
         <v>128</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.002168287036</v>
+        <v>46149.1688349537</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.69343840278</v>
+        <v>46169.86010506944</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -3581,11 +3581,11 @@
         <v>131</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.002173333334</v>
+        <v>46149.16884</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46185.357815497686</v>
+        <v>46185.52448216435</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>132</v>
@@ -3640,11 +3640,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.00217770833</v>
+        <v>46149.168844375</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.69310417824</v>
+        <v>46169.85977084491</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3703,11 +3703,11 @@
         <v>139</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.00218226852</v>
+        <v>46149.16884893518</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.69337840278</v>
+        <v>46169.86004506944</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -3762,11 +3762,11 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.00218697917</v>
+        <v>46149.16885364584</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.69339541667</v>
+        <v>46169.86006208333</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3821,11 +3821,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.002191770836</v>
+        <v>46149.1688584375</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.69312092593</v>
+        <v>46169.85978759259</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -3884,11 +3884,11 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.00224469908</v>
+        <v>46149.16891136574</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.69332421296</v>
+        <v>46169.85999087963</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>91</v>
@@ -3937,11 +3937,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.002250590274</v>
+        <v>46149.168917256946</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69334290509</v>
+        <v>46169.860009571756</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>151</v>
@@ -3990,11 +3990,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.0022559375</v>
+        <v>46149.16892260416</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.69313453704</v>
+        <v>46169.859801203704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4053,11 +4053,11 @@
         <v>158</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.00226620371</v>
+        <v>46149.168932870365</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69326101852</v>
+        <v>46169.85992768519</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>97</v>
@@ -4106,11 +4106,11 @@
         <v>160</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.0022712963</v>
+        <v>46149.16893796297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.693275451384</v>
+        <v>46169.859942118055</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>161</v>
@@ -4159,11 +4159,11 @@
         <v>163</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.002276238425</v>
+        <v>46149.16894290509</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.69329935186</v>
+        <v>46169.859966018514</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>164</v>
@@ -4212,11 +4212,11 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.0022791088</v>
+        <v>46149.16894577546</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.693163819444</v>
+        <v>46169.85983048611</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>168</v>
@@ -4275,11 +4275,11 @@
         <v>170</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.002283043985</v>
+        <v>46149.16894971065</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.693206805554</v>
+        <v>46169.85987347222</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>94</v>
@@ -4326,11 +4326,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.002287615745</v>
+        <v>46149.1689542824</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.69323024305</v>
+        <v>46169.85989690972</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4377,11 +4377,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.00201474537</v>
+        <v>46149.16868141203</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.34826416666</v>
+        <v>46184.514930833335</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4424,13 +4424,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.00229319444</v>
+        <v>46149.16895986111</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.34825659722</v>
+        <v>46184.514923263894</v>
       </c>
       <c r="D48" s="5">
-        <v>46184.34827644676</v>
+        <v>46184.51494311343</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4489,11 +4489,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.00229898148</v>
+        <v>46149.16896564815</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.348264722226</v>
+        <v>46184.51493138889</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>
@@ -4552,11 +4552,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.002305497685</v>
+        <v>46149.16897216435</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46184.00210819444</v>
+        <v>46184.168774861115</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>85</v>
@@ -4613,11 +4613,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.00232021991</v>
+        <v>46149.16898688657</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.43178033565</v>
+        <v>46155.59844700231</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4676,11 +4676,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.00232474537</v>
+        <v>46149.168991412036</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.43188986111</v>
+        <v>46155.59855652778</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4727,11 +4727,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46149.00233350694</v>
+        <v>46149.16900017361</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.43188626158</v>
+        <v>46155.59855292824</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>195</v>
@@ -4778,11 +4778,11 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.41115071759</v>
+        <v>46155.577817384255</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.43188179398</v>
+        <v>46155.59854846065</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4829,11 +4829,11 @@
         <v>199</v>
       </c>
       <c r="B55" s="9">
-        <v>46155.41116238426</v>
+        <v>46155.577829050926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.43187822917</v>
+        <v>46155.59854489584</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -4880,11 +4880,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.002338425926</v>
+        <v>46149.1690050926</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.39226760417</v>
+        <v>46155.55893427083</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4927,11 +4927,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.00234274306</v>
+        <v>46149.16900940972</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46155.43200141204</v>
+        <v>46155.5986680787</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4990,11 +4990,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.00234849537</v>
+        <v>46149.16901516204</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46176.004980150465</v>
+        <v>46176.17164681713</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5053,11 +5053,11 @@
         <v>212</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.00235440972</v>
+        <v>46149.16902107639</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46155.43199861111</v>
+        <v>46155.59866527778</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>213</v>
@@ -5116,11 +5116,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.00235954861</v>
+        <v>46149.16902621528</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46176.004980185186</v>
+        <v>46176.17164685186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -5179,11 +5179,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.002363692125</v>
+        <v>46149.1690303588</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.43199493056</v>
+        <v>46155.59866159722</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>219</v>
@@ -5242,11 +5242,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.002368217596</v>
+        <v>46149.16903488426</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.43237927083</v>
+        <v>46155.5990459375</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5305,11 +5305,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.00237244213</v>
+        <v>46149.1690391088</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46155.4022115625</v>
+        <v>46155.56887822917</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5352,11 +5352,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.00237577547</v>
+        <v>46149.169042442125</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.410576712966</v>
+        <v>46161.57724337963</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>226</v>
@@ -5415,11 +5415,11 @@
         <v>230</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.002382708335</v>
+        <v>46149.169049375</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.43258655093</v>
+        <v>46155.59925321759</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>195</v>
@@ -5468,11 +5468,11 @@
         <v>233</v>
       </c>
       <c r="B66" s="5">
-        <v>46149.00238950232</v>
+        <v>46149.16905616898</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.432582939815</v>
+        <v>46155.59924960649</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>195</v>
@@ -5521,11 +5521,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.3954075</v>
+        <v>46155.562074166664</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.43258009259</v>
+        <v>46155.59924675926</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>195</v>
@@ -5574,11 +5574,11 @@
         <v>237</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.395428749995</v>
+        <v>46155.562095416666</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.432576956024</v>
+        <v>46155.59924362268</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>195</v>
@@ -5627,11 +5627,11 @@
         <v>238</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.0024380324</v>
+        <v>46149.169104699075</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.43267354167</v>
+        <v>46155.59934020833</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>239</v>
@@ -5690,11 +5690,11 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.00244297454</v>
+        <v>46149.1691096412</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.432840706024</v>
+        <v>46155.59950737268</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>195</v>
@@ -5743,11 +5743,11 @@
         <v>243</v>
       </c>
       <c r="B71" s="9">
-        <v>46149.002448252315</v>
+        <v>46149.16911491899</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.432837824075</v>
+        <v>46155.59950449074</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>195</v>
@@ -5796,11 +5796,11 @@
         <v>244</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.395558958335</v>
+        <v>46155.562225625</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.43283494213</v>
+        <v>46155.5995016088</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>195</v>
@@ -5849,11 +5849,11 @@
         <v>245</v>
       </c>
       <c r="B73" s="9">
-        <v>46155.39557891204</v>
+        <v>46155.56224557871</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.432830324076</v>
+        <v>46155.59949699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>195</v>
@@ -5902,11 +5902,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.00245310186</v>
+        <v>46149.169119768514</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.43271318287</v>
+        <v>46155.59937984953</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>247</v>
@@ -5965,11 +5965,11 @@
         <v>248</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.00245699074</v>
+        <v>46149.16912365741</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.43296878472</v>
+        <v>46155.59963545139</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>195</v>
@@ -6018,11 +6018,11 @@
         <v>250</v>
       </c>
       <c r="B76" s="5">
-        <v>46149.00246241898</v>
+        <v>46149.16912908565</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.43296608796</v>
+        <v>46155.59963275463</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -6071,11 +6071,11 @@
         <v>251</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.39566523148</v>
+        <v>46155.56233189815</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.432963287036</v>
+        <v>46155.59962995371</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>195</v>
@@ -6124,11 +6124,11 @@
         <v>253</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.395677685185</v>
+        <v>46155.562344351856</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.432959224534</v>
+        <v>46155.599625891206</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6177,11 +6177,11 @@
         <v>255</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.002467453705</v>
+        <v>46149.16913412037</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46155.40453425926</v>
+        <v>46155.57120092593</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>201</v>
@@ -6224,11 +6224,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.00247041667</v>
+        <v>46149.16913708333</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.00432209491</v>
+        <v>46182.17098876157</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6285,11 +6285,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.0024755787</v>
+        <v>46149.16914224537</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46165.01433276621</v>
+        <v>46165.180999432865</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6348,11 +6348,11 @@
         <v>263</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.0024806713</v>
+        <v>46149.16914733796</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.43318782408</v>
+        <v>46155.59985449074</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>264</v>
@@ -6411,11 +6411,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.002485694444</v>
+        <v>46149.16915236111</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.433183402776</v>
+        <v>46155.59985006944</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6474,11 +6474,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.002490659725</v>
+        <v>46149.16915732639</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.41604099537</v>
+        <v>46155.58270766203</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>269</v>
@@ -6521,11 +6521,11 @@
         <v>271</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.00249383102</v>
+        <v>46149.16916049768</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.433808553236</v>
+        <v>46155.60047521991</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>272</v>
@@ -6584,11 +6584,11 @@
         <v>274</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.00250018519</v>
+        <v>46149.16916685185</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.433358483795</v>
+        <v>46155.60002515046</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>195</v>
@@ -6637,11 +6637,11 @@
         <v>276</v>
       </c>
       <c r="B87" s="9">
-        <v>46149.002503703705</v>
+        <v>46149.16917037037</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.43335565973</v>
+        <v>46155.60002232638</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6690,11 +6690,11 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.39579900463</v>
+        <v>46155.5624656713</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.433599375</v>
+        <v>46155.60026604167</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>252</v>
@@ -6743,11 +6743,11 @@
         <v>279</v>
       </c>
       <c r="B89" s="9">
-        <v>46155.39582859953</v>
+        <v>46155.562495266204</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.4336925463</v>
+        <v>46155.600359212964</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>254</v>
@@ -6796,11 +6796,11 @@
         <v>280</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.002507384255</v>
+        <v>46149.16917405093</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.43397510417</v>
+        <v>46155.600641770834</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>281</v>
@@ -6859,11 +6859,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.0025116551</v>
+        <v>46149.169178321754</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.433939571754</v>
+        <v>46155.600606238426</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -6910,11 +6910,11 @@
         <v>285</v>
       </c>
       <c r="B92" s="5">
-        <v>46149.00251648148</v>
+        <v>46149.169183148144</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.43393666667</v>
+        <v>46155.60060333333</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>195</v>
@@ -6961,11 +6961,11 @@
         <v>286</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.3958999537</v>
+        <v>46155.56256662037</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.43393358796</v>
+        <v>46155.600600254635</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -7012,11 +7012,11 @@
         <v>288</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.3959118287</v>
+        <v>46155.56257849537</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.43392862269</v>
+        <v>46155.60059528935</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7063,11 +7063,11 @@
         <v>290</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.002521296294</v>
+        <v>46149.169187962965</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.434126782406</v>
+        <v>46155.60079344908</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>291</v>
@@ -7126,11 +7126,11 @@
         <v>292</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.00252525463</v>
+        <v>46149.1691919213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.43409681713</v>
+        <v>46155.600763483795</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>195</v>
@@ -7177,11 +7177,11 @@
         <v>294</v>
       </c>
       <c r="B97" s="9">
-        <v>46149.002530937505</v>
+        <v>46149.16919760416</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.43409390046</v>
+        <v>46155.60076056713</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>195</v>
@@ -7228,11 +7228,11 @@
         <v>295</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.39599376157</v>
+        <v>46155.562660428244</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.43409085648</v>
+        <v>46155.60075752315</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>195</v>
@@ -7279,11 +7279,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46155.3960052662</v>
+        <v>46155.56267193287</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.43408697916</v>
+        <v>46155.600753645835</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>195</v>
@@ -7330,11 +7330,11 @@
         <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.002536458334</v>
+        <v>46149.169203125</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.43427597222</v>
+        <v>46155.60094263889</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>300</v>
@@ -7393,11 +7393,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.00254027778</v>
+        <v>46149.16920694444</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.43425140047</v>
+        <v>46155.600918067124</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>195</v>
@@ -7444,11 +7444,11 @@
         <v>304</v>
       </c>
       <c r="B102" s="5">
-        <v>46149.002545358795</v>
+        <v>46149.16921202546</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.43424851852</v>
+        <v>46155.60091518519</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>195</v>
@@ -7495,11 +7495,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.396075185185</v>
+        <v>46155.562741851856</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.43424549769</v>
+        <v>46155.60091216435</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>195</v>
@@ -7546,11 +7546,11 @@
         <v>308</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.396088379624</v>
+        <v>46155.562755046296</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.43424113426</v>
+        <v>46155.60090780092</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>195</v>
@@ -7597,11 +7597,11 @@
         <v>310</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.00255023148</v>
+        <v>46149.16921689815</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.43443113426</v>
+        <v>46155.60109780093</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>311</v>
@@ -7660,11 +7660,11 @@
         <v>312</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.00255405092</v>
+        <v>46149.169220717595</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.43439899306</v>
+        <v>46155.60106565972</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>195</v>
@@ -7713,11 +7713,11 @@
         <v>314</v>
       </c>
       <c r="B107" s="9">
-        <v>46149.0025591088</v>
+        <v>46149.16922577546</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.43439587963</v>
+        <v>46155.601062546295</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>195</v>
@@ -7766,11 +7766,11 @@
         <v>315</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.39619076389</v>
+        <v>46155.56285743056</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.434392696756</v>
+        <v>46155.60105936343</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>195</v>
@@ -7819,11 +7819,11 @@
         <v>317</v>
       </c>
       <c r="B109" s="9">
-        <v>46155.39617944445</v>
+        <v>46155.56284611111</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.43438899306</v>
+        <v>46155.60105565972</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>195</v>
@@ -7872,11 +7872,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.0026037037</v>
+        <v>46149.169270370374</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.43460684028</v>
+        <v>46155.601273506945</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>319</v>
@@ -7935,11 +7935,11 @@
         <v>321</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.002618576385</v>
+        <v>46149.16928524306</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.434663796295</v>
+        <v>46155.60133046296</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>195</v>
@@ -7986,11 +7986,11 @@
         <v>323</v>
       </c>
       <c r="B112" s="5">
-        <v>46149.00262461806</v>
+        <v>46149.16929128472</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.43465982639</v>
+        <v>46155.60132649305</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>195</v>
@@ -8037,11 +8037,11 @@
         <v>324</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.396270694444</v>
+        <v>46155.562937361115</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.43465675926</v>
+        <v>46155.60132342593</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>195</v>
@@ -8088,11 +8088,11 @@
         <v>326</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.3962828588</v>
+        <v>46155.56294952546</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.434652233795</v>
+        <v>46155.60131890046</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>195</v>
@@ -8139,11 +8139,11 @@
         <v>327</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.00263028935</v>
+        <v>46149.16929695602</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.42410851852</v>
+        <v>46155.590775185185</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>328</v>
@@ -8186,11 +8186,11 @@
         <v>330</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.002634375</v>
+        <v>46149.169301041664</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.43480287037</v>
+        <v>46155.60146953704</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>331</v>
@@ -8247,11 +8247,11 @@
         <v>335</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.00264047454</v>
+        <v>46149.1693071412</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.43477612268</v>
+        <v>46155.60144278935</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>195</v>
@@ -8298,11 +8298,11 @@
         <v>337</v>
       </c>
       <c r="B118" s="5">
-        <v>46149.002645671295</v>
+        <v>46149.16931233797</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.4347725463</v>
+        <v>46155.60143921296</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>195</v>
@@ -8349,11 +8349,11 @@
         <v>339</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.39636403935</v>
+        <v>46155.56303070602</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.43476962963</v>
+        <v>46155.601436296296</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>195</v>
@@ -8400,11 +8400,11 @@
         <v>340</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.396393449075</v>
+        <v>46155.56306011574</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.4347652662</v>
+        <v>46155.60143193287</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>195</v>
@@ -8451,11 +8451,11 @@
         <v>341</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.00265083333</v>
+        <v>46149.1693175</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.43499337963</v>
+        <v>46155.6016600463</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>342</v>
@@ -8514,11 +8514,11 @@
         <v>343</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.00265581018</v>
+        <v>46149.16932247685</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.43496309027</v>
+        <v>46155.601629756944</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>195</v>
@@ -8567,11 +8567,11 @@
         <v>345</v>
       </c>
       <c r="B123" s="9">
-        <v>46149.002661631945</v>
+        <v>46149.16932829861</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.43496021991</v>
+        <v>46155.60162688658</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>195</v>
@@ -8620,11 +8620,11 @@
         <v>346</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.39646754629</v>
+        <v>46155.56313421296</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.43495775463</v>
+        <v>46155.601624421295</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>195</v>
@@ -8673,11 +8673,11 @@
         <v>348</v>
       </c>
       <c r="B125" s="9">
-        <v>46155.39647927083</v>
+        <v>46155.5631459375</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.43495400463</v>
+        <v>46155.601620671296</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>195</v>
@@ -8726,11 +8726,11 @@
         <v>350</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.002667002314</v>
+        <v>46149.16933366898</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.43525380787</v>
+        <v>46155.60192047454</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>351</v>
@@ -8789,11 +8789,11 @@
         <v>353</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.00267217593</v>
+        <v>46149.16933884259</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.43518712963</v>
+        <v>46155.601853796295</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>195</v>
@@ -8840,11 +8840,11 @@
         <v>355</v>
       </c>
       <c r="B128" s="5">
-        <v>46149.002680150465</v>
+        <v>46149.16934681713</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.43518783565</v>
+        <v>46155.60185450231</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>195</v>
@@ -8891,11 +8891,11 @@
         <v>357</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.39656795139</v>
+        <v>46155.56323461806</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.43518863426</v>
+        <v>46155.60185530093</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>254</v>
@@ -8942,11 +8942,11 @@
         <v>359</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.3965587037</v>
+        <v>46155.563225370366</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.43518936343</v>
+        <v>46155.60185603009</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>252</v>
@@ -8993,11 +8993,11 @@
         <v>361</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.00268677084</v>
+        <v>46149.1693534375</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.43549829861</v>
+        <v>46155.60216496528</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>362</v>
@@ -9056,11 +9056,11 @@
         <v>364</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.00269243056</v>
+        <v>46149.16935909722</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.435465613424</v>
+        <v>46155.602132280095</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>195</v>
@@ -9107,11 +9107,11 @@
         <v>365</v>
       </c>
       <c r="B133" s="9">
-        <v>46149.00269746528</v>
+        <v>46149.16936413194</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.43546230324</v>
+        <v>46155.602128969906</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>195</v>
@@ -9158,11 +9158,11 @@
         <v>366</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.396656111116</v>
+        <v>46155.56332277777</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.435458356485</v>
+        <v>46155.60212502315</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>252</v>
@@ -9209,11 +9209,11 @@
         <v>367</v>
       </c>
       <c r="B135" s="9">
-        <v>46155.39666601852</v>
+        <v>46155.56333268518</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.43545379629</v>
+        <v>46155.602120462965</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>254</v>
@@ -9260,11 +9260,11 @@
         <v>368</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.00270247685</v>
+        <v>46149.16936914352</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.43572224537</v>
+        <v>46155.60238891204</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>369</v>
@@ -9307,11 +9307,11 @@
         <v>371</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.00270646991</v>
+        <v>46149.169373136574</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46155.43555115741</v>
+        <v>46155.602217824075</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>372</v>
@@ -9370,11 +9370,11 @@
         <v>375</v>
       </c>
       <c r="B138" s="5">
-        <v>46149.00275068287</v>
+        <v>46149.169417349534</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46155.43583071759</v>
+        <v>46155.60249738426</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>376</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46181.17810721065</v>
+        <v>46188.16967509259</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46181.17810721065</v>
+        <v>46188.16967743056</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46181.17810777778</v>
+        <v>46188.16967888889</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>93</v>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46181.178107280095</v>
+        <v>46188.169680694446</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -333,118 +333,118 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4315</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214596725443928</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>1214596725443938</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036201</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4315</t>
+  </si>
+  <si>
+    <t>1214563704105176</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036211</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036226</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315,Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1214596725445208</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214596725445226</t>
+  </si>
+  <si>
+    <t>rodete OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4315,Generación OC Rodete OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772319023</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4315,rodete OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725454716</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4315</t>
+  </si>
+  <si>
+    <t>rodete OT 4315,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214596725454734</t>
+  </si>
+  <si>
+    <t>Motor OT 4315</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214596725443928</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>1214596725443938</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036201</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4315</t>
-  </si>
-  <si>
-    <t>1214563704105176</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036211</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036226</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315,Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1214596725445208</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214596725445226</t>
-  </si>
-  <si>
-    <t>rodete OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4315,Generación OC Rodete OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772319023</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4315,rodete OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725454716</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4315</t>
-  </si>
-  <si>
-    <t>rodete OT 4315,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214596725454734</t>
-  </si>
-  <si>
-    <t>Motor OT 4315</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
   </si>
   <si>
     <t>1214596772320275</t>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.16967509259</v>
+        <v>46189.188732361115</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2787,29 +2787,29 @@
       <c r="R19" s="9">
         <v>46188</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>87</v>
+      <c r="S19" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5">
         <v>46149.168789351854</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.16967743056</v>
+        <v>46189.1887321875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2842,7 +2842,7 @@
         <v>85</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2850,29 +2850,29 @@
       <c r="R20" s="5">
         <v>46188</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>87</v>
+      <c r="S20" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B21" s="9">
         <v>46149.16879285879</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.16967888889</v>
+        <v>46189.18873256944</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2905,7 +2905,7 @@
         <v>85</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2913,29 +2913,29 @@
       <c r="R21" s="9">
         <v>46188</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>87</v>
+      <c r="S21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46149.16879642361</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46188.169680694446</v>
+        <v>46189.18873219907</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2968,7 +2968,7 @@
         <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q22" s="5">
         <v>46185</v>
@@ -2976,19 +2976,19 @@
       <c r="R22" s="5">
         <v>46188</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>87</v>
+      <c r="S22" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168676875</v>
@@ -2998,7 +2998,7 @@
         <v>46155.55343407407</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3022,7 +3022,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168800127314</v>
@@ -3045,16 +3045,16 @@
         <v>46169.85973167824</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3072,13 +3072,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46157</v>
@@ -3093,12 +3093,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46149.168804155095</v>
@@ -3108,16 +3108,16 @@
         <v>46169.86020572917</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="I25" s="9">
         <v>46157</v>
@@ -3135,29 +3135,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16880861111</v>
@@ -3167,16 +3167,16 @@
         <v>46169.86022740741</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46161</v>
@@ -3194,29 +3194,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881337963</v>
@@ -3226,16 +3226,16 @@
         <v>46179.17667454861</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3253,13 +3253,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="9">
         <v>46157</v>
@@ -3274,12 +3274,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46149.16881752315</v>
@@ -3289,16 +3289,16 @@
         <v>46169.86015417824</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46157</v>
@@ -3316,29 +3316,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
         <v>46149.168821851854</v>
@@ -3348,16 +3348,16 @@
         <v>46178.170599363424</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="I29" s="9">
         <v>46161</v>
@@ -3375,48 +3375,48 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46149.1688262963</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.85976040509</v>
+        <v>46189.171886875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3434,13 +3434,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q30" s="5">
         <v>46157</v>
@@ -3448,14 +3448,14 @@
       <c r="R30" s="5">
         <v>46196</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>109</v>
+      <c r="S30" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3476,10 +3476,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="I31" s="9">
         <v>46157</v>
@@ -3497,7 +3497,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>72</v>
@@ -3508,13 +3508,13 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3535,10 +3535,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3556,7 +3556,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>126</v>
@@ -3567,13 +3567,13 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3594,10 +3594,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="I33" s="9">
         <v>46168</v>
@@ -3615,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>126</v>
@@ -3626,13 +3626,13 @@
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3674,13 +3674,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q34" s="5">
         <v>46189</v>
@@ -3689,13 +3689,13 @@
         <v>46199</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3748,13 +3748,13 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3807,13 +3807,13 @@
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3855,7 +3855,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>147</v>
@@ -3870,13 +3870,13 @@
         <v>46199</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3891,7 +3891,7 @@
         <v>46169.85999087963</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3921,7 +3921,7 @@
         <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>149</v>
@@ -3974,7 +3974,7 @@
         <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>152</v>
@@ -4024,7 +4024,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>157</v>
@@ -4039,13 +4039,13 @@
         <v>46230</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4060,7 +4060,7 @@
         <v>46169.85992768519</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4090,7 +4090,7 @@
         <v>154</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>159</v>
@@ -4143,7 +4143,7 @@
         <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>162</v>
@@ -4246,7 +4246,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>169</v>
@@ -4261,13 +4261,13 @@
         <v>46210</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4282,7 +4282,7 @@
         <v>46169.85987347222</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4310,7 +4310,7 @@
         <v>168</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>171</v>
@@ -4361,7 +4361,7 @@
         <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>174</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4599,13 +4599,13 @@
         <v>46153</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4662,13 +4662,13 @@
         <v>46241</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4976,13 +4976,13 @@
         <v>46203</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5102,13 +5102,13 @@
         <v>46203</v>
       </c>
       <c r="S59" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5228,13 +5228,13 @@
         <v>46212</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5291,13 +5291,13 @@
         <v>46216</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5401,13 +5401,13 @@
         <v>46219</v>
       </c>
       <c r="S64" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5676,13 +5676,13 @@
         <v>46226</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5951,13 +5951,13 @@
         <v>46227</v>
       </c>
       <c r="S74" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6259,7 +6259,7 @@
         <v>201</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>259</v>
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6322,7 +6322,7 @@
         <v>201</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>262</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6397,13 +6397,13 @@
         <v>46197</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6460,13 +6460,13 @@
         <v>46231</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6570,13 +6570,13 @@
         <v>46234</v>
       </c>
       <c r="S85" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T85" s="10">
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6845,13 +6845,13 @@
         <v>46237</v>
       </c>
       <c r="S90" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T90" s="6">
         <v>0</v>
       </c>
       <c r="U90" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -7112,13 +7112,13 @@
         <v>46238</v>
       </c>
       <c r="S95" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7379,13 +7379,13 @@
         <v>46239</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7646,13 +7646,13 @@
         <v>46240</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7921,13 +7921,13 @@
         <v>46244</v>
       </c>
       <c r="S110" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
       </c>
       <c r="U110" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8233,13 +8233,13 @@
         <v>46245</v>
       </c>
       <c r="S116" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
       </c>
       <c r="U116" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8500,13 +8500,13 @@
         <v>46246</v>
       </c>
       <c r="S121" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T121" s="10">
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -8775,13 +8775,13 @@
         <v>46247</v>
       </c>
       <c r="S126" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T126" s="6">
         <v>0</v>
       </c>
       <c r="U126" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
@@ -9042,13 +9042,13 @@
         <v>46248</v>
       </c>
       <c r="S131" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T131" s="10">
         <v>0</v>
       </c>
       <c r="U131" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -9356,13 +9356,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -9419,13 +9419,13 @@
         <v>46255</v>
       </c>
       <c r="S138" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T138" s="6">
         <v>0</v>
       </c>
       <c r="U138" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.86004506944</v>
+        <v>46190.16888383102</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>140</v>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.85999087963</v>
+        <v>46190.16888201389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>90</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.59985449074</v>
+        <v>46190.1987571875</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>264</v>
@@ -6396,8 +6396,8 @@
       <c r="R82" s="5">
         <v>46197</v>
       </c>
-      <c r="S82" s="7" t="s">
-        <v>108</v>
+      <c r="S82" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46183.870698784725</v>
+        <v>46191.54697938658</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="378">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.85987347222</v>
+        <v>46191.68554611111</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>93</v>
@@ -4288,9 +4288,11 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>137</v>
+      </c>
       <c r="I45" s="9">
         <v>46189</v>
       </c>
@@ -4330,7 +4332,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.85989690972</v>
+        <v>46191.68560096065</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4339,9 +4341,11 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6"/>
+        <v>136</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="I46" s="5">
         <v>46191</v>
       </c>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.85977084491</v>
+        <v>46192.19869972223</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3688,8 +3688,8 @@
       <c r="R34" s="5">
         <v>46199</v>
       </c>
-      <c r="S34" s="7" t="s">
-        <v>108</v>
+      <c r="S34" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.85978759259</v>
+        <v>46192.19869975695</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>146</v>
@@ -3869,8 +3869,8 @@
       <c r="R37" s="9">
         <v>46199</v>
       </c>
-      <c r="S37" s="7" t="s">
-        <v>108</v>
+      <c r="S37" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T37" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46191.54697938658</v>
+        <v>46192.552709386575</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -3404,7 +3404,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46189.171886875</v>
+        <v>46196.168625578706</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.86010506944</v>
+        <v>46196.16862795139</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>129</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46155.5986680787</v>
+        <v>46196.2065696412</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4979,8 +4979,8 @@
       <c r="R57" s="9">
         <v>46203</v>
       </c>
-      <c r="S57" s="7" t="s">
-        <v>108</v>
+      <c r="S57" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46155.59866527778</v>
+        <v>46196.20656958333</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>213</v>
@@ -5105,8 +5105,8 @@
       <c r="R59" s="9">
         <v>46203</v>
       </c>
-      <c r="S59" s="7" t="s">
-        <v>108</v>
+      <c r="S59" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="372">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -213,9 +213,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor,Analisis de costeo</t>
-  </si>
-  <si>
     <t>1214596734024341</t>
   </si>
   <si>
@@ -231,7 +228,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>propuesta motor OT 4315,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
+    <t>propuesta motor OT 4315,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1214596734024361</t>
@@ -249,7 +246,7 @@
 </t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete OT 4315,propuesta alabes OT 4315,Analisis de costeo</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete OT 4315,propuesta alabes OT 4315</t>
   </si>
   <si>
     <t>1214596623962646</t>
@@ -258,63 +255,51 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Planos preliminar,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1214596969796695</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Costos,Ingenieria Jefe de proyecto:</t>
+    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214563704105174</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4315,propuesta nucleo rodete OT 4315,propuesta motor OT 4315,propuesta Corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725443693</t>
+  </si>
+  <si>
+    <t>propuesta motor OT 4315</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725443713</t>
+  </si>
+  <si>
+    <t>propuesta alabes OT 4315</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>1214596623962872</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete OT 4315</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT 4315</t>
   </si>
   <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214563704105174</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4315,propuesta nucleo rodete OT 4315,propuesta motor OT 4315,propuesta Corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725443693</t>
-  </si>
-  <si>
-    <t>propuesta motor OT 4315</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725443713</t>
-  </si>
-  <si>
-    <t>propuesta alabes OT 4315</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>1214596623962872</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete OT 4315</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4315</t>
-  </si>
-  <si>
     <t>1214596623962892</t>
   </si>
   <si>
@@ -1201,9 +1186,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Despacho</t>
   </si>
 </sst>
 </file>
@@ -1727,7 +1709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:U137"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2200,9 +2182,11 @@
       <c r="B10" s="5">
         <v>46149.16866752315</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46196.871632326394</v>
+      </c>
       <c r="D10" s="5">
-        <v>46183.87068861111</v>
+        <v>46196.87164857639</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2229,7 +2213,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2237,12 +2221,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="9">
         <v>46149.168747881944</v>
@@ -2251,19 +2239,19 @@
         <v>46183.87067072917</v>
       </c>
       <c r="D11" s="9">
-        <v>46183.87068918982</v>
+        <v>46196.869429768514</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I11" s="9">
         <v>46153</v>
@@ -2275,7 +2263,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2287,7 +2275,7 @@
         <v>41</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="9">
         <v>46153</v>
@@ -2307,7 +2295,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46149.16875297454</v>
@@ -2316,19 +2304,19 @@
         <v>46183.87067740741</v>
       </c>
       <c r="D12" s="5">
-        <v>46183.87069256944</v>
+        <v>46196.86942973379</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="I12" s="5">
         <v>46153</v>
@@ -2340,7 +2328,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2352,7 +2340,7 @@
         <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46153</v>
@@ -2372,7 +2360,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46149.168757997686</v>
@@ -2381,19 +2369,19 @@
         <v>46183.87068302083</v>
       </c>
       <c r="D13" s="9">
-        <v>46183.87069938658</v>
+        <v>46196.869429722225</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I13" s="9">
         <v>46153</v>
@@ -2417,7 +2405,7 @@
         <v>41</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="9">
         <v>46153</v>
@@ -2437,90 +2425,82 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.168762754634</v>
+        <v>46149.16867222222</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46183.87069876157</v>
+        <v>46196.87158398148</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46153</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46161</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="P14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>46153</v>
-      </c>
-      <c r="R14" s="5">
-        <v>46161</v>
-      </c>
-      <c r="S14" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.16867222222</v>
-      </c>
-      <c r="C15" s="10"/>
+        <v>46149.16877023148</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46196.87156641204</v>
+      </c>
       <c r="D15" s="9">
-        <v>46155.55222564815</v>
+        <v>46196.871587870366</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
+        <v>51</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46155</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46156</v>
+      </c>
       <c r="K15" s="10" t="s">
         <v>26</v>
       </c>
@@ -2528,45 +2508,57 @@
         <v>26</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>46155</v>
+      </c>
+      <c r="R15" s="9">
+        <v>46156</v>
+      </c>
+      <c r="S15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="10">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.16877023148</v>
-      </c>
-      <c r="C16" s="6"/>
+        <v>46149.16877512731</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46196.87157603009</v>
+      </c>
       <c r="D16" s="5">
-        <v>46192.552709386575</v>
+        <v>46196.871593379634</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="I16" s="5">
         <v>46155</v>
@@ -2584,13 +2576,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46155</v>
@@ -2602,34 +2594,34 @@
         <v>33</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.16877512731</v>
+        <v>46149.168779988424</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46183.87069552083</v>
+        <v>46183.870695335645</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="I17" s="9">
         <v>46155</v>
@@ -2647,13 +2639,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2668,37 +2660,37 @@
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.168779988424</v>
+        <v>46149.168784837966</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46183.870695335645</v>
+        <v>46189.188732361115</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>79</v>
       </c>
       <c r="I18" s="5">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="J18" s="5">
-        <v>46156</v>
+        <v>46188</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>26</v>
@@ -2710,19 +2702,19 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="R18" s="5">
-        <v>46156</v>
+        <v>46188</v>
       </c>
       <c r="S18" s="11" t="s">
         <v>33</v>
@@ -2730,32 +2722,32 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>67</v>
+      <c r="U18" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.168784837966</v>
+        <v>46149.168789351854</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.188732361115</v>
+        <v>46189.1887321875</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I19" s="9">
         <v>46185</v>
@@ -2773,13 +2765,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2794,31 +2786,31 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.168789351854</v>
+        <v>46149.16879285879</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.1887321875</v>
+        <v>46189.18873256944</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I20" s="5">
         <v>46185</v>
@@ -2836,13 +2828,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2857,31 +2849,31 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.16879285879</v>
+        <v>46149.16879642361</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.18873256944</v>
+        <v>46189.18873219907</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I21" s="9">
         <v>46185</v>
@@ -2899,13 +2891,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2920,38 +2912,32 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.16879642361</v>
+        <v>46149.168676875</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46189.18873219907</v>
+        <v>46155.55343407407</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="5">
-        <v>46185</v>
-      </c>
-      <c r="J22" s="5">
-        <v>46188</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2959,56 +2945,52 @@
         <v>26</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>46185</v>
-      </c>
-      <c r="R22" s="5">
-        <v>46188</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.168676875</v>
+        <v>46149.168800127314</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46155.55343407407</v>
+        <v>46169.85973167824</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="I23" s="9">
+        <v>46157</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46162</v>
+      </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
       </c>
@@ -3016,33 +2998,43 @@
         <v>26</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>99</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
+        <v>93</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46157</v>
+      </c>
+      <c r="R23" s="9">
+        <v>46162</v>
+      </c>
+      <c r="S23" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="10">
+        <v>0</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.168800127314</v>
+        <v>46149.168804155095</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.85973167824</v>
+        <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3051,16 +3043,16 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
       </c>
       <c r="J24" s="5">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -3072,117 +3064,113 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>46157</v>
-      </c>
-      <c r="R24" s="5">
-        <v>46162</v>
-      </c>
-      <c r="S24" s="11" t="s">
-        <v>33</v>
+        <v>102</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.168804155095</v>
+        <v>46149.16880861111</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.86020572917</v>
+        <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46161</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46162</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="P25" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46157</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46160</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.16880861111</v>
+        <v>46149.16881337963</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.86022740741</v>
+        <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I26" s="5">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="J26" s="5">
-        <v>46162</v>
+        <v>46178</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>26</v>
@@ -3194,54 +3182,58 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="7" t="s">
-        <v>108</v>
+        <v>93</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>46157</v>
+      </c>
+      <c r="R26" s="5">
+        <v>46178</v>
+      </c>
+      <c r="S26" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.16881337963</v>
+        <v>46149.16881752315</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46179.17667454861</v>
+        <v>46169.86015417824</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
       </c>
       <c r="J27" s="9">
-        <v>46178</v>
+        <v>46160</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>26</v>
@@ -3253,58 +3245,54 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46157</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46178</v>
-      </c>
-      <c r="S27" s="11" t="s">
-        <v>33</v>
+        <v>112</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.16881752315</v>
+        <v>46149.168821851854</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.86015417824</v>
+        <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I28" s="5">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="J28" s="5">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -3316,113 +3304,117 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.168821851854</v>
+        <v>46149.1688262963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46178.170599363424</v>
+        <v>46196.168625578706</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46157</v>
+      </c>
+      <c r="J29" s="9">
+        <v>46196</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46157</v>
+      </c>
+      <c r="R29" s="9">
+        <v>46196</v>
+      </c>
+      <c r="S29" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="9">
-        <v>46161</v>
-      </c>
-      <c r="J29" s="9">
-        <v>46178</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.1688262963</v>
+        <v>46149.168830532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46196.168625578706</v>
+        <v>46196.87158207176</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
       </c>
       <c r="J30" s="5">
-        <v>46196</v>
+        <v>46167</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3434,58 +3426,54 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>46157</v>
-      </c>
-      <c r="R30" s="5">
-        <v>46196</v>
-      </c>
-      <c r="S30" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.168830532406</v>
+        <v>46149.1688349537</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46169.86009178241</v>
+        <v>46196.16862795139</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I31" s="9">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="J31" s="9">
-        <v>46167</v>
+        <v>46196</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>26</v>
@@ -3497,54 +3485,54 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.1688349537</v>
+        <v>46149.16884</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46196.16862795139</v>
+        <v>46185.52448216435</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
       </c>
       <c r="J32" s="5">
-        <v>46196</v>
+        <v>46176</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3556,54 +3544,54 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.16884</v>
+        <v>46149.168844375</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46185.52448216435</v>
+        <v>46192.19869972223</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>103</v>
-      </c>
       <c r="I33" s="9">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="J33" s="9">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3615,24 +3603,28 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="7" t="s">
-        <v>108</v>
+        <v>93</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>46189</v>
+      </c>
+      <c r="R33" s="9">
+        <v>46199</v>
+      </c>
+      <c r="S33" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3640,11 +3632,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.168844375</v>
+        <v>46149.16884893518</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46192.19869972223</v>
+        <v>46190.16888383102</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3653,16 +3645,16 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
       </c>
       <c r="J34" s="5">
-        <v>46199</v>
+        <v>46190</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3674,58 +3666,54 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46199</v>
-      </c>
-      <c r="S34" s="12" t="s">
-        <v>124</v>
+        <v>136</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.16884893518</v>
+        <v>46149.16885364584</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46190.16888383102</v>
+        <v>46169.86006208333</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I35" s="9">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="J35" s="9">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>26</v>
@@ -3737,51 +3725,51 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="O35" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="O35" s="10" t="s">
-        <v>82</v>
-      </c>
       <c r="P35" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.16885364584</v>
+        <v>46149.1688584375</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.86006208333</v>
+        <v>46192.19869975695</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="J36" s="5">
         <v>46199</v>
@@ -3796,54 +3784,58 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="7" t="s">
-        <v>108</v>
+        <v>26</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46189</v>
+      </c>
+      <c r="R36" s="5">
+        <v>46199</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.1688584375</v>
+        <v>46149.16891136574</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46192.19869975695</v>
+        <v>46190.16888201389</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
       </c>
       <c r="J37" s="9">
-        <v>46199</v>
+        <v>46190</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3855,58 +3847,48 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>46189</v>
-      </c>
-      <c r="R37" s="9">
-        <v>46199</v>
-      </c>
-      <c r="S37" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="T37" s="10">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.16891136574</v>
+        <v>46149.168917256946</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46190.16888201389</v>
+        <v>46169.860009571756</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="J38" s="5">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3918,13 +3900,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3934,32 +3916,32 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.168917256946</v>
+        <v>46149.16892260416</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.860009571756</v>
+        <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="I39" s="9">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="J39" s="9">
-        <v>46199</v>
+        <v>46230</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3971,48 +3953,58 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>46189</v>
+      </c>
+      <c r="R39" s="9">
+        <v>46230</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T39" s="10">
+        <v>0</v>
+      </c>
+      <c r="U39" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.16892260416</v>
+        <v>46149.168932870365</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.859801203704</v>
+        <v>46169.85992768519</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
       </c>
       <c r="J40" s="5">
-        <v>46230</v>
+        <v>46197</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -4024,58 +4016,48 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46230</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.168932870365</v>
+        <v>46149.16893796297</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.85992768519</v>
+        <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I41" s="9">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="J41" s="9">
-        <v>46197</v>
+        <v>46226</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>26</v>
@@ -4087,13 +4069,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4103,50 +4085,50 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.16893796297</v>
+        <v>46149.16894290509</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859942118055</v>
+        <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H42" s="6" t="s">
+      <c r="I42" s="5">
+        <v>46227</v>
+      </c>
+      <c r="J42" s="5">
+        <v>46230</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="I42" s="5">
-        <v>46198</v>
-      </c>
-      <c r="J42" s="5">
-        <v>46226</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4156,85 +4138,95 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.16894290509</v>
+        <v>46149.16894577546</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.859966018514</v>
+        <v>46169.85983048611</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I43" s="9">
+        <v>46189</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46210</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O43" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="I43" s="9">
-        <v>46227</v>
-      </c>
-      <c r="J43" s="9">
-        <v>46230</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
+      <c r="Q43" s="9">
+        <v>46189</v>
+      </c>
+      <c r="R43" s="9">
+        <v>46210</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T43" s="10">
+        <v>0</v>
+      </c>
+      <c r="U43" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.16894577546</v>
+        <v>46149.16894971065</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.85983048611</v>
+        <v>46191.68554611111</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
       </c>
       <c r="J44" s="5">
-        <v>46210</v>
+        <v>46190</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4246,58 +4238,48 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>169</v>
+        <v>87</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46210</v>
-      </c>
-      <c r="S44" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.16894971065</v>
+        <v>46149.1689542824</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46191.68554611111</v>
+        <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I45" s="9">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="J45" s="9">
-        <v>46190</v>
+        <v>46210</v>
       </c>
       <c r="K45" s="10" t="s">
         <v>26</v>
@@ -4309,13 +4291,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4325,33 +4307,27 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.1689542824</v>
+        <v>46149.16868141203</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46191.68560096065</v>
+        <v>46184.514930833335</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46191</v>
-      </c>
-      <c r="J46" s="5">
-        <v>46210</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
       <c r="K46" s="6" t="s">
         <v>26</v>
       </c>
@@ -4359,16 +4335,16 @@
         <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4378,27 +4354,35 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46149.16895986111</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46184.514923263894</v>
+      </c>
+      <c r="D47" s="9">
+        <v>46184.51494311343</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B47" s="9">
-        <v>46149.16868141203</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9">
-        <v>46184.514930833335</v>
-      </c>
-      <c r="E47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="I47" s="9">
+        <v>46162</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46168</v>
+      </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
       </c>
@@ -4406,35 +4390,43 @@
         <v>26</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="P47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
+      <c r="Q47" s="9">
+        <v>46162</v>
+      </c>
+      <c r="R47" s="9">
+        <v>46168</v>
+      </c>
+      <c r="S47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T47" s="10">
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.16895986111</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46184.514923263894</v>
-      </c>
+        <v>46149.16896564815</v>
+      </c>
+      <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46184.51494311343</v>
+        <v>46184.51493138889</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4443,79 +4435,77 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I48" s="5">
+        <v>46177</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46183</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="P48" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I48" s="5">
-        <v>46162</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46168</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="Q48" s="5">
-        <v>46162</v>
+        <v>46146</v>
       </c>
       <c r="R48" s="5">
-        <v>46168</v>
+        <v>46183</v>
       </c>
       <c r="S48" s="11" t="s">
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>1</v>
-      </c>
-      <c r="U48" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U48" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.16896564815</v>
+        <v>46149.16897216435</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.51493138889</v>
+        <v>46184.168774861115</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="I49" s="9">
-        <v>46177</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="I49" s="10"/>
       <c r="J49" s="9">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>26</v>
@@ -4527,56 +4517,58 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
-        <v>46146</v>
+        <v>46184</v>
       </c>
       <c r="R49" s="9">
-        <v>46183</v>
-      </c>
-      <c r="S49" s="11" t="s">
-        <v>33</v>
+        <v>46153</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.16897216435</v>
+        <v>46149.16898688657</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46184.168774861115</v>
+        <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I50" s="6"/>
+        <v>187</v>
+      </c>
+      <c r="I50" s="5">
+        <v>46241</v>
+      </c>
       <c r="J50" s="5">
-        <v>46184</v>
+        <v>46241</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4588,28 +4580,28 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>26</v>
       </c>
       <c r="Q50" s="5">
-        <v>46184</v>
+        <v>46241</v>
       </c>
       <c r="R50" s="5">
-        <v>46153</v>
+        <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4617,11 +4609,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.16898688657</v>
+        <v>46149.168991412036</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.59844700231</v>
+        <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4630,14 +4622,12 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="I51" s="9">
-        <v>46241</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I51" s="10"/>
       <c r="J51" s="9">
         <v>46241</v>
       </c>
@@ -4651,52 +4641,42 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>46241</v>
-      </c>
-      <c r="R51" s="9">
-        <v>46241</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.168991412036</v>
+        <v>46149.16900017361</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.59855652778</v>
+        <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4712,13 +4692,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="O52" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4728,26 +4708,26 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46149.16900017361</v>
+        <v>46155.577817384255</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.59855292824</v>
+        <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4763,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="O53" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="O53" s="10" t="s">
-        <v>195</v>
-      </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4779,26 +4759,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.577817384255</v>
+        <v>46155.577829050926</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.59854846065</v>
+        <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4814,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="O54" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="P54" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4830,31 +4810,27 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46155.577829050926</v>
+        <v>46149.1690050926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.59854489584</v>
+        <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>53</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H55" s="10"/>
       <c r="I55" s="10"/>
-      <c r="J55" s="9">
-        <v>46241</v>
-      </c>
+      <c r="J55" s="10"/>
       <c r="K55" s="10" t="s">
         <v>26</v>
       </c>
@@ -4862,16 +4838,16 @@
         <v>26</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>195</v>
+        <v>26</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4881,27 +4857,33 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.1690050926</v>
+        <v>46149.16900940972</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46155.55893427083</v>
+        <v>46196.2065696412</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
+      <c r="I56" s="5">
+        <v>46202</v>
+      </c>
+      <c r="J56" s="5">
+        <v>46203</v>
+      </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
       </c>
@@ -4909,33 +4891,43 @@
         <v>26</v>
       </c>
       <c r="M56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>46202</v>
+      </c>
+      <c r="R56" s="5">
+        <v>46203</v>
+      </c>
+      <c r="S56" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="N56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
+      <c r="U56" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.16900940972</v>
+        <v>46149.16901516204</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46196.2065696412</v>
+        <v>46176.17164681713</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4944,142 +4936,142 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="9">
+        <v>46204</v>
+      </c>
+      <c r="J57" s="9">
+        <v>46205</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O57" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="P57" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="I57" s="9">
-        <v>46202</v>
-      </c>
-      <c r="J57" s="9">
-        <v>46203</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="Q57" s="9">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="R57" s="9">
-        <v>46203</v>
-      </c>
-      <c r="S57" s="12" t="s">
-        <v>124</v>
+        <v>46175</v>
+      </c>
+      <c r="S57" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.16901516204</v>
+        <v>46149.16902107639</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46176.17164681713</v>
+        <v>46196.20656958333</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I58" s="5">
+        <v>46202</v>
+      </c>
+      <c r="J58" s="5">
+        <v>46203</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I58" s="5">
-        <v>46204</v>
-      </c>
-      <c r="J58" s="5">
-        <v>46205</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>211</v>
-      </c>
       <c r="Q58" s="5">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="R58" s="5">
-        <v>46175</v>
-      </c>
-      <c r="S58" s="11" t="s">
-        <v>33</v>
+        <v>46203</v>
+      </c>
+      <c r="S58" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.16902107639</v>
+        <v>46149.16902621528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46196.20656958333</v>
+        <v>46176.17164685186</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="I59" s="9">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="J59" s="9">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -5091,58 +5083,58 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="R59" s="9">
-        <v>46203</v>
-      </c>
-      <c r="S59" s="12" t="s">
-        <v>124</v>
+        <v>46175</v>
+      </c>
+      <c r="S59" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.16902621528</v>
+        <v>46149.1690303588</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46176.17164685186</v>
+        <v>46155.59866159722</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="J60" s="5">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -5154,58 +5146,58 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
-        <v>46174</v>
+        <v>46211</v>
       </c>
       <c r="R60" s="5">
-        <v>46175</v>
-      </c>
-      <c r="S60" s="11" t="s">
-        <v>33</v>
+        <v>46212</v>
+      </c>
+      <c r="S60" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.1690303588</v>
+        <v>46149.16903488426</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.59866159722</v>
+        <v>46155.5990459375</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="I61" s="9">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="J61" s="9">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="K61" s="10" t="s">
         <v>26</v>
@@ -5217,59 +5209,53 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="9">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="R61" s="9">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.16903488426</v>
+        <v>46149.1690391088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.5990459375</v>
+        <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I62" s="5">
-        <v>46213</v>
-      </c>
-      <c r="J62" s="5">
-        <v>46216</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
       <c r="K62" s="6" t="s">
         <v>26</v>
       </c>
@@ -5277,56 +5263,52 @@
         <v>26</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>46213</v>
-      </c>
-      <c r="R62" s="5">
-        <v>46216</v>
-      </c>
-      <c r="S62" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.1690391088</v>
+        <v>46149.169042442125</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46155.56887822917</v>
+        <v>46161.57724337963</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
+      <c r="I63" s="9">
+        <v>46217</v>
+      </c>
+      <c r="J63" s="9">
+        <v>46219</v>
+      </c>
       <c r="K63" s="10" t="s">
         <v>26</v>
       </c>
@@ -5334,45 +5316,55 @@
         <v>26</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>46217</v>
+      </c>
+      <c r="R63" s="9">
+        <v>46219</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T63" s="10">
+        <v>0</v>
+      </c>
+      <c r="U63" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.169042442125</v>
+        <v>46149.169049375</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46161.57724337963</v>
+        <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5390,52 +5382,42 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46217</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46219</v>
-      </c>
-      <c r="S64" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.169049375</v>
+        <v>46149.16905616898</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.59925321759</v>
+        <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5453,13 +5435,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5469,26 +5451,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46149.16905616898</v>
+        <v>46155.562074166664</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.59924960649</v>
+        <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5506,13 +5488,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5522,26 +5504,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.562074166664</v>
+        <v>46155.562095416666</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.59924675926</v>
+        <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5559,13 +5541,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5575,32 +5557,32 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46155.562095416666</v>
+        <v>46149.169104699075</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.59924362268</v>
+        <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I68" s="5">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="J68" s="5">
-        <v>46219</v>
+        <v>46226</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5612,42 +5594,52 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+        <v>218</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>46220</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46226</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T68" s="6">
+        <v>0</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.169104699075</v>
+        <v>46149.1691096412</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.59934020833</v>
+        <v>46155.59950737268</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5665,52 +5657,42 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q69" s="9">
-        <v>46220</v>
-      </c>
-      <c r="R69" s="9">
-        <v>46226</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.1691096412</v>
+        <v>46149.16911491899</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.59950737268</v>
+        <v>46155.59950449074</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5728,13 +5710,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5744,26 +5726,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46149.16911491899</v>
+        <v>46155.562225625</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.59950449074</v>
+        <v>46155.5995016088</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5781,13 +5763,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5797,26 +5779,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.562225625</v>
+        <v>46155.56224557871</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.5995016088</v>
+        <v>46155.59949699074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5834,13 +5816,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5850,32 +5832,32 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
-        <v>46155.56224557871</v>
+        <v>46149.169119768514</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.59949699074</v>
+        <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="I73" s="9">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="J73" s="9">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5887,42 +5869,52 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="10"/>
-      <c r="T73" s="10"/>
-      <c r="U73" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>46227</v>
+      </c>
+      <c r="R73" s="9">
+        <v>46227</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T73" s="10">
+        <v>0</v>
+      </c>
+      <c r="U73" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.169119768514</v>
+        <v>46149.16912365741</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.59937984953</v>
+        <v>46155.59963545139</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -5940,52 +5932,42 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46227</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46227</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.16912365741</v>
+        <v>46149.16912908565</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.59963545139</v>
+        <v>46155.59963275463</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6003,13 +5985,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6019,26 +6001,26 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
-        <v>46149.16912908565</v>
+        <v>46155.56233189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.59963275463</v>
+        <v>46155.59962995371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6056,13 +6038,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6072,26 +6054,26 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.56233189815</v>
+        <v>46155.562344351856</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.59962995371</v>
+        <v>46155.599625891206</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6109,13 +6091,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6125,33 +6107,27 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46155.562344351856</v>
+        <v>46149.16913412037</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.599625891206</v>
+        <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I78" s="5">
-        <v>46227</v>
-      </c>
-      <c r="J78" s="5">
-        <v>46227</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
       <c r="K78" s="6" t="s">
         <v>26</v>
       </c>
@@ -6159,16 +6135,16 @@
         <v>26</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>254</v>
+        <v>26</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6178,27 +6154,31 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.16913412037</v>
+        <v>46149.16913708333</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46155.57120092593</v>
+        <v>46182.17098876157</v>
       </c>
       <c r="E79" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="10"/>
       <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
+      <c r="J79" s="9">
+        <v>46181</v>
+      </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
       </c>
@@ -6206,49 +6186,61 @@
         <v>26</v>
       </c>
       <c r="M79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>46181</v>
+      </c>
+      <c r="R79" s="9">
+        <v>46181</v>
+      </c>
+      <c r="S79" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T79" s="10">
         <v>0</v>
       </c>
-      <c r="N79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
+      <c r="U79" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.16913708333</v>
+        <v>46149.16914224537</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.17098876157</v>
+        <v>46165.180999432865</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I80" s="6"/>
+        <v>201</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46164</v>
+      </c>
       <c r="J80" s="5">
-        <v>46181</v>
+        <v>46164</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6260,19 +6252,19 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="5">
-        <v>46181</v>
+        <v>46164</v>
       </c>
       <c r="R80" s="5">
-        <v>46181</v>
+        <v>46164</v>
       </c>
       <c r="S80" s="11" t="s">
         <v>33</v>
@@ -6281,37 +6273,37 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.16914224537</v>
+        <v>46149.16914733796</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46165.180999432865</v>
+        <v>46190.1987571875</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I81" s="9">
-        <v>46164</v>
+        <v>46197</v>
       </c>
       <c r="J81" s="9">
-        <v>46164</v>
+        <v>46197</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6323,58 +6315,58 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Q81" s="9">
-        <v>46164</v>
+        <v>46197</v>
       </c>
       <c r="R81" s="9">
-        <v>46164</v>
-      </c>
-      <c r="S81" s="11" t="s">
-        <v>33</v>
+        <v>46197</v>
+      </c>
+      <c r="S81" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.16914733796</v>
+        <v>46149.16915236111</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46190.1987571875</v>
+        <v>46155.59985006944</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="I82" s="5">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="J82" s="5">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -6386,59 +6378,53 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>262</v>
       </c>
       <c r="Q82" s="5">
-        <v>46197</v>
+        <v>46231</v>
       </c>
       <c r="R82" s="5">
-        <v>46197</v>
-      </c>
-      <c r="S82" s="12" t="s">
-        <v>124</v>
+        <v>46231</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.16915236111</v>
+        <v>46149.16915732639</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.59985006944</v>
+        <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="I83" s="9">
-        <v>46231</v>
-      </c>
-      <c r="J83" s="9">
-        <v>46231</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="10"/>
+      <c r="I83" s="10"/>
+      <c r="J83" s="10"/>
       <c r="K83" s="10" t="s">
         <v>26</v>
       </c>
@@ -6446,56 +6432,52 @@
         <v>26</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>161</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q83" s="9">
-        <v>46231</v>
-      </c>
-      <c r="R83" s="9">
-        <v>46231</v>
-      </c>
-      <c r="S83" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.16915732639</v>
+        <v>46149.16916049768</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.58270766203</v>
+        <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46230</v>
+      </c>
+      <c r="J84" s="5">
+        <v>46234</v>
+      </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
       </c>
@@ -6503,45 +6485,55 @@
         <v>26</v>
       </c>
       <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46230</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46234</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="N84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+      <c r="U84" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.16916049768</v>
+        <v>46149.16916685185</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.60047521991</v>
+        <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I85" s="9">
         <v>46230</v>
@@ -6559,52 +6551,42 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>46230</v>
-      </c>
-      <c r="R85" s="9">
-        <v>46234</v>
-      </c>
-      <c r="S85" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T85" s="10">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.16916685185</v>
+        <v>46149.16917037037</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.60002515046</v>
+        <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I86" s="5">
         <v>46230</v>
@@ -6622,10 +6604,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6638,26 +6620,26 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
-        <v>46149.16917037037</v>
+        <v>46155.5624656713</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.60002232638</v>
+        <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I87" s="9">
         <v>46230</v>
@@ -6675,13 +6657,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>275</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6691,26 +6673,26 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.5624656713</v>
+        <v>46155.562495266204</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.60026604167</v>
+        <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I88" s="5">
         <v>46230</v>
@@ -6728,13 +6710,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6744,32 +6726,32 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
-        <v>46155.562495266204</v>
+        <v>46149.16917405093</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.600359212964</v>
+        <v>46155.600641770834</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I89" s="9">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J89" s="9">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
@@ -6781,46 +6763,54 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="10"/>
-      <c r="T89" s="10"/>
-      <c r="U89" s="10"/>
+        <v>264</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>46237</v>
+      </c>
+      <c r="R89" s="9">
+        <v>46237</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T89" s="10">
+        <v>0</v>
+      </c>
+      <c r="U89" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.16917405093</v>
+        <v>46149.169178321754</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.600641770834</v>
+        <v>46155.600606238426</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>281</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I90" s="5">
-        <v>46237</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I90" s="6"/>
       <c r="J90" s="5">
         <v>46237</v>
       </c>
@@ -6834,52 +6824,42 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46237</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46237</v>
-      </c>
-      <c r="S90" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.169178321754</v>
+        <v>46149.169183148144</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.600606238426</v>
+        <v>46155.60060333333</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6895,13 +6875,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6911,26 +6891,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46149.169183148144</v>
+        <v>46155.56256662037</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.60060333333</v>
+        <v>46155.600600254635</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6946,13 +6926,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6962,26 +6942,26 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.56256662037</v>
+        <v>46155.56257849537</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.600600254635</v>
+        <v>46155.60059528935</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6997,13 +6977,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7013,30 +6993,32 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
-        <v>46155.56257849537</v>
+        <v>46149.169187962965</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.60059528935</v>
+        <v>46155.60079344908</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>195</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I94" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46238</v>
+      </c>
       <c r="J94" s="5">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -7048,46 +7030,54 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+        <v>264</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46238</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46238</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T94" s="6">
+        <v>0</v>
+      </c>
+      <c r="U94" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.169187962965</v>
+        <v>46149.1691919213</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.60079344908</v>
+        <v>46155.600763483795</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>291</v>
+        <v>190</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I95" s="9">
-        <v>46238</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I95" s="10"/>
       <c r="J95" s="9">
         <v>46238</v>
       </c>
@@ -7101,52 +7091,42 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>217</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q95" s="9">
-        <v>46238</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46238</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.1691919213</v>
+        <v>46149.16919760416</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.600763483795</v>
+        <v>46155.60076056713</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7162,13 +7142,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7178,26 +7158,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
-        <v>46149.16919760416</v>
+        <v>46155.562660428244</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.60076056713</v>
+        <v>46155.60075752315</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7213,10 +7193,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>291</v>
@@ -7229,26 +7209,26 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.562660428244</v>
+        <v>46155.56267193287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.60075752315</v>
+        <v>46155.600753645835</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7264,13 +7244,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>293</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7280,30 +7260,32 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B99" s="9">
-        <v>46155.56267193287</v>
+        <v>46149.169203125</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.600753645835</v>
+        <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I99" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="I99" s="9">
+        <v>46239</v>
+      </c>
       <c r="J99" s="9">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K99" s="10" t="s">
         <v>26</v>
@@ -7315,46 +7297,54 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>298</v>
+        <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q99" s="10"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="10"/>
-      <c r="T99" s="10"/>
-      <c r="U99" s="10"/>
+        <v>264</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>46239</v>
+      </c>
+      <c r="R99" s="9">
+        <v>46239</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T99" s="10">
+        <v>0</v>
+      </c>
+      <c r="U99" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.169203125</v>
+        <v>46149.16920694444</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.60094263889</v>
+        <v>46155.600918067124</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I100" s="5">
-        <v>46239</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46239</v>
       </c>
@@ -7368,52 +7358,42 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>217</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>46239</v>
-      </c>
-      <c r="R100" s="5">
-        <v>46239</v>
-      </c>
-      <c r="S100" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T100" s="6">
-        <v>0</v>
-      </c>
-      <c r="U100" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.16920694444</v>
+        <v>46149.16921202546</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.600918067124</v>
+        <v>46155.60091518519</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7429,13 +7409,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="O101" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="O101" s="10" t="s">
-        <v>302</v>
-      </c>
       <c r="P101" s="10" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7445,26 +7425,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
-        <v>46149.16921202546</v>
+        <v>46155.562741851856</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.60091518519</v>
+        <v>46155.60091216435</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7480,13 +7460,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7496,26 +7476,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.562741851856</v>
+        <v>46155.562755046296</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.60091216435</v>
+        <v>46155.60090780092</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7531,13 +7511,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7547,30 +7527,32 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
-        <v>46155.562755046296</v>
+        <v>46149.16921689815</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.60090780092</v>
+        <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>195</v>
+        <v>306</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I104" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="I104" s="5">
+        <v>46240</v>
+      </c>
       <c r="J104" s="5">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7582,42 +7564,52 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>309</v>
+        <v>212</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
+        <v>264</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>46240</v>
+      </c>
+      <c r="R104" s="5">
+        <v>46240</v>
+      </c>
+      <c r="S104" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T104" s="6">
+        <v>0</v>
+      </c>
+      <c r="U104" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.16921689815</v>
+        <v>46149.169220717595</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.60109780093</v>
+        <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I105" s="9">
         <v>46240</v>
@@ -7635,52 +7627,42 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q105" s="9">
-        <v>46240</v>
-      </c>
-      <c r="R105" s="9">
-        <v>46240</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T105" s="10">
-        <v>0</v>
-      </c>
-      <c r="U105" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.169220717595</v>
+        <v>46149.16922577546</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.60106565972</v>
+        <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I106" s="5">
         <v>46240</v>
@@ -7698,13 +7680,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7714,26 +7696,26 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
-        <v>46149.16922577546</v>
+        <v>46155.56285743056</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.601062546295</v>
+        <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I107" s="9">
         <v>46240</v>
@@ -7751,13 +7733,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="O107" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P107" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="O107" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="P107" s="10" t="s">
-        <v>313</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7767,26 +7749,26 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.56285743056</v>
+        <v>46155.56284611111</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.60105936343</v>
+        <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7804,13 +7786,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7820,32 +7802,32 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B109" s="9">
-        <v>46155.56284611111</v>
+        <v>46149.169270370374</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.60105565972</v>
+        <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>195</v>
+        <v>314</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I109" s="9">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="J109" s="9">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="K109" s="10" t="s">
         <v>26</v>
@@ -7857,46 +7839,54 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q109" s="10"/>
-      <c r="R109" s="10"/>
-      <c r="S109" s="10"/>
-      <c r="T109" s="10"/>
-      <c r="U109" s="10"/>
+        <v>315</v>
+      </c>
+      <c r="Q109" s="9">
+        <v>46244</v>
+      </c>
+      <c r="R109" s="9">
+        <v>46244</v>
+      </c>
+      <c r="S109" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T109" s="10">
+        <v>0</v>
+      </c>
+      <c r="U109" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.169270370374</v>
+        <v>46149.16928524306</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.601273506945</v>
+        <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>319</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I110" s="5">
-        <v>46244</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46244</v>
       </c>
@@ -7910,52 +7900,42 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q110" s="5">
-        <v>46244</v>
-      </c>
-      <c r="R110" s="5">
-        <v>46244</v>
-      </c>
-      <c r="S110" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.16928524306</v>
+        <v>46149.16929128472</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.60133046296</v>
+        <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9">
@@ -7971,13 +7951,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7987,26 +7967,26 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
-        <v>46149.16929128472</v>
+        <v>46155.562937361115</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.60132649305</v>
+        <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8022,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8038,26 +8018,26 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.562937361115</v>
+        <v>46155.56294952546</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.60132342593</v>
+        <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8073,13 +8053,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8089,31 +8069,27 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
-        <v>46155.56294952546</v>
+        <v>46149.16929695602</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.60131890046</v>
+        <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
       <c r="I114" s="6"/>
-      <c r="J114" s="5">
-        <v>46244</v>
-      </c>
+      <c r="J114" s="6"/>
       <c r="K114" s="6" t="s">
         <v>26</v>
       </c>
@@ -8121,16 +8097,16 @@
         <v>26</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>319</v>
+        <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>195</v>
+        <v>324</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>325</v>
+        <v>26</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8140,27 +8116,31 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.16929695602</v>
+        <v>46149.169301041664</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.590775185185</v>
+        <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="F115" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="10"/>
       <c r="I115" s="10"/>
-      <c r="J115" s="10"/>
+      <c r="J115" s="9">
+        <v>46245</v>
+      </c>
       <c r="K115" s="10" t="s">
         <v>26</v>
       </c>
@@ -8168,45 +8148,55 @@
         <v>26</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>26</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>329</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q115" s="10"/>
-      <c r="R115" s="10"/>
-      <c r="S115" s="10"/>
-      <c r="T115" s="10"/>
-      <c r="U115" s="10"/>
+        <v>323</v>
+      </c>
+      <c r="Q115" s="9">
+        <v>46245</v>
+      </c>
+      <c r="R115" s="9">
+        <v>46245</v>
+      </c>
+      <c r="S115" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T115" s="10">
+        <v>0</v>
+      </c>
+      <c r="U115" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.169301041664</v>
+        <v>46149.1693071412</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.60146953704</v>
+        <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>331</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8222,52 +8212,42 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q116" s="5">
-        <v>46245</v>
-      </c>
-      <c r="R116" s="5">
-        <v>46245</v>
-      </c>
-      <c r="S116" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T116" s="6">
-        <v>0</v>
-      </c>
-      <c r="U116" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.1693071412</v>
+        <v>46149.16931233797</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.60144278935</v>
+        <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8283,13 +8263,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8299,26 +8279,26 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46149.16931233797</v>
+        <v>46155.56303070602</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.60143921296</v>
+        <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8334,13 +8314,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8350,26 +8330,26 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.56303070602</v>
+        <v>46155.56306011574</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.601436296296</v>
+        <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8385,13 +8365,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8401,30 +8381,32 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
-        <v>46155.56306011574</v>
+        <v>46149.1693175</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.60143193287</v>
+        <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>195</v>
+        <v>337</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>332</v>
+        <v>73</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="I120" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="I120" s="5">
+        <v>46246</v>
+      </c>
       <c r="J120" s="5">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>26</v>
@@ -8436,42 +8418,52 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q120" s="6"/>
-      <c r="R120" s="6"/>
-      <c r="S120" s="6"/>
-      <c r="T120" s="6"/>
-      <c r="U120" s="6"/>
+        <v>323</v>
+      </c>
+      <c r="Q120" s="5">
+        <v>46246</v>
+      </c>
+      <c r="R120" s="5">
+        <v>46246</v>
+      </c>
+      <c r="S120" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T120" s="6">
+        <v>0</v>
+      </c>
+      <c r="U120" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.1693175</v>
+        <v>46149.16932247685</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.6016600463</v>
+        <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>342</v>
+        <v>190</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I121" s="9">
         <v>46246</v>
@@ -8489,52 +8481,42 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q121" s="9">
-        <v>46246</v>
-      </c>
-      <c r="R121" s="9">
-        <v>46246</v>
-      </c>
-      <c r="S121" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T121" s="10">
-        <v>0</v>
-      </c>
-      <c r="U121" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="10"/>
+      <c r="S121" s="10"/>
+      <c r="T121" s="10"/>
+      <c r="U121" s="10"/>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.16932247685</v>
+        <v>46149.16932829861</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.601629756944</v>
+        <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I122" s="5">
         <v>46246</v>
@@ -8552,13 +8534,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8568,26 +8550,26 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
-        <v>46149.16932829861</v>
+        <v>46155.56313421296</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.60162688658</v>
+        <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I123" s="9">
         <v>46246</v>
@@ -8605,13 +8587,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="O123" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P123" s="10" t="s">
         <v>342</v>
-      </c>
-      <c r="O123" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="P123" s="10" t="s">
-        <v>344</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8621,26 +8603,26 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.56313421296</v>
+        <v>46155.5631459375</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.601624421295</v>
+        <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I124" s="5">
         <v>46246</v>
@@ -8658,13 +8640,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8674,32 +8656,32 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46155.5631459375</v>
+        <v>46149.16933366898</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.601620671296</v>
+        <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>195</v>
+        <v>346</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="I125" s="9">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="J125" s="9">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K125" s="10" t="s">
         <v>26</v>
@@ -8711,46 +8693,54 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>195</v>
+        <v>347</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q125" s="10"/>
-      <c r="R125" s="10"/>
-      <c r="S125" s="10"/>
-      <c r="T125" s="10"/>
-      <c r="U125" s="10"/>
+        <v>323</v>
+      </c>
+      <c r="Q125" s="9">
+        <v>46247</v>
+      </c>
+      <c r="R125" s="9">
+        <v>46247</v>
+      </c>
+      <c r="S125" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T125" s="10">
+        <v>0</v>
+      </c>
+      <c r="U125" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.16933366898</v>
+        <v>46149.16933884259</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.60192047454</v>
+        <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>351</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="I126" s="5">
-        <v>46247</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="I126" s="6"/>
       <c r="J126" s="5">
         <v>46247</v>
       </c>
@@ -8764,52 +8754,42 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>352</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q126" s="5">
-        <v>46247</v>
-      </c>
-      <c r="R126" s="5">
-        <v>46247</v>
-      </c>
-      <c r="S126" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T126" s="6">
-        <v>0</v>
-      </c>
-      <c r="U126" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="6"/>
+      <c r="T126" s="6"/>
+      <c r="U126" s="6"/>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.16933884259</v>
+        <v>46149.16934681713</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.601853796295</v>
+        <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8825,13 +8805,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="O127" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P127" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="O127" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="P127" s="10" t="s">
-        <v>354</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8841,26 +8821,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B128" s="5">
-        <v>46149.16934681713</v>
+        <v>46155.56323461806</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.60185450231</v>
+        <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8876,13 +8856,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8892,26 +8872,26 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.56323461806</v>
+        <v>46155.563225370366</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.60185530093</v>
+        <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8927,13 +8907,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8943,30 +8923,32 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B130" s="5">
-        <v>46155.563225370366</v>
+        <v>46149.1693534375</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.60185603009</v>
+        <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>252</v>
+        <v>357</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="I130" s="6"/>
+        <v>223</v>
+      </c>
+      <c r="I130" s="5">
+        <v>46248</v>
+      </c>
       <c r="J130" s="5">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K130" s="6" t="s">
         <v>26</v>
@@ -8978,46 +8960,54 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>195</v>
+        <v>347</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q130" s="6"/>
-      <c r="R130" s="6"/>
-      <c r="S130" s="6"/>
-      <c r="T130" s="6"/>
-      <c r="U130" s="6"/>
+        <v>358</v>
+      </c>
+      <c r="Q130" s="5">
+        <v>46248</v>
+      </c>
+      <c r="R130" s="5">
+        <v>46248</v>
+      </c>
+      <c r="S130" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T130" s="6">
+        <v>0</v>
+      </c>
+      <c r="U130" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.1693534375</v>
+        <v>46149.16935909722</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.60216496528</v>
+        <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>362</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="I131" s="9">
-        <v>46248</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="I131" s="10"/>
       <c r="J131" s="9">
         <v>46248</v>
       </c>
@@ -9031,52 +9021,42 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>352</v>
+        <v>190</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q131" s="9">
-        <v>46248</v>
-      </c>
-      <c r="R131" s="9">
-        <v>46248</v>
-      </c>
-      <c r="S131" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T131" s="10">
-        <v>0</v>
-      </c>
-      <c r="U131" s="11" t="s">
-        <v>87</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
+      <c r="T131" s="10"/>
+      <c r="U131" s="10"/>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.16935909722</v>
+        <v>46149.16936413194</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.602132280095</v>
+        <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9092,13 +9072,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9108,26 +9088,26 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B133" s="9">
-        <v>46149.16936413194</v>
+        <v>46155.56332277777</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.602128969906</v>
+        <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9143,13 +9123,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9159,26 +9139,26 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.56332277777</v>
+        <v>46155.56333268518</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.60212502315</v>
+        <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9194,13 +9174,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9210,31 +9190,27 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B135" s="9">
-        <v>46155.56333268518</v>
+        <v>46149.16936914352</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.602120462965</v>
+        <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>254</v>
+        <v>364</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>228</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H135" s="10"/>
       <c r="I135" s="10"/>
-      <c r="J135" s="9">
-        <v>46248</v>
-      </c>
+      <c r="J135" s="10"/>
       <c r="K135" s="10" t="s">
         <v>26</v>
       </c>
@@ -9242,16 +9218,16 @@
         <v>26</v>
       </c>
       <c r="M135" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>362</v>
+        <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>254</v>
+        <v>365</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>362</v>
+        <v>26</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9261,27 +9237,33 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.16936914352</v>
+        <v>46149.169373136574</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.60238891204</v>
+        <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="F136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
+      <c r="I136" s="5">
+        <v>46251</v>
+      </c>
+      <c r="J136" s="5">
+        <v>46255</v>
+      </c>
       <c r="K136" s="6" t="s">
         <v>26</v>
       </c>
@@ -9289,45 +9271,55 @@
         <v>26</v>
       </c>
       <c r="M136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N136" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="P136" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q136" s="5">
+        <v>46251</v>
+      </c>
+      <c r="R136" s="5">
+        <v>46255</v>
+      </c>
+      <c r="S136" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T136" s="6">
         <v>0</v>
       </c>
-      <c r="N136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O136" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="6"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
+      <c r="U136" s="11" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.169373136574</v>
+        <v>46149.169417349534</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46155.602217824075</v>
+        <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>373</v>
+        <v>51</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>374</v>
+        <v>52</v>
       </c>
       <c r="I137" s="9">
         <v>46251</v>
@@ -9345,13 +9337,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>
@@ -9360,76 +9352,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B138" s="5">
-        <v>46149.169417349534</v>
-      </c>
-      <c r="C138" s="6"/>
-      <c r="D138" s="5">
-        <v>46155.60249738426</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I138" s="5">
-        <v>46251</v>
-      </c>
-      <c r="J138" s="5">
-        <v>46255</v>
-      </c>
-      <c r="K138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N138" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="O138" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q138" s="5">
-        <v>46251</v>
-      </c>
-      <c r="R138" s="5">
-        <v>46255</v>
-      </c>
-      <c r="S138" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="T138" s="6">
-        <v>0</v>
-      </c>
-      <c r="U138" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4232 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
     <t>1214596725492919</t>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="371">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -297,9 +297,6 @@
     <t>Propuesta compras:,Generación OC Rodete OT 4315</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214596623962892</t>
   </si>
   <si>
@@ -429,49 +426,49 @@
     <t>Generación OC motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
   </si>
   <si>
+    <t>1214596772320275</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4315</t>
+  </si>
+  <si>
+    <t>Motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772320293</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Motor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772322550</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Motor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772322568</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596772320275</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4315</t>
-  </si>
-  <si>
-    <t>Motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772320293</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Motor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772322550</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Motor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772322568</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
   </si>
   <si>
     <t>1214596969807197</t>
@@ -2432,7 +2429,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46196.87158398148</v>
+        <v>46197.5026965625</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2607,9 +2604,11 @@
       <c r="B17" s="9">
         <v>46149.168779988424</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46197.50268954861</v>
+      </c>
       <c r="D17" s="9">
-        <v>46183.870695335645</v>
+        <v>46197.502708472224</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2657,15 +2656,15 @@
         <v>33</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46149.168784837966</v>
@@ -2675,16 +2674,16 @@
         <v>46189.188732361115</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="I18" s="5">
         <v>46185</v>
@@ -2705,10 +2704,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2723,12 +2722,12 @@
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46149.168789351854</v>
@@ -2738,16 +2737,16 @@
         <v>46189.1887321875</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="I19" s="9">
         <v>46185</v>
@@ -2768,10 +2767,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2786,12 +2785,12 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46149.16879285879</v>
@@ -2801,16 +2800,16 @@
         <v>46189.18873256944</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="I20" s="5">
         <v>46185</v>
@@ -2831,10 +2830,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2849,12 +2848,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46149.16879642361</v>
@@ -2864,16 +2863,16 @@
         <v>46189.18873219907</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="I21" s="9">
         <v>46185</v>
@@ -2894,10 +2893,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2912,12 +2911,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46149.168676875</v>
@@ -2927,7 +2926,7 @@
         <v>46155.55343407407</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2951,7 +2950,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2964,7 +2963,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168800127314</v>
@@ -2974,16 +2973,16 @@
         <v>46169.85973167824</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -3001,13 +3000,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="9">
         <v>46157</v>
@@ -3022,12 +3021,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3037,16 +3036,16 @@
         <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3064,29 +3063,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3096,16 +3095,16 @@
         <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3123,29 +3122,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3155,16 +3154,16 @@
         <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3182,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3203,31 +3202,31 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.86015417824</v>
+        <v>46197.50269849537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3245,29 +3244,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3277,16 +3276,16 @@
         <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3304,48 +3303,48 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46196.168625578706</v>
+        <v>46197.20554309028</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3363,13 +3362,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <v>46157</v>
@@ -3377,19 +3376,19 @@
       <c r="R29" s="9">
         <v>46196</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>119</v>
+      <c r="S29" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3399,16 +3398,16 @@
         <v>46196.87158207176</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3426,29 +3425,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
@@ -3458,16 +3457,16 @@
         <v>46196.16862795139</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3485,29 +3484,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3517,16 +3516,16 @@
         <v>46185.52448216435</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3544,29 +3543,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3576,16 +3575,16 @@
         <v>46192.19869972223</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>132</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3603,13 +3602,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="9">
         <v>46189</v>
@@ -3618,18 +3617,18 @@
         <v>46199</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3639,16 +3638,16 @@
         <v>46190.16888383102</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3666,29 +3665,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3698,16 +3697,16 @@
         <v>46169.86006208333</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3725,29 +3724,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3757,16 +3756,16 @@
         <v>46192.19869975695</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3784,10 +3783,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3799,18 +3798,18 @@
         <v>46199</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3820,16 +3819,16 @@
         <v>46190.16888201389</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3847,13 +3846,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3863,7 +3862,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3873,16 +3872,16 @@
         <v>46169.860009571756</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3900,13 +3899,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3916,7 +3915,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3926,16 +3925,16 @@
         <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -3953,10 +3952,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3968,37 +3967,37 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.85992768519</v>
+        <v>46197.16885377315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4016,13 +4015,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4032,7 +4031,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4042,16 +4041,16 @@
         <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4069,13 +4068,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4085,7 +4084,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4095,16 +4094,16 @@
         <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4122,10 +4121,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4138,7 +4137,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4148,16 +4147,16 @@
         <v>46169.85983048611</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4175,10 +4174,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4190,18 +4189,18 @@
         <v>46210</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4211,16 +4210,16 @@
         <v>46191.68554611111</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4238,13 +4237,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4254,7 +4253,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4264,16 +4263,16 @@
         <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4291,13 +4290,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4307,7 +4306,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4317,7 +4316,7 @@
         <v>46184.514930833335</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4341,7 +4340,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4354,7 +4353,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4366,16 +4365,16 @@
         <v>46184.51494311343</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4393,13 +4392,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4419,7 +4418,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4429,16 +4428,16 @@
         <v>46184.51493138889</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4456,13 +4455,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4477,12 +4476,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4492,16 +4491,16 @@
         <v>46184.168774861115</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4517,13 +4516,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4532,18 +4531,18 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4553,16 +4552,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4580,10 +4579,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4595,18 +4594,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4616,7 +4615,7 @@
         <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4641,13 +4640,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4657,7 +4656,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4667,7 +4666,7 @@
         <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4692,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4708,7 +4707,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4718,7 +4717,7 @@
         <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4743,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4759,7 +4758,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4769,7 +4768,7 @@
         <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4794,13 +4793,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4810,7 +4809,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4820,7 +4819,7 @@
         <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4844,7 +4843,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4857,7 +4856,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4867,16 +4866,16 @@
         <v>46196.2065696412</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4894,13 +4893,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4909,18 +4908,18 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -4930,16 +4929,16 @@
         <v>46176.17164681713</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -4957,13 +4956,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>206</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -4978,12 +4977,12 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -4993,16 +4992,16 @@
         <v>46196.20656958333</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5020,13 +5019,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5035,18 +5034,18 @@
         <v>46203</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5056,16 +5055,16 @@
         <v>46176.17164685186</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5083,13 +5082,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5104,12 +5103,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5119,16 +5118,16 @@
         <v>46155.59866159722</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5146,13 +5145,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5161,18 +5160,18 @@
         <v>46212</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5182,16 +5181,16 @@
         <v>46155.5990459375</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5209,13 +5208,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5224,18 +5223,18 @@
         <v>46216</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5245,7 +5244,7 @@
         <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5269,7 +5268,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5282,7 +5281,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5292,16 +5291,16 @@
         <v>46161.57724337963</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5319,13 +5318,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5334,18 +5333,18 @@
         <v>46219</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5355,16 +5354,16 @@
         <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5382,13 +5381,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5398,7 +5397,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5408,16 +5407,16 @@
         <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5435,13 +5434,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5451,7 +5450,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5461,16 +5460,16 @@
         <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5488,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5504,7 +5503,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5514,16 +5513,16 @@
         <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5541,13 +5540,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5557,7 +5556,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5567,16 +5566,16 @@
         <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5594,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5609,18 +5608,18 @@
         <v>46226</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5630,16 +5629,16 @@
         <v>46155.59950737268</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5657,13 +5656,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5673,7 +5672,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5683,16 +5682,16 @@
         <v>46155.59950449074</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5710,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5726,7 +5725,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5736,16 +5735,16 @@
         <v>46155.5995016088</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5763,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5779,7 +5778,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5789,16 +5788,16 @@
         <v>46155.59949699074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5816,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5832,7 +5831,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5842,16 +5841,16 @@
         <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5869,13 +5868,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -5884,18 +5883,18 @@
         <v>46227</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -5905,16 +5904,16 @@
         <v>46155.59963545139</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -5932,13 +5931,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5948,7 +5947,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -5958,16 +5957,16 @@
         <v>46155.59963275463</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -5985,13 +5984,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6001,7 +6000,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6011,16 +6010,16 @@
         <v>46155.59962995371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6038,13 +6037,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6054,7 +6053,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6064,16 +6063,16 @@
         <v>46155.599625891206</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6091,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6107,7 +6106,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6117,7 +6116,7 @@
         <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6141,7 +6140,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6154,7 +6153,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6164,16 +6163,16 @@
         <v>46182.17098876157</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6189,13 +6188,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6210,12 +6209,12 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6225,16 +6224,16 @@
         <v>46165.180999432865</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6252,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6273,31 +6272,31 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46190.1987571875</v>
+        <v>46197.168855717595</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6315,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6330,18 +6329,18 @@
         <v>46197</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6351,16 +6350,16 @@
         <v>46155.59985006944</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6378,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6393,18 +6392,18 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6414,7 +6413,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6438,7 +6437,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6451,7 +6450,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
@@ -6461,7 +6460,7 @@
         <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6488,13 +6487,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6503,18 +6502,18 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46149.16916685185</v>
@@ -6524,7 +6523,7 @@
         <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6551,10 +6550,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6567,7 +6566,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46149.16917037037</v>
@@ -6577,7 +6576,7 @@
         <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6604,10 +6603,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6620,7 +6619,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46155.5624656713</v>
@@ -6630,7 +6629,7 @@
         <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6657,13 +6656,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6673,7 +6672,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46155.562495266204</v>
@@ -6683,7 +6682,7 @@
         <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6710,13 +6709,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6726,7 +6725,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B89" s="9">
         <v>46149.16917405093</v>
@@ -6736,7 +6735,7 @@
         <v>46155.600641770834</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6763,13 +6762,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6778,18 +6777,18 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46149.169178321754</v>
@@ -6799,7 +6798,7 @@
         <v>46155.600606238426</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6824,13 +6823,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6840,7 +6839,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46149.169183148144</v>
@@ -6850,7 +6849,7 @@
         <v>46155.60060333333</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6875,13 +6874,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>278</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>279</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6891,7 +6890,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46155.56256662037</v>
@@ -6901,7 +6900,7 @@
         <v>46155.600600254635</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6926,13 +6925,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6942,7 +6941,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="9">
         <v>46155.56257849537</v>
@@ -6952,7 +6951,7 @@
         <v>46155.60059528935</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6977,13 +6976,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6993,7 +6992,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46149.169187962965</v>
@@ -7003,7 +7002,7 @@
         <v>46155.60079344908</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7030,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7045,18 +7044,18 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46149.1691919213</v>
@@ -7066,7 +7065,7 @@
         <v>46155.600763483795</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7091,13 +7090,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7107,7 +7106,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46149.16919760416</v>
@@ -7117,7 +7116,7 @@
         <v>46155.60076056713</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7142,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7158,7 +7157,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="9">
         <v>46155.562660428244</v>
@@ -7168,7 +7167,7 @@
         <v>46155.60075752315</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7193,13 +7192,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7209,7 +7208,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46155.56267193287</v>
@@ -7219,7 +7218,7 @@
         <v>46155.600753645835</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7244,13 +7243,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7260,7 +7259,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B99" s="9">
         <v>46149.169203125</v>
@@ -7270,7 +7269,7 @@
         <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7297,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7312,18 +7311,18 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46149.16920694444</v>
@@ -7333,7 +7332,7 @@
         <v>46155.600918067124</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7358,13 +7357,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7374,7 +7373,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B101" s="9">
         <v>46149.16921202546</v>
@@ -7384,7 +7383,7 @@
         <v>46155.60091518519</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7409,13 +7408,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7425,7 +7424,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B102" s="5">
         <v>46155.562741851856</v>
@@ -7435,7 +7434,7 @@
         <v>46155.60091216435</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7460,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7476,7 +7475,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B103" s="9">
         <v>46155.562755046296</v>
@@ -7486,7 +7485,7 @@
         <v>46155.60090780092</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7511,13 +7510,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7527,7 +7526,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B104" s="5">
         <v>46149.16921689815</v>
@@ -7537,7 +7536,7 @@
         <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7564,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7579,18 +7578,18 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B105" s="9">
         <v>46149.169220717595</v>
@@ -7600,7 +7599,7 @@
         <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7627,13 +7626,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7643,7 +7642,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B106" s="5">
         <v>46149.16922577546</v>
@@ -7653,7 +7652,7 @@
         <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7680,13 +7679,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7696,7 +7695,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B107" s="9">
         <v>46155.56285743056</v>
@@ -7706,7 +7705,7 @@
         <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7733,13 +7732,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7749,7 +7748,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46155.56284611111</v>
@@ -7759,7 +7758,7 @@
         <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7786,13 +7785,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7802,7 +7801,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B109" s="9">
         <v>46149.169270370374</v>
@@ -7812,7 +7811,7 @@
         <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7839,13 +7838,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7854,18 +7853,18 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46149.16928524306</v>
@@ -7875,7 +7874,7 @@
         <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7900,13 +7899,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7916,7 +7915,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B111" s="9">
         <v>46149.16929128472</v>
@@ -7926,7 +7925,7 @@
         <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7951,13 +7950,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7967,7 +7966,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46155.562937361115</v>
@@ -7977,7 +7976,7 @@
         <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8002,13 +8001,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8018,7 +8017,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B113" s="9">
         <v>46155.56294952546</v>
@@ -8028,7 +8027,7 @@
         <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8053,13 +8052,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8069,7 +8068,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B114" s="5">
         <v>46149.16929695602</v>
@@ -8079,7 +8078,7 @@
         <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8103,7 +8102,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8116,7 +8115,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B115" s="9">
         <v>46149.169301041664</v>
@@ -8126,16 +8125,16 @@
         <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="F115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="10" t="s">
+      <c r="H115" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>328</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8151,13 +8150,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8166,18 +8165,18 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46149.1693071412</v>
@@ -8187,16 +8186,16 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8212,13 +8211,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8228,7 +8227,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B117" s="9">
         <v>46149.16931233797</v>
@@ -8238,16 +8237,16 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>328</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8263,13 +8262,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8279,7 +8278,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46155.56303070602</v>
@@ -8289,16 +8288,16 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8314,13 +8313,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8330,7 +8329,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
         <v>46155.56306011574</v>
@@ -8340,16 +8339,16 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>328</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8365,13 +8364,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8381,7 +8380,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B120" s="5">
         <v>46149.1693175</v>
@@ -8391,7 +8390,7 @@
         <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8418,13 +8417,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8433,18 +8432,18 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B121" s="9">
         <v>46149.16932247685</v>
@@ -8454,7 +8453,7 @@
         <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8481,13 +8480,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8497,7 +8496,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46149.16932829861</v>
@@ -8507,7 +8506,7 @@
         <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8534,13 +8533,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8550,7 +8549,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B123" s="9">
         <v>46155.56313421296</v>
@@ -8560,7 +8559,7 @@
         <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8587,13 +8586,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8603,7 +8602,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46155.5631459375</v>
@@ -8613,7 +8612,7 @@
         <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8640,13 +8639,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8656,7 +8655,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B125" s="9">
         <v>46149.16933366898</v>
@@ -8666,16 +8665,16 @@
         <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8693,13 +8692,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8708,18 +8707,18 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B126" s="5">
         <v>46149.16933884259</v>
@@ -8729,16 +8728,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8754,13 +8753,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8770,7 +8769,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B127" s="9">
         <v>46149.16934681713</v>
@@ -8780,16 +8779,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8805,13 +8804,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8821,7 +8820,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B128" s="5">
         <v>46155.56323461806</v>
@@ -8831,16 +8830,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8856,13 +8855,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8872,7 +8871,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B129" s="9">
         <v>46155.563225370366</v>
@@ -8882,16 +8881,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8907,13 +8906,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8923,7 +8922,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B130" s="5">
         <v>46149.1693534375</v>
@@ -8933,16 +8932,16 @@
         <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -8960,13 +8959,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -8975,18 +8974,18 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B131" s="9">
         <v>46149.16935909722</v>
@@ -8996,16 +8995,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9021,13 +9020,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9037,7 +9036,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B132" s="5">
         <v>46149.16936413194</v>
@@ -9047,16 +9046,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9072,13 +9071,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9088,7 +9087,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B133" s="9">
         <v>46155.56332277777</v>
@@ -9098,16 +9097,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9123,13 +9122,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9139,7 +9138,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B134" s="5">
         <v>46155.56333268518</v>
@@ -9149,16 +9148,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9174,13 +9173,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9190,7 +9189,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B135" s="9">
         <v>46149.16936914352</v>
@@ -9200,7 +9199,7 @@
         <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9224,7 +9223,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9237,7 +9236,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46149.169373136574</v>
@@ -9247,16 +9246,16 @@
         <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G136" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="F136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G136" s="6" t="s">
+      <c r="H136" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9274,13 +9273,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9289,18 +9288,18 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B137" s="9">
         <v>46149.169417349534</v>
@@ -9310,7 +9309,7 @@
         <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9337,13 +9336,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>
@@ -9352,13 +9351,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1809,13 +1809,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.168662384254</v>
+        <v>46149.0019957176</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87291253472</v>
+        <v>46175.70624586806</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87292444444</v>
+        <v>46175.706257777776</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1862,13 +1862,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.16873268518</v>
+        <v>46149.00206601852</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87288527778</v>
+        <v>46175.706218611114</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87291335648</v>
+        <v>46175.70624668981</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1925,13 +1925,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.16873607639</v>
+        <v>46149.00206940972</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87288591435</v>
+        <v>46175.70621924769</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87291327547</v>
+        <v>46175.706246608795</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1988,13 +1988,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.16873881944</v>
+        <v>46149.002072152776</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.87288634259</v>
+        <v>46175.70621967592</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87291446759</v>
+        <v>46175.706247800925</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2051,13 +2051,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.16874162037</v>
+        <v>46149.00207495371</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872886736106</v>
+        <v>46175.70622006945</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87291319444</v>
+        <v>46175.70624652778</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2114,13 +2114,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.16874480324</v>
+        <v>46149.002078136575</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.872887314814</v>
+        <v>46175.70622064815</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.8729128125</v>
+        <v>46175.70624614583</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2177,13 +2177,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.16866752315</v>
+        <v>46149.00200085648</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.871632326394</v>
+        <v>46196.70496565972</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.87164857639</v>
+        <v>46196.70498190972</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2230,13 +2230,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.168747881944</v>
+        <v>46149.00208121528</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.87067072917</v>
+        <v>46183.7040040625</v>
       </c>
       <c r="D11" s="9">
-        <v>46196.869429768514</v>
+        <v>46196.70276310186</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2295,13 +2295,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.16875297454</v>
+        <v>46149.00208630787</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.87067740741</v>
+        <v>46183.70401074074</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.86942973379</v>
+        <v>46196.70276306713</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2360,13 +2360,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.168757997686</v>
+        <v>46149.002091331015</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.87068302083</v>
+        <v>46183.70401635417</v>
       </c>
       <c r="D13" s="9">
-        <v>46196.869429722225</v>
+        <v>46196.70276305555</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2425,11 +2425,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.16867222222</v>
+        <v>46149.00200555555</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.5026965625</v>
+        <v>46197.33602989583</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2472,13 +2472,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.16877023148</v>
+        <v>46149.00210356481</v>
       </c>
       <c r="C15" s="9">
-        <v>46196.87156641204</v>
+        <v>46196.70489974537</v>
       </c>
       <c r="D15" s="9">
-        <v>46196.871587870366</v>
+        <v>46196.70492120371</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2537,13 +2537,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.16877512731</v>
+        <v>46149.00210846065</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.87157603009</v>
+        <v>46196.70490936343</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.871593379634</v>
+        <v>46196.70492671296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2602,13 +2602,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.168779988424</v>
+        <v>46149.00211332176</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.50268954861</v>
+        <v>46197.336022881944</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.502708472224</v>
+        <v>46197.33604180555</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2667,11 +2667,11 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.168784837966</v>
+        <v>46149.002118171295</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46189.188732361115</v>
+        <v>46189.022065694444</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2730,11 +2730,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.168789351854</v>
+        <v>46149.00212268518</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.1887321875</v>
+        <v>46189.02206552083</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2793,11 +2793,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.16879285879</v>
+        <v>46149.00212619213</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.18873256944</v>
+        <v>46189.02206590278</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2856,11 +2856,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.16879642361</v>
+        <v>46149.00212975695</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.18873219907</v>
+        <v>46189.02206553241</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2919,11 +2919,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.168676875</v>
+        <v>46149.002010208336</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46155.55343407407</v>
+        <v>46155.386767407406</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2966,11 +2966,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.168800127314</v>
+        <v>46149.00213346065</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.85973167824</v>
+        <v>46169.693065011576</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3029,11 +3029,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.168804155095</v>
+        <v>46149.00213748842</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.87158508102</v>
+        <v>46196.704918414354</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3088,11 +3088,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.16880861111</v>
+        <v>46149.002141944446</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.86022740741</v>
+        <v>46169.693560740736</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3147,11 +3147,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.16881337963</v>
+        <v>46149.00214671296</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.17667454861</v>
+        <v>46179.010007881945</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3210,11 +3210,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.16881752315</v>
+        <v>46149.00215085648</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.50269849537</v>
+        <v>46197.3360318287</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3269,11 +3269,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.168821851854</v>
+        <v>46149.00215518518</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.170599363424</v>
+        <v>46178.00393269676</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3328,11 +3328,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.1688262963</v>
+        <v>46149.00215962963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46197.20554309028</v>
+        <v>46197.03887642361</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3391,11 +3391,11 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.168830532406</v>
+        <v>46149.00216386574</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46196.87158207176</v>
+        <v>46196.70491540509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3450,11 +3450,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.1688349537</v>
+        <v>46149.002168287036</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46196.16862795139</v>
+        <v>46196.001961284725</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3509,11 +3509,11 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.16884</v>
+        <v>46149.002173333334</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46185.52448216435</v>
+        <v>46185.357815497686</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3568,11 +3568,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.168844375</v>
+        <v>46149.00217770833</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46192.19869972223</v>
+        <v>46192.032033055555</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3631,11 +3631,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.16884893518</v>
+        <v>46149.00218226852</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.16888383102</v>
+        <v>46190.00221716435</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3690,11 +3690,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.16885364584</v>
+        <v>46149.00218697917</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.86006208333</v>
+        <v>46169.69339541667</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3749,11 +3749,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.1688584375</v>
+        <v>46149.002191770836</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.19869975695</v>
+        <v>46192.032033090276</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3812,11 +3812,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.16891136574</v>
+        <v>46149.00224469908</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.16888201389</v>
+        <v>46190.002215347224</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -3865,11 +3865,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.168917256946</v>
+        <v>46149.002250590274</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.860009571756</v>
+        <v>46169.69334290509</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3918,11 +3918,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.16892260416</v>
+        <v>46149.0022559375</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.859801203704</v>
+        <v>46169.69313453704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3981,11 +3981,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.168932870365</v>
+        <v>46149.00226620371</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.16885377315</v>
+        <v>46197.00218710648</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4034,11 +4034,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.16893796297</v>
+        <v>46149.0022712963</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.859942118055</v>
+        <v>46169.693275451384</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4087,11 +4087,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.16894290509</v>
+        <v>46149.002276238425</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859966018514</v>
+        <v>46169.69329935186</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -4140,11 +4140,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.16894577546</v>
+        <v>46149.0022791088</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.85983048611</v>
+        <v>46169.693163819444</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4203,11 +4203,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.16894971065</v>
+        <v>46149.002283043985</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.68554611111</v>
+        <v>46191.51887944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4256,11 +4256,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.1689542824</v>
+        <v>46149.002287615745</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46191.68560096065</v>
+        <v>46191.518934293985</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4309,11 +4309,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.16868141203</v>
+        <v>46149.00201474537</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46184.514930833335</v>
+        <v>46184.34826416666</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4356,13 +4356,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.16895986111</v>
+        <v>46149.00229319444</v>
       </c>
       <c r="C47" s="9">
-        <v>46184.514923263894</v>
+        <v>46184.34825659722</v>
       </c>
       <c r="D47" s="9">
-        <v>46184.51494311343</v>
+        <v>46184.34827644676</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4421,11 +4421,11 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.16896564815</v>
+        <v>46149.00229898148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46184.51493138889</v>
+        <v>46184.348264722226</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4484,11 +4484,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.16897216435</v>
+        <v>46149.002305497685</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.168774861115</v>
+        <v>46184.00210819444</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4545,11 +4545,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.16898688657</v>
+        <v>46149.00232021991</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.59844700231</v>
+        <v>46155.43178033565</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4608,11 +4608,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.168991412036</v>
+        <v>46149.00232474537</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.59855652778</v>
+        <v>46155.43188986111</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4659,11 +4659,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.16900017361</v>
+        <v>46149.00233350694</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.59855292824</v>
+        <v>46155.43188626158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4710,11 +4710,11 @@
         <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.577817384255</v>
+        <v>46155.41115071759</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.59854846065</v>
+        <v>46155.43188179398</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>189</v>
@@ -4761,11 +4761,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.577829050926</v>
+        <v>46155.41116238426</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.59854489584</v>
+        <v>46155.43187822917</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -4812,11 +4812,11 @@
         <v>194</v>
       </c>
       <c r="B55" s="9">
-        <v>46149.1690050926</v>
+        <v>46149.002338425926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.55893427083</v>
+        <v>46155.39226760417</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -4859,11 +4859,11 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.16900940972</v>
+        <v>46149.00234274306</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.2065696412</v>
+        <v>46196.03990297454</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -4922,11 +4922,11 @@
         <v>202</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.16901516204</v>
+        <v>46149.00234849537</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46176.17164681713</v>
+        <v>46176.004980150465</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>203</v>
@@ -4985,11 +4985,11 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.16902107639</v>
+        <v>46149.00235440972</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.20656958333</v>
+        <v>46196.039902916666</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -5048,11 +5048,11 @@
         <v>209</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.16902621528</v>
+        <v>46149.00235954861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.17164685186</v>
+        <v>46176.004980185186</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>210</v>
@@ -5111,11 +5111,11 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.1690303588</v>
+        <v>46149.002363692125</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.59866159722</v>
+        <v>46155.43199493056</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5174,11 +5174,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.16903488426</v>
+        <v>46149.002368217596</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.5990459375</v>
+        <v>46155.43237927083</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>214</v>
@@ -5237,11 +5237,11 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.1690391088</v>
+        <v>46149.00237244213</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.56887822917</v>
+        <v>46155.4022115625</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5284,11 +5284,11 @@
         <v>219</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.169042442125</v>
+        <v>46149.00237577547</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.57724337963</v>
+        <v>46161.410576712966</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>220</v>
@@ -5347,11 +5347,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.169049375</v>
+        <v>46149.002382708335</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.59925321759</v>
+        <v>46155.43258655093</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>189</v>
@@ -5400,11 +5400,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.16905616898</v>
+        <v>46149.00238950232</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.59924960649</v>
+        <v>46155.432582939815</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>189</v>
@@ -5453,11 +5453,11 @@
         <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.562074166664</v>
+        <v>46155.3954075</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.59924675926</v>
+        <v>46155.43258009259</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>189</v>
@@ -5506,11 +5506,11 @@
         <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.562095416666</v>
+        <v>46155.395428749995</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.59924362268</v>
+        <v>46155.432576956024</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>189</v>
@@ -5559,11 +5559,11 @@
         <v>232</v>
       </c>
       <c r="B68" s="5">
-        <v>46149.169104699075</v>
+        <v>46149.0024380324</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.59934020833</v>
+        <v>46155.43267354167</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>233</v>
@@ -5622,11 +5622,11 @@
         <v>234</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.1691096412</v>
+        <v>46149.00244297454</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.59950737268</v>
+        <v>46155.432840706024</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>189</v>
@@ -5675,11 +5675,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.16911491899</v>
+        <v>46149.002448252315</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.59950449074</v>
+        <v>46155.432837824075</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>189</v>
@@ -5728,11 +5728,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.562225625</v>
+        <v>46155.395558958335</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.5995016088</v>
+        <v>46155.43283494213</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>189</v>
@@ -5781,11 +5781,11 @@
         <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.56224557871</v>
+        <v>46155.39557891204</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.59949699074</v>
+        <v>46155.432830324076</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>189</v>
@@ -5834,11 +5834,11 @@
         <v>240</v>
       </c>
       <c r="B73" s="9">
-        <v>46149.169119768514</v>
+        <v>46149.00245310186</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.59937984953</v>
+        <v>46155.43271318287</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>241</v>
@@ -5897,11 +5897,11 @@
         <v>242</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.16912365741</v>
+        <v>46149.00245699074</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.59963545139</v>
+        <v>46155.43296878472</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>189</v>
@@ -5950,11 +5950,11 @@
         <v>244</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.16912908565</v>
+        <v>46149.00246241898</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.59963275463</v>
+        <v>46155.43296608796</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>189</v>
@@ -6003,11 +6003,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.56233189815</v>
+        <v>46155.39566523148</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.59962995371</v>
+        <v>46155.432963287036</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>189</v>
@@ -6056,11 +6056,11 @@
         <v>247</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.562344351856</v>
+        <v>46155.395677685185</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.599625891206</v>
+        <v>46155.432959224534</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>189</v>
@@ -6109,11 +6109,11 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46149.16913412037</v>
+        <v>46149.002467453705</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.57120092593</v>
+        <v>46155.40453425926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6156,11 +6156,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.16913708333</v>
+        <v>46149.00247041667</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.17098876157</v>
+        <v>46182.00432209491</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>252</v>
@@ -6217,11 +6217,11 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.16914224537</v>
+        <v>46149.0024755787</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46165.180999432865</v>
+        <v>46165.01433276621</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>255</v>
@@ -6280,11 +6280,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.16914733796</v>
+        <v>46149.0024806713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46197.168855717595</v>
+        <v>46197.00218905092</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>258</v>
@@ -6343,11 +6343,11 @@
         <v>259</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.16915236111</v>
+        <v>46149.002485694444</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.59985006944</v>
+        <v>46155.433183402776</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>260</v>
@@ -6406,11 +6406,11 @@
         <v>262</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.16915732639</v>
+        <v>46149.002490659725</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.58270766203</v>
+        <v>46155.41604099537</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>263</v>
@@ -6453,11 +6453,11 @@
         <v>265</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.16916049768</v>
+        <v>46149.00249383102</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.60047521991</v>
+        <v>46155.433808553236</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>266</v>
@@ -6516,11 +6516,11 @@
         <v>268</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.16916685185</v>
+        <v>46149.00250018519</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.60002515046</v>
+        <v>46155.433358483795</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>189</v>
@@ -6569,11 +6569,11 @@
         <v>270</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.16917037037</v>
+        <v>46149.002503703705</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.60002232638</v>
+        <v>46155.43335565973</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>189</v>
@@ -6622,11 +6622,11 @@
         <v>271</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.5624656713</v>
+        <v>46155.39579900463</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.60026604167</v>
+        <v>46155.433599375</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>246</v>
@@ -6675,11 +6675,11 @@
         <v>273</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.562495266204</v>
+        <v>46155.39582859953</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.600359212964</v>
+        <v>46155.4336925463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>248</v>
@@ -6728,11 +6728,11 @@
         <v>274</v>
       </c>
       <c r="B89" s="9">
-        <v>46149.16917405093</v>
+        <v>46149.002507384255</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.600641770834</v>
+        <v>46155.43397510417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>275</v>
@@ -6791,11 +6791,11 @@
         <v>276</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.169178321754</v>
+        <v>46149.0025116551</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.600606238426</v>
+        <v>46155.433939571754</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>189</v>
@@ -6842,11 +6842,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.169183148144</v>
+        <v>46149.00251648148</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.60060333333</v>
+        <v>46155.43393666667</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>189</v>
@@ -6893,11 +6893,11 @@
         <v>280</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.56256662037</v>
+        <v>46155.3958999537</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.600600254635</v>
+        <v>46155.43393358796</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>189</v>
@@ -6944,11 +6944,11 @@
         <v>282</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.56257849537</v>
+        <v>46155.3959118287</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.60059528935</v>
+        <v>46155.43392862269</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>189</v>
@@ -6995,11 +6995,11 @@
         <v>284</v>
       </c>
       <c r="B94" s="5">
-        <v>46149.169187962965</v>
+        <v>46149.002521296294</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.60079344908</v>
+        <v>46155.434126782406</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>285</v>
@@ -7058,11 +7058,11 @@
         <v>286</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.1691919213</v>
+        <v>46149.00252525463</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.600763483795</v>
+        <v>46155.43409681713</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>189</v>
@@ -7109,11 +7109,11 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.16919760416</v>
+        <v>46149.002530937505</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.60076056713</v>
+        <v>46155.43409390046</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>189</v>
@@ -7160,11 +7160,11 @@
         <v>289</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.562660428244</v>
+        <v>46155.39599376157</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.60075752315</v>
+        <v>46155.43409085648</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>189</v>
@@ -7211,11 +7211,11 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.56267193287</v>
+        <v>46155.3960052662</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.600753645835</v>
+        <v>46155.43408697916</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>189</v>
@@ -7262,11 +7262,11 @@
         <v>293</v>
       </c>
       <c r="B99" s="9">
-        <v>46149.169203125</v>
+        <v>46149.002536458334</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.60094263889</v>
+        <v>46155.43427597222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>294</v>
@@ -7325,11 +7325,11 @@
         <v>295</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.16920694444</v>
+        <v>46149.00254027778</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.600918067124</v>
+        <v>46155.43425140047</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>189</v>
@@ -7376,11 +7376,11 @@
         <v>298</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.16921202546</v>
+        <v>46149.002545358795</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.60091518519</v>
+        <v>46155.43424851852</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>189</v>
@@ -7427,11 +7427,11 @@
         <v>300</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.562741851856</v>
+        <v>46155.396075185185</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.60091216435</v>
+        <v>46155.43424549769</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>189</v>
@@ -7478,11 +7478,11 @@
         <v>302</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.562755046296</v>
+        <v>46155.396088379624</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.60090780092</v>
+        <v>46155.43424113426</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>189</v>
@@ -7529,11 +7529,11 @@
         <v>304</v>
       </c>
       <c r="B104" s="5">
-        <v>46149.16921689815</v>
+        <v>46149.00255023148</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.60109780093</v>
+        <v>46155.43443113426</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>305</v>
@@ -7592,11 +7592,11 @@
         <v>306</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.169220717595</v>
+        <v>46149.00255405092</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.60106565972</v>
+        <v>46155.43439899306</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>189</v>
@@ -7645,11 +7645,11 @@
         <v>308</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.16922577546</v>
+        <v>46149.0025591088</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.601062546295</v>
+        <v>46155.43439587963</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>189</v>
@@ -7698,11 +7698,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.56285743056</v>
+        <v>46155.39619076389</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.60105936343</v>
+        <v>46155.434392696756</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>189</v>
@@ -7751,11 +7751,11 @@
         <v>311</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.56284611111</v>
+        <v>46155.39617944445</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.60105565972</v>
+        <v>46155.43438899306</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>189</v>
@@ -7804,11 +7804,11 @@
         <v>312</v>
       </c>
       <c r="B109" s="9">
-        <v>46149.169270370374</v>
+        <v>46149.0026037037</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.601273506945</v>
+        <v>46155.43460684028</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>313</v>
@@ -7867,11 +7867,11 @@
         <v>315</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.16928524306</v>
+        <v>46149.002618576385</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.60133046296</v>
+        <v>46155.434663796295</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>189</v>
@@ -7918,11 +7918,11 @@
         <v>317</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.16929128472</v>
+        <v>46149.00262461806</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.60132649305</v>
+        <v>46155.43465982639</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>189</v>
@@ -7969,11 +7969,11 @@
         <v>318</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.562937361115</v>
+        <v>46155.396270694444</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.60132342593</v>
+        <v>46155.43465675926</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>189</v>
@@ -8020,11 +8020,11 @@
         <v>320</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.56294952546</v>
+        <v>46155.3962828588</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.60131890046</v>
+        <v>46155.434652233795</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>189</v>
@@ -8071,11 +8071,11 @@
         <v>321</v>
       </c>
       <c r="B114" s="5">
-        <v>46149.16929695602</v>
+        <v>46149.00263028935</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.590775185185</v>
+        <v>46155.42410851852</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>322</v>
@@ -8118,11 +8118,11 @@
         <v>324</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.169301041664</v>
+        <v>46149.002634375</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.60146953704</v>
+        <v>46155.43480287037</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>325</v>
@@ -8179,11 +8179,11 @@
         <v>329</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.1693071412</v>
+        <v>46149.00264047454</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.60144278935</v>
+        <v>46155.43477612268</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>189</v>
@@ -8230,11 +8230,11 @@
         <v>331</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.16931233797</v>
+        <v>46149.002645671295</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.60143921296</v>
+        <v>46155.4347725463</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>189</v>
@@ -8281,11 +8281,11 @@
         <v>333</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.56303070602</v>
+        <v>46155.39636403935</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.601436296296</v>
+        <v>46155.43476962963</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>189</v>
@@ -8332,11 +8332,11 @@
         <v>334</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.56306011574</v>
+        <v>46155.396393449075</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.60143193287</v>
+        <v>46155.4347652662</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>189</v>
@@ -8383,11 +8383,11 @@
         <v>335</v>
       </c>
       <c r="B120" s="5">
-        <v>46149.1693175</v>
+        <v>46149.00265083333</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6016600463</v>
+        <v>46155.43499337963</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>336</v>
@@ -8446,11 +8446,11 @@
         <v>337</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.16932247685</v>
+        <v>46149.00265581018</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.601629756944</v>
+        <v>46155.43496309027</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>189</v>
@@ -8499,11 +8499,11 @@
         <v>339</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.16932829861</v>
+        <v>46149.002661631945</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.60162688658</v>
+        <v>46155.43496021991</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>189</v>
@@ -8552,11 +8552,11 @@
         <v>340</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.56313421296</v>
+        <v>46155.39646754629</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.601624421295</v>
+        <v>46155.43495775463</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>189</v>
@@ -8605,11 +8605,11 @@
         <v>342</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.5631459375</v>
+        <v>46155.39647927083</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.601620671296</v>
+        <v>46155.43495400463</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>189</v>
@@ -8658,11 +8658,11 @@
         <v>344</v>
       </c>
       <c r="B125" s="9">
-        <v>46149.16933366898</v>
+        <v>46149.002667002314</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.60192047454</v>
+        <v>46155.43525380787</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>345</v>
@@ -8721,11 +8721,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.16933884259</v>
+        <v>46149.00267217593</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.601853796295</v>
+        <v>46155.43518712963</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>189</v>
@@ -8772,11 +8772,11 @@
         <v>349</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.16934681713</v>
+        <v>46149.002680150465</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.60185450231</v>
+        <v>46155.43518783565</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>189</v>
@@ -8823,11 +8823,11 @@
         <v>351</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.56323461806</v>
+        <v>46155.39656795139</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.60185530093</v>
+        <v>46155.43518863426</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>248</v>
@@ -8874,11 +8874,11 @@
         <v>353</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.563225370366</v>
+        <v>46155.3965587037</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.60185603009</v>
+        <v>46155.43518936343</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>246</v>
@@ -8925,11 +8925,11 @@
         <v>355</v>
       </c>
       <c r="B130" s="5">
-        <v>46149.1693534375</v>
+        <v>46149.00268677084</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.60216496528</v>
+        <v>46155.43549829861</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>356</v>
@@ -8988,11 +8988,11 @@
         <v>358</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.16935909722</v>
+        <v>46149.00269243056</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.602132280095</v>
+        <v>46155.435465613424</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>189</v>
@@ -9039,11 +9039,11 @@
         <v>359</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.16936413194</v>
+        <v>46149.00269746528</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.602128969906</v>
+        <v>46155.43546230324</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>189</v>
@@ -9090,11 +9090,11 @@
         <v>360</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.56332277777</v>
+        <v>46155.396656111116</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.60212502315</v>
+        <v>46155.435458356485</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>246</v>
@@ -9141,11 +9141,11 @@
         <v>361</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.56333268518</v>
+        <v>46155.39666601852</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.602120462965</v>
+        <v>46155.43545379629</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>248</v>
@@ -9192,11 +9192,11 @@
         <v>362</v>
       </c>
       <c r="B135" s="9">
-        <v>46149.16936914352</v>
+        <v>46149.00270247685</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.60238891204</v>
+        <v>46155.43572224537</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>363</v>
@@ -9239,11 +9239,11 @@
         <v>365</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.169373136574</v>
+        <v>46149.00270646991</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.602217824075</v>
+        <v>46155.43555115741</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>366</v>
@@ -9302,11 +9302,11 @@
         <v>369</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.169417349534</v>
+        <v>46149.00275068287</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.86942971065</v>
+        <v>46196.702763043984</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>370</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="373">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -594,28 +594,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214596734094501</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214596734094526</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214596734094501</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214596734094526</t>
   </si>
   <si>
     <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
@@ -1809,13 +1815,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.0019957176</v>
+        <v>46149.168662384254</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70624586806</v>
+        <v>46175.87291253472</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706257777776</v>
+        <v>46175.87292444444</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1862,13 +1868,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.00206601852</v>
+        <v>46149.16873268518</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.706218611114</v>
+        <v>46175.87288527778</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70624668981</v>
+        <v>46175.87291335648</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1925,13 +1931,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.00206940972</v>
+        <v>46149.16873607639</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70621924769</v>
+        <v>46175.87288591435</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.706246608795</v>
+        <v>46175.87291327547</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1988,13 +1994,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.002072152776</v>
+        <v>46149.16873881944</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.70621967592</v>
+        <v>46175.87288634259</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.706247800925</v>
+        <v>46175.87291446759</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2051,13 +2057,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.00207495371</v>
+        <v>46149.16874162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70622006945</v>
+        <v>46175.872886736106</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70624652778</v>
+        <v>46175.87291319444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2114,13 +2120,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.002078136575</v>
+        <v>46149.16874480324</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70622064815</v>
+        <v>46175.872887314814</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70624614583</v>
+        <v>46175.8729128125</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2177,13 +2183,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.00200085648</v>
+        <v>46149.16866752315</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.70496565972</v>
+        <v>46196.871632326394</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.70498190972</v>
+        <v>46196.87164857639</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2230,13 +2236,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.00208121528</v>
+        <v>46149.168747881944</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.7040040625</v>
+        <v>46183.87067072917</v>
       </c>
       <c r="D11" s="9">
-        <v>46196.70276310186</v>
+        <v>46196.869429768514</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2295,13 +2301,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.00208630787</v>
+        <v>46149.16875297454</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.70401074074</v>
+        <v>46183.87067740741</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.70276306713</v>
+        <v>46196.86942973379</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2360,13 +2366,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.002091331015</v>
+        <v>46149.168757997686</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.70401635417</v>
+        <v>46183.87068302083</v>
       </c>
       <c r="D13" s="9">
-        <v>46196.70276305555</v>
+        <v>46196.869429722225</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2425,11 +2431,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.00200555555</v>
+        <v>46149.16867222222</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.33602989583</v>
+        <v>46197.5026965625</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2472,13 +2478,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.00210356481</v>
+        <v>46149.16877023148</v>
       </c>
       <c r="C15" s="9">
-        <v>46196.70489974537</v>
+        <v>46196.87156641204</v>
       </c>
       <c r="D15" s="9">
-        <v>46196.70492120371</v>
+        <v>46196.871587870366</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2537,13 +2543,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.00210846065</v>
+        <v>46149.16877512731</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.70490936343</v>
+        <v>46196.87157603009</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.70492671296</v>
+        <v>46196.871593379634</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2602,13 +2608,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.00211332176</v>
+        <v>46149.168779988424</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.336022881944</v>
+        <v>46197.50268954861</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.33604180555</v>
+        <v>46197.502708472224</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2667,11 +2673,11 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.002118171295</v>
+        <v>46149.168784837966</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46189.022065694444</v>
+        <v>46189.188732361115</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2730,11 +2736,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.00212268518</v>
+        <v>46149.168789351854</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.02206552083</v>
+        <v>46189.1887321875</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2793,11 +2799,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.00212619213</v>
+        <v>46149.16879285879</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.02206590278</v>
+        <v>46189.18873256944</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2856,11 +2862,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.00212975695</v>
+        <v>46149.16879642361</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.02206553241</v>
+        <v>46189.18873219907</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2919,11 +2925,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.002010208336</v>
+        <v>46149.168676875</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46155.386767407406</v>
+        <v>46155.55343407407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2966,11 +2972,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.00213346065</v>
+        <v>46149.168800127314</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.693065011576</v>
+        <v>46169.85973167824</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3029,11 +3035,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.00213748842</v>
+        <v>46149.168804155095</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.704918414354</v>
+        <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3088,11 +3094,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.002141944446</v>
+        <v>46149.16880861111</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.693560740736</v>
+        <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3147,11 +3153,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.00214671296</v>
+        <v>46149.16881337963</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.010007881945</v>
+        <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3210,11 +3216,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.00215085648</v>
+        <v>46149.16881752315</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.3360318287</v>
+        <v>46197.50269849537</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3269,11 +3275,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.00215518518</v>
+        <v>46149.168821851854</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.00393269676</v>
+        <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3328,11 +3334,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.00215962963</v>
+        <v>46149.1688262963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46197.03887642361</v>
+        <v>46197.20554309028</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3391,11 +3397,11 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.00216386574</v>
+        <v>46149.168830532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46196.70491540509</v>
+        <v>46196.87158207176</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3450,11 +3456,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.002168287036</v>
+        <v>46149.1688349537</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46196.001961284725</v>
+        <v>46196.16862795139</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3509,11 +3515,11 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.002173333334</v>
+        <v>46149.16884</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46185.357815497686</v>
+        <v>46185.52448216435</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3568,11 +3574,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.00217770833</v>
+        <v>46149.168844375</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46192.032033055555</v>
+        <v>46192.19869972223</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3631,11 +3637,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.00218226852</v>
+        <v>46149.16884893518</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.00221716435</v>
+        <v>46190.16888383102</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3690,11 +3696,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.00218697917</v>
+        <v>46149.16885364584</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.69339541667</v>
+        <v>46169.86006208333</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3749,11 +3755,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.002191770836</v>
+        <v>46149.1688584375</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.032033090276</v>
+        <v>46192.19869975695</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3812,11 +3818,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.00224469908</v>
+        <v>46149.16891136574</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.002215347224</v>
+        <v>46190.16888201389</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -3865,11 +3871,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.002250590274</v>
+        <v>46149.168917256946</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.69334290509</v>
+        <v>46169.860009571756</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3918,11 +3924,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.0022559375</v>
+        <v>46149.16892260416</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69313453704</v>
+        <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3981,11 +3987,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.00226620371</v>
+        <v>46149.168932870365</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.00218710648</v>
+        <v>46197.16885377315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4034,11 +4040,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.0022712963</v>
+        <v>46149.16893796297</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.693275451384</v>
+        <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4087,11 +4093,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.002276238425</v>
+        <v>46149.16894290509</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69329935186</v>
+        <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -4140,11 +4146,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.0022791088</v>
+        <v>46149.16894577546</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.693163819444</v>
+        <v>46169.85983048611</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4203,11 +4209,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.002283043985</v>
+        <v>46149.16894971065</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.51887944444</v>
+        <v>46191.68554611111</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4256,11 +4262,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.002287615745</v>
+        <v>46149.1689542824</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46191.518934293985</v>
+        <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4309,11 +4315,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.00201474537</v>
+        <v>46149.16868141203</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46184.34826416666</v>
+        <v>46184.514930833335</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4356,13 +4362,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.00229319444</v>
+        <v>46149.16895986111</v>
       </c>
       <c r="C47" s="9">
-        <v>46184.34825659722</v>
+        <v>46184.514923263894</v>
       </c>
       <c r="D47" s="9">
-        <v>46184.34827644676</v>
+        <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4421,11 +4427,11 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.00229898148</v>
+        <v>46149.16896564815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46184.348264722226</v>
+        <v>46197.71372509259</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4484,11 +4490,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.002305497685</v>
+        <v>46149.16897216435</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.00210819444</v>
+        <v>46184.168774861115</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4497,10 +4503,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4522,7 +4528,7 @@
         <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4542,26 +4548,26 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.00232021991</v>
+        <v>46149.16898688657</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.43178033565</v>
+        <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4582,7 +4588,7 @@
         <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4605,17 +4611,17 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.00232474537</v>
+        <v>46149.168991412036</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.43188986111</v>
+        <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4640,13 +4646,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4656,17 +4662,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.00233350694</v>
+        <v>46149.16900017361</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.43188626158</v>
+        <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4691,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4707,17 +4713,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.41115071759</v>
+        <v>46155.577817384255</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.43188179398</v>
+        <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4742,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4758,17 +4764,17 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.41116238426</v>
+        <v>46155.577829050926</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.43187822917</v>
+        <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4793,13 +4799,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4809,17 +4815,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46149.002338425926</v>
+        <v>46149.1690050926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.39226760417</v>
+        <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4843,7 +4849,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4856,26 +4862,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.00234274306</v>
+        <v>46149.16900940972</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.03990297454</v>
+        <v>46196.2065696412</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4893,13 +4899,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4919,17 +4925,17 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.00234849537</v>
+        <v>46149.16901516204</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46176.004980150465</v>
+        <v>46176.17164681713</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4956,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -4982,26 +4988,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.00235440972</v>
+        <v>46149.16902107639</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.039902916666</v>
+        <v>46196.20656958333</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5019,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5045,17 +5051,17 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.00235954861</v>
+        <v>46149.16902621528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.004980185186</v>
+        <v>46176.17164685186</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5082,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5108,26 +5114,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.002363692125</v>
+        <v>46149.1690303588</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.43199493056</v>
+        <v>46155.59866159722</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5145,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5171,17 +5177,17 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.002368217596</v>
+        <v>46149.16903488426</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.43237927083</v>
+        <v>46155.5990459375</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5208,13 +5214,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5234,17 +5240,17 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.00237244213</v>
+        <v>46149.1690391088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.4022115625</v>
+        <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5268,7 +5274,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5281,26 +5287,26 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.00237577547</v>
+        <v>46149.169042442125</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.410576712966</v>
+        <v>46161.57724337963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5318,13 +5324,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5344,26 +5350,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.002382708335</v>
+        <v>46149.169049375</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.43258655093</v>
+        <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5381,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5397,26 +5403,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.00238950232</v>
+        <v>46149.16905616898</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.432582939815</v>
+        <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5434,13 +5440,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5450,26 +5456,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.3954075</v>
+        <v>46155.562074166664</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.43258009259</v>
+        <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5487,13 +5493,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5503,26 +5509,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.395428749995</v>
+        <v>46155.562095416666</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.432576956024</v>
+        <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5540,13 +5546,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5556,26 +5562,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46149.0024380324</v>
+        <v>46149.169104699075</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.43267354167</v>
+        <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5593,13 +5599,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5619,26 +5625,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.00244297454</v>
+        <v>46149.1691096412</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.432840706024</v>
+        <v>46155.59950737268</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5656,13 +5662,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5672,26 +5678,26 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.002448252315</v>
+        <v>46149.16911491899</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.432837824075</v>
+        <v>46155.59950449074</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5709,13 +5715,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5725,26 +5731,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.395558958335</v>
+        <v>46155.562225625</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.43283494213</v>
+        <v>46155.5995016088</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5762,13 +5768,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5778,26 +5784,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.39557891204</v>
+        <v>46155.56224557871</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.432830324076</v>
+        <v>46155.59949699074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5815,13 +5821,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5831,17 +5837,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46149.00245310186</v>
+        <v>46149.169119768514</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.43271318287</v>
+        <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5868,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -5894,17 +5900,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.00245699074</v>
+        <v>46149.16912365741</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.43296878472</v>
+        <v>46155.59963545139</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5931,13 +5937,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5947,17 +5953,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.00246241898</v>
+        <v>46149.16912908565</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.43296608796</v>
+        <v>46155.59963275463</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5984,13 +5990,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6000,17 +6006,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.39566523148</v>
+        <v>46155.56233189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.432963287036</v>
+        <v>46155.59962995371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6037,13 +6043,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6053,17 +6059,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.395677685185</v>
+        <v>46155.562344351856</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.432959224534</v>
+        <v>46155.599625891206</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6090,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6106,17 +6112,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46149.002467453705</v>
+        <v>46149.16913412037</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.40453425926</v>
+        <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6140,7 +6146,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6153,26 +6159,26 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.00247041667</v>
+        <v>46149.16913708333</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.00432209491</v>
+        <v>46182.17098876157</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6188,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6214,26 +6220,26 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.0024755787</v>
+        <v>46149.16914224537</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46165.01433276621</v>
+        <v>46165.180999432865</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6251,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6277,26 +6283,26 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.0024806713</v>
+        <v>46149.16914733796</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46197.00218905092</v>
+        <v>46197.168855717595</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6314,13 +6320,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6340,26 +6346,26 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.002485694444</v>
+        <v>46149.16915236111</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.433183402776</v>
+        <v>46155.59985006944</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6377,13 +6383,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>155</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6403,17 +6409,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.002490659725</v>
+        <v>46149.16915732639</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.41604099537</v>
+        <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6437,7 +6443,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6450,17 +6456,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.00249383102</v>
+        <v>46149.16916049768</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.433808553236</v>
+        <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6487,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6513,17 +6519,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.00250018519</v>
+        <v>46149.16916685185</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.433358483795</v>
+        <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6550,10 +6556,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6566,17 +6572,17 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.002503703705</v>
+        <v>46149.16917037037</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.43335565973</v>
+        <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6603,10 +6609,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6619,17 +6625,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.39579900463</v>
+        <v>46155.5624656713</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.433599375</v>
+        <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6656,13 +6662,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6672,17 +6678,17 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.39582859953</v>
+        <v>46155.562495266204</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.4336925463</v>
+        <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6709,13 +6715,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6725,17 +6731,17 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
-        <v>46149.002507384255</v>
+        <v>46149.16917405093</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.43397510417</v>
+        <v>46155.600641770834</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6762,13 +6768,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6788,17 +6794,17 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.0025116551</v>
+        <v>46149.169178321754</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.433939571754</v>
+        <v>46155.600606238426</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6823,13 +6829,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6839,17 +6845,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.00251648148</v>
+        <v>46149.169183148144</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.43393666667</v>
+        <v>46155.60060333333</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6874,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6890,17 +6896,17 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.3958999537</v>
+        <v>46155.56256662037</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.43393358796</v>
+        <v>46155.600600254635</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6925,13 +6931,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6941,17 +6947,17 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.3959118287</v>
+        <v>46155.56257849537</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.43392862269</v>
+        <v>46155.60059528935</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6976,13 +6982,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6992,17 +6998,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46149.002521296294</v>
+        <v>46149.169187962965</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.434126782406</v>
+        <v>46155.60079344908</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7029,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7055,17 +7061,17 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.00252525463</v>
+        <v>46149.1691919213</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.43409681713</v>
+        <v>46155.600763483795</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7090,13 +7096,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O95" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="P95" s="10" t="s">
         <v>287</v>
-      </c>
-      <c r="P95" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7106,17 +7112,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.002530937505</v>
+        <v>46149.16919760416</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.43409390046</v>
+        <v>46155.60076056713</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7141,13 +7147,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7157,17 +7163,17 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.39599376157</v>
+        <v>46155.562660428244</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.43409085648</v>
+        <v>46155.60075752315</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7192,13 +7198,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7208,17 +7214,17 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.3960052662</v>
+        <v>46155.56267193287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.43408697916</v>
+        <v>46155.600753645835</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7243,13 +7249,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7259,17 +7265,17 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B99" s="9">
-        <v>46149.002536458334</v>
+        <v>46149.169203125</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.43427597222</v>
+        <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7296,13 +7302,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7322,17 +7328,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.00254027778</v>
+        <v>46149.16920694444</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.43425140047</v>
+        <v>46155.600918067124</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7357,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7373,17 +7379,17 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.002545358795</v>
+        <v>46149.16921202546</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.43424851852</v>
+        <v>46155.60091518519</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7408,13 +7414,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O101" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P101" s="10" t="s">
         <v>299</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7424,17 +7430,17 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.396075185185</v>
+        <v>46155.562741851856</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.43424549769</v>
+        <v>46155.60091216435</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7459,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7475,17 +7481,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.396088379624</v>
+        <v>46155.562755046296</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.43424113426</v>
+        <v>46155.60090780092</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7510,13 +7516,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7526,17 +7532,17 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
-        <v>46149.00255023148</v>
+        <v>46149.16921689815</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.43443113426</v>
+        <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7563,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7589,17 +7595,17 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.00255405092</v>
+        <v>46149.169220717595</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.43439899306</v>
+        <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7626,13 +7632,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7642,17 +7648,17 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.0025591088</v>
+        <v>46149.16922577546</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.43439587963</v>
+        <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7679,13 +7685,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7695,17 +7701,17 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.39619076389</v>
+        <v>46155.56285743056</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.434392696756</v>
+        <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7732,13 +7738,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7748,17 +7754,17 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.39617944445</v>
+        <v>46155.56284611111</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.43438899306</v>
+        <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7785,13 +7791,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7801,17 +7807,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B109" s="9">
-        <v>46149.0026037037</v>
+        <v>46149.169270370374</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.43460684028</v>
+        <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7838,13 +7844,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7864,17 +7870,17 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.002618576385</v>
+        <v>46149.16928524306</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.434663796295</v>
+        <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7899,13 +7905,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7915,17 +7921,17 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.00262461806</v>
+        <v>46149.16929128472</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.43465982639</v>
+        <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7950,13 +7956,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7966,17 +7972,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.396270694444</v>
+        <v>46155.562937361115</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.43465675926</v>
+        <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8001,13 +8007,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8017,17 +8023,17 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.3962828588</v>
+        <v>46155.56294952546</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.434652233795</v>
+        <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8052,13 +8058,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8068,17 +8074,17 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46149.00263028935</v>
+        <v>46149.16929695602</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.42410851852</v>
+        <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8102,7 +8108,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8115,26 +8121,26 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.002634375</v>
+        <v>46149.169301041664</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.43480287037</v>
+        <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8150,13 +8156,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8176,26 +8182,26 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.00264047454</v>
+        <v>46149.1693071412</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.43477612268</v>
+        <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8211,13 +8217,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8227,26 +8233,26 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.002645671295</v>
+        <v>46149.16931233797</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.4347725463</v>
+        <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8262,13 +8268,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8278,26 +8284,26 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.39636403935</v>
+        <v>46155.56303070602</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.43476962963</v>
+        <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8313,13 +8319,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8329,26 +8335,26 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.396393449075</v>
+        <v>46155.56306011574</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.4347652662</v>
+        <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8364,13 +8370,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8380,17 +8386,17 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46149.00265083333</v>
+        <v>46149.1693175</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.43499337963</v>
+        <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8417,13 +8423,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8443,17 +8449,17 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.00265581018</v>
+        <v>46149.16932247685</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.43496309027</v>
+        <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8480,13 +8486,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8496,17 +8502,17 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.002661631945</v>
+        <v>46149.16932829861</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.43496021991</v>
+        <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8533,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8549,17 +8555,17 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.39646754629</v>
+        <v>46155.56313421296</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.43495775463</v>
+        <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8586,13 +8592,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8602,17 +8608,17 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.39647927083</v>
+        <v>46155.5631459375</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.43495400463</v>
+        <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8639,13 +8645,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8655,26 +8661,26 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B125" s="9">
-        <v>46149.002667002314</v>
+        <v>46149.16933366898</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.43525380787</v>
+        <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8692,13 +8698,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8718,26 +8724,26 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.00267217593</v>
+        <v>46149.16933884259</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.43518712963</v>
+        <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8753,13 +8759,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8769,26 +8775,26 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.002680150465</v>
+        <v>46149.16934681713</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.43518783565</v>
+        <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8804,13 +8810,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8820,26 +8826,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.39656795139</v>
+        <v>46155.56323461806</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.43518863426</v>
+        <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8855,13 +8861,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8871,26 +8877,26 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.3965587037</v>
+        <v>46155.563225370366</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.43518936343</v>
+        <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8906,13 +8912,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8922,26 +8928,26 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B130" s="5">
-        <v>46149.00268677084</v>
+        <v>46149.1693534375</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.43549829861</v>
+        <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -8959,13 +8965,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -8985,26 +8991,26 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.00269243056</v>
+        <v>46149.16935909722</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.435465613424</v>
+        <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9020,13 +9026,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9036,26 +9042,26 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.00269746528</v>
+        <v>46149.16936413194</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.43546230324</v>
+        <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9071,13 +9077,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9087,26 +9093,26 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.396656111116</v>
+        <v>46155.56332277777</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.435458356485</v>
+        <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9122,13 +9128,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9138,26 +9144,26 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.39666601852</v>
+        <v>46155.56333268518</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.43545379629</v>
+        <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9173,13 +9179,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9189,17 +9195,17 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B135" s="9">
-        <v>46149.00270247685</v>
+        <v>46149.16936914352</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.43572224537</v>
+        <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9223,7 +9229,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9236,26 +9242,26 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.00270646991</v>
+        <v>46149.169373136574</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.43555115741</v>
+        <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9273,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9299,17 +9305,17 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.00275068287</v>
+        <v>46149.169417349534</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.702763043984</v>
+        <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9336,13 +9342,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46197.168855717595</v>
+        <v>46198.171336064814</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6334,8 +6334,8 @@
       <c r="R81" s="9">
         <v>46197</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>132</v>
+      <c r="S81" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1815,13 +1815,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.168662384254</v>
+        <v>46149.0019957176</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87291253472</v>
+        <v>46175.70624586806</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87292444444</v>
+        <v>46175.706257777776</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1868,13 +1868,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.16873268518</v>
+        <v>46149.00206601852</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87288527778</v>
+        <v>46175.706218611114</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87291335648</v>
+        <v>46175.70624668981</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1931,13 +1931,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.16873607639</v>
+        <v>46149.00206940972</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87288591435</v>
+        <v>46175.70621924769</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87291327547</v>
+        <v>46175.706246608795</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1994,13 +1994,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.16873881944</v>
+        <v>46149.002072152776</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.87288634259</v>
+        <v>46175.70621967592</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87291446759</v>
+        <v>46175.706247800925</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2057,13 +2057,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.16874162037</v>
+        <v>46149.00207495371</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872886736106</v>
+        <v>46175.70622006945</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87291319444</v>
+        <v>46175.70624652778</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2120,13 +2120,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.16874480324</v>
+        <v>46149.002078136575</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.872887314814</v>
+        <v>46175.70622064815</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.8729128125</v>
+        <v>46175.70624614583</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2183,13 +2183,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.16866752315</v>
+        <v>46149.00200085648</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.871632326394</v>
+        <v>46196.70496565972</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.87164857639</v>
+        <v>46196.70498190972</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2236,13 +2236,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.168747881944</v>
+        <v>46149.00208121528</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.87067072917</v>
+        <v>46183.7040040625</v>
       </c>
       <c r="D11" s="9">
-        <v>46196.869429768514</v>
+        <v>46196.70276310186</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2301,13 +2301,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.16875297454</v>
+        <v>46149.00208630787</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.87067740741</v>
+        <v>46183.70401074074</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.86942973379</v>
+        <v>46196.70276306713</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2366,13 +2366,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.168757997686</v>
+        <v>46149.002091331015</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.87068302083</v>
+        <v>46183.70401635417</v>
       </c>
       <c r="D13" s="9">
-        <v>46196.869429722225</v>
+        <v>46196.70276305555</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2431,11 +2431,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.16867222222</v>
+        <v>46149.00200555555</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.5026965625</v>
+        <v>46197.33602989583</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2478,13 +2478,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.16877023148</v>
+        <v>46149.00210356481</v>
       </c>
       <c r="C15" s="9">
-        <v>46196.87156641204</v>
+        <v>46196.70489974537</v>
       </c>
       <c r="D15" s="9">
-        <v>46196.871587870366</v>
+        <v>46196.70492120371</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2543,13 +2543,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.16877512731</v>
+        <v>46149.00210846065</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.87157603009</v>
+        <v>46196.70490936343</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.871593379634</v>
+        <v>46196.70492671296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2608,13 +2608,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.168779988424</v>
+        <v>46149.00211332176</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.50268954861</v>
+        <v>46197.336022881944</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.502708472224</v>
+        <v>46197.33604180555</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2673,11 +2673,11 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.168784837966</v>
+        <v>46149.002118171295</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46189.188732361115</v>
+        <v>46189.022065694444</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2736,11 +2736,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.168789351854</v>
+        <v>46149.00212268518</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.1887321875</v>
+        <v>46189.02206552083</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2799,11 +2799,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.16879285879</v>
+        <v>46149.00212619213</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.18873256944</v>
+        <v>46189.02206590278</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2862,11 +2862,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.16879642361</v>
+        <v>46149.00212975695</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.18873219907</v>
+        <v>46189.02206553241</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2925,11 +2925,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.168676875</v>
+        <v>46149.002010208336</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46155.55343407407</v>
+        <v>46155.386767407406</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2972,11 +2972,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.168800127314</v>
+        <v>46149.00213346065</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.85973167824</v>
+        <v>46169.693065011576</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3035,11 +3035,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.168804155095</v>
+        <v>46149.00213748842</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.87158508102</v>
+        <v>46196.704918414354</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3094,11 +3094,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.16880861111</v>
+        <v>46149.002141944446</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.86022740741</v>
+        <v>46169.693560740736</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3153,11 +3153,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.16881337963</v>
+        <v>46149.00214671296</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.17667454861</v>
+        <v>46179.010007881945</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3216,11 +3216,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.16881752315</v>
+        <v>46149.00215085648</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.50269849537</v>
+        <v>46197.3360318287</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3275,11 +3275,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.168821851854</v>
+        <v>46149.00215518518</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.170599363424</v>
+        <v>46178.00393269676</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3334,11 +3334,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.1688262963</v>
+        <v>46149.00215962963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46197.20554309028</v>
+        <v>46197.03887642361</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3397,11 +3397,11 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.168830532406</v>
+        <v>46149.00216386574</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46196.87158207176</v>
+        <v>46196.70491540509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3456,11 +3456,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.1688349537</v>
+        <v>46149.002168287036</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46196.16862795139</v>
+        <v>46196.001961284725</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3515,11 +3515,11 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.16884</v>
+        <v>46149.002173333334</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46185.52448216435</v>
+        <v>46185.357815497686</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3574,11 +3574,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.168844375</v>
+        <v>46149.00217770833</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46192.19869972223</v>
+        <v>46192.032033055555</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3637,11 +3637,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.16884893518</v>
+        <v>46149.00218226852</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.16888383102</v>
+        <v>46190.00221716435</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3696,11 +3696,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.16885364584</v>
+        <v>46149.00218697917</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.86006208333</v>
+        <v>46169.69339541667</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3755,11 +3755,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.1688584375</v>
+        <v>46149.002191770836</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.19869975695</v>
+        <v>46192.032033090276</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3818,11 +3818,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.16891136574</v>
+        <v>46149.00224469908</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.16888201389</v>
+        <v>46190.002215347224</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -3871,11 +3871,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.168917256946</v>
+        <v>46149.002250590274</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.860009571756</v>
+        <v>46169.69334290509</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3924,11 +3924,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.16892260416</v>
+        <v>46149.0022559375</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.859801203704</v>
+        <v>46169.69313453704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3987,11 +3987,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.168932870365</v>
+        <v>46149.00226620371</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.16885377315</v>
+        <v>46197.00218710648</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4040,11 +4040,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.16893796297</v>
+        <v>46149.0022712963</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.859942118055</v>
+        <v>46169.693275451384</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4093,11 +4093,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.16894290509</v>
+        <v>46149.002276238425</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859966018514</v>
+        <v>46169.69329935186</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -4146,11 +4146,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.16894577546</v>
+        <v>46149.0022791088</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.85983048611</v>
+        <v>46169.693163819444</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4209,11 +4209,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.16894971065</v>
+        <v>46149.002283043985</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.68554611111</v>
+        <v>46191.51887944444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4262,11 +4262,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.1689542824</v>
+        <v>46149.002287615745</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46191.68560096065</v>
+        <v>46191.518934293985</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4315,11 +4315,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.16868141203</v>
+        <v>46149.00201474537</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46184.514930833335</v>
+        <v>46184.34826416666</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4362,13 +4362,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.16895986111</v>
+        <v>46149.00229319444</v>
       </c>
       <c r="C47" s="9">
-        <v>46184.514923263894</v>
+        <v>46184.34825659722</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.71368634259</v>
+        <v>46197.54701967593</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4427,11 +4427,11 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.16896564815</v>
+        <v>46149.00229898148</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.71372509259</v>
+        <v>46197.54705842593</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4490,11 +4490,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.16897216435</v>
+        <v>46149.002305497685</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.168774861115</v>
+        <v>46184.00210819444</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4551,11 +4551,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.16898688657</v>
+        <v>46149.00232021991</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.59844700231</v>
+        <v>46155.43178033565</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4614,11 +4614,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.168991412036</v>
+        <v>46149.00232474537</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.59855652778</v>
+        <v>46155.43188986111</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4665,11 +4665,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.16900017361</v>
+        <v>46149.00233350694</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.59855292824</v>
+        <v>46155.43188626158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4716,11 +4716,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.577817384255</v>
+        <v>46155.41115071759</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.59854846065</v>
+        <v>46155.43188179398</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>191</v>
@@ -4767,11 +4767,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.577829050926</v>
+        <v>46155.41116238426</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.59854489584</v>
+        <v>46155.43187822917</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4818,11 +4818,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46149.1690050926</v>
+        <v>46149.002338425926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.55893427083</v>
+        <v>46155.39226760417</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4865,11 +4865,11 @@
         <v>199</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.16900940972</v>
+        <v>46149.00234274306</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.2065696412</v>
+        <v>46196.03990297454</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -4928,11 +4928,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.16901516204</v>
+        <v>46149.00234849537</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46176.17164681713</v>
+        <v>46176.004980150465</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>205</v>
@@ -4991,11 +4991,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.16902107639</v>
+        <v>46149.00235440972</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.20656958333</v>
+        <v>46196.039902916666</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5054,11 +5054,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.16902621528</v>
+        <v>46149.00235954861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.17164685186</v>
+        <v>46176.004980185186</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5117,11 +5117,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.1690303588</v>
+        <v>46149.002363692125</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.59866159722</v>
+        <v>46155.43199493056</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>215</v>
@@ -5180,11 +5180,11 @@
         <v>217</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.16903488426</v>
+        <v>46149.002368217596</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.5990459375</v>
+        <v>46155.43237927083</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5243,11 +5243,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.1690391088</v>
+        <v>46149.00237244213</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.56887822917</v>
+        <v>46155.4022115625</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5290,11 +5290,11 @@
         <v>221</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.169042442125</v>
+        <v>46149.00237577547</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.57724337963</v>
+        <v>46161.410576712966</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>
@@ -5353,11 +5353,11 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.169049375</v>
+        <v>46149.002382708335</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.59925321759</v>
+        <v>46155.43258655093</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>191</v>
@@ -5406,11 +5406,11 @@
         <v>229</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.16905616898</v>
+        <v>46149.00238950232</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.59924960649</v>
+        <v>46155.432582939815</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>191</v>
@@ -5459,11 +5459,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.562074166664</v>
+        <v>46155.3954075</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.59924675926</v>
+        <v>46155.43258009259</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>191</v>
@@ -5512,11 +5512,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.562095416666</v>
+        <v>46155.395428749995</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.59924362268</v>
+        <v>46155.432576956024</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>191</v>
@@ -5565,11 +5565,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46149.169104699075</v>
+        <v>46149.0024380324</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.59934020833</v>
+        <v>46155.43267354167</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5628,11 +5628,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.1691096412</v>
+        <v>46149.00244297454</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.59950737268</v>
+        <v>46155.432840706024</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>191</v>
@@ -5681,11 +5681,11 @@
         <v>239</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.16911491899</v>
+        <v>46149.002448252315</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.59950449074</v>
+        <v>46155.432837824075</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>191</v>
@@ -5734,11 +5734,11 @@
         <v>240</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.562225625</v>
+        <v>46155.395558958335</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.5995016088</v>
+        <v>46155.43283494213</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>191</v>
@@ -5787,11 +5787,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.56224557871</v>
+        <v>46155.39557891204</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.59949699074</v>
+        <v>46155.432830324076</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>191</v>
@@ -5840,11 +5840,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46149.169119768514</v>
+        <v>46149.00245310186</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.59937984953</v>
+        <v>46155.43271318287</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>243</v>
@@ -5903,11 +5903,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.16912365741</v>
+        <v>46149.00245699074</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.59963545139</v>
+        <v>46155.43296878472</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>191</v>
@@ -5956,11 +5956,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.16912908565</v>
+        <v>46149.00246241898</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.59963275463</v>
+        <v>46155.43296608796</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>191</v>
@@ -6009,11 +6009,11 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.56233189815</v>
+        <v>46155.39566523148</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.59962995371</v>
+        <v>46155.432963287036</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>191</v>
@@ -6062,11 +6062,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.562344351856</v>
+        <v>46155.395677685185</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.599625891206</v>
+        <v>46155.432959224534</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>191</v>
@@ -6115,11 +6115,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46149.16913412037</v>
+        <v>46149.002467453705</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.57120092593</v>
+        <v>46155.40453425926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>197</v>
@@ -6162,11 +6162,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.16913708333</v>
+        <v>46149.00247041667</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.17098876157</v>
+        <v>46182.00432209491</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>254</v>
@@ -6223,11 +6223,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.16914224537</v>
+        <v>46149.0024755787</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46165.180999432865</v>
+        <v>46165.01433276621</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6286,11 +6286,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.16914733796</v>
+        <v>46149.0024806713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.171336064814</v>
+        <v>46198.00466939815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6349,11 +6349,11 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.16915236111</v>
+        <v>46149.002485694444</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.59985006944</v>
+        <v>46155.433183402776</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6412,11 +6412,11 @@
         <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.16915732639</v>
+        <v>46149.002490659725</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.58270766203</v>
+        <v>46155.41604099537</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6459,11 +6459,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.16916049768</v>
+        <v>46149.00249383102</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.60047521991</v>
+        <v>46155.433808553236</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6522,11 +6522,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.16916685185</v>
+        <v>46149.00250018519</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.60002515046</v>
+        <v>46155.433358483795</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>191</v>
@@ -6575,11 +6575,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.16917037037</v>
+        <v>46149.002503703705</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.60002232638</v>
+        <v>46155.43335565973</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6628,11 +6628,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.5624656713</v>
+        <v>46155.39579900463</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.60026604167</v>
+        <v>46155.433599375</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>248</v>
@@ -6681,11 +6681,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.562495266204</v>
+        <v>46155.39582859953</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.600359212964</v>
+        <v>46155.4336925463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>250</v>
@@ -6734,11 +6734,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="9">
-        <v>46149.16917405093</v>
+        <v>46149.002507384255</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.600641770834</v>
+        <v>46155.43397510417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>277</v>
@@ -6797,11 +6797,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.169178321754</v>
+        <v>46149.0025116551</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.600606238426</v>
+        <v>46155.433939571754</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>191</v>
@@ -6848,11 +6848,11 @@
         <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.169183148144</v>
+        <v>46149.00251648148</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.60060333333</v>
+        <v>46155.43393666667</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>191</v>
@@ -6899,11 +6899,11 @@
         <v>282</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.56256662037</v>
+        <v>46155.3958999537</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.600600254635</v>
+        <v>46155.43393358796</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -6950,11 +6950,11 @@
         <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.56257849537</v>
+        <v>46155.3959118287</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.60059528935</v>
+        <v>46155.43392862269</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7001,11 +7001,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46149.169187962965</v>
+        <v>46149.002521296294</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.60079344908</v>
+        <v>46155.434126782406</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7064,11 +7064,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.1691919213</v>
+        <v>46149.00252525463</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.600763483795</v>
+        <v>46155.43409681713</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>191</v>
@@ -7115,11 +7115,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.16919760416</v>
+        <v>46149.002530937505</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.60076056713</v>
+        <v>46155.43409390046</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7166,11 +7166,11 @@
         <v>291</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.562660428244</v>
+        <v>46155.39599376157</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.60075752315</v>
+        <v>46155.43409085648</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7217,11 +7217,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.56267193287</v>
+        <v>46155.3960052662</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.600753645835</v>
+        <v>46155.43408697916</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>191</v>
@@ -7268,11 +7268,11 @@
         <v>295</v>
       </c>
       <c r="B99" s="9">
-        <v>46149.169203125</v>
+        <v>46149.002536458334</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.60094263889</v>
+        <v>46155.43427597222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>296</v>
@@ -7331,11 +7331,11 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.16920694444</v>
+        <v>46149.00254027778</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.600918067124</v>
+        <v>46155.43425140047</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7382,11 +7382,11 @@
         <v>300</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.16921202546</v>
+        <v>46149.002545358795</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.60091518519</v>
+        <v>46155.43424851852</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>191</v>
@@ -7433,11 +7433,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.562741851856</v>
+        <v>46155.396075185185</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.60091216435</v>
+        <v>46155.43424549769</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7484,11 +7484,11 @@
         <v>304</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.562755046296</v>
+        <v>46155.396088379624</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.60090780092</v>
+        <v>46155.43424113426</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -7535,11 +7535,11 @@
         <v>306</v>
       </c>
       <c r="B104" s="5">
-        <v>46149.16921689815</v>
+        <v>46149.00255023148</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.60109780093</v>
+        <v>46155.43443113426</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>307</v>
@@ -7598,11 +7598,11 @@
         <v>308</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.169220717595</v>
+        <v>46149.00255405092</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.60106565972</v>
+        <v>46155.43439899306</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>191</v>
@@ -7651,11 +7651,11 @@
         <v>310</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.16922577546</v>
+        <v>46149.0025591088</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.601062546295</v>
+        <v>46155.43439587963</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>191</v>
@@ -7704,11 +7704,11 @@
         <v>311</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.56285743056</v>
+        <v>46155.39619076389</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.60105936343</v>
+        <v>46155.434392696756</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>191</v>
@@ -7757,11 +7757,11 @@
         <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.56284611111</v>
+        <v>46155.39617944445</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.60105565972</v>
+        <v>46155.43438899306</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>191</v>
@@ -7810,11 +7810,11 @@
         <v>314</v>
       </c>
       <c r="B109" s="9">
-        <v>46149.169270370374</v>
+        <v>46149.0026037037</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.601273506945</v>
+        <v>46155.43460684028</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>315</v>
@@ -7873,11 +7873,11 @@
         <v>317</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.16928524306</v>
+        <v>46149.002618576385</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.60133046296</v>
+        <v>46155.434663796295</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>191</v>
@@ -7924,11 +7924,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.16929128472</v>
+        <v>46149.00262461806</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.60132649305</v>
+        <v>46155.43465982639</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>191</v>
@@ -7975,11 +7975,11 @@
         <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.562937361115</v>
+        <v>46155.396270694444</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.60132342593</v>
+        <v>46155.43465675926</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>191</v>
@@ -8026,11 +8026,11 @@
         <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.56294952546</v>
+        <v>46155.3962828588</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.60131890046</v>
+        <v>46155.434652233795</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>191</v>
@@ -8077,11 +8077,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46149.16929695602</v>
+        <v>46149.00263028935</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.590775185185</v>
+        <v>46155.42410851852</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8124,11 +8124,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.169301041664</v>
+        <v>46149.002634375</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.60146953704</v>
+        <v>46155.43480287037</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>327</v>
@@ -8185,11 +8185,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.1693071412</v>
+        <v>46149.00264047454</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.60144278935</v>
+        <v>46155.43477612268</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>191</v>
@@ -8236,11 +8236,11 @@
         <v>333</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.16931233797</v>
+        <v>46149.002645671295</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.60143921296</v>
+        <v>46155.4347725463</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>191</v>
@@ -8287,11 +8287,11 @@
         <v>335</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.56303070602</v>
+        <v>46155.39636403935</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.601436296296</v>
+        <v>46155.43476962963</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>191</v>
@@ -8338,11 +8338,11 @@
         <v>336</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.56306011574</v>
+        <v>46155.396393449075</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.60143193287</v>
+        <v>46155.4347652662</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>191</v>
@@ -8389,11 +8389,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46149.1693175</v>
+        <v>46149.00265083333</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6016600463</v>
+        <v>46155.43499337963</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8452,11 +8452,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.16932247685</v>
+        <v>46149.00265581018</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.601629756944</v>
+        <v>46155.43496309027</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>191</v>
@@ -8505,11 +8505,11 @@
         <v>341</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.16932829861</v>
+        <v>46149.002661631945</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.60162688658</v>
+        <v>46155.43496021991</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>191</v>
@@ -8558,11 +8558,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.56313421296</v>
+        <v>46155.39646754629</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.601624421295</v>
+        <v>46155.43495775463</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>191</v>
@@ -8611,11 +8611,11 @@
         <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.5631459375</v>
+        <v>46155.39647927083</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.601620671296</v>
+        <v>46155.43495400463</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>191</v>
@@ -8664,11 +8664,11 @@
         <v>346</v>
       </c>
       <c r="B125" s="9">
-        <v>46149.16933366898</v>
+        <v>46149.002667002314</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.60192047454</v>
+        <v>46155.43525380787</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>347</v>
@@ -8727,11 +8727,11 @@
         <v>349</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.16933884259</v>
+        <v>46149.00267217593</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.601853796295</v>
+        <v>46155.43518712963</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>191</v>
@@ -8778,11 +8778,11 @@
         <v>351</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.16934681713</v>
+        <v>46149.002680150465</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.60185450231</v>
+        <v>46155.43518783565</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>191</v>
@@ -8829,11 +8829,11 @@
         <v>353</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.56323461806</v>
+        <v>46155.39656795139</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.60185530093</v>
+        <v>46155.43518863426</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>250</v>
@@ -8880,11 +8880,11 @@
         <v>355</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.563225370366</v>
+        <v>46155.3965587037</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.60185603009</v>
+        <v>46155.43518936343</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>248</v>
@@ -8931,11 +8931,11 @@
         <v>357</v>
       </c>
       <c r="B130" s="5">
-        <v>46149.1693534375</v>
+        <v>46149.00268677084</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.60216496528</v>
+        <v>46155.43549829861</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>358</v>
@@ -8994,11 +8994,11 @@
         <v>360</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.16935909722</v>
+        <v>46149.00269243056</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.602132280095</v>
+        <v>46155.435465613424</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>191</v>
@@ -9045,11 +9045,11 @@
         <v>361</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.16936413194</v>
+        <v>46149.00269746528</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.602128969906</v>
+        <v>46155.43546230324</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>191</v>
@@ -9096,11 +9096,11 @@
         <v>362</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.56332277777</v>
+        <v>46155.396656111116</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.60212502315</v>
+        <v>46155.435458356485</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>248</v>
@@ -9147,11 +9147,11 @@
         <v>363</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.56333268518</v>
+        <v>46155.39666601852</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.602120462965</v>
+        <v>46155.43545379629</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>250</v>
@@ -9198,11 +9198,11 @@
         <v>364</v>
       </c>
       <c r="B135" s="9">
-        <v>46149.16936914352</v>
+        <v>46149.00270247685</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.60238891204</v>
+        <v>46155.43572224537</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>365</v>
@@ -9245,11 +9245,11 @@
         <v>367</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.169373136574</v>
+        <v>46149.00270646991</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.602217824075</v>
+        <v>46155.43555115741</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>368</v>
@@ -9308,11 +9308,11 @@
         <v>371</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.169417349534</v>
+        <v>46149.00275068287</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.86942971065</v>
+        <v>46196.702763043984</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>372</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1815,13 +1815,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.0019957176</v>
+        <v>46149.168662384254</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70624586806</v>
+        <v>46175.87291253472</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706257777776</v>
+        <v>46175.87292444444</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1868,13 +1868,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.00206601852</v>
+        <v>46149.16873268518</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.706218611114</v>
+        <v>46175.87288527778</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70624668981</v>
+        <v>46175.87291335648</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1931,13 +1931,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.00206940972</v>
+        <v>46149.16873607639</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70621924769</v>
+        <v>46175.87288591435</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.706246608795</v>
+        <v>46175.87291327547</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1994,13 +1994,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.002072152776</v>
+        <v>46149.16873881944</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.70621967592</v>
+        <v>46175.87288634259</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.706247800925</v>
+        <v>46175.87291446759</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2057,13 +2057,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.00207495371</v>
+        <v>46149.16874162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70622006945</v>
+        <v>46175.872886736106</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70624652778</v>
+        <v>46175.87291319444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2120,13 +2120,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.002078136575</v>
+        <v>46149.16874480324</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70622064815</v>
+        <v>46175.872887314814</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70624614583</v>
+        <v>46175.8729128125</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2183,13 +2183,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.00200085648</v>
+        <v>46149.16866752315</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.70496565972</v>
+        <v>46196.871632326394</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.70498190972</v>
+        <v>46196.87164857639</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2236,13 +2236,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.00208121528</v>
+        <v>46149.168747881944</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.7040040625</v>
+        <v>46183.87067072917</v>
       </c>
       <c r="D11" s="9">
-        <v>46196.70276310186</v>
+        <v>46196.869429768514</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2301,13 +2301,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.00208630787</v>
+        <v>46149.16875297454</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.70401074074</v>
+        <v>46183.87067740741</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.70276306713</v>
+        <v>46196.86942973379</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2366,13 +2366,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.002091331015</v>
+        <v>46149.168757997686</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.70401635417</v>
+        <v>46183.87068302083</v>
       </c>
       <c r="D13" s="9">
-        <v>46196.70276305555</v>
+        <v>46196.869429722225</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2431,11 +2431,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.00200555555</v>
+        <v>46149.16867222222</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.33602989583</v>
+        <v>46197.5026965625</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2478,13 +2478,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.00210356481</v>
+        <v>46149.16877023148</v>
       </c>
       <c r="C15" s="9">
-        <v>46196.70489974537</v>
+        <v>46196.87156641204</v>
       </c>
       <c r="D15" s="9">
-        <v>46196.70492120371</v>
+        <v>46196.871587870366</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2543,13 +2543,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.00210846065</v>
+        <v>46149.16877512731</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.70490936343</v>
+        <v>46196.87157603009</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.70492671296</v>
+        <v>46196.871593379634</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2608,13 +2608,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.00211332176</v>
+        <v>46149.168779988424</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.336022881944</v>
+        <v>46197.50268954861</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.33604180555</v>
+        <v>46197.502708472224</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2673,11 +2673,11 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.002118171295</v>
+        <v>46149.168784837966</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46189.022065694444</v>
+        <v>46189.188732361115</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2736,11 +2736,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.00212268518</v>
+        <v>46149.168789351854</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.02206552083</v>
+        <v>46189.1887321875</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2799,11 +2799,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.00212619213</v>
+        <v>46149.16879285879</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.02206590278</v>
+        <v>46189.18873256944</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2862,11 +2862,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.00212975695</v>
+        <v>46149.16879642361</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.02206553241</v>
+        <v>46189.18873219907</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2925,11 +2925,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.002010208336</v>
+        <v>46149.168676875</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46155.386767407406</v>
+        <v>46155.55343407407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2972,11 +2972,11 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.00213346065</v>
+        <v>46149.168800127314</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.693065011576</v>
+        <v>46169.85973167824</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -3035,11 +3035,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.00213748842</v>
+        <v>46149.168804155095</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.704918414354</v>
+        <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3094,11 +3094,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.002141944446</v>
+        <v>46149.16880861111</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.693560740736</v>
+        <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3153,11 +3153,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.00214671296</v>
+        <v>46149.16881337963</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.010007881945</v>
+        <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3216,11 +3216,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.00215085648</v>
+        <v>46149.16881752315</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.3360318287</v>
+        <v>46197.50269849537</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3275,11 +3275,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.00215518518</v>
+        <v>46149.168821851854</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.00393269676</v>
+        <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3334,11 +3334,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.00215962963</v>
+        <v>46149.1688262963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46197.03887642361</v>
+        <v>46197.20554309028</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3397,11 +3397,11 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.00216386574</v>
+        <v>46149.168830532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46196.70491540509</v>
+        <v>46196.87158207176</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3456,11 +3456,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.002168287036</v>
+        <v>46149.1688349537</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46196.001961284725</v>
+        <v>46196.16862795139</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3515,11 +3515,11 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.002173333334</v>
+        <v>46149.16884</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46185.357815497686</v>
+        <v>46185.52448216435</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3574,11 +3574,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.00217770833</v>
+        <v>46149.168844375</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46192.032033055555</v>
+        <v>46192.19869972223</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3637,11 +3637,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.00218226852</v>
+        <v>46149.16884893518</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.00221716435</v>
+        <v>46190.16888383102</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3696,11 +3696,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.00218697917</v>
+        <v>46149.16885364584</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.69339541667</v>
+        <v>46169.86006208333</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3755,11 +3755,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.002191770836</v>
+        <v>46149.1688584375</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.032033090276</v>
+        <v>46192.19869975695</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3818,11 +3818,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.00224469908</v>
+        <v>46149.16891136574</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.002215347224</v>
+        <v>46190.16888201389</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>84</v>
@@ -3871,11 +3871,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.002250590274</v>
+        <v>46149.168917256946</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.69334290509</v>
+        <v>46169.860009571756</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3924,11 +3924,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.0022559375</v>
+        <v>46149.16892260416</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69313453704</v>
+        <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3987,11 +3987,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.00226620371</v>
+        <v>46149.168932870365</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.00218710648</v>
+        <v>46197.16885377315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>90</v>
@@ -4040,11 +4040,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.0022712963</v>
+        <v>46149.16893796297</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.693275451384</v>
+        <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4093,11 +4093,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.002276238425</v>
+        <v>46149.16894290509</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69329935186</v>
+        <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -4146,11 +4146,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.0022791088</v>
+        <v>46149.16894577546</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.693163819444</v>
+        <v>46169.85983048611</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4209,11 +4209,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.002283043985</v>
+        <v>46149.16894971065</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.51887944444</v>
+        <v>46191.68554611111</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>87</v>
@@ -4262,11 +4262,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.002287615745</v>
+        <v>46149.1689542824</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46191.518934293985</v>
+        <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4315,11 +4315,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.00201474537</v>
+        <v>46149.16868141203</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46184.34826416666</v>
+        <v>46184.514930833335</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4362,13 +4362,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.00229319444</v>
+        <v>46149.16895986111</v>
       </c>
       <c r="C47" s="9">
-        <v>46184.34825659722</v>
+        <v>46184.514923263894</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.54701967593</v>
+        <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4427,11 +4427,11 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.00229898148</v>
+        <v>46149.16896564815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.54705842593</v>
+        <v>46197.71372509259</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4490,11 +4490,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.002305497685</v>
+        <v>46149.16897216435</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46184.00210819444</v>
+        <v>46184.168774861115</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4551,11 +4551,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.00232021991</v>
+        <v>46149.16898688657</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.43178033565</v>
+        <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4614,11 +4614,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.00232474537</v>
+        <v>46149.168991412036</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.43188986111</v>
+        <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4665,11 +4665,11 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.00233350694</v>
+        <v>46149.16900017361</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.43188626158</v>
+        <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4716,11 +4716,11 @@
         <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.41115071759</v>
+        <v>46155.577817384255</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.43188179398</v>
+        <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>191</v>
@@ -4767,11 +4767,11 @@
         <v>195</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.41116238426</v>
+        <v>46155.577829050926</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.43187822917</v>
+        <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -4818,11 +4818,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46149.002338425926</v>
+        <v>46149.1690050926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.39226760417</v>
+        <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4865,11 +4865,11 @@
         <v>199</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.00234274306</v>
+        <v>46149.16900940972</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.03990297454</v>
+        <v>46196.2065696412</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -4928,11 +4928,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.00234849537</v>
+        <v>46149.16901516204</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46176.004980150465</v>
+        <v>46176.17164681713</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>205</v>
@@ -4991,11 +4991,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.00235440972</v>
+        <v>46149.16902107639</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.039902916666</v>
+        <v>46196.20656958333</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5054,11 +5054,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.00235954861</v>
+        <v>46149.16902621528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.004980185186</v>
+        <v>46176.17164685186</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5117,11 +5117,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.002363692125</v>
+        <v>46149.1690303588</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.43199493056</v>
+        <v>46155.59866159722</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>215</v>
@@ -5180,11 +5180,11 @@
         <v>217</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.002368217596</v>
+        <v>46149.16903488426</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.43237927083</v>
+        <v>46155.5990459375</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5243,11 +5243,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.00237244213</v>
+        <v>46149.1690391088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.4022115625</v>
+        <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5290,11 +5290,11 @@
         <v>221</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.00237577547</v>
+        <v>46149.169042442125</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.410576712966</v>
+        <v>46161.57724337963</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>
@@ -5353,11 +5353,11 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.002382708335</v>
+        <v>46149.169049375</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.43258655093</v>
+        <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>191</v>
@@ -5406,11 +5406,11 @@
         <v>229</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.00238950232</v>
+        <v>46149.16905616898</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.432582939815</v>
+        <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>191</v>
@@ -5459,11 +5459,11 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.3954075</v>
+        <v>46155.562074166664</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.43258009259</v>
+        <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>191</v>
@@ -5512,11 +5512,11 @@
         <v>233</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.395428749995</v>
+        <v>46155.562095416666</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.432576956024</v>
+        <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>191</v>
@@ -5565,11 +5565,11 @@
         <v>234</v>
       </c>
       <c r="B68" s="5">
-        <v>46149.0024380324</v>
+        <v>46149.169104699075</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.43267354167</v>
+        <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5628,11 +5628,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.00244297454</v>
+        <v>46149.1691096412</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.432840706024</v>
+        <v>46155.59950737268</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>191</v>
@@ -5681,11 +5681,11 @@
         <v>239</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.002448252315</v>
+        <v>46149.16911491899</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.432837824075</v>
+        <v>46155.59950449074</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>191</v>
@@ -5734,11 +5734,11 @@
         <v>240</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.395558958335</v>
+        <v>46155.562225625</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.43283494213</v>
+        <v>46155.5995016088</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>191</v>
@@ -5787,11 +5787,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.39557891204</v>
+        <v>46155.56224557871</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.432830324076</v>
+        <v>46155.59949699074</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>191</v>
@@ -5840,11 +5840,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46149.00245310186</v>
+        <v>46149.169119768514</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.43271318287</v>
+        <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>243</v>
@@ -5903,11 +5903,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.00245699074</v>
+        <v>46149.16912365741</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.43296878472</v>
+        <v>46155.59963545139</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>191</v>
@@ -5956,11 +5956,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.00246241898</v>
+        <v>46149.16912908565</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.43296608796</v>
+        <v>46155.59963275463</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>191</v>
@@ -6009,11 +6009,11 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.39566523148</v>
+        <v>46155.56233189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.432963287036</v>
+        <v>46155.59962995371</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>191</v>
@@ -6062,11 +6062,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.395677685185</v>
+        <v>46155.562344351856</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.432959224534</v>
+        <v>46155.599625891206</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>191</v>
@@ -6115,11 +6115,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46149.002467453705</v>
+        <v>46149.16913412037</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.40453425926</v>
+        <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>197</v>
@@ -6162,11 +6162,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.00247041667</v>
+        <v>46149.16913708333</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.00432209491</v>
+        <v>46182.17098876157</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>254</v>
@@ -6223,11 +6223,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.0024755787</v>
+        <v>46149.16914224537</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46165.01433276621</v>
+        <v>46165.180999432865</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6286,11 +6286,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.0024806713</v>
+        <v>46149.16914733796</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.00466939815</v>
+        <v>46198.171336064814</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6349,11 +6349,11 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.002485694444</v>
+        <v>46149.16915236111</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.433183402776</v>
+        <v>46155.59985006944</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6412,11 +6412,11 @@
         <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.002490659725</v>
+        <v>46149.16915732639</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.41604099537</v>
+        <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6459,11 +6459,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.00249383102</v>
+        <v>46149.16916049768</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.433808553236</v>
+        <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6522,11 +6522,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.00250018519</v>
+        <v>46149.16916685185</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.433358483795</v>
+        <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>191</v>
@@ -6575,11 +6575,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.002503703705</v>
+        <v>46149.16917037037</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.43335565973</v>
+        <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6628,11 +6628,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.39579900463</v>
+        <v>46155.5624656713</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.433599375</v>
+        <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>248</v>
@@ -6681,11 +6681,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.39582859953</v>
+        <v>46155.562495266204</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.4336925463</v>
+        <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>250</v>
@@ -6734,11 +6734,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="9">
-        <v>46149.002507384255</v>
+        <v>46149.16917405093</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.43397510417</v>
+        <v>46155.600641770834</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>277</v>
@@ -6797,11 +6797,11 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.0025116551</v>
+        <v>46149.169178321754</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.433939571754</v>
+        <v>46155.600606238426</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>191</v>
@@ -6848,11 +6848,11 @@
         <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.00251648148</v>
+        <v>46149.169183148144</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.43393666667</v>
+        <v>46155.60060333333</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>191</v>
@@ -6899,11 +6899,11 @@
         <v>282</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.3958999537</v>
+        <v>46155.56256662037</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.43393358796</v>
+        <v>46155.600600254635</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -6950,11 +6950,11 @@
         <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.3959118287</v>
+        <v>46155.56257849537</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.43392862269</v>
+        <v>46155.60059528935</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7001,11 +7001,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46149.002521296294</v>
+        <v>46149.169187962965</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.434126782406</v>
+        <v>46155.60079344908</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7064,11 +7064,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.00252525463</v>
+        <v>46149.1691919213</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.43409681713</v>
+        <v>46155.600763483795</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>191</v>
@@ -7115,11 +7115,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.002530937505</v>
+        <v>46149.16919760416</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.43409390046</v>
+        <v>46155.60076056713</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7166,11 +7166,11 @@
         <v>291</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.39599376157</v>
+        <v>46155.562660428244</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.43409085648</v>
+        <v>46155.60075752315</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7217,11 +7217,11 @@
         <v>293</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.3960052662</v>
+        <v>46155.56267193287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.43408697916</v>
+        <v>46155.600753645835</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>191</v>
@@ -7268,11 +7268,11 @@
         <v>295</v>
       </c>
       <c r="B99" s="9">
-        <v>46149.002536458334</v>
+        <v>46149.169203125</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.43427597222</v>
+        <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>296</v>
@@ -7331,11 +7331,11 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.00254027778</v>
+        <v>46149.16920694444</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.43425140047</v>
+        <v>46155.600918067124</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7382,11 +7382,11 @@
         <v>300</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.002545358795</v>
+        <v>46149.16921202546</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.43424851852</v>
+        <v>46155.60091518519</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>191</v>
@@ -7433,11 +7433,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.396075185185</v>
+        <v>46155.562741851856</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.43424549769</v>
+        <v>46155.60091216435</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7484,11 +7484,11 @@
         <v>304</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.396088379624</v>
+        <v>46155.562755046296</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.43424113426</v>
+        <v>46155.60090780092</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -7535,11 +7535,11 @@
         <v>306</v>
       </c>
       <c r="B104" s="5">
-        <v>46149.00255023148</v>
+        <v>46149.16921689815</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.43443113426</v>
+        <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>307</v>
@@ -7598,11 +7598,11 @@
         <v>308</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.00255405092</v>
+        <v>46149.169220717595</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.43439899306</v>
+        <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>191</v>
@@ -7651,11 +7651,11 @@
         <v>310</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.0025591088</v>
+        <v>46149.16922577546</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.43439587963</v>
+        <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>191</v>
@@ -7704,11 +7704,11 @@
         <v>311</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.39619076389</v>
+        <v>46155.56285743056</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.434392696756</v>
+        <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>191</v>
@@ -7757,11 +7757,11 @@
         <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.39617944445</v>
+        <v>46155.56284611111</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.43438899306</v>
+        <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>191</v>
@@ -7810,11 +7810,11 @@
         <v>314</v>
       </c>
       <c r="B109" s="9">
-        <v>46149.0026037037</v>
+        <v>46149.169270370374</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.43460684028</v>
+        <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>315</v>
@@ -7873,11 +7873,11 @@
         <v>317</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.002618576385</v>
+        <v>46149.16928524306</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.434663796295</v>
+        <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>191</v>
@@ -7924,11 +7924,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.00262461806</v>
+        <v>46149.16929128472</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.43465982639</v>
+        <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>191</v>
@@ -7975,11 +7975,11 @@
         <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.396270694444</v>
+        <v>46155.562937361115</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.43465675926</v>
+        <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>191</v>
@@ -8026,11 +8026,11 @@
         <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.3962828588</v>
+        <v>46155.56294952546</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.434652233795</v>
+        <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>191</v>
@@ -8077,11 +8077,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46149.00263028935</v>
+        <v>46149.16929695602</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.42410851852</v>
+        <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8124,11 +8124,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.002634375</v>
+        <v>46149.169301041664</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.43480287037</v>
+        <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>327</v>
@@ -8185,11 +8185,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.00264047454</v>
+        <v>46149.1693071412</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.43477612268</v>
+        <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>191</v>
@@ -8236,11 +8236,11 @@
         <v>333</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.002645671295</v>
+        <v>46149.16931233797</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.4347725463</v>
+        <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>191</v>
@@ -8287,11 +8287,11 @@
         <v>335</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.39636403935</v>
+        <v>46155.56303070602</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.43476962963</v>
+        <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>191</v>
@@ -8338,11 +8338,11 @@
         <v>336</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.396393449075</v>
+        <v>46155.56306011574</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.4347652662</v>
+        <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>191</v>
@@ -8389,11 +8389,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46149.00265083333</v>
+        <v>46149.1693175</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.43499337963</v>
+        <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8452,11 +8452,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.00265581018</v>
+        <v>46149.16932247685</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.43496309027</v>
+        <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>191</v>
@@ -8505,11 +8505,11 @@
         <v>341</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.002661631945</v>
+        <v>46149.16932829861</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.43496021991</v>
+        <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>191</v>
@@ -8558,11 +8558,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.39646754629</v>
+        <v>46155.56313421296</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.43495775463</v>
+        <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>191</v>
@@ -8611,11 +8611,11 @@
         <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.39647927083</v>
+        <v>46155.5631459375</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.43495400463</v>
+        <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>191</v>
@@ -8664,11 +8664,11 @@
         <v>346</v>
       </c>
       <c r="B125" s="9">
-        <v>46149.002667002314</v>
+        <v>46149.16933366898</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.43525380787</v>
+        <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>347</v>
@@ -8727,11 +8727,11 @@
         <v>349</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.00267217593</v>
+        <v>46149.16933884259</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.43518712963</v>
+        <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>191</v>
@@ -8778,11 +8778,11 @@
         <v>351</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.002680150465</v>
+        <v>46149.16934681713</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.43518783565</v>
+        <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>191</v>
@@ -8829,11 +8829,11 @@
         <v>353</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.39656795139</v>
+        <v>46155.56323461806</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.43518863426</v>
+        <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>250</v>
@@ -8880,11 +8880,11 @@
         <v>355</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.3965587037</v>
+        <v>46155.563225370366</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.43518936343</v>
+        <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>248</v>
@@ -8931,11 +8931,11 @@
         <v>357</v>
       </c>
       <c r="B130" s="5">
-        <v>46149.00268677084</v>
+        <v>46149.1693534375</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.43549829861</v>
+        <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>358</v>
@@ -8994,11 +8994,11 @@
         <v>360</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.00269243056</v>
+        <v>46149.16935909722</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.435465613424</v>
+        <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>191</v>
@@ -9045,11 +9045,11 @@
         <v>361</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.00269746528</v>
+        <v>46149.16936413194</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.43546230324</v>
+        <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>191</v>
@@ -9096,11 +9096,11 @@
         <v>362</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.396656111116</v>
+        <v>46155.56332277777</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.435458356485</v>
+        <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>248</v>
@@ -9147,11 +9147,11 @@
         <v>363</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.39666601852</v>
+        <v>46155.56333268518</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.43545379629</v>
+        <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>250</v>
@@ -9198,11 +9198,11 @@
         <v>364</v>
       </c>
       <c r="B135" s="9">
-        <v>46149.00270247685</v>
+        <v>46149.16936914352</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.43572224537</v>
+        <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>365</v>
@@ -9245,11 +9245,11 @@
         <v>367</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.00270646991</v>
+        <v>46149.169373136574</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.43555115741</v>
+        <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>368</v>
@@ -9308,11 +9308,11 @@
         <v>371</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.00275068287</v>
+        <v>46149.169417349534</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.702763043984</v>
+        <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>372</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46196.87158207176</v>
+        <v>46198.80594373842</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -3578,7 +3578,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46192.19869972223</v>
+        <v>46199.16976211805</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.86006208333</v>
+        <v>46199.16976567129</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.19869975695</v>
+        <v>46199.169766875</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.860009571756</v>
+        <v>46199.16976444444</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="374">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -613,6 +613,9 @@
   </si>
   <si>
     <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214596734094526</t>
@@ -3338,7 +3341,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46197.20554309028</v>
+        <v>46199.75288726852</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3399,9 +3402,11 @@
       <c r="B30" s="5">
         <v>46149.168830532406</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46199.752829537036</v>
+      </c>
       <c r="D30" s="5">
-        <v>46198.80594373842</v>
+        <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3460,7 +3465,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46196.16862795139</v>
+        <v>46199.752836423606</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3517,9 +3522,11 @@
       <c r="B32" s="5">
         <v>46149.16884</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46199.75287768518</v>
+      </c>
       <c r="D32" s="5">
-        <v>46185.52448216435</v>
+        <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -4431,7 +4438,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.71372509259</v>
+        <v>46199.752894212965</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4481,13 +4488,13 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="11" t="s">
-        <v>81</v>
+      <c r="U48" s="12" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4503,10 +4510,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4528,7 +4535,7 @@
         <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4548,7 +4555,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4558,16 +4565,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4588,7 +4595,7 @@
         <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4611,7 +4618,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4621,7 +4628,7 @@
         <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4646,13 +4653,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4662,7 +4669,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4672,7 +4679,7 @@
         <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4697,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4713,7 +4720,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4723,7 +4730,7 @@
         <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4748,13 +4755,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4764,7 +4771,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4774,7 +4781,7 @@
         <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4799,13 +4806,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4815,7 +4822,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4825,7 +4832,7 @@
         <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4849,7 +4856,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4862,7 +4869,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4872,16 +4879,16 @@
         <v>46196.2065696412</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4899,13 +4906,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4925,7 +4932,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -4935,7 +4942,7 @@
         <v>46176.17164681713</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4962,13 +4969,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -4988,7 +4995,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -4998,16 +5005,16 @@
         <v>46196.20656958333</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5025,13 +5032,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5051,7 +5058,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5061,7 +5068,7 @@
         <v>46176.17164685186</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5088,13 +5095,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5114,7 +5121,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5124,16 +5131,16 @@
         <v>46155.59866159722</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5151,13 +5158,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5177,7 +5184,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5187,7 +5194,7 @@
         <v>46155.5990459375</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5214,13 +5221,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5240,7 +5247,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5250,7 +5257,7 @@
         <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5274,7 +5281,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5287,7 +5294,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5297,16 +5304,16 @@
         <v>46161.57724337963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5324,13 +5331,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5350,7 +5357,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5360,16 +5367,16 @@
         <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5387,13 +5394,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5403,7 +5410,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5413,16 +5420,16 @@
         <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5440,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5456,7 +5463,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5466,16 +5473,16 @@
         <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5493,13 +5500,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5509,7 +5516,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5519,16 +5526,16 @@
         <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5546,13 +5553,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5562,7 +5569,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5572,16 +5579,16 @@
         <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5599,13 +5606,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5625,7 +5632,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5635,16 +5642,16 @@
         <v>46155.59950737268</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5662,13 +5669,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5678,7 +5685,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5688,16 +5695,16 @@
         <v>46155.59950449074</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5715,13 +5722,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5731,7 +5738,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5741,16 +5748,16 @@
         <v>46155.5995016088</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5768,13 +5775,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5784,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5794,16 +5801,16 @@
         <v>46155.59949699074</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5821,13 +5828,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5837,7 +5844,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5847,7 +5854,7 @@
         <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5874,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -5900,7 +5907,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -5910,7 +5917,7 @@
         <v>46155.59963545139</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5937,13 +5944,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5953,7 +5960,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -5963,7 +5970,7 @@
         <v>46155.59963275463</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5990,13 +5997,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6006,7 +6013,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6016,7 +6023,7 @@
         <v>46155.59962995371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6043,13 +6050,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6059,7 +6066,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6069,7 +6076,7 @@
         <v>46155.599625891206</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6096,13 +6103,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6112,7 +6119,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6122,7 +6129,7 @@
         <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6146,7 +6153,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6159,7 +6166,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6169,16 +6176,16 @@
         <v>46182.17098876157</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6194,13 +6201,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6220,7 +6227,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6230,16 +6237,16 @@
         <v>46165.180999432865</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6257,13 +6264,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6283,7 +6290,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6293,16 +6300,16 @@
         <v>46198.171336064814</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6320,13 +6327,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6346,7 +6353,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6356,16 +6363,16 @@
         <v>46155.59985006944</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6383,13 +6390,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>155</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6409,7 +6416,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6419,7 +6426,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6443,7 +6450,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6456,7 +6463,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
@@ -6466,7 +6473,7 @@
         <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6493,13 +6500,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6519,7 +6526,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B85" s="9">
         <v>46149.16916685185</v>
@@ -6529,7 +6536,7 @@
         <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6556,10 +6563,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6572,7 +6579,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B86" s="5">
         <v>46149.16917037037</v>
@@ -6582,7 +6589,7 @@
         <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6609,10 +6616,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6625,7 +6632,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" s="9">
         <v>46155.5624656713</v>
@@ -6635,7 +6642,7 @@
         <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6662,13 +6669,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6678,7 +6685,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46155.562495266204</v>
@@ -6688,7 +6695,7 @@
         <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6715,13 +6722,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6731,7 +6738,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
         <v>46149.16917405093</v>
@@ -6741,7 +6748,7 @@
         <v>46155.600641770834</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6768,13 +6775,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6794,7 +6801,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46149.169178321754</v>
@@ -6804,7 +6811,7 @@
         <v>46155.600606238426</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6829,13 +6836,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6845,7 +6852,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B91" s="9">
         <v>46149.169183148144</v>
@@ -6855,7 +6862,7 @@
         <v>46155.60060333333</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6880,13 +6887,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6896,7 +6903,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B92" s="5">
         <v>46155.56256662037</v>
@@ -6906,7 +6913,7 @@
         <v>46155.600600254635</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6931,13 +6938,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6947,7 +6954,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B93" s="9">
         <v>46155.56257849537</v>
@@ -6957,7 +6964,7 @@
         <v>46155.60059528935</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6982,13 +6989,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6998,7 +7005,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B94" s="5">
         <v>46149.169187962965</v>
@@ -7008,7 +7015,7 @@
         <v>46155.60079344908</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7035,13 +7042,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7061,7 +7068,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B95" s="9">
         <v>46149.1691919213</v>
@@ -7071,7 +7078,7 @@
         <v>46155.600763483795</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7096,13 +7103,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7112,7 +7119,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B96" s="5">
         <v>46149.16919760416</v>
@@ -7122,7 +7129,7 @@
         <v>46155.60076056713</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7147,13 +7154,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7163,7 +7170,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B97" s="9">
         <v>46155.562660428244</v>
@@ -7173,7 +7180,7 @@
         <v>46155.60075752315</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7198,13 +7205,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7214,7 +7221,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46155.56267193287</v>
@@ -7224,7 +7231,7 @@
         <v>46155.600753645835</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7249,13 +7256,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7265,7 +7272,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B99" s="9">
         <v>46149.169203125</v>
@@ -7275,7 +7282,7 @@
         <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7302,13 +7309,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7328,7 +7335,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46149.16920694444</v>
@@ -7338,7 +7345,7 @@
         <v>46155.600918067124</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7363,13 +7370,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7379,7 +7386,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B101" s="9">
         <v>46149.16921202546</v>
@@ -7389,7 +7396,7 @@
         <v>46155.60091518519</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7414,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7430,7 +7437,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46155.562741851856</v>
@@ -7440,7 +7447,7 @@
         <v>46155.60091216435</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7465,13 +7472,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7481,7 +7488,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B103" s="9">
         <v>46155.562755046296</v>
@@ -7491,7 +7498,7 @@
         <v>46155.60090780092</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7516,13 +7523,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7532,7 +7539,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
         <v>46149.16921689815</v>
@@ -7542,7 +7549,7 @@
         <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7569,13 +7576,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7595,7 +7602,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B105" s="9">
         <v>46149.169220717595</v>
@@ -7605,7 +7612,7 @@
         <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7632,13 +7639,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7648,7 +7655,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
         <v>46149.16922577546</v>
@@ -7658,7 +7665,7 @@
         <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7685,13 +7692,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7701,7 +7708,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B107" s="9">
         <v>46155.56285743056</v>
@@ -7711,7 +7718,7 @@
         <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7738,13 +7745,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7754,7 +7761,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B108" s="5">
         <v>46155.56284611111</v>
@@ -7764,7 +7771,7 @@
         <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7791,13 +7798,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7807,7 +7814,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B109" s="9">
         <v>46149.169270370374</v>
@@ -7817,7 +7824,7 @@
         <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7844,13 +7851,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7870,7 +7877,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B110" s="5">
         <v>46149.16928524306</v>
@@ -7880,7 +7887,7 @@
         <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7905,13 +7912,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7921,7 +7928,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B111" s="9">
         <v>46149.16929128472</v>
@@ -7931,7 +7938,7 @@
         <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7956,13 +7963,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7972,7 +7979,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B112" s="5">
         <v>46155.562937361115</v>
@@ -7982,7 +7989,7 @@
         <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8007,13 +8014,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8023,7 +8030,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B113" s="9">
         <v>46155.56294952546</v>
@@ -8033,7 +8040,7 @@
         <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8058,13 +8065,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8074,7 +8081,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B114" s="5">
         <v>46149.16929695602</v>
@@ -8084,7 +8091,7 @@
         <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8108,7 +8115,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8121,7 +8128,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B115" s="9">
         <v>46149.169301041664</v>
@@ -8131,16 +8138,16 @@
         <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8156,13 +8163,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8182,7 +8189,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B116" s="5">
         <v>46149.1693071412</v>
@@ -8192,16 +8199,16 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8217,13 +8224,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8233,7 +8240,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B117" s="9">
         <v>46149.16931233797</v>
@@ -8243,16 +8250,16 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8268,13 +8275,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8284,7 +8291,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B118" s="5">
         <v>46155.56303070602</v>
@@ -8294,16 +8301,16 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8319,13 +8326,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8335,7 +8342,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B119" s="9">
         <v>46155.56306011574</v>
@@ -8345,16 +8352,16 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8370,13 +8377,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8386,7 +8393,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46149.1693175</v>
@@ -8396,7 +8403,7 @@
         <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8423,13 +8430,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8449,7 +8456,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B121" s="9">
         <v>46149.16932247685</v>
@@ -8459,7 +8466,7 @@
         <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8486,13 +8493,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8502,7 +8509,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B122" s="5">
         <v>46149.16932829861</v>
@@ -8512,7 +8519,7 @@
         <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8539,13 +8546,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8555,7 +8562,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B123" s="9">
         <v>46155.56313421296</v>
@@ -8565,7 +8572,7 @@
         <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8592,13 +8599,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8608,7 +8615,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B124" s="5">
         <v>46155.5631459375</v>
@@ -8618,7 +8625,7 @@
         <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8645,13 +8652,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8661,7 +8668,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B125" s="9">
         <v>46149.16933366898</v>
@@ -8671,16 +8678,16 @@
         <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8698,13 +8705,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8724,7 +8731,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B126" s="5">
         <v>46149.16933884259</v>
@@ -8734,16 +8741,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8759,13 +8766,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8775,7 +8782,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B127" s="9">
         <v>46149.16934681713</v>
@@ -8785,16 +8792,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8810,13 +8817,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8826,7 +8833,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B128" s="5">
         <v>46155.56323461806</v>
@@ -8836,16 +8843,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8861,13 +8868,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8877,7 +8884,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B129" s="9">
         <v>46155.563225370366</v>
@@ -8887,16 +8894,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8912,13 +8919,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8928,7 +8935,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B130" s="5">
         <v>46149.1693534375</v>
@@ -8938,16 +8945,16 @@
         <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -8965,13 +8972,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -8991,7 +8998,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B131" s="9">
         <v>46149.16935909722</v>
@@ -9001,16 +9008,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9026,13 +9033,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9042,7 +9049,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B132" s="5">
         <v>46149.16936413194</v>
@@ -9052,16 +9059,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9077,13 +9084,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9093,7 +9100,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B133" s="9">
         <v>46155.56332277777</v>
@@ -9103,16 +9110,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9128,13 +9135,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9144,7 +9151,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B134" s="5">
         <v>46155.56333268518</v>
@@ -9154,16 +9161,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9179,13 +9186,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9195,7 +9202,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B135" s="9">
         <v>46149.16936914352</v>
@@ -9205,7 +9212,7 @@
         <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9229,7 +9236,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9242,7 +9249,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B136" s="5">
         <v>46149.169373136574</v>
@@ -9252,16 +9259,16 @@
         <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9279,13 +9286,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9305,7 +9312,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B137" s="9">
         <v>46149.169417349534</v>
@@ -9315,7 +9322,7 @@
         <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9342,13 +9349,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="374">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -315,60 +315,63 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4315</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214596725443928</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>1214596725443938</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036201</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4315</t>
+  </si>
+  <si>
+    <t>1214563704105176</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036211</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1214596725443928</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>1214596725443938</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036201</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4315</t>
-  </si>
-  <si>
-    <t>1214563704105176</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036211</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
     <t>1214596734036226</t>
   </si>
   <si>
@@ -613,9 +616,6 @@
   </si>
   <si>
     <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214596734094526</t>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46189.188732361115</v>
+        <v>46199.77909486111</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2730,7 +2730,7 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
+      <c r="U18" s="12" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46189.1887321875</v>
+        <v>46199.779095300924</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2793,7 +2793,7 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="U19" s="12" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46189.18873256944</v>
+        <v>46199.77909486111</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2856,7 +2856,7 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
+      <c r="U20" s="12" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.18873219907</v>
+        <v>46199.77909490741</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2919,7 +2919,7 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="U21" s="12" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3045,7 +3045,7 @@
         <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3078,23 +3078,23 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3104,7 +3104,7 @@
         <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3134,26 +3134,26 @@
         <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3163,7 +3163,7 @@
         <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3193,7 +3193,7 @@
         <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>92</v>
@@ -3211,12 +3211,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
@@ -3226,7 +3226,7 @@
         <v>46197.50269849537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3253,29 +3253,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3285,7 +3285,7 @@
         <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3312,29 +3312,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
@@ -3344,7 +3344,7 @@
         <v>46199.75288726852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3374,7 +3374,7 @@
         <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>92</v>
@@ -3392,12 +3392,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3409,7 +3409,7 @@
         <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3436,29 +3436,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
@@ -3468,7 +3468,7 @@
         <v>46199.752836423606</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3495,29 +3495,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3529,7 +3529,7 @@
         <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3556,29 +3556,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3588,16 +3588,16 @@
         <v>46199.16976211805</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3618,7 +3618,7 @@
         <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>92</v>
@@ -3630,18 +3630,18 @@
         <v>46199</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3651,16 +3651,16 @@
         <v>46190.16888383102</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3678,29 +3678,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3710,16 +3710,16 @@
         <v>46199.16976567129</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3737,29 +3737,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3769,16 +3769,16 @@
         <v>46199.169766875</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3799,7 +3799,7 @@
         <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3811,18 +3811,18 @@
         <v>46199</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3838,10 +3838,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3859,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3885,16 +3885,16 @@
         <v>46199.16976444444</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3912,13 +3912,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3928,7 +3928,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3938,16 +3938,16 @@
         <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -3968,7 +3968,7 @@
         <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3980,18 +3980,18 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4007,10 +4007,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4028,13 +4028,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4054,16 +4054,16 @@
         <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4081,13 +4081,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4107,16 +4107,16 @@
         <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4134,10 +4134,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4160,16 +4160,16 @@
         <v>46169.85983048611</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4190,7 +4190,7 @@
         <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4202,18 +4202,18 @@
         <v>46210</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4229,10 +4229,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4250,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4276,16 +4276,16 @@
         <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4303,13 +4303,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4319,17 +4319,17 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46184.514930833335</v>
+        <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4353,7 +4353,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4362,11 +4362,13 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4378,16 +4380,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4405,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4431,26 +4433,28 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46199.779006689816</v>
+      </c>
       <c r="D48" s="5">
-        <v>46199.752894212965</v>
+        <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4468,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4486,10 +4490,10 @@
         <v>33</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="12" t="s">
-        <v>181</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4499,9 +4503,11 @@
       <c r="B49" s="9">
         <v>46149.16897216435</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46199.779062685186</v>
+      </c>
       <c r="D49" s="9">
-        <v>46184.168774861115</v>
+        <v>46199.77907827546</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4529,10 +4535,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>185</v>
@@ -4544,13 +4550,13 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4592,7 +4598,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>190</v>
@@ -4607,13 +4613,13 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4909,7 +4915,7 @@
         <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>204</v>
@@ -4921,13 +4927,13 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4948,10 +4954,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -4990,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5035,7 +5041,7 @@
         <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>211</v>
@@ -5047,13 +5053,13 @@
         <v>46203</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5074,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5116,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5161,7 +5167,7 @@
         <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>217</v>
@@ -5173,13 +5179,13 @@
         <v>46212</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5200,10 +5206,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5236,13 +5242,13 @@
         <v>46216</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5346,13 +5352,13 @@
         <v>46219</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5621,13 +5627,13 @@
         <v>46226</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5639,7 +5645,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46155.59950737268</v>
+        <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>192</v>
@@ -5692,7 +5698,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46155.59950449074</v>
+        <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>192</v>
@@ -5745,7 +5751,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46155.5995016088</v>
+        <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>192</v>
@@ -5798,7 +5804,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46155.59949699074</v>
+        <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>192</v>
@@ -5860,10 +5866,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5896,13 +5902,13 @@
         <v>46227</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5914,7 +5920,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46155.59963545139</v>
+        <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>192</v>
@@ -5923,10 +5929,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -5967,7 +5973,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46155.59963275463</v>
+        <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>192</v>
@@ -5976,10 +5982,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6020,7 +6026,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46155.59962995371</v>
+        <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>192</v>
@@ -6029,10 +6035,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6073,7 +6079,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46155.599625891206</v>
+        <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>192</v>
@@ -6082,10 +6088,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6204,7 +6210,7 @@
         <v>198</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>256</v>
@@ -6222,7 +6228,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6267,7 +6273,7 @@
         <v>198</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>259</v>
@@ -6285,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6330,7 +6336,7 @@
         <v>198</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>259</v>
@@ -6348,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6393,7 +6399,7 @@
         <v>198</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>264</v>
@@ -6405,13 +6411,13 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6515,13 +6521,13 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6790,13 +6796,13 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6808,7 +6814,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.600606238426</v>
+        <v>46199.77908100694</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>192</v>
@@ -6859,7 +6865,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46155.60060333333</v>
+        <v>46199.77908144676</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>192</v>
@@ -6910,7 +6916,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46155.600600254635</v>
+        <v>46199.77908483797</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>192</v>
@@ -6961,7 +6967,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46155.60059528935</v>
+        <v>46199.779085277776</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>192</v>
@@ -7057,13 +7063,13 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7075,7 +7081,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46155.600763483795</v>
+        <v>46199.779080567125</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>192</v>
@@ -7126,7 +7132,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.60076056713</v>
+        <v>46199.779077430554</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>192</v>
@@ -7177,7 +7183,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46155.60075752315</v>
+        <v>46199.779084340276</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>192</v>
@@ -7228,7 +7234,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46155.600753645835</v>
+        <v>46199.779085752314</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>192</v>
@@ -7324,13 +7330,13 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7342,7 +7348,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46155.600918067124</v>
+        <v>46199.779077858795</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>192</v>
@@ -7393,7 +7399,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46155.60091518519</v>
+        <v>46199.77908177083</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>192</v>
@@ -7444,7 +7450,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46155.60091216435</v>
+        <v>46199.77908608796</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>192</v>
@@ -7495,7 +7501,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46155.60090780092</v>
+        <v>46199.77908645834</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>192</v>
@@ -7591,13 +7597,13 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7866,13 +7872,13 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8178,13 +8184,13 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8445,13 +8451,13 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8720,13 +8726,13 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -8987,13 +8993,13 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9301,13 +9307,13 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -9364,13 +9370,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -471,220 +471,220 @@
     <t>Generación OC materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
   </si>
   <si>
+    <t>1214596969807197</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596969807215</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>1214596969814573</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 ,Generación OC Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>1214596969796648</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4315 ,Materiales Corte Plasma  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772340020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772340035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa OT 4315</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772340045</t>
+  </si>
+  <si>
+    <t>Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472897</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa OT 4315,Control de calidad fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472912</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214596725472956</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472966</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472981</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214563704105178</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214596624002438</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214596734094501</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214596734094526</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624006635</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105084</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105094</t>
+  </si>
+  <si>
+    <t>1214739697907509</t>
+  </si>
+  <si>
+    <t>1214739697907510</t>
+  </si>
+  <si>
+    <t>1214596734105104</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112602</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596969807197</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596969807215</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>1214596969814573</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 ,Generación OC Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>1214596969796648</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4315 ,Materiales Corte Plasma  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772340020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772340035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa OT 4315</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772340045</t>
-  </si>
-  <si>
-    <t>Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472897</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa OT 4315,Control de calidad fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472912</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214596725472956</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472966</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472981</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214563704105178</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214596624002438</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214596734094501</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214596734094526</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624006635</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105084</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105094</t>
-  </si>
-  <si>
-    <t>1214739697907509</t>
-  </si>
-  <si>
-    <t>1214739697907510</t>
-  </si>
-  <si>
-    <t>1214596734105104</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112602</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214596734112622</t>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46199.16976211805</v>
+        <v>46200.194168518516</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3629,8 +3629,8 @@
       <c r="R33" s="9">
         <v>46199</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>133</v>
+      <c r="S33" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3651,7 +3651,7 @@
         <v>46190.16888383102</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3684,7 +3684,7 @@
         <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3710,7 +3710,7 @@
         <v>46199.16976567129</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3740,10 +3740,10 @@
         <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3759,17 +3759,17 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46199.169766875</v>
+        <v>46200.194168437505</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3799,7 +3799,7 @@
         <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3810,8 +3810,8 @@
       <c r="R36" s="5">
         <v>46199</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>133</v>
+      <c r="S36" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3859,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3885,7 +3885,7 @@
         <v>46199.16976444444</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3912,13 +3912,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3928,7 +3928,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3938,16 +3938,16 @@
         <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -3968,7 +3968,7 @@
         <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4007,10 +4007,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4028,13 +4028,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4044,7 +4044,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4054,16 +4054,16 @@
         <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4081,13 +4081,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4107,16 +4107,16 @@
         <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4134,10 +4134,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4160,7 +4160,7 @@
         <v>46169.85983048611</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4190,7 +4190,7 @@
         <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4213,7 +4213,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4250,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4276,7 +4276,7 @@
         <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4303,13 +4303,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4329,7 +4329,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4353,7 +4353,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4380,16 +4380,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4407,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4445,16 +4445,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4472,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4516,10 +4516,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4535,13 +4535,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4571,16 +4571,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4598,10 +4598,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4634,7 +4634,7 @@
         <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4659,13 +4659,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4685,7 +4685,7 @@
         <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4710,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4736,7 +4736,7 @@
         <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4761,13 +4761,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4787,7 +4787,7 @@
         <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4812,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4838,7 +4838,7 @@
         <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4862,7 +4862,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4885,16 +4885,16 @@
         <v>46196.2065696412</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4912,13 +4912,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4927,7 +4927,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -4975,7 +4975,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>207</v>
@@ -5017,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5038,10 +5038,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>211</v>
@@ -5053,7 +5053,7 @@
         <v>46203</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -5080,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5101,7 +5101,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>210</v>
@@ -5143,10 +5143,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5164,10 +5164,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>217</v>
@@ -5206,10 +5206,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5227,7 +5227,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>216</v>
@@ -5373,7 +5373,7 @@
         <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5426,7 +5426,7 @@
         <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5459,7 +5459,7 @@
         <v>231</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5479,7 +5479,7 @@
         <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5512,7 +5512,7 @@
         <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5532,7 +5532,7 @@
         <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5565,7 +5565,7 @@
         <v>233</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5615,7 +5615,7 @@
         <v>220</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>220</v>
@@ -5648,7 +5648,7 @@
         <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5701,7 +5701,7 @@
         <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5754,7 +5754,7 @@
         <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5787,7 +5787,7 @@
         <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5807,7 +5807,7 @@
         <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5840,7 +5840,7 @@
         <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5866,10 +5866,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5890,7 +5890,7 @@
         <v>220</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>220</v>
@@ -5923,16 +5923,16 @@
         <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -5976,16 +5976,16 @@
         <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6029,16 +6029,16 @@
         <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6082,16 +6082,16 @@
         <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6135,7 +6135,7 @@
         <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6188,10 +6188,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6207,7 +6207,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>114</v>
@@ -6249,10 +6249,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6270,7 +6270,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>105</v>
@@ -6312,10 +6312,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6333,7 +6333,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>123</v>
@@ -6375,10 +6375,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6396,10 +6396,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>264</v>
@@ -6542,7 +6542,7 @@
         <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6595,7 +6595,7 @@
         <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6678,7 +6678,7 @@
         <v>269</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6731,7 +6731,7 @@
         <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>275</v>
@@ -6817,7 +6817,7 @@
         <v>46199.77908100694</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6868,7 +6868,7 @@
         <v>46199.77908144676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6919,7 +6919,7 @@
         <v>46199.77908483797</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6970,7 +6970,7 @@
         <v>46199.779085277776</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7084,7 +7084,7 @@
         <v>46199.779080567125</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7135,7 +7135,7 @@
         <v>46199.779077430554</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7186,7 +7186,7 @@
         <v>46199.779084340276</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7237,7 +7237,7 @@
         <v>46199.779085752314</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7351,7 +7351,7 @@
         <v>46199.779077858795</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7402,7 +7402,7 @@
         <v>46199.77908177083</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7453,7 +7453,7 @@
         <v>46199.77908608796</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7504,7 +7504,7 @@
         <v>46199.77908645834</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7618,7 +7618,7 @@
         <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7648,7 +7648,7 @@
         <v>308</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>310</v>
@@ -7671,7 +7671,7 @@
         <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7701,7 +7701,7 @@
         <v>308</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>310</v>
@@ -7724,7 +7724,7 @@
         <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7754,7 +7754,7 @@
         <v>308</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>313</v>
@@ -7777,7 +7777,7 @@
         <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7807,7 +7807,7 @@
         <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>313</v>
@@ -7893,7 +7893,7 @@
         <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7921,7 +7921,7 @@
         <v>316</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>319</v>
@@ -7944,7 +7944,7 @@
         <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7972,7 +7972,7 @@
         <v>316</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>319</v>
@@ -7995,7 +7995,7 @@
         <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8023,7 +8023,7 @@
         <v>316</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>322</v>
@@ -8046,7 +8046,7 @@
         <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8074,7 +8074,7 @@
         <v>316</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>322</v>
@@ -8205,7 +8205,7 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8233,7 +8233,7 @@
         <v>328</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>333</v>
@@ -8256,7 +8256,7 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8284,7 +8284,7 @@
         <v>328</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>335</v>
@@ -8307,7 +8307,7 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8335,7 +8335,7 @@
         <v>328</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>335</v>
@@ -8358,7 +8358,7 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8386,7 +8386,7 @@
         <v>328</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>335</v>
@@ -8472,7 +8472,7 @@
         <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8502,7 +8502,7 @@
         <v>339</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>341</v>
@@ -8525,7 +8525,7 @@
         <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8555,7 +8555,7 @@
         <v>339</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>341</v>
@@ -8578,7 +8578,7 @@
         <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8608,7 +8608,7 @@
         <v>339</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>344</v>
@@ -8631,7 +8631,7 @@
         <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8661,7 +8661,7 @@
         <v>339</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>346</v>
@@ -8747,7 +8747,7 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8775,7 +8775,7 @@
         <v>348</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>351</v>
@@ -8798,7 +8798,7 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8826,7 +8826,7 @@
         <v>348</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>353</v>
@@ -8877,7 +8877,7 @@
         <v>348</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>355</v>
@@ -8928,7 +8928,7 @@
         <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>357</v>
@@ -9014,7 +9014,7 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9042,7 +9042,7 @@
         <v>359</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>359</v>
@@ -9065,7 +9065,7 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9093,7 +9093,7 @@
         <v>359</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>359</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -564,6 +564,9 @@
     <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214596725472966</t>
   </si>
   <si>
@@ -682,9 +685,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214596734112622</t>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.85983048611</v>
+        <v>46203.185002569444</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>162</v>
@@ -4201,8 +4201,8 @@
       <c r="R43" s="9">
         <v>46210</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>103</v>
+      <c r="S43" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -4213,7 +4213,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4256,7 +4256,7 @@
         <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4276,7 +4276,7 @@
         <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4309,7 +4309,7 @@
         <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4329,7 +4329,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4353,7 +4353,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4380,16 +4380,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4407,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4445,16 +4445,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4472,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4498,7 +4498,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4516,10 +4516,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4535,13 +4535,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4571,16 +4571,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4598,10 +4598,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4634,7 +4634,7 @@
         <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4659,13 +4659,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4685,7 +4685,7 @@
         <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4710,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4736,7 +4736,7 @@
         <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4761,13 +4761,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4787,7 +4787,7 @@
         <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4812,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4838,7 +4838,7 @@
         <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4862,7 +4862,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4875,26 +4875,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46196.2065696412</v>
+        <v>46203.16988410879</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4912,13 +4912,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4927,7 +4927,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>207</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46196.20656958333</v>
+        <v>46203.169886585645</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -5017,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5038,7 +5038,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>145</v>
@@ -5053,7 +5053,7 @@
         <v>46203</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>210</v>
@@ -5143,10 +5143,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5164,10 +5164,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>217</v>
@@ -5227,7 +5227,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>216</v>
@@ -5373,7 +5373,7 @@
         <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5426,7 +5426,7 @@
         <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5459,7 +5459,7 @@
         <v>231</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5479,7 +5479,7 @@
         <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5512,7 +5512,7 @@
         <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5532,7 +5532,7 @@
         <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5565,7 +5565,7 @@
         <v>233</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5615,7 +5615,7 @@
         <v>220</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>220</v>
@@ -5648,7 +5648,7 @@
         <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5701,7 +5701,7 @@
         <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5754,7 +5754,7 @@
         <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5787,7 +5787,7 @@
         <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5807,7 +5807,7 @@
         <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5840,7 +5840,7 @@
         <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5890,7 +5890,7 @@
         <v>220</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>220</v>
@@ -5923,7 +5923,7 @@
         <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5976,7 +5976,7 @@
         <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6029,7 +6029,7 @@
         <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6082,7 +6082,7 @@
         <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6135,7 +6135,7 @@
         <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6188,10 +6188,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6207,7 +6207,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>114</v>
@@ -6249,10 +6249,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6270,7 +6270,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>105</v>
@@ -6312,10 +6312,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6333,7 +6333,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>123</v>
@@ -6375,10 +6375,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6396,7 +6396,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>155</v>
@@ -6542,7 +6542,7 @@
         <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6595,7 +6595,7 @@
         <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6678,7 +6678,7 @@
         <v>269</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6731,7 +6731,7 @@
         <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>275</v>
@@ -6817,7 +6817,7 @@
         <v>46199.77908100694</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6868,7 +6868,7 @@
         <v>46199.77908144676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6919,7 +6919,7 @@
         <v>46199.77908483797</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6970,7 +6970,7 @@
         <v>46199.779085277776</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7084,7 +7084,7 @@
         <v>46199.779080567125</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7135,7 +7135,7 @@
         <v>46199.779077430554</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7186,7 +7186,7 @@
         <v>46199.779084340276</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7237,7 +7237,7 @@
         <v>46199.779085752314</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7351,7 +7351,7 @@
         <v>46199.779077858795</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7402,7 +7402,7 @@
         <v>46199.77908177083</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7453,7 +7453,7 @@
         <v>46199.77908608796</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7504,7 +7504,7 @@
         <v>46199.77908645834</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7618,7 +7618,7 @@
         <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7648,7 +7648,7 @@
         <v>308</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>310</v>
@@ -7671,7 +7671,7 @@
         <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7701,7 +7701,7 @@
         <v>308</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>310</v>
@@ -7724,7 +7724,7 @@
         <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7754,7 +7754,7 @@
         <v>308</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>313</v>
@@ -7777,7 +7777,7 @@
         <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7807,7 +7807,7 @@
         <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>313</v>
@@ -7893,7 +7893,7 @@
         <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7921,7 +7921,7 @@
         <v>316</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>319</v>
@@ -7944,7 +7944,7 @@
         <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7972,7 +7972,7 @@
         <v>316</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>319</v>
@@ -7995,7 +7995,7 @@
         <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8023,7 +8023,7 @@
         <v>316</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>322</v>
@@ -8046,7 +8046,7 @@
         <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8074,7 +8074,7 @@
         <v>316</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>322</v>
@@ -8205,7 +8205,7 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8233,7 +8233,7 @@
         <v>328</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>333</v>
@@ -8256,7 +8256,7 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8284,7 +8284,7 @@
         <v>328</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>335</v>
@@ -8307,7 +8307,7 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8335,7 +8335,7 @@
         <v>328</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>335</v>
@@ -8358,7 +8358,7 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8386,7 +8386,7 @@
         <v>328</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>335</v>
@@ -8472,7 +8472,7 @@
         <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8502,7 +8502,7 @@
         <v>339</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>341</v>
@@ -8525,7 +8525,7 @@
         <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8555,7 +8555,7 @@
         <v>339</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>341</v>
@@ -8578,7 +8578,7 @@
         <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8608,7 +8608,7 @@
         <v>339</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>344</v>
@@ -8631,7 +8631,7 @@
         <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8661,7 +8661,7 @@
         <v>339</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>346</v>
@@ -8747,7 +8747,7 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8775,7 +8775,7 @@
         <v>348</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>351</v>
@@ -8798,7 +8798,7 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8826,7 +8826,7 @@
         <v>348</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>353</v>
@@ -8877,7 +8877,7 @@
         <v>348</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>355</v>
@@ -8928,7 +8928,7 @@
         <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>357</v>
@@ -9014,7 +9014,7 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9042,7 +9042,7 @@
         <v>359</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>359</v>
@@ -9065,7 +9065,7 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9093,7 +9093,7 @@
         <v>359</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>359</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46203.16988410879</v>
+        <v>46204.1910444213</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4926,8 +4926,8 @@
       <c r="R56" s="5">
         <v>46203</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>164</v>
+      <c r="S56" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46203.169886585645</v>
+        <v>46204.1910445949</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -5052,8 +5052,8 @@
       <c r="R58" s="5">
         <v>46203</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>164</v>
+      <c r="S58" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="374">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -315,280 +315,280 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4315</t>
   </si>
   <si>
+    <t>1214596725443928</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  OT 4315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>1214596725443938</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036201</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4315</t>
+  </si>
+  <si>
+    <t>1214563704105176</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>1214596734036211</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214596734036226</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315,Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1214596725445208</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214596725445226</t>
+  </si>
+  <si>
+    <t>rodete OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4315,Generación OC Rodete OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772319023</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4315,rodete OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725454716</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4315</t>
+  </si>
+  <si>
+    <t>rodete OT 4315,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214596725454734</t>
+  </si>
+  <si>
+    <t>Motor OT 4315</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772320275</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4315</t>
+  </si>
+  <si>
+    <t>Motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772320293</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Motor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772322550</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Motor OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772322568</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596969807197</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596969807215</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser  OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4315</t>
+  </si>
+  <si>
+    <t>1214596969814573</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 ,Generación OC Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>1214596969796648</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4315 ,Materiales Corte Plasma  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772340020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772340035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa OT 4315</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>1214596772340045</t>
+  </si>
+  <si>
+    <t>Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472897</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa OT 4315,Control de calidad fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472912</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214596725472956</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1214596725472966</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472981</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214563704105178</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214596725443928</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  OT 4315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>1214596725443938</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036201</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4315</t>
-  </si>
-  <si>
-    <t>1214563704105176</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>1214596734036211</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214596734036226</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315,Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1214596725445208</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214596725445226</t>
-  </si>
-  <si>
-    <t>rodete OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4315,Generación OC Rodete OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772319023</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4315,rodete OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725454716</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4315</t>
-  </si>
-  <si>
-    <t>rodete OT 4315,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214596725454734</t>
-  </si>
-  <si>
-    <t>Motor OT 4315</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772320275</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4315</t>
-  </si>
-  <si>
-    <t>Motor OT 4315,Fabricación motor OT 4315,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772320293</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Motor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772322550</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Motor OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772322568</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596969807197</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4315,Fabricacion Corte Laser  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596969807215</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser  OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>1214596969814573</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 ,Generación OC Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>1214596969796648</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4315 ,Materiales Corte Plasma  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772340020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma OT 4315 </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772340035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa OT 4315</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>1214596772340045</t>
-  </si>
-  <si>
-    <t>Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472897</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa OT 4315,Control de calidad fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472912</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214596725472956</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1214596725472966</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472981</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214563704105178</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
   </si>
   <si>
     <t>1214596624002438</t>
@@ -2436,9 +2436,11 @@
       <c r="B14" s="5">
         <v>46149.16867222222</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46204.91290795139</v>
+      </c>
       <c r="D14" s="5">
-        <v>46197.5026965625</v>
+        <v>46204.912918587965</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2473,8 +2475,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2678,9 +2684,11 @@
       <c r="B18" s="5">
         <v>46149.168784837966</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46204.91285559028</v>
+      </c>
       <c r="D18" s="5">
-        <v>46199.77909486111</v>
+        <v>46204.91287212963</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2728,25 +2736,27 @@
         <v>33</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46149.168789351854</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46204.91289165509</v>
+      </c>
       <c r="D19" s="9">
-        <v>46199.779095300924</v>
+        <v>46204.91290902778</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2779,7 +2789,7 @@
         <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2791,25 +2801,27 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46149.16879285879</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46204.91205277778</v>
+      </c>
       <c r="D20" s="5">
-        <v>46199.77909486111</v>
+        <v>46204.91223577547</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2842,7 +2854,7 @@
         <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2854,25 +2866,27 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46149.16879642361</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46204.911869143514</v>
+      </c>
       <c r="D21" s="9">
-        <v>46199.77909490741</v>
+        <v>46204.91200600694</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2905,7 +2919,7 @@
         <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2917,15 +2931,15 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46149.168676875</v>
@@ -2935,7 +2949,7 @@
         <v>46155.55343407407</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2959,7 +2973,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2972,7 +2986,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168800127314</v>
@@ -2982,16 +2996,16 @@
         <v>46169.85973167824</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -3009,13 +3023,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="9">
         <v>46157</v>
@@ -3030,12 +3044,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3045,16 +3059,16 @@
         <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3072,29 +3086,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3104,16 +3118,16 @@
         <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3131,29 +3145,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3163,16 +3177,16 @@
         <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3190,13 +3204,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3211,12 +3225,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
@@ -3226,16 +3240,16 @@
         <v>46197.50269849537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3253,29 +3267,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3285,16 +3299,16 @@
         <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3312,29 +3326,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
@@ -3344,16 +3358,16 @@
         <v>46199.75288726852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3371,13 +3385,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="9">
         <v>46157</v>
@@ -3392,12 +3406,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3409,16 +3423,16 @@
         <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3436,29 +3450,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
@@ -3468,16 +3482,16 @@
         <v>46199.752836423606</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3495,29 +3509,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3529,16 +3543,16 @@
         <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3556,29 +3570,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3588,16 +3602,16 @@
         <v>46200.194168518516</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3615,13 +3629,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="9">
         <v>46189</v>
@@ -3636,31 +3650,31 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.16888383102</v>
+        <v>46204.91286611111</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3678,29 +3692,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3710,16 +3724,16 @@
         <v>46199.16976567129</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3737,29 +3751,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3769,16 +3783,16 @@
         <v>46200.194168437505</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3796,10 +3810,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3817,31 +3831,31 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46190.16888201389</v>
+        <v>46204.91289927083</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3859,13 +3873,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3875,7 +3889,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3885,16 +3899,16 @@
         <v>46199.16976444444</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3912,13 +3926,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3928,7 +3942,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3938,16 +3952,16 @@
         <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -3965,10 +3979,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3980,37 +3994,37 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46197.16885377315</v>
+        <v>46204.91187768518</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4028,13 +4042,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4044,7 +4058,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4054,16 +4068,16 @@
         <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4081,13 +4095,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4097,7 +4111,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4107,16 +4121,16 @@
         <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4134,10 +4148,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4150,7 +4164,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4160,16 +4174,16 @@
         <v>46203.185002569444</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4187,10 +4201,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4202,37 +4216,37 @@
         <v>46210</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46191.68554611111</v>
+        <v>46204.91205900463</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4250,13 +4264,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4266,7 +4280,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4276,16 +4290,16 @@
         <v>46191.68560096065</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4303,13 +4317,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4319,7 +4333,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4329,7 +4343,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4353,7 +4367,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4363,7 +4377,7 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4407,7 +4421,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
@@ -4472,7 +4486,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>180</v>
@@ -4535,7 +4549,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>179</v>
@@ -4550,7 +4564,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4598,7 +4612,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>190</v>
@@ -4613,13 +4627,13 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4915,7 +4929,7 @@
         <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>204</v>
@@ -4933,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4954,10 +4968,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -4996,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5041,7 +5055,7 @@
         <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>211</v>
@@ -5059,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5080,10 +5094,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5122,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5167,7 +5181,7 @@
         <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>217</v>
@@ -5179,13 +5193,13 @@
         <v>46212</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5206,10 +5220,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5242,13 +5256,13 @@
         <v>46216</v>
       </c>
       <c r="S61" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5352,13 +5366,13 @@
         <v>46219</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5627,13 +5641,13 @@
         <v>46226</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5866,10 +5880,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5902,13 +5916,13 @@
         <v>46227</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5929,10 +5943,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -5982,10 +5996,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6035,10 +6049,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6088,10 +6102,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6210,7 +6224,7 @@
         <v>198</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>256</v>
@@ -6228,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6273,7 +6287,7 @@
         <v>198</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>259</v>
@@ -6291,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6336,7 +6350,7 @@
         <v>198</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>259</v>
@@ -6354,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6399,7 +6413,7 @@
         <v>198</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>264</v>
@@ -6411,13 +6425,13 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6521,13 +6535,13 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6796,13 +6810,13 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7063,13 +7077,13 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7330,13 +7344,13 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7597,13 +7611,13 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7872,13 +7886,13 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8184,13 +8198,13 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8451,13 +8465,13 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8726,13 +8740,13 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -8993,13 +9007,13 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9307,13 +9321,13 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -9370,13 +9384,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1818,13 +1818,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.168662384254</v>
+        <v>46149.0019957176</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87291253472</v>
+        <v>46175.70624586806</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87292444444</v>
+        <v>46175.706257777776</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1871,13 +1871,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.16873268518</v>
+        <v>46149.00206601852</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87288527778</v>
+        <v>46175.706218611114</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87291335648</v>
+        <v>46175.70624668981</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1934,13 +1934,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.16873607639</v>
+        <v>46149.00206940972</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87288591435</v>
+        <v>46175.70621924769</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87291327547</v>
+        <v>46175.706246608795</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1997,13 +1997,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.16873881944</v>
+        <v>46149.002072152776</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.87288634259</v>
+        <v>46175.70621967592</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87291446759</v>
+        <v>46175.706247800925</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2060,13 +2060,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.16874162037</v>
+        <v>46149.00207495371</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.872886736106</v>
+        <v>46175.70622006945</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87291319444</v>
+        <v>46175.70624652778</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2123,13 +2123,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.16874480324</v>
+        <v>46149.002078136575</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.872887314814</v>
+        <v>46175.70622064815</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.8729128125</v>
+        <v>46175.70624614583</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2186,13 +2186,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.16866752315</v>
+        <v>46149.00200085648</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.871632326394</v>
+        <v>46196.70496565972</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.87164857639</v>
+        <v>46196.70498190972</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2239,13 +2239,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.168747881944</v>
+        <v>46149.00208121528</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.87067072917</v>
+        <v>46183.7040040625</v>
       </c>
       <c r="D11" s="9">
-        <v>46196.869429768514</v>
+        <v>46196.70276310186</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2304,13 +2304,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.16875297454</v>
+        <v>46149.00208630787</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.87067740741</v>
+        <v>46183.70401074074</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.86942973379</v>
+        <v>46196.70276306713</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2369,13 +2369,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.168757997686</v>
+        <v>46149.002091331015</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.87068302083</v>
+        <v>46183.70401635417</v>
       </c>
       <c r="D13" s="9">
-        <v>46196.869429722225</v>
+        <v>46196.70276305555</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2434,13 +2434,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.16867222222</v>
+        <v>46149.00200555555</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.91290795139</v>
+        <v>46204.74624128472</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.912918587965</v>
+        <v>46204.7462519213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2487,13 +2487,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.16877023148</v>
+        <v>46149.00210356481</v>
       </c>
       <c r="C15" s="9">
-        <v>46196.87156641204</v>
+        <v>46196.70489974537</v>
       </c>
       <c r="D15" s="9">
-        <v>46196.871587870366</v>
+        <v>46196.70492120371</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2552,13 +2552,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.16877512731</v>
+        <v>46149.00210846065</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.87157603009</v>
+        <v>46196.70490936343</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.871593379634</v>
+        <v>46196.70492671296</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2617,13 +2617,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.168779988424</v>
+        <v>46149.00211332176</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.50268954861</v>
+        <v>46197.336022881944</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.502708472224</v>
+        <v>46197.33604180555</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2682,13 +2682,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.168784837966</v>
+        <v>46149.002118171295</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.91285559028</v>
+        <v>46204.746188923615</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.91287212963</v>
+        <v>46204.74620546296</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2747,13 +2747,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.168789351854</v>
+        <v>46149.00212268518</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.91289165509</v>
+        <v>46204.74622498843</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.91290902778</v>
+        <v>46204.746242361114</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2812,13 +2812,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.16879285879</v>
+        <v>46149.00212619213</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.91205277778</v>
+        <v>46204.74538611111</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.91223577547</v>
+        <v>46204.745569108796</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2877,13 +2877,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.16879642361</v>
+        <v>46149.00212975695</v>
       </c>
       <c r="C21" s="9">
-        <v>46204.911869143514</v>
+        <v>46204.74520247686</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.91200600694</v>
+        <v>46204.74533934028</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2942,11 +2942,11 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.168676875</v>
+        <v>46149.002010208336</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46155.55343407407</v>
+        <v>46155.386767407406</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2989,11 +2989,11 @@
         <v>93</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.168800127314</v>
+        <v>46149.00213346065</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.85973167824</v>
+        <v>46169.693065011576</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>94</v>
@@ -3052,11 +3052,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.168804155095</v>
+        <v>46149.00213748842</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.87158508102</v>
+        <v>46196.704918414354</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3111,11 +3111,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.16880861111</v>
+        <v>46149.002141944446</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.86022740741</v>
+        <v>46169.693560740736</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3170,11 +3170,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.16881337963</v>
+        <v>46149.00214671296</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.17667454861</v>
+        <v>46179.010007881945</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3233,11 +3233,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.16881752315</v>
+        <v>46149.00215085648</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.50269849537</v>
+        <v>46197.3360318287</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3292,11 +3292,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.168821851854</v>
+        <v>46149.00215518518</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.170599363424</v>
+        <v>46178.00393269676</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3351,11 +3351,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.1688262963</v>
+        <v>46149.00215962963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46199.75288726852</v>
+        <v>46199.58622060185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3414,13 +3414,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.168830532406</v>
+        <v>46149.00216386574</v>
       </c>
       <c r="C30" s="5">
-        <v>46199.752829537036</v>
+        <v>46199.58616287037</v>
       </c>
       <c r="D30" s="5">
-        <v>46199.75283171296</v>
+        <v>46199.5861650463</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3475,11 +3475,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.1688349537</v>
+        <v>46149.002168287036</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46199.752836423606</v>
+        <v>46199.58616975695</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3534,13 +3534,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.16884</v>
+        <v>46149.002173333334</v>
       </c>
       <c r="C32" s="5">
-        <v>46199.75287768518</v>
+        <v>46199.58621101852</v>
       </c>
       <c r="D32" s="5">
-        <v>46199.752879155094</v>
+        <v>46199.58621248843</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3595,11 +3595,11 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.168844375</v>
+        <v>46149.00217770833</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46200.194168518516</v>
+        <v>46200.02750185185</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3658,11 +3658,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.16884893518</v>
+        <v>46149.00218226852</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46204.91286611111</v>
+        <v>46204.746199444446</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3717,11 +3717,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.16885364584</v>
+        <v>46149.00218697917</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46199.16976567129</v>
+        <v>46199.00309900463</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3776,11 +3776,11 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.1688584375</v>
+        <v>46149.002191770836</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46200.194168437505</v>
+        <v>46200.02750177083</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3839,11 +3839,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.16891136574</v>
+        <v>46149.00224469908</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46204.91289927083</v>
+        <v>46204.74623260417</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>83</v>
@@ -3892,11 +3892,11 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.168917256946</v>
+        <v>46149.002250590274</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46199.16976444444</v>
+        <v>46199.00309777778</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -3945,11 +3945,11 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.16892260416</v>
+        <v>46149.0022559375</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.859801203704</v>
+        <v>46169.69313453704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4008,11 +4008,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.168932870365</v>
+        <v>46149.00226620371</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46204.91187768518</v>
+        <v>46204.74521101852</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>89</v>
@@ -4061,11 +4061,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.16893796297</v>
+        <v>46149.0022712963</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.859942118055</v>
+        <v>46169.693275451384</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4114,11 +4114,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.16894290509</v>
+        <v>46149.002276238425</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859966018514</v>
+        <v>46169.69329935186</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4167,11 +4167,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.16894577546</v>
+        <v>46149.0022791088</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46203.185002569444</v>
+        <v>46203.01833590277</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4230,11 +4230,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.16894971065</v>
+        <v>46149.002283043985</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46204.91205900463</v>
+        <v>46204.745392337965</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>86</v>
@@ -4283,11 +4283,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.1689542824</v>
+        <v>46149.002287615745</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46191.68560096065</v>
+        <v>46191.518934293985</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4336,11 +4336,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.16868141203</v>
+        <v>46149.00201474537</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46199.77902613426</v>
+        <v>46199.61235946759</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4385,13 +4385,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.16895986111</v>
+        <v>46149.00229319444</v>
       </c>
       <c r="C47" s="9">
-        <v>46184.514923263894</v>
+        <v>46184.34825659722</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.71368634259</v>
+        <v>46197.54701967593</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4450,13 +4450,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.16896564815</v>
+        <v>46149.00229898148</v>
       </c>
       <c r="C48" s="5">
-        <v>46199.779006689816</v>
+        <v>46199.612340023144</v>
       </c>
       <c r="D48" s="5">
-        <v>46199.779022372684</v>
+        <v>46199.61235570602</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4515,13 +4515,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.16897216435</v>
+        <v>46149.002305497685</v>
       </c>
       <c r="C49" s="9">
-        <v>46199.779062685186</v>
+        <v>46199.61239601852</v>
       </c>
       <c r="D49" s="9">
-        <v>46199.77907827546</v>
+        <v>46199.612411608796</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4578,11 +4578,11 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.16898688657</v>
+        <v>46149.00232021991</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.59844700231</v>
+        <v>46155.43178033565</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4641,11 +4641,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.168991412036</v>
+        <v>46149.00232474537</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.59855652778</v>
+        <v>46155.43188986111</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4692,11 +4692,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.16900017361</v>
+        <v>46149.00233350694</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.59855292824</v>
+        <v>46155.43188626158</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4743,11 +4743,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.577817384255</v>
+        <v>46155.41115071759</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.59854846065</v>
+        <v>46155.43188179398</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -4794,11 +4794,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.577829050926</v>
+        <v>46155.41116238426</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.59854489584</v>
+        <v>46155.43187822917</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -4845,11 +4845,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="9">
-        <v>46149.1690050926</v>
+        <v>46149.002338425926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.55893427083</v>
+        <v>46155.39226760417</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>198</v>
@@ -4892,11 +4892,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.16900940972</v>
+        <v>46149.00234274306</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46204.1910444213</v>
+        <v>46204.02437775463</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4955,11 +4955,11 @@
         <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.16901516204</v>
+        <v>46149.00234849537</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46176.17164681713</v>
+        <v>46205.00165636574</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -5018,11 +5018,11 @@
         <v>209</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.16902107639</v>
+        <v>46149.00235440972</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46204.1910445949</v>
+        <v>46204.02437792824</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -5081,11 +5081,11 @@
         <v>212</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.16902621528</v>
+        <v>46149.00235954861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46176.17164685186</v>
+        <v>46205.001650983795</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>213</v>
@@ -5144,11 +5144,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.1690303588</v>
+        <v>46149.002363692125</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46155.59866159722</v>
+        <v>46205.029112557866</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -5192,8 +5192,8 @@
       <c r="R60" s="5">
         <v>46212</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>102</v>
+      <c r="S60" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5207,11 +5207,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.16903488426</v>
+        <v>46149.002368217596</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.5990459375</v>
+        <v>46155.43237927083</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>217</v>
@@ -5270,11 +5270,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.1690391088</v>
+        <v>46149.00237244213</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.56887822917</v>
+        <v>46155.4022115625</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5317,11 +5317,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.169042442125</v>
+        <v>46149.00237577547</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.57724337963</v>
+        <v>46161.410576712966</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5380,11 +5380,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.169049375</v>
+        <v>46149.002382708335</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.59925321759</v>
+        <v>46155.43258655093</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>192</v>
@@ -5433,11 +5433,11 @@
         <v>230</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.16905616898</v>
+        <v>46149.00238950232</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.59924960649</v>
+        <v>46155.432582939815</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>192</v>
@@ -5486,11 +5486,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.562074166664</v>
+        <v>46155.3954075</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.59924675926</v>
+        <v>46155.43258009259</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>192</v>
@@ -5539,11 +5539,11 @@
         <v>234</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.562095416666</v>
+        <v>46155.395428749995</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.59924362268</v>
+        <v>46155.432576956024</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>192</v>
@@ -5592,11 +5592,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46149.169104699075</v>
+        <v>46149.0024380324</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.59934020833</v>
+        <v>46155.43267354167</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5655,11 +5655,11 @@
         <v>237</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.1691096412</v>
+        <v>46149.00244297454</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46199.779078356485</v>
+        <v>46199.61241168981</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>192</v>
@@ -5708,11 +5708,11 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.16911491899</v>
+        <v>46149.002448252315</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.77907907407</v>
+        <v>46199.61241240741</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>192</v>
@@ -5761,11 +5761,11 @@
         <v>241</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.562225625</v>
+        <v>46155.395558958335</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46199.77908222222</v>
+        <v>46199.61241555556</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>192</v>
@@ -5814,11 +5814,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.56224557871</v>
+        <v>46155.39557891204</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46199.7790828588</v>
+        <v>46199.61241619213</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>192</v>
@@ -5867,11 +5867,11 @@
         <v>243</v>
       </c>
       <c r="B73" s="9">
-        <v>46149.169119768514</v>
+        <v>46149.00245310186</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.59937984953</v>
+        <v>46155.43271318287</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>244</v>
@@ -5930,11 +5930,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.16912365741</v>
+        <v>46149.00245699074</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46199.77907962963</v>
+        <v>46199.61241296296</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>192</v>
@@ -5983,11 +5983,11 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.16912908565</v>
+        <v>46149.00246241898</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.77908010417</v>
+        <v>46199.6124134375</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>192</v>
@@ -6036,11 +6036,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.56233189815</v>
+        <v>46155.39566523148</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46199.779083437505</v>
+        <v>46199.61241677083</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>192</v>
@@ -6089,11 +6089,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.562344351856</v>
+        <v>46155.395677685185</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46199.779083877314</v>
+        <v>46199.61241721065</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>192</v>
@@ -6142,11 +6142,11 @@
         <v>252</v>
       </c>
       <c r="B78" s="5">
-        <v>46149.16913412037</v>
+        <v>46149.002467453705</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.57120092593</v>
+        <v>46155.40453425926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>198</v>
@@ -6189,11 +6189,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.16913708333</v>
+        <v>46149.00247041667</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.17098876157</v>
+        <v>46182.00432209491</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6250,11 +6250,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.16914224537</v>
+        <v>46149.0024755787</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46165.180999432865</v>
+        <v>46165.01433276621</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6313,11 +6313,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.16914733796</v>
+        <v>46149.0024806713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.171336064814</v>
+        <v>46198.00466939815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6376,11 +6376,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.16915236111</v>
+        <v>46149.002485694444</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.59985006944</v>
+        <v>46155.433183402776</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6439,11 +6439,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.16915732639</v>
+        <v>46149.002490659725</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.58270766203</v>
+        <v>46155.41604099537</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6486,11 +6486,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.16916049768</v>
+        <v>46149.00249383102</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.60047521991</v>
+        <v>46155.433808553236</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>269</v>
@@ -6549,11 +6549,11 @@
         <v>271</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.16916685185</v>
+        <v>46149.00250018519</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.60002515046</v>
+        <v>46155.433358483795</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>192</v>
@@ -6602,11 +6602,11 @@
         <v>273</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.16917037037</v>
+        <v>46149.002503703705</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.60002232638</v>
+        <v>46155.43335565973</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>192</v>
@@ -6655,11 +6655,11 @@
         <v>274</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.5624656713</v>
+        <v>46155.39579900463</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.60026604167</v>
+        <v>46155.433599375</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>249</v>
@@ -6708,11 +6708,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.562495266204</v>
+        <v>46155.39582859953</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.600359212964</v>
+        <v>46155.4336925463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>251</v>
@@ -6761,11 +6761,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46149.16917405093</v>
+        <v>46149.002507384255</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.600641770834</v>
+        <v>46155.43397510417</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>278</v>
@@ -6824,11 +6824,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.169178321754</v>
+        <v>46149.0025116551</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46199.77908100694</v>
+        <v>46199.61241434028</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>192</v>
@@ -6875,11 +6875,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.169183148144</v>
+        <v>46149.00251648148</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46199.77908144676</v>
+        <v>46199.61241478009</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>192</v>
@@ -6926,11 +6926,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.56256662037</v>
+        <v>46155.3958999537</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46199.77908483797</v>
+        <v>46199.612418171295</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>192</v>
@@ -6977,11 +6977,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.56257849537</v>
+        <v>46155.3959118287</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46199.779085277776</v>
+        <v>46199.61241861111</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>192</v>
@@ -7028,11 +7028,11 @@
         <v>287</v>
       </c>
       <c r="B94" s="5">
-        <v>46149.169187962965</v>
+        <v>46149.002521296294</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.60079344908</v>
+        <v>46155.434126782406</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>288</v>
@@ -7091,11 +7091,11 @@
         <v>289</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.1691919213</v>
+        <v>46149.00252525463</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46199.779080567125</v>
+        <v>46199.61241390047</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>192</v>
@@ -7142,11 +7142,11 @@
         <v>291</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.16919760416</v>
+        <v>46149.002530937505</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46199.779077430554</v>
+        <v>46199.61241076389</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>192</v>
@@ -7193,11 +7193,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.562660428244</v>
+        <v>46155.39599376157</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46199.779084340276</v>
+        <v>46199.61241767361</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>192</v>
@@ -7244,11 +7244,11 @@
         <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.56267193287</v>
+        <v>46155.3960052662</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46199.779085752314</v>
+        <v>46199.61241908565</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>192</v>
@@ -7295,11 +7295,11 @@
         <v>296</v>
       </c>
       <c r="B99" s="9">
-        <v>46149.169203125</v>
+        <v>46149.002536458334</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.60094263889</v>
+        <v>46155.43427597222</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>297</v>
@@ -7358,11 +7358,11 @@
         <v>298</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.16920694444</v>
+        <v>46149.00254027778</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46199.779077858795</v>
+        <v>46199.61241119213</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>192</v>
@@ -7409,11 +7409,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.16921202546</v>
+        <v>46149.002545358795</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46199.77908177083</v>
+        <v>46199.612415104166</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>192</v>
@@ -7460,11 +7460,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.562741851856</v>
+        <v>46155.396075185185</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46199.77908608796</v>
+        <v>46199.6124194213</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>192</v>
@@ -7511,11 +7511,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.562755046296</v>
+        <v>46155.396088379624</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46199.77908645834</v>
+        <v>46199.612419791665</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>192</v>
@@ -7562,11 +7562,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46149.16921689815</v>
+        <v>46149.00255023148</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.60109780093</v>
+        <v>46155.43443113426</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>308</v>
@@ -7625,11 +7625,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.169220717595</v>
+        <v>46149.00255405092</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.60106565972</v>
+        <v>46155.43439899306</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>192</v>
@@ -7678,11 +7678,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.16922577546</v>
+        <v>46149.0025591088</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.601062546295</v>
+        <v>46155.43439587963</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>192</v>
@@ -7731,11 +7731,11 @@
         <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.56285743056</v>
+        <v>46155.39619076389</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.60105936343</v>
+        <v>46155.434392696756</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>192</v>
@@ -7784,11 +7784,11 @@
         <v>314</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.56284611111</v>
+        <v>46155.39617944445</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.60105565972</v>
+        <v>46155.43438899306</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>192</v>
@@ -7837,11 +7837,11 @@
         <v>315</v>
       </c>
       <c r="B109" s="9">
-        <v>46149.169270370374</v>
+        <v>46149.0026037037</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.601273506945</v>
+        <v>46155.43460684028</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>316</v>
@@ -7900,11 +7900,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.16928524306</v>
+        <v>46149.002618576385</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.60133046296</v>
+        <v>46155.434663796295</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>192</v>
@@ -7951,11 +7951,11 @@
         <v>320</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.16929128472</v>
+        <v>46149.00262461806</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.60132649305</v>
+        <v>46155.43465982639</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>192</v>
@@ -8002,11 +8002,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.562937361115</v>
+        <v>46155.396270694444</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.60132342593</v>
+        <v>46155.43465675926</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>192</v>
@@ -8053,11 +8053,11 @@
         <v>323</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.56294952546</v>
+        <v>46155.3962828588</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.60131890046</v>
+        <v>46155.434652233795</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>192</v>
@@ -8104,11 +8104,11 @@
         <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46149.16929695602</v>
+        <v>46149.00263028935</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.590775185185</v>
+        <v>46155.42410851852</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>325</v>
@@ -8151,11 +8151,11 @@
         <v>327</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.169301041664</v>
+        <v>46149.002634375</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.60146953704</v>
+        <v>46155.43480287037</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>328</v>
@@ -8212,11 +8212,11 @@
         <v>332</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.1693071412</v>
+        <v>46149.00264047454</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.60144278935</v>
+        <v>46155.43477612268</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>192</v>
@@ -8263,11 +8263,11 @@
         <v>334</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.16931233797</v>
+        <v>46149.002645671295</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.60143921296</v>
+        <v>46155.4347725463</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>192</v>
@@ -8314,11 +8314,11 @@
         <v>336</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.56303070602</v>
+        <v>46155.39636403935</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.601436296296</v>
+        <v>46155.43476962963</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>192</v>
@@ -8365,11 +8365,11 @@
         <v>337</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.56306011574</v>
+        <v>46155.396393449075</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.60143193287</v>
+        <v>46155.4347652662</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>192</v>
@@ -8416,11 +8416,11 @@
         <v>338</v>
       </c>
       <c r="B120" s="5">
-        <v>46149.1693175</v>
+        <v>46149.00265083333</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6016600463</v>
+        <v>46155.43499337963</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>339</v>
@@ -8479,11 +8479,11 @@
         <v>340</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.16932247685</v>
+        <v>46149.00265581018</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.601629756944</v>
+        <v>46155.43496309027</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>192</v>
@@ -8532,11 +8532,11 @@
         <v>342</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.16932829861</v>
+        <v>46149.002661631945</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.60162688658</v>
+        <v>46155.43496021991</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>192</v>
@@ -8585,11 +8585,11 @@
         <v>343</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.56313421296</v>
+        <v>46155.39646754629</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.601624421295</v>
+        <v>46155.43495775463</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>192</v>
@@ -8638,11 +8638,11 @@
         <v>345</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.5631459375</v>
+        <v>46155.39647927083</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.601620671296</v>
+        <v>46155.43495400463</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>192</v>
@@ -8691,11 +8691,11 @@
         <v>347</v>
       </c>
       <c r="B125" s="9">
-        <v>46149.16933366898</v>
+        <v>46149.002667002314</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.60192047454</v>
+        <v>46155.43525380787</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>348</v>
@@ -8754,11 +8754,11 @@
         <v>350</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.16933884259</v>
+        <v>46149.00267217593</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.601853796295</v>
+        <v>46155.43518712963</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>192</v>
@@ -8805,11 +8805,11 @@
         <v>352</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.16934681713</v>
+        <v>46149.002680150465</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.60185450231</v>
+        <v>46155.43518783565</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>192</v>
@@ -8856,11 +8856,11 @@
         <v>354</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.56323461806</v>
+        <v>46155.39656795139</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.60185530093</v>
+        <v>46155.43518863426</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>251</v>
@@ -8907,11 +8907,11 @@
         <v>356</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.563225370366</v>
+        <v>46155.3965587037</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.60185603009</v>
+        <v>46155.43518936343</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>249</v>
@@ -8958,11 +8958,11 @@
         <v>358</v>
       </c>
       <c r="B130" s="5">
-        <v>46149.1693534375</v>
+        <v>46149.00268677084</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.60216496528</v>
+        <v>46155.43549829861</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>359</v>
@@ -9021,11 +9021,11 @@
         <v>361</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.16935909722</v>
+        <v>46149.00269243056</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.602132280095</v>
+        <v>46155.435465613424</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>192</v>
@@ -9072,11 +9072,11 @@
         <v>362</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.16936413194</v>
+        <v>46149.00269746528</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.602128969906</v>
+        <v>46155.43546230324</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>192</v>
@@ -9123,11 +9123,11 @@
         <v>363</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.56332277777</v>
+        <v>46155.396656111116</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.60212502315</v>
+        <v>46155.435458356485</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>249</v>
@@ -9174,11 +9174,11 @@
         <v>364</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.56333268518</v>
+        <v>46155.39666601852</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.602120462965</v>
+        <v>46155.43545379629</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>251</v>
@@ -9225,11 +9225,11 @@
         <v>365</v>
       </c>
       <c r="B135" s="9">
-        <v>46149.16936914352</v>
+        <v>46149.00270247685</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.60238891204</v>
+        <v>46155.43572224537</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>366</v>
@@ -9272,11 +9272,11 @@
         <v>368</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.169373136574</v>
+        <v>46149.00270646991</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.602217824075</v>
+        <v>46155.43555115741</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>369</v>
@@ -9335,11 +9335,11 @@
         <v>372</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.169417349534</v>
+        <v>46149.00275068287</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.86942971065</v>
+        <v>46196.702763043984</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>373</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1818,13 +1818,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46149.0019957176</v>
+        <v>46149.168662384254</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70624586806</v>
+        <v>46175.87291253472</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706257777776</v>
+        <v>46175.87292444444</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1871,13 +1871,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46149.00206601852</v>
+        <v>46149.16873268518</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.706218611114</v>
+        <v>46175.87288527778</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70624668981</v>
+        <v>46175.87291335648</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1934,13 +1934,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46149.00206940972</v>
+        <v>46149.16873607639</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70621924769</v>
+        <v>46175.87288591435</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.706246608795</v>
+        <v>46175.87291327547</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1997,13 +1997,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="9">
-        <v>46149.002072152776</v>
+        <v>46149.16873881944</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.70621967592</v>
+        <v>46175.87288634259</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.706247800925</v>
+        <v>46175.87291446759</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2060,13 +2060,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46149.00207495371</v>
+        <v>46149.16874162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70622006945</v>
+        <v>46175.872886736106</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.70624652778</v>
+        <v>46175.87291319444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2123,13 +2123,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="9">
-        <v>46149.002078136575</v>
+        <v>46149.16874480324</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70622064815</v>
+        <v>46175.872887314814</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70624614583</v>
+        <v>46175.8729128125</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2186,13 +2186,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46149.00200085648</v>
+        <v>46149.16866752315</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.70496565972</v>
+        <v>46196.871632326394</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.70498190972</v>
+        <v>46196.87164857639</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2239,13 +2239,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46149.00208121528</v>
+        <v>46149.168747881944</v>
       </c>
       <c r="C11" s="9">
-        <v>46183.7040040625</v>
+        <v>46183.87067072917</v>
       </c>
       <c r="D11" s="9">
-        <v>46196.70276310186</v>
+        <v>46196.869429768514</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2304,13 +2304,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46149.00208630787</v>
+        <v>46149.16875297454</v>
       </c>
       <c r="C12" s="5">
-        <v>46183.70401074074</v>
+        <v>46183.87067740741</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.70276306713</v>
+        <v>46196.86942973379</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2369,13 +2369,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46149.002091331015</v>
+        <v>46149.168757997686</v>
       </c>
       <c r="C13" s="9">
-        <v>46183.70401635417</v>
+        <v>46183.87068302083</v>
       </c>
       <c r="D13" s="9">
-        <v>46196.70276305555</v>
+        <v>46196.869429722225</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2434,13 +2434,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46149.00200555555</v>
+        <v>46149.16867222222</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.74624128472</v>
+        <v>46204.91290795139</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.7462519213</v>
+        <v>46204.912918587965</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2487,13 +2487,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46149.00210356481</v>
+        <v>46149.16877023148</v>
       </c>
       <c r="C15" s="9">
-        <v>46196.70489974537</v>
+        <v>46196.87156641204</v>
       </c>
       <c r="D15" s="9">
-        <v>46196.70492120371</v>
+        <v>46196.871587870366</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>66</v>
@@ -2552,13 +2552,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46149.00210846065</v>
+        <v>46149.16877512731</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.70490936343</v>
+        <v>46196.87157603009</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.70492671296</v>
+        <v>46196.871593379634</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2617,13 +2617,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="9">
-        <v>46149.00211332176</v>
+        <v>46149.168779988424</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.336022881944</v>
+        <v>46197.50268954861</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.33604180555</v>
+        <v>46197.502708472224</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2682,13 +2682,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46149.002118171295</v>
+        <v>46149.168784837966</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.746188923615</v>
+        <v>46204.91285559028</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.74620546296</v>
+        <v>46204.91287212963</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2747,13 +2747,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46149.00212268518</v>
+        <v>46149.168789351854</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.74622498843</v>
+        <v>46204.91289165509</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.746242361114</v>
+        <v>46204.91290902778</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2812,13 +2812,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46149.00212619213</v>
+        <v>46149.16879285879</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.74538611111</v>
+        <v>46204.91205277778</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.745569108796</v>
+        <v>46204.91223577547</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2877,13 +2877,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46149.00212975695</v>
+        <v>46149.16879642361</v>
       </c>
       <c r="C21" s="9">
-        <v>46204.74520247686</v>
+        <v>46204.911869143514</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.74533934028</v>
+        <v>46204.91200600694</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2942,11 +2942,11 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46149.002010208336</v>
+        <v>46149.168676875</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46155.386767407406</v>
+        <v>46205.60770953704</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2989,11 +2989,11 @@
         <v>93</v>
       </c>
       <c r="B23" s="9">
-        <v>46149.00213346065</v>
+        <v>46149.168800127314</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46169.693065011576</v>
+        <v>46169.85973167824</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>94</v>
@@ -3052,11 +3052,11 @@
         <v>99</v>
       </c>
       <c r="B24" s="5">
-        <v>46149.00213748842</v>
+        <v>46149.168804155095</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46196.704918414354</v>
+        <v>46196.87158508102</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>
@@ -3111,11 +3111,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="9">
-        <v>46149.002141944446</v>
+        <v>46149.16880861111</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.693560740736</v>
+        <v>46169.86022740741</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3170,11 +3170,11 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46149.00214671296</v>
+        <v>46149.16881337963</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46179.010007881945</v>
+        <v>46179.17667454861</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3233,11 +3233,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46149.00215085648</v>
+        <v>46149.16881752315</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.3360318287</v>
+        <v>46197.50269849537</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3292,11 +3292,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46149.00215518518</v>
+        <v>46149.168821851854</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46178.00393269676</v>
+        <v>46178.170599363424</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3351,11 +3351,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46149.00215962963</v>
+        <v>46149.1688262963</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46199.58622060185</v>
+        <v>46199.75288726852</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3414,13 +3414,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46149.00216386574</v>
+        <v>46149.168830532406</v>
       </c>
       <c r="C30" s="5">
-        <v>46199.58616287037</v>
+        <v>46199.752829537036</v>
       </c>
       <c r="D30" s="5">
-        <v>46199.5861650463</v>
+        <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3475,11 +3475,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="9">
-        <v>46149.002168287036</v>
+        <v>46149.1688349537</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46199.58616975695</v>
+        <v>46199.752836423606</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3534,13 +3534,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46149.002173333334</v>
+        <v>46149.16884</v>
       </c>
       <c r="C32" s="5">
-        <v>46199.58621101852</v>
+        <v>46199.75287768518</v>
       </c>
       <c r="D32" s="5">
-        <v>46199.58621248843</v>
+        <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3595,11 +3595,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="9">
-        <v>46149.00217770833</v>
-      </c>
-      <c r="C33" s="10"/>
+        <v>46149.168844375</v>
+      </c>
+      <c r="C33" s="9">
+        <v>46205.60769827546</v>
+      </c>
       <c r="D33" s="9">
-        <v>46200.02750185185</v>
+        <v>46205.60771266204</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>128</v>
@@ -3647,10 +3649,10 @@
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3658,11 +3660,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46149.00218226852</v>
-      </c>
-      <c r="C34" s="6"/>
+        <v>46149.16884893518</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46205.60761925926</v>
+      </c>
       <c r="D34" s="5">
-        <v>46204.746199444446</v>
+        <v>46205.60762148148</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3717,11 +3721,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46149.00218697917</v>
-      </c>
-      <c r="C35" s="10"/>
+        <v>46149.16885364584</v>
+      </c>
+      <c r="C35" s="9">
+        <v>46205.6076822801</v>
+      </c>
       <c r="D35" s="9">
-        <v>46199.00309900463</v>
+        <v>46205.60768407407</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3776,11 +3782,13 @@
         <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46149.002191770836</v>
-      </c>
-      <c r="C36" s="6"/>
+        <v>46149.1688584375</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46205.60893457176</v>
+      </c>
       <c r="D36" s="5">
-        <v>46200.02750177083</v>
+        <v>46205.608947719906</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>139</v>
@@ -3828,10 +3836,10 @@
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3839,11 +3847,13 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46149.00224469908</v>
-      </c>
-      <c r="C37" s="10"/>
+        <v>46149.16891136574</v>
+      </c>
+      <c r="C37" s="9">
+        <v>46205.60888251157</v>
+      </c>
       <c r="D37" s="9">
-        <v>46204.74623260417</v>
+        <v>46205.60888410879</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>83</v>
@@ -3892,11 +3902,13 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46149.002250590274</v>
-      </c>
-      <c r="C38" s="6"/>
+        <v>46149.168917256946</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46205.608918356476</v>
+      </c>
       <c r="D38" s="5">
-        <v>46199.00309777778</v>
+        <v>46205.60892006944</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -3945,11 +3957,11 @@
         <v>146</v>
       </c>
       <c r="B39" s="9">
-        <v>46149.0022559375</v>
+        <v>46149.16892260416</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69313453704</v>
+        <v>46169.859801203704</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4008,11 +4020,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46149.00226620371</v>
+        <v>46149.168932870365</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46204.74521101852</v>
+        <v>46204.91187768518</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>89</v>
@@ -4061,11 +4073,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46149.0022712963</v>
+        <v>46149.16893796297</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.693275451384</v>
+        <v>46169.859942118055</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4114,11 +4126,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46149.002276238425</v>
+        <v>46149.16894290509</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69329935186</v>
+        <v>46169.859966018514</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4167,11 +4179,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46149.0022791088</v>
-      </c>
-      <c r="C43" s="10"/>
+        <v>46149.16894577546</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46205.61327819445</v>
+      </c>
       <c r="D43" s="9">
-        <v>46203.01833590277</v>
+        <v>46205.61328953704</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4219,10 +4233,10 @@
         <v>163</v>
       </c>
       <c r="T43" s="10">
-        <v>0</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4230,11 +4244,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46149.002283043985</v>
-      </c>
-      <c r="C44" s="6"/>
+        <v>46149.16894971065</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46205.61322614583</v>
+      </c>
       <c r="D44" s="5">
-        <v>46204.745392337965</v>
+        <v>46205.613227546295</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>86</v>
@@ -4283,11 +4299,13 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46149.002287615745</v>
-      </c>
-      <c r="C45" s="10"/>
+        <v>46149.1689542824</v>
+      </c>
+      <c r="C45" s="9">
+        <v>46205.61326421297</v>
+      </c>
       <c r="D45" s="9">
-        <v>46191.518934293985</v>
+        <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4336,11 +4354,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46149.00201474537</v>
+        <v>46149.16868141203</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46199.61235946759</v>
+        <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4385,13 +4403,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46149.00229319444</v>
+        <v>46149.16895986111</v>
       </c>
       <c r="C47" s="9">
-        <v>46184.34825659722</v>
+        <v>46184.514923263894</v>
       </c>
       <c r="D47" s="9">
-        <v>46197.54701967593</v>
+        <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4450,13 +4468,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46149.00229898148</v>
+        <v>46149.16896564815</v>
       </c>
       <c r="C48" s="5">
-        <v>46199.612340023144</v>
+        <v>46199.779006689816</v>
       </c>
       <c r="D48" s="5">
-        <v>46199.61235570602</v>
+        <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4515,13 +4533,13 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46149.002305497685</v>
+        <v>46149.16897216435</v>
       </c>
       <c r="C49" s="9">
-        <v>46199.61239601852</v>
+        <v>46199.779062685186</v>
       </c>
       <c r="D49" s="9">
-        <v>46199.612411608796</v>
+        <v>46199.77907827546</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4578,11 +4596,11 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46149.00232021991</v>
+        <v>46149.16898688657</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.43178033565</v>
+        <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4641,11 +4659,11 @@
         <v>191</v>
       </c>
       <c r="B51" s="9">
-        <v>46149.00232474537</v>
+        <v>46149.168991412036</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.43188986111</v>
+        <v>46155.59855652778</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4692,11 +4710,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46149.00233350694</v>
+        <v>46149.16900017361</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.43188626158</v>
+        <v>46155.59855292824</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4743,11 +4761,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46155.41115071759</v>
+        <v>46155.577817384255</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.43188179398</v>
+        <v>46155.59854846065</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -4794,11 +4812,11 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46155.41116238426</v>
+        <v>46155.577829050926</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.43187822917</v>
+        <v>46155.59854489584</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -4845,11 +4863,11 @@
         <v>197</v>
       </c>
       <c r="B55" s="9">
-        <v>46149.002338425926</v>
+        <v>46149.1690050926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46155.39226760417</v>
+        <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>198</v>
@@ -4892,11 +4910,11 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46149.00234274306</v>
+        <v>46149.16900940972</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46204.02437775463</v>
+        <v>46205.60769931713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>201</v>
@@ -4946,8 +4964,8 @@
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="11" t="s">
-        <v>98</v>
+      <c r="U56" s="12" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4955,11 +4973,11 @@
         <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46149.00234849537</v>
+        <v>46149.16901516204</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46205.00165636574</v>
+        <v>46205.16832303241</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -5018,11 +5036,11 @@
         <v>209</v>
       </c>
       <c r="B58" s="5">
-        <v>46149.00235440972</v>
+        <v>46149.16902107639</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46204.02437792824</v>
+        <v>46205.60894056713</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>210</v>
@@ -5072,8 +5090,8 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="11" t="s">
-        <v>98</v>
+      <c r="U58" s="12" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5081,11 +5099,11 @@
         <v>212</v>
       </c>
       <c r="B59" s="9">
-        <v>46149.00235954861</v>
+        <v>46149.16902621528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46205.001650983795</v>
+        <v>46205.16831765046</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>213</v>
@@ -5144,11 +5162,11 @@
         <v>215</v>
       </c>
       <c r="B60" s="5">
-        <v>46149.002363692125</v>
+        <v>46149.1690303588</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46205.029112557866</v>
+        <v>46205.61327966435</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -5198,8 +5216,8 @@
       <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="U60" s="11" t="s">
-        <v>98</v>
+      <c r="U60" s="12" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5207,11 +5225,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46149.002368217596</v>
+        <v>46149.16903488426</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.43237927083</v>
+        <v>46155.5990459375</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>217</v>
@@ -5270,11 +5288,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46149.00237244213</v>
+        <v>46149.1690391088</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.4022115625</v>
+        <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5317,11 +5335,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46149.00237577547</v>
+        <v>46149.169042442125</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.410576712966</v>
+        <v>46161.57724337963</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5380,11 +5398,11 @@
         <v>227</v>
       </c>
       <c r="B64" s="5">
-        <v>46149.002382708335</v>
+        <v>46149.169049375</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.43258655093</v>
+        <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>192</v>
@@ -5433,11 +5451,11 @@
         <v>230</v>
       </c>
       <c r="B65" s="9">
-        <v>46149.00238950232</v>
+        <v>46149.16905616898</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.432582939815</v>
+        <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>192</v>
@@ -5486,11 +5504,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46155.3954075</v>
+        <v>46155.562074166664</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.43258009259</v>
+        <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>192</v>
@@ -5539,11 +5557,11 @@
         <v>234</v>
       </c>
       <c r="B67" s="9">
-        <v>46155.395428749995</v>
+        <v>46155.562095416666</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.432576956024</v>
+        <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>192</v>
@@ -5592,11 +5610,11 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46149.0024380324</v>
+        <v>46149.169104699075</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.43267354167</v>
+        <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5655,11 +5673,11 @@
         <v>237</v>
       </c>
       <c r="B69" s="9">
-        <v>46149.00244297454</v>
+        <v>46149.1691096412</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46199.61241168981</v>
+        <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>192</v>
@@ -5708,11 +5726,11 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46149.002448252315</v>
+        <v>46149.16911491899</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.61241240741</v>
+        <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>192</v>
@@ -5761,11 +5779,11 @@
         <v>241</v>
       </c>
       <c r="B71" s="9">
-        <v>46155.395558958335</v>
+        <v>46155.562225625</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46199.61241555556</v>
+        <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>192</v>
@@ -5814,11 +5832,11 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46155.39557891204</v>
+        <v>46155.56224557871</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46199.61241619213</v>
+        <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>192</v>
@@ -5867,11 +5885,11 @@
         <v>243</v>
       </c>
       <c r="B73" s="9">
-        <v>46149.00245310186</v>
+        <v>46149.169119768514</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.43271318287</v>
+        <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>244</v>
@@ -5930,11 +5948,11 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46149.00245699074</v>
+        <v>46149.16912365741</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46199.61241296296</v>
+        <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>192</v>
@@ -5983,11 +6001,11 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46149.00246241898</v>
+        <v>46149.16912908565</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.6124134375</v>
+        <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>192</v>
@@ -6036,11 +6054,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46155.39566523148</v>
+        <v>46155.56233189815</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46199.61241677083</v>
+        <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>192</v>
@@ -6089,11 +6107,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46155.395677685185</v>
+        <v>46155.562344351856</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46199.61241721065</v>
+        <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>192</v>
@@ -6142,11 +6160,11 @@
         <v>252</v>
       </c>
       <c r="B78" s="5">
-        <v>46149.002467453705</v>
+        <v>46149.16913412037</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.40453425926</v>
+        <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>198</v>
@@ -6189,11 +6207,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46149.00247041667</v>
+        <v>46149.16913708333</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.00432209491</v>
+        <v>46182.17098876157</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6250,11 +6268,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46149.0024755787</v>
+        <v>46149.16914224537</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46165.01433276621</v>
+        <v>46165.180999432865</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6313,11 +6331,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46149.0024806713</v>
+        <v>46149.16914733796</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46198.00466939815</v>
+        <v>46198.171336064814</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6376,11 +6394,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46149.002485694444</v>
+        <v>46149.16915236111</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.433183402776</v>
+        <v>46155.59985006944</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6439,11 +6457,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46149.002490659725</v>
+        <v>46149.16915732639</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.41604099537</v>
+        <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6486,11 +6504,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46149.00249383102</v>
+        <v>46149.16916049768</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.433808553236</v>
+        <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>269</v>
@@ -6549,11 +6567,11 @@
         <v>271</v>
       </c>
       <c r="B85" s="9">
-        <v>46149.00250018519</v>
+        <v>46149.16916685185</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.433358483795</v>
+        <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>192</v>
@@ -6602,11 +6620,11 @@
         <v>273</v>
       </c>
       <c r="B86" s="5">
-        <v>46149.002503703705</v>
+        <v>46149.16917037037</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.43335565973</v>
+        <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>192</v>
@@ -6655,11 +6673,11 @@
         <v>274</v>
       </c>
       <c r="B87" s="9">
-        <v>46155.39579900463</v>
+        <v>46155.5624656713</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.433599375</v>
+        <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>249</v>
@@ -6708,11 +6726,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46155.39582859953</v>
+        <v>46155.562495266204</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.4336925463</v>
+        <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>251</v>
@@ -6761,11 +6779,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46149.002507384255</v>
+        <v>46149.16917405093</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.43397510417</v>
+        <v>46155.600641770834</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>278</v>
@@ -6824,11 +6842,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46149.0025116551</v>
+        <v>46149.169178321754</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46199.61241434028</v>
+        <v>46199.77908100694</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>192</v>
@@ -6875,11 +6893,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46149.00251648148</v>
+        <v>46149.169183148144</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46199.61241478009</v>
+        <v>46199.77908144676</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>192</v>
@@ -6926,11 +6944,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46155.3958999537</v>
+        <v>46155.56256662037</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46199.612418171295</v>
+        <v>46199.77908483797</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>192</v>
@@ -6977,11 +6995,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46155.3959118287</v>
+        <v>46155.56257849537</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46199.61241861111</v>
+        <v>46199.779085277776</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>192</v>
@@ -7028,11 +7046,11 @@
         <v>287</v>
       </c>
       <c r="B94" s="5">
-        <v>46149.002521296294</v>
+        <v>46149.169187962965</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.434126782406</v>
+        <v>46155.60079344908</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>288</v>
@@ -7091,11 +7109,11 @@
         <v>289</v>
       </c>
       <c r="B95" s="9">
-        <v>46149.00252525463</v>
+        <v>46149.1691919213</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46199.61241390047</v>
+        <v>46199.779080567125</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>192</v>
@@ -7142,11 +7160,11 @@
         <v>291</v>
       </c>
       <c r="B96" s="5">
-        <v>46149.002530937505</v>
+        <v>46149.16919760416</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46199.61241076389</v>
+        <v>46199.779077430554</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>192</v>
@@ -7193,11 +7211,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46155.39599376157</v>
+        <v>46155.562660428244</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46199.61241767361</v>
+        <v>46199.779084340276</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>192</v>
@@ -7244,11 +7262,11 @@
         <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46155.3960052662</v>
+        <v>46155.56267193287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46199.61241908565</v>
+        <v>46199.779085752314</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>192</v>
@@ -7295,11 +7313,11 @@
         <v>296</v>
       </c>
       <c r="B99" s="9">
-        <v>46149.002536458334</v>
+        <v>46149.169203125</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.43427597222</v>
+        <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>297</v>
@@ -7358,11 +7376,11 @@
         <v>298</v>
       </c>
       <c r="B100" s="5">
-        <v>46149.00254027778</v>
+        <v>46149.16920694444</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46199.61241119213</v>
+        <v>46199.779077858795</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>192</v>
@@ -7409,11 +7427,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46149.002545358795</v>
+        <v>46149.16921202546</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46199.612415104166</v>
+        <v>46199.77908177083</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>192</v>
@@ -7460,11 +7478,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46155.396075185185</v>
+        <v>46155.562741851856</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46199.6124194213</v>
+        <v>46199.77908608796</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>192</v>
@@ -7511,11 +7529,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46155.396088379624</v>
+        <v>46155.562755046296</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46199.612419791665</v>
+        <v>46199.77908645834</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>192</v>
@@ -7562,11 +7580,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46149.00255023148</v>
+        <v>46149.16921689815</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.43443113426</v>
+        <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>308</v>
@@ -7625,11 +7643,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46149.00255405092</v>
+        <v>46149.169220717595</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.43439899306</v>
+        <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>192</v>
@@ -7678,11 +7696,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46149.0025591088</v>
+        <v>46149.16922577546</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.43439587963</v>
+        <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>192</v>
@@ -7731,11 +7749,11 @@
         <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46155.39619076389</v>
+        <v>46155.56285743056</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.434392696756</v>
+        <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>192</v>
@@ -7784,11 +7802,11 @@
         <v>314</v>
       </c>
       <c r="B108" s="5">
-        <v>46155.39617944445</v>
+        <v>46155.56284611111</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.43438899306</v>
+        <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>192</v>
@@ -7837,11 +7855,11 @@
         <v>315</v>
       </c>
       <c r="B109" s="9">
-        <v>46149.0026037037</v>
+        <v>46149.169270370374</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.43460684028</v>
+        <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>316</v>
@@ -7900,11 +7918,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46149.002618576385</v>
+        <v>46149.16928524306</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.434663796295</v>
+        <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>192</v>
@@ -7951,11 +7969,11 @@
         <v>320</v>
       </c>
       <c r="B111" s="9">
-        <v>46149.00262461806</v>
+        <v>46149.16929128472</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.43465982639</v>
+        <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>192</v>
@@ -8002,11 +8020,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46155.396270694444</v>
+        <v>46155.562937361115</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.43465675926</v>
+        <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>192</v>
@@ -8053,11 +8071,11 @@
         <v>323</v>
       </c>
       <c r="B113" s="9">
-        <v>46155.3962828588</v>
+        <v>46155.56294952546</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.434652233795</v>
+        <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>192</v>
@@ -8104,11 +8122,11 @@
         <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46149.00263028935</v>
+        <v>46149.16929695602</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.42410851852</v>
+        <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>325</v>
@@ -8151,11 +8169,11 @@
         <v>327</v>
       </c>
       <c r="B115" s="9">
-        <v>46149.002634375</v>
+        <v>46149.169301041664</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.43480287037</v>
+        <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>328</v>
@@ -8212,11 +8230,11 @@
         <v>332</v>
       </c>
       <c r="B116" s="5">
-        <v>46149.00264047454</v>
+        <v>46149.1693071412</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.43477612268</v>
+        <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>192</v>
@@ -8263,11 +8281,11 @@
         <v>334</v>
       </c>
       <c r="B117" s="9">
-        <v>46149.002645671295</v>
+        <v>46149.16931233797</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.4347725463</v>
+        <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>192</v>
@@ -8314,11 +8332,11 @@
         <v>336</v>
       </c>
       <c r="B118" s="5">
-        <v>46155.39636403935</v>
+        <v>46155.56303070602</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.43476962963</v>
+        <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>192</v>
@@ -8365,11 +8383,11 @@
         <v>337</v>
       </c>
       <c r="B119" s="9">
-        <v>46155.396393449075</v>
+        <v>46155.56306011574</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.4347652662</v>
+        <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>192</v>
@@ -8416,11 +8434,11 @@
         <v>338</v>
       </c>
       <c r="B120" s="5">
-        <v>46149.00265083333</v>
+        <v>46149.1693175</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.43499337963</v>
+        <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>339</v>
@@ -8479,11 +8497,11 @@
         <v>340</v>
       </c>
       <c r="B121" s="9">
-        <v>46149.00265581018</v>
+        <v>46149.16932247685</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.43496309027</v>
+        <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>192</v>
@@ -8532,11 +8550,11 @@
         <v>342</v>
       </c>
       <c r="B122" s="5">
-        <v>46149.002661631945</v>
+        <v>46149.16932829861</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.43496021991</v>
+        <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>192</v>
@@ -8585,11 +8603,11 @@
         <v>343</v>
       </c>
       <c r="B123" s="9">
-        <v>46155.39646754629</v>
+        <v>46155.56313421296</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.43495775463</v>
+        <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>192</v>
@@ -8638,11 +8656,11 @@
         <v>345</v>
       </c>
       <c r="B124" s="5">
-        <v>46155.39647927083</v>
+        <v>46155.5631459375</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.43495400463</v>
+        <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>192</v>
@@ -8691,11 +8709,11 @@
         <v>347</v>
       </c>
       <c r="B125" s="9">
-        <v>46149.002667002314</v>
+        <v>46149.16933366898</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.43525380787</v>
+        <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>348</v>
@@ -8754,11 +8772,11 @@
         <v>350</v>
       </c>
       <c r="B126" s="5">
-        <v>46149.00267217593</v>
+        <v>46149.16933884259</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.43518712963</v>
+        <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>192</v>
@@ -8805,11 +8823,11 @@
         <v>352</v>
       </c>
       <c r="B127" s="9">
-        <v>46149.002680150465</v>
+        <v>46149.16934681713</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.43518783565</v>
+        <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>192</v>
@@ -8856,11 +8874,11 @@
         <v>354</v>
       </c>
       <c r="B128" s="5">
-        <v>46155.39656795139</v>
+        <v>46155.56323461806</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.43518863426</v>
+        <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>251</v>
@@ -8907,11 +8925,11 @@
         <v>356</v>
       </c>
       <c r="B129" s="9">
-        <v>46155.3965587037</v>
+        <v>46155.563225370366</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.43518936343</v>
+        <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>249</v>
@@ -8958,11 +8976,11 @@
         <v>358</v>
       </c>
       <c r="B130" s="5">
-        <v>46149.00268677084</v>
+        <v>46149.1693534375</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.43549829861</v>
+        <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>359</v>
@@ -9021,11 +9039,11 @@
         <v>361</v>
       </c>
       <c r="B131" s="9">
-        <v>46149.00269243056</v>
+        <v>46149.16935909722</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.435465613424</v>
+        <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>192</v>
@@ -9072,11 +9090,11 @@
         <v>362</v>
       </c>
       <c r="B132" s="5">
-        <v>46149.00269746528</v>
+        <v>46149.16936413194</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.43546230324</v>
+        <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>192</v>
@@ -9123,11 +9141,11 @@
         <v>363</v>
       </c>
       <c r="B133" s="9">
-        <v>46155.396656111116</v>
+        <v>46155.56332277777</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.435458356485</v>
+        <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>249</v>
@@ -9174,11 +9192,11 @@
         <v>364</v>
       </c>
       <c r="B134" s="5">
-        <v>46155.39666601852</v>
+        <v>46155.56333268518</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.43545379629</v>
+        <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>251</v>
@@ -9225,11 +9243,11 @@
         <v>365</v>
       </c>
       <c r="B135" s="9">
-        <v>46149.00270247685</v>
+        <v>46149.16936914352</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46155.43572224537</v>
+        <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>366</v>
@@ -9272,11 +9290,11 @@
         <v>368</v>
       </c>
       <c r="B136" s="5">
-        <v>46149.00270646991</v>
+        <v>46149.169373136574</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.43555115741</v>
+        <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>369</v>
@@ -9335,11 +9353,11 @@
         <v>372</v>
       </c>
       <c r="B137" s="9">
-        <v>46149.00275068287</v>
+        <v>46149.169417349534</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.702763043984</v>
+        <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>373</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -3959,9 +3959,11 @@
       <c r="B39" s="9">
         <v>46149.16892260416</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46205.843624166664</v>
+      </c>
       <c r="D39" s="9">
-        <v>46169.859801203704</v>
+        <v>46205.84364175926</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4009,10 +4011,10 @@
         <v>102</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4022,9 +4024,11 @@
       <c r="B40" s="5">
         <v>46149.168932870365</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46205.8435071412</v>
+      </c>
       <c r="D40" s="5">
-        <v>46204.91187768518</v>
+        <v>46205.843509259255</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>89</v>
@@ -4075,9 +4079,11 @@
       <c r="B41" s="9">
         <v>46149.16893796297</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46205.84357833333</v>
+      </c>
       <c r="D41" s="9">
-        <v>46169.859942118055</v>
+        <v>46205.84357975694</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4130,7 +4136,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.859966018514</v>
+        <v>46205.843587766205</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -6398,7 +6404,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46155.59985006944</v>
+        <v>46205.84359559028</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6448,8 +6454,8 @@
       <c r="T82" s="6">
         <v>0</v>
       </c>
-      <c r="U82" s="11" t="s">
-        <v>98</v>
+      <c r="U82" s="12" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2688,7 +2688,7 @@
         <v>46204.91285559028</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.91287212963</v>
+        <v>46206.56521946759</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2753,7 +2753,7 @@
         <v>46204.91289165509</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.91290902778</v>
+        <v>46206.56539268518</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2818,7 +2818,7 @@
         <v>46204.91205277778</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.91223577547</v>
+        <v>46206.56555653935</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2883,7 +2883,7 @@
         <v>46204.911869143514</v>
       </c>
       <c r="D21" s="9">
-        <v>46204.91200600694</v>
+        <v>46206.56578831018</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46155.5990459375</v>
+        <v>46209.16767226852</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>217</v>
@@ -5279,8 +5279,8 @@
       <c r="R61" s="9">
         <v>46216</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>102</v>
+      <c r="S61" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46155.59855652778</v>
+        <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>192</v>
@@ -4678,10 +4678,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46155.59855292824</v>
+        <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4729,10 +4729,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46155.59854846065</v>
+        <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>192</v>
@@ -4780,10 +4780,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46155.59854489584</v>
+        <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>192</v>
@@ -4831,10 +4831,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -561,169 +561,169 @@
     <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
   </si>
   <si>
+    <t>1214596725472966</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472981</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214563704105178</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214596624002438</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214596734094501</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214596734094526</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624006635</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105084</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105094</t>
+  </si>
+  <si>
+    <t>1214739697907509</t>
+  </si>
+  <si>
+    <t>1214739697907510</t>
+  </si>
+  <si>
+    <t>1214596734105104</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112602</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734114879</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596624027372</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624027387</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596725472966</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472981</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214563704105178</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214596624002438</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214596734094501</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214596734094526</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624006635</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105084</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105094</t>
-  </si>
-  <si>
-    <t>1214739697907509</t>
-  </si>
-  <si>
-    <t>1214739697907510</t>
-  </si>
-  <si>
-    <t>1214596734105104</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112602</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734114879</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596624027372</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624027387</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
   </si>
   <si>
     <t>1214596624027530</t>
@@ -4191,7 +4191,7 @@
         <v>46205.61327819445</v>
       </c>
       <c r="D43" s="9">
-        <v>46205.61328953704</v>
+        <v>46211.19248402778</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4235,8 +4235,8 @@
       <c r="R43" s="9">
         <v>46210</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>163</v>
+      <c r="S43" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T43" s="10">
         <v>1</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4292,7 +4292,7 @@
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4314,7 +4314,7 @@
         <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4347,7 +4347,7 @@
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4357,7 +4357,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4367,7 +4367,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4391,7 +4391,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4401,12 +4401,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4418,16 +4418,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4445,13 +4445,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4483,16 +4483,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4510,13 +4510,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4554,10 +4554,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4573,13 +4573,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4609,16 +4609,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4636,10 +4636,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4672,16 +4672,16 @@
         <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4697,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4723,16 +4723,16 @@
         <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4748,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4764,7 +4764,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4774,16 +4774,16 @@
         <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4799,13 +4799,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4825,16 +4825,16 @@
         <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4850,13 +4850,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4866,7 +4866,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4876,7 +4876,7 @@
         <v>46155.55893427083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4900,7 +4900,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4923,16 +4923,16 @@
         <v>46205.60769931713</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4950,13 +4950,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4971,12 +4971,12 @@
         <v>0</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -4986,7 +4986,7 @@
         <v>46205.16832303241</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5013,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5039,7 +5039,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5049,16 +5049,16 @@
         <v>46205.60894056713</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5076,13 +5076,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5097,12 +5097,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5112,7 +5112,7 @@
         <v>46205.16831765046</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5139,13 +5139,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5175,16 +5175,16 @@
         <v>46205.61327966435</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5202,13 +5202,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5217,13 +5217,13 @@
         <v>46212</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5238,7 +5238,7 @@
         <v>46209.16767226852</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5265,13 +5265,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5280,7 +5280,7 @@
         <v>46216</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -5411,7 +5411,7 @@
         <v>46155.59925321759</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5464,7 +5464,7 @@
         <v>46155.59924960649</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5497,7 +5497,7 @@
         <v>231</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5517,7 +5517,7 @@
         <v>46155.59924675926</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5550,7 +5550,7 @@
         <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5570,7 +5570,7 @@
         <v>46155.59924362268</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5603,7 +5603,7 @@
         <v>233</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5653,7 +5653,7 @@
         <v>220</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>220</v>
@@ -5686,7 +5686,7 @@
         <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5739,7 +5739,7 @@
         <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5792,7 +5792,7 @@
         <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5825,7 +5825,7 @@
         <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5845,7 +5845,7 @@
         <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5878,7 +5878,7 @@
         <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5928,7 +5928,7 @@
         <v>220</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>220</v>
@@ -5961,7 +5961,7 @@
         <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6014,7 +6014,7 @@
         <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6067,7 +6067,7 @@
         <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6120,7 +6120,7 @@
         <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6173,7 +6173,7 @@
         <v>46155.57120092593</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6226,10 +6226,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6245,7 +6245,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>113</v>
@@ -6287,10 +6287,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6308,7 +6308,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>104</v>
@@ -6350,10 +6350,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6371,7 +6371,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>122</v>
@@ -6413,10 +6413,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6434,7 +6434,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>154</v>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6580,7 +6580,7 @@
         <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6633,7 +6633,7 @@
         <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6716,7 +6716,7 @@
         <v>269</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6769,7 +6769,7 @@
         <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>275</v>
@@ -6822,7 +6822,7 @@
         <v>266</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>266</v>
@@ -6855,7 +6855,7 @@
         <v>46199.77908100694</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6906,7 +6906,7 @@
         <v>46199.77908144676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6957,7 +6957,7 @@
         <v>46199.77908483797</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7008,7 +7008,7 @@
         <v>46199.779085277776</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7089,7 +7089,7 @@
         <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>266</v>
@@ -7122,7 +7122,7 @@
         <v>46199.779080567125</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7173,7 +7173,7 @@
         <v>46199.779077430554</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7224,7 +7224,7 @@
         <v>46199.779084340276</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7275,7 +7275,7 @@
         <v>46199.779085752314</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7356,7 +7356,7 @@
         <v>266</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>266</v>
@@ -7389,7 +7389,7 @@
         <v>46199.779077858795</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7440,7 +7440,7 @@
         <v>46199.77908177083</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7491,7 +7491,7 @@
         <v>46199.77908608796</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7542,7 +7542,7 @@
         <v>46199.77908645834</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7623,7 +7623,7 @@
         <v>266</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>266</v>
@@ -7656,7 +7656,7 @@
         <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7686,7 +7686,7 @@
         <v>308</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>310</v>
@@ -7709,7 +7709,7 @@
         <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7739,7 +7739,7 @@
         <v>308</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>310</v>
@@ -7762,7 +7762,7 @@
         <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7792,7 +7792,7 @@
         <v>308</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>313</v>
@@ -7815,7 +7815,7 @@
         <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7845,7 +7845,7 @@
         <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>313</v>
@@ -7898,7 +7898,7 @@
         <v>266</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>317</v>
@@ -7931,7 +7931,7 @@
         <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7959,7 +7959,7 @@
         <v>316</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>319</v>
@@ -7982,7 +7982,7 @@
         <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8010,7 +8010,7 @@
         <v>316</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>319</v>
@@ -8033,7 +8033,7 @@
         <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8061,7 +8061,7 @@
         <v>316</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>322</v>
@@ -8084,7 +8084,7 @@
         <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8112,7 +8112,7 @@
         <v>316</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>322</v>
@@ -8243,7 +8243,7 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8271,7 +8271,7 @@
         <v>328</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>333</v>
@@ -8294,7 +8294,7 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8322,7 +8322,7 @@
         <v>328</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>335</v>
@@ -8345,7 +8345,7 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8373,7 +8373,7 @@
         <v>328</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>335</v>
@@ -8396,7 +8396,7 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8424,7 +8424,7 @@
         <v>328</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>335</v>
@@ -8477,7 +8477,7 @@
         <v>325</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>325</v>
@@ -8510,7 +8510,7 @@
         <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8540,7 +8540,7 @@
         <v>339</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>341</v>
@@ -8563,7 +8563,7 @@
         <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8593,7 +8593,7 @@
         <v>339</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>341</v>
@@ -8616,7 +8616,7 @@
         <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8646,7 +8646,7 @@
         <v>339</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>344</v>
@@ -8669,7 +8669,7 @@
         <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8699,7 +8699,7 @@
         <v>339</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>346</v>
@@ -8785,7 +8785,7 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8813,7 +8813,7 @@
         <v>348</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>351</v>
@@ -8836,7 +8836,7 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8864,7 +8864,7 @@
         <v>348</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>353</v>
@@ -8915,7 +8915,7 @@
         <v>348</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>355</v>
@@ -8966,7 +8966,7 @@
         <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>357</v>
@@ -9052,7 +9052,7 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9080,7 +9080,7 @@
         <v>359</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>359</v>
@@ -9103,7 +9103,7 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9131,7 +9131,7 @@
         <v>359</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>359</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5172,7 +5172,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46205.61327966435</v>
+        <v>46212.16822195602</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>215</v>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46161.57724337963</v>
+        <v>46212.17235166667</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5389,8 +5389,8 @@
       <c r="R63" s="9">
         <v>46219</v>
       </c>
-      <c r="S63" s="7" t="s">
-        <v>102</v>
+      <c r="S63" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -366,19 +366,19 @@
     <t>Generación OC Alabe OT 4315,Fabricación Alabe OT 4315</t>
   </si>
   <si>
+    <t>1214596734036226</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Alabe OT 4315,Fabricación Alabe OT 4315</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214596734036226</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Alabe OT 4315,Fabricación Alabe OT 4315</t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1214596725445208</t>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46205.60770953704</v>
+        <v>46212.66494016204</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2991,9 +2991,11 @@
       <c r="B23" s="9">
         <v>46149.168800127314</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46212.664802025465</v>
+      </c>
       <c r="D23" s="9">
-        <v>46169.85973167824</v>
+        <v>46212.66481476852</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>94</v>
@@ -3041,25 +3043,27 @@
         <v>33</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46212.664752557874</v>
+      </c>
       <c r="D24" s="5">
-        <v>46196.87158508102</v>
+        <v>46212.66475459491</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3092,18 +3096,18 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3113,9 +3117,11 @@
       <c r="B25" s="9">
         <v>46149.16880861111</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46212.66478641204</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.86022740741</v>
+        <v>46212.66478789352</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -3148,7 +3154,7 @@
         <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>105</v>
@@ -3156,13 +3162,13 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3172,9 +3178,11 @@
       <c r="B26" s="5">
         <v>46149.16881337963</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46212.664931990745</v>
+      </c>
       <c r="D26" s="5">
-        <v>46179.17667454861</v>
+        <v>46212.66494965278</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3222,10 +3230,10 @@
         <v>33</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3235,9 +3243,11 @@
       <c r="B27" s="9">
         <v>46149.16881752315</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46212.66487011574</v>
+      </c>
       <c r="D27" s="9">
-        <v>46197.50269849537</v>
+        <v>46212.664871597226</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3278,13 +3288,13 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3294,9 +3304,11 @@
       <c r="B28" s="5">
         <v>46149.168821851854</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46212.66491304398</v>
+      </c>
       <c r="D28" s="5">
-        <v>46178.170599363424</v>
+        <v>46212.664914918976</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3337,13 +3349,13 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3406,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3461,13 +3473,13 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3520,13 +3532,13 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3581,13 +3593,13 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3707,13 +3719,13 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3768,13 +3780,13 @@
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4008,7 +4020,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4588,7 +4600,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4651,13 +4663,13 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5034,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5160,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5286,7 +5298,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5396,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5665,13 +5677,13 @@
         <v>46226</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5940,13 +5952,13 @@
         <v>46227</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6170,7 +6182,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46155.57120092593</v>
+        <v>46212.66505685185</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>197</v>
@@ -6215,9 +6227,11 @@
       <c r="B79" s="9">
         <v>46149.16913708333</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46212.66504260417</v>
+      </c>
       <c r="D79" s="9">
-        <v>46182.17098876157</v>
+        <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6263,10 +6277,10 @@
         <v>33</v>
       </c>
       <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U79" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6276,9 +6290,11 @@
       <c r="B80" s="5">
         <v>46149.16914224537</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46212.665051261574</v>
+      </c>
       <c r="D80" s="5">
-        <v>46165.180999432865</v>
+        <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6326,10 +6342,10 @@
         <v>33</v>
       </c>
       <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+      <c r="U80" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6392,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6449,7 +6465,7 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
@@ -6559,13 +6575,13 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6834,13 +6850,13 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6852,7 +6868,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46199.77908100694</v>
+        <v>46212.6650581713</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>191</v>
@@ -6903,7 +6919,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46199.77908144676</v>
+        <v>46212.665059328705</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>191</v>
@@ -6954,7 +6970,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46199.77908483797</v>
+        <v>46212.66505967593</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -7005,7 +7021,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46199.779085277776</v>
+        <v>46212.66506008102</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7101,13 +7117,13 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7119,7 +7135,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46199.779080567125</v>
+        <v>46212.665048483796</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>191</v>
@@ -7170,7 +7186,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46199.779077430554</v>
+        <v>46212.66504763889</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>
@@ -7221,7 +7237,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46199.779084340276</v>
+        <v>46212.665048993054</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7272,7 +7288,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46199.779085752314</v>
+        <v>46212.665049456016</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>191</v>
@@ -7368,13 +7384,13 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7635,13 +7651,13 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7910,13 +7926,13 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8222,13 +8238,13 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8489,13 +8505,13 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8764,13 +8780,13 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -9031,13 +9047,13 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9345,13 +9361,13 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -9408,13 +9424,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -723,10 +723,10 @@
     <t>Control de calidad Mecanizado</t>
   </si>
   <si>
+    <t>1214596624027530</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596624027530</t>
   </si>
   <si>
     <t>1214596624027545</t>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46212.16822195602</v>
+        <v>46213.20552466435</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>215</v>
@@ -5228,8 +5228,8 @@
       <c r="R60" s="5">
         <v>46212</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>217</v>
+      <c r="S60" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5240,7 +5240,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5292,7 +5292,7 @@
         <v>46216</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>46219</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46155.600641770834</v>
+        <v>46213.50801929398</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>278</v>
@@ -6866,9 +6866,11 @@
       <c r="B90" s="5">
         <v>46149.169178321754</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46213.50800253473</v>
+      </c>
       <c r="D90" s="5">
-        <v>46212.6650581713</v>
+        <v>46213.508005578704</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>191</v>
@@ -6917,9 +6919,11 @@
       <c r="B91" s="9">
         <v>46149.169183148144</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46213.50801122685</v>
+      </c>
       <c r="D91" s="9">
-        <v>46212.665059328705</v>
+        <v>46213.508012962964</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>191</v>
@@ -7072,7 +7076,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46155.60079344908</v>
+        <v>46213.50808509259</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>288</v>
@@ -7133,9 +7137,11 @@
       <c r="B95" s="9">
         <v>46149.1691919213</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="9">
+        <v>46213.508068599534</v>
+      </c>
       <c r="D95" s="9">
-        <v>46212.665048483796</v>
+        <v>46213.50807009259</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>191</v>
@@ -7184,9 +7190,11 @@
       <c r="B96" s="5">
         <v>46149.16919760416</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46213.50807769676</v>
+      </c>
       <c r="D96" s="5">
-        <v>46212.66504763889</v>
+        <v>46213.50808212963</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>191</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46209.16767226852</v>
+        <v>46216.16866572917</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="374">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -4883,9 +4883,11 @@
       <c r="B55" s="9">
         <v>46149.1690050926</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46216.83961519676</v>
+      </c>
       <c r="D55" s="9">
-        <v>46155.55893427083</v>
+        <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4920,8 +4922,12 @@
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
       <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
+      <c r="T55" s="10">
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
@@ -4930,9 +4936,11 @@
       <c r="B56" s="5">
         <v>46149.16900940972</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46216.839534756946</v>
+      </c>
       <c r="D56" s="5">
-        <v>46205.60769931713</v>
+        <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -4980,10 +4988,10 @@
         <v>33</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4993,9 +5001,11 @@
       <c r="B57" s="9">
         <v>46149.16901516204</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46216.83958197916</v>
+      </c>
       <c r="D57" s="9">
-        <v>46205.16832303241</v>
+        <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>205</v>
@@ -5043,10 +5053,10 @@
         <v>33</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5056,9 +5066,11 @@
       <c r="B58" s="5">
         <v>46149.16902107639</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46216.839544409726</v>
+      </c>
       <c r="D58" s="5">
-        <v>46205.60894056713</v>
+        <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5106,10 +5118,10 @@
         <v>33</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="12" t="s">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5119,9 +5131,11 @@
       <c r="B59" s="9">
         <v>46149.16902621528</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46216.83958944444</v>
+      </c>
       <c r="D59" s="9">
-        <v>46205.16831765046</v>
+        <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5169,10 +5183,10 @@
         <v>33</v>
       </c>
       <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5182,9 +5196,11 @@
       <c r="B60" s="5">
         <v>46149.1690303588</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46216.839551620375</v>
+      </c>
       <c r="D60" s="5">
-        <v>46213.20552466435</v>
+        <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>215</v>
@@ -5232,10 +5248,10 @@
         <v>33</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="12" t="s">
-        <v>171</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5245,9 +5261,11 @@
       <c r="B61" s="9">
         <v>46149.16903488426</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46216.83960126157</v>
+      </c>
       <c r="D61" s="9">
-        <v>46216.16866572917</v>
+        <v>46216.83990553241</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5295,10 +5313,10 @@
         <v>218</v>
       </c>
       <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5420,7 +5438,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46155.59925321759</v>
+        <v>46216.83960648148</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>191</v>
@@ -5473,7 +5491,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46155.59924960649</v>
+        <v>46216.839607754635</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>191</v>
@@ -5526,7 +5544,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.59924675926</v>
+        <v>46216.83960883102</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>191</v>
@@ -5579,7 +5597,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46155.59924362268</v>
+        <v>46216.83960983796</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>191</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="374">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -351,6 +351,9 @@
     <t>Motor OT 4315,Alabe OT 4315,rodete OT 4315,Materiales corte Laser OT 4315</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214596734036211</t>
   </si>
   <si>
@@ -583,9 +586,6 @@
   </si>
   <si>
     <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214596624002438</t>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46212.66494016204</v>
+        <v>46216.87167356482</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2982,11 +2982,13 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168800127314</v>
@@ -2998,16 +3000,16 @@
         <v>46212.66481476852</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -3028,7 +3030,7 @@
         <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>91</v>
@@ -3051,7 +3053,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3063,16 +3065,16 @@
         <v>46212.66475459491</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3090,29 +3092,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3124,16 +3126,16 @@
         <v>46212.66478789352</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3151,29 +3153,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3185,16 +3187,16 @@
         <v>46212.66494965278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3215,7 +3217,7 @@
         <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>91</v>
@@ -3238,7 +3240,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
@@ -3250,16 +3252,16 @@
         <v>46212.664871597226</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3277,29 +3279,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3311,16 +3313,16 @@
         <v>46212.664914918976</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3338,48 +3340,50 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46216.871654560186</v>
+      </c>
       <c r="D29" s="9">
-        <v>46199.75288726852</v>
+        <v>46216.87176959491</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3400,7 +3404,7 @@
         <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>91</v>
@@ -3415,15 +3419,15 @@
         <v>33</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3435,16 +3439,16 @@
         <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3462,48 +3466,50 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46216.87163922454</v>
+      </c>
       <c r="D31" s="9">
-        <v>46199.752836423606</v>
+        <v>46216.87164077546</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3521,29 +3527,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3555,16 +3561,16 @@
         <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3582,29 +3588,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3616,16 +3622,16 @@
         <v>46205.60771266204</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3646,7 +3652,7 @@
         <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>91</v>
@@ -3669,7 +3675,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3681,16 +3687,16 @@
         <v>46205.60762148148</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3708,29 +3714,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3742,16 +3748,16 @@
         <v>46205.60768407407</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3769,29 +3775,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3803,16 +3809,16 @@
         <v>46205.608947719906</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3833,7 +3839,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3856,7 +3862,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3874,10 +3880,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3895,13 +3901,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3911,7 +3917,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3923,16 +3929,16 @@
         <v>46205.60892006944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3950,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3966,7 +3972,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3978,16 +3984,16 @@
         <v>46205.84364175926</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -4008,7 +4014,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4020,7 +4026,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4031,7 +4037,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4049,10 +4055,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4070,13 +4076,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4086,7 +4092,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4098,16 +4104,16 @@
         <v>46205.84357975694</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4125,13 +4131,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4141,7 +4147,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4151,16 +4157,16 @@
         <v>46205.843587766205</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4178,10 +4184,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4194,7 +4200,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4206,16 +4212,16 @@
         <v>46211.19248402778</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4236,7 +4242,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4259,7 +4265,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4277,10 +4283,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4298,13 +4304,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4314,7 +4320,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4326,16 +4332,16 @@
         <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4353,13 +4359,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4369,7 +4375,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4379,7 +4385,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4403,7 +4409,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4413,7 +4419,7 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>171</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4457,7 +4463,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
@@ -4522,7 +4528,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>179</v>
@@ -4585,7 +4591,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>178</v>
@@ -4600,7 +4606,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4648,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>189</v>
@@ -4663,13 +4669,13 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4973,7 +4979,7 @@
         <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>203</v>
@@ -5014,10 +5020,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -5103,7 +5109,7 @@
         <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>210</v>
@@ -5144,10 +5150,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5233,7 +5239,7 @@
         <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>216</v>
@@ -5274,10 +5280,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5426,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5695,13 +5701,13 @@
         <v>46226</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5934,10 +5940,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5970,13 +5976,13 @@
         <v>46227</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5997,10 +6003,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -6050,10 +6056,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6103,10 +6109,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6156,10 +6162,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6200,7 +6206,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46212.66505685185</v>
+        <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>197</v>
@@ -6236,7 +6242,9 @@
       <c r="R78" s="6"/>
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+      <c r="U78" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
@@ -6280,7 +6288,7 @@
         <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>256</v>
@@ -6345,7 +6353,7 @@
         <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>259</v>
@@ -6373,9 +6381,11 @@
       <c r="B81" s="9">
         <v>46149.16914733796</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="9">
+        <v>46216.871819039356</v>
+      </c>
       <c r="D81" s="9">
-        <v>46198.171336064814</v>
+        <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6408,7 +6418,7 @@
         <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>259</v>
@@ -6423,10 +6433,10 @@
         <v>33</v>
       </c>
       <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U81" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6471,7 +6481,7 @@
         <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>264</v>
@@ -6483,13 +6493,13 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>171</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6593,13 +6603,13 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6868,13 +6878,13 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7139,13 +7149,13 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7410,13 +7420,13 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7428,7 +7438,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46199.779077858795</v>
+        <v>46216.87182809028</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7479,7 +7489,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46199.77908177083</v>
+        <v>46216.87182944444</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>191</v>
@@ -7530,7 +7540,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46199.77908608796</v>
+        <v>46216.87183001157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7581,7 +7591,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46199.77908645834</v>
+        <v>46216.871830648146</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -7677,13 +7687,13 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7952,13 +7962,13 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8264,13 +8274,13 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8531,13 +8541,13 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8806,13 +8816,13 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -9073,13 +9083,13 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9387,13 +9397,13 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -9450,13 +9460,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -726,31 +726,31 @@
     <t>1214596624027530</t>
   </si>
   <si>
+    <t>1214596624027545</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214596624027555</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596624027545</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214596624027555</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5271,7 +5271,7 @@
         <v>46216.83960126157</v>
       </c>
       <c r="D61" s="9">
-        <v>46216.83990553241</v>
+        <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5315,8 +5315,8 @@
       <c r="R61" s="9">
         <v>46216</v>
       </c>
-      <c r="S61" s="12" t="s">
-        <v>218</v>
+      <c r="S61" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T61" s="10">
         <v>1</v>
@@ -5327,7 +5327,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5337,7 +5337,7 @@
         <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5361,7 +5361,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5374,7 +5374,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5384,16 +5384,16 @@
         <v>46212.17235166667</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5411,13 +5411,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5426,7 +5426,7 @@
         <v>46219</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5453,10 +5453,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5474,7 +5474,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>228</v>
@@ -5506,10 +5506,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5527,7 +5527,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>231</v>
@@ -5559,10 +5559,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5580,7 +5580,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>233</v>
@@ -5612,10 +5612,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5633,7 +5633,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>233</v>
@@ -5665,10 +5665,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5686,13 +5686,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5728,10 +5728,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5781,10 +5781,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5834,10 +5834,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5887,10 +5887,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5961,13 +5961,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -8780,10 +8780,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8843,10 +8843,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8894,10 +8894,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8945,10 +8945,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8996,10 +8996,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -9047,10 +9047,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -9110,10 +9110,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9161,10 +9161,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9212,10 +9212,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9263,10 +9263,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="371">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -291,9 +291,6 @@
     <t>propuesta nucleo rodete OT 4315</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4315</t>
   </si>
   <si>
@@ -301,12 +298,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4315</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2632,11 +2623,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46155</v>
       </c>
@@ -2659,7 +2648,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2679,7 +2668,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46149.168784837966</v>
@@ -2691,17 +2680,15 @@
         <v>46206.56521946759</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46185</v>
       </c>
@@ -2721,10 +2708,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2744,7 +2731,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" s="9">
         <v>46149.168789351854</v>
@@ -2756,17 +2743,15 @@
         <v>46206.56539268518</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46185</v>
       </c>
@@ -2786,10 +2771,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2809,7 +2794,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46149.16879285879</v>
@@ -2821,17 +2806,15 @@
         <v>46206.56555653935</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46185</v>
       </c>
@@ -2851,10 +2834,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2874,7 +2857,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B21" s="9">
         <v>46149.16879642361</v>
@@ -2886,17 +2869,15 @@
         <v>46206.56578831018</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="9">
         <v>46185</v>
       </c>
@@ -2916,10 +2897,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2939,7 +2920,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46149.168676875</v>
@@ -2949,7 +2930,7 @@
         <v>46216.87167356482</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2973,7 +2954,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2983,12 +2964,12 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168800127314</v>
@@ -3000,16 +2981,16 @@
         <v>46212.66481476852</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -3027,13 +3008,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q23" s="9">
         <v>46157</v>
@@ -3053,7 +3034,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3065,16 +3046,16 @@
         <v>46212.66475459491</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3092,29 +3073,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3126,16 +3107,16 @@
         <v>46212.66478789352</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3153,29 +3134,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3187,16 +3168,16 @@
         <v>46212.66494965278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3214,13 +3195,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3240,7 +3221,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
@@ -3252,16 +3233,16 @@
         <v>46212.664871597226</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3279,29 +3260,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3313,16 +3294,16 @@
         <v>46212.664914918976</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3340,29 +3321,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
@@ -3374,16 +3355,16 @@
         <v>46216.87176959491</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3401,13 +3382,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q29" s="9">
         <v>46157</v>
@@ -3427,7 +3408,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3439,16 +3420,16 @@
         <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3466,29 +3447,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
@@ -3500,16 +3481,16 @@
         <v>46216.87164077546</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3527,29 +3508,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3561,16 +3542,16 @@
         <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3588,29 +3569,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3622,16 +3603,16 @@
         <v>46205.60771266204</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3649,13 +3630,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q33" s="9">
         <v>46189</v>
@@ -3675,7 +3656,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3687,16 +3668,16 @@
         <v>46205.60762148148</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3714,29 +3695,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3748,16 +3729,16 @@
         <v>46205.60768407407</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3775,29 +3756,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3809,16 +3790,16 @@
         <v>46205.608947719906</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3836,10 +3817,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3862,7 +3843,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3874,16 +3855,16 @@
         <v>46205.60888410879</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3901,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3917,7 +3898,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3929,16 +3910,16 @@
         <v>46205.60892006944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3956,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3972,7 +3953,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3984,16 +3965,16 @@
         <v>46205.84364175926</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -4011,10 +3992,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4026,7 +4007,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4037,7 +4018,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4049,16 +4030,16 @@
         <v>46205.843509259255</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4076,13 +4057,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4092,7 +4073,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4104,16 +4085,16 @@
         <v>46205.84357975694</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4131,13 +4112,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4147,7 +4128,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4157,16 +4138,16 @@
         <v>46205.843587766205</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4184,10 +4165,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4200,7 +4181,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4212,16 +4193,16 @@
         <v>46211.19248402778</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4239,10 +4220,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4265,7 +4246,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4277,16 +4258,16 @@
         <v>46205.613227546295</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4304,13 +4285,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4320,7 +4301,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4332,16 +4313,16 @@
         <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4359,13 +4340,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4375,7 +4356,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4385,7 +4366,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4409,7 +4390,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4419,12 +4400,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4436,16 +4417,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4463,13 +4444,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4489,7 +4470,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4501,16 +4482,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4528,13 +4509,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4554,7 +4535,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4566,16 +4547,16 @@
         <v>46199.77907827546</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4591,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4606,7 +4587,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4617,7 +4598,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4627,16 +4608,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4654,10 +4635,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4669,18 +4650,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4690,16 +4671,16 @@
         <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4715,13 +4696,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4731,7 +4712,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4741,16 +4722,16 @@
         <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4766,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4782,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4792,16 +4773,16 @@
         <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4817,13 +4798,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4833,7 +4814,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4843,16 +4824,16 @@
         <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4868,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4884,7 +4865,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4896,7 +4877,7 @@
         <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4920,7 +4901,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4937,7 +4918,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4949,16 +4930,16 @@
         <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4976,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -5002,7 +4983,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -5014,16 +4995,16 @@
         <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -5041,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5067,7 +5048,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5079,16 +5060,16 @@
         <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5106,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5132,7 +5113,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5144,16 +5125,16 @@
         <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5171,13 +5152,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5197,7 +5178,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5209,16 +5190,16 @@
         <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5236,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5262,7 +5243,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5274,16 +5255,16 @@
         <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5301,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5327,7 +5308,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5337,7 +5318,7 @@
         <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5361,7 +5342,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5374,7 +5355,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5384,16 +5365,16 @@
         <v>46212.17235166667</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5411,13 +5392,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5426,18 +5407,18 @@
         <v>46219</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5447,16 +5428,16 @@
         <v>46216.83960648148</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5474,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5490,7 +5471,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5500,16 +5481,16 @@
         <v>46216.839607754635</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5527,13 +5508,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5543,7 +5524,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5553,16 +5534,16 @@
         <v>46216.83960883102</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5580,13 +5561,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5596,7 +5577,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5606,16 +5587,16 @@
         <v>46216.83960983796</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5633,13 +5614,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5649,7 +5630,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5659,16 +5640,16 @@
         <v>46155.59934020833</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5686,13 +5667,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5701,18 +5682,18 @@
         <v>46226</v>
       </c>
       <c r="S68" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5722,16 +5703,16 @@
         <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5749,13 +5730,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="O69" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5765,7 +5746,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5775,16 +5756,16 @@
         <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5802,13 +5783,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5818,7 +5799,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5828,16 +5809,16 @@
         <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5855,13 +5836,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5871,7 +5852,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5881,16 +5862,16 @@
         <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5908,13 +5889,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5924,7 +5905,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5934,16 +5915,16 @@
         <v>46155.59937984953</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5961,13 +5942,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -5976,18 +5957,18 @@
         <v>46227</v>
       </c>
       <c r="S73" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -5997,16 +5978,16 @@
         <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -6024,13 +6005,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6040,7 +6021,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -6050,16 +6031,16 @@
         <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6077,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6093,7 +6074,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6103,16 +6084,16 @@
         <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6130,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6146,7 +6127,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6156,16 +6137,16 @@
         <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6183,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6199,7 +6180,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6209,7 +6190,7 @@
         <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6233,7 +6214,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6243,12 +6224,12 @@
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
       <c r="U78" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6260,16 +6241,16 @@
         <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6285,13 +6266,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6311,7 +6292,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6323,16 +6304,16 @@
         <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6350,13 +6331,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6376,7 +6357,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6388,16 +6369,16 @@
         <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6415,13 +6396,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6441,7 +6422,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6451,16 +6432,16 @@
         <v>46205.84359559028</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6478,13 +6459,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6493,18 +6474,18 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6514,7 +6495,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6538,7 +6519,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6551,7 +6532,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
@@ -6561,17 +6542,15 @@
         <v>46155.60047521991</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46230</v>
       </c>
@@ -6588,13 +6567,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6603,18 +6582,18 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46149.16916685185</v>
@@ -6624,17 +6603,15 @@
         <v>46155.60002515046</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="10"/>
       <c r="I85" s="9">
         <v>46230</v>
       </c>
@@ -6651,10 +6628,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="O85" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6667,7 +6644,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46149.16917037037</v>
@@ -6677,17 +6654,15 @@
         <v>46155.60002232638</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46230</v>
       </c>
@@ -6704,10 +6679,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="O86" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6720,7 +6695,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46155.5624656713</v>
@@ -6730,17 +6705,15 @@
         <v>46155.60026604167</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
       <c r="I87" s="9">
         <v>46230</v>
       </c>
@@ -6757,13 +6730,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6773,7 +6746,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46155.562495266204</v>
@@ -6783,17 +6756,15 @@
         <v>46155.600359212964</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46230</v>
       </c>
@@ -6810,13 +6781,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6826,7 +6797,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B89" s="9">
         <v>46149.16917405093</v>
@@ -6836,17 +6807,15 @@
         <v>46213.50801929398</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
       <c r="I89" s="9">
         <v>46237</v>
       </c>
@@ -6863,13 +6832,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6878,18 +6847,18 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46149.169178321754</v>
@@ -6901,17 +6870,15 @@
         <v>46213.508005578704</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
         <v>46237</v>
@@ -6926,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6942,7 +6909,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46149.169183148144</v>
@@ -6954,17 +6921,15 @@
         <v>46213.508012962964</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="10"/>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
         <v>46237</v>
@@ -6979,13 +6944,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>278</v>
-      </c>
-      <c r="O91" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6995,7 +6960,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46155.56256662037</v>
@@ -7005,17 +6970,15 @@
         <v>46212.66505967593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46237</v>
@@ -7030,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7046,7 +7009,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B93" s="9">
         <v>46155.56257849537</v>
@@ -7056,17 +7019,15 @@
         <v>46212.66506008102</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
         <v>46237</v>
@@ -7081,13 +7042,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>278</v>
-      </c>
-      <c r="O93" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7097,7 +7058,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46149.169187962965</v>
@@ -7107,17 +7068,15 @@
         <v>46213.50808509259</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46238</v>
       </c>
@@ -7134,13 +7093,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7149,18 +7108,18 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46149.1691919213</v>
@@ -7172,17 +7131,15 @@
         <v>46213.50807009259</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="10"/>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
         <v>46238</v>
@@ -7197,13 +7154,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7213,7 +7170,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46149.16919760416</v>
@@ -7225,17 +7182,15 @@
         <v>46213.50808212963</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
         <v>46238</v>
@@ -7250,13 +7205,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7266,7 +7221,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B97" s="9">
         <v>46155.562660428244</v>
@@ -7276,17 +7231,15 @@
         <v>46212.665048993054</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="10"/>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
         <v>46238</v>
@@ -7301,13 +7254,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7317,7 +7270,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46155.56267193287</v>
@@ -7327,17 +7280,15 @@
         <v>46212.665049456016</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46238</v>
@@ -7352,13 +7303,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7368,7 +7319,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B99" s="9">
         <v>46149.169203125</v>
@@ -7378,17 +7329,15 @@
         <v>46155.60094263889</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="10"/>
       <c r="I99" s="9">
         <v>46239</v>
       </c>
@@ -7405,13 +7354,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7420,18 +7369,18 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46149.16920694444</v>
@@ -7441,17 +7390,15 @@
         <v>46216.87182809028</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46239</v>
@@ -7466,13 +7413,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>300</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7482,7 +7429,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B101" s="9">
         <v>46149.16921202546</v>
@@ -7492,17 +7439,15 @@
         <v>46216.87182944444</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="10"/>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
         <v>46239</v>
@@ -7517,13 +7462,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="O101" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="P101" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="O101" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>300</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7533,7 +7478,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B102" s="5">
         <v>46155.562741851856</v>
@@ -7543,17 +7488,15 @@
         <v>46216.87183001157</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
         <v>46239</v>
@@ -7568,13 +7511,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7584,7 +7527,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B103" s="9">
         <v>46155.562755046296</v>
@@ -7594,17 +7537,15 @@
         <v>46216.871830648146</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="10"/>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46239</v>
@@ -7619,13 +7560,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7635,7 +7576,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B104" s="5">
         <v>46149.16921689815</v>
@@ -7645,17 +7586,15 @@
         <v>46155.60109780093</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46240</v>
       </c>
@@ -7672,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7687,18 +7626,18 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B105" s="9">
         <v>46149.169220717595</v>
@@ -7708,17 +7647,15 @@
         <v>46155.60106565972</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="10"/>
       <c r="I105" s="9">
         <v>46240</v>
       </c>
@@ -7735,13 +7672,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7751,7 +7688,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B106" s="5">
         <v>46149.16922577546</v>
@@ -7761,17 +7698,15 @@
         <v>46155.601062546295</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46240</v>
       </c>
@@ -7788,13 +7723,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7804,7 +7739,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B107" s="9">
         <v>46155.56285743056</v>
@@ -7814,17 +7749,15 @@
         <v>46155.60105936343</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="10"/>
       <c r="I107" s="9">
         <v>46240</v>
       </c>
@@ -7841,13 +7774,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7857,7 +7790,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46155.56284611111</v>
@@ -7867,17 +7800,15 @@
         <v>46155.60105565972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46240</v>
       </c>
@@ -7894,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7910,7 +7841,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B109" s="9">
         <v>46149.169270370374</v>
@@ -7920,17 +7851,15 @@
         <v>46155.601273506945</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="10"/>
       <c r="I109" s="9">
         <v>46244</v>
       </c>
@@ -7947,13 +7876,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7962,18 +7891,18 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46149.16928524306</v>
@@ -7983,17 +7912,15 @@
         <v>46155.60133046296</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46244</v>
@@ -8008,13 +7935,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P110" s="6" t="s">
         <v>316</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>319</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8024,7 +7951,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B111" s="9">
         <v>46149.16929128472</v>
@@ -8034,17 +7961,15 @@
         <v>46155.60132649305</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="10"/>
       <c r="I111" s="10"/>
       <c r="J111" s="9">
         <v>46244</v>
@@ -8059,13 +7984,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="O111" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>316</v>
-      </c>
-      <c r="O111" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>319</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8075,7 +8000,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46155.562937361115</v>
@@ -8085,17 +8010,15 @@
         <v>46155.60132342593</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
         <v>46244</v>
@@ -8110,13 +8033,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8126,7 +8049,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B113" s="9">
         <v>46155.56294952546</v>
@@ -8136,17 +8059,15 @@
         <v>46155.60131890046</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="10"/>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
         <v>46244</v>
@@ -8161,13 +8082,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8177,7 +8098,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B114" s="5">
         <v>46149.16929695602</v>
@@ -8187,7 +8108,7 @@
         <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8211,7 +8132,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8224,7 +8145,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B115" s="9">
         <v>46149.169301041664</v>
@@ -8234,16 +8155,16 @@
         <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8259,13 +8180,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8274,18 +8195,18 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46149.1693071412</v>
@@ -8295,16 +8216,16 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8320,13 +8241,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8336,7 +8257,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B117" s="9">
         <v>46149.16931233797</v>
@@ -8346,16 +8267,16 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8371,13 +8292,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8387,7 +8308,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46155.56303070602</v>
@@ -8397,16 +8318,16 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8422,13 +8343,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8438,7 +8359,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
         <v>46155.56306011574</v>
@@ -8448,16 +8369,16 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8473,13 +8394,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8489,7 +8410,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B120" s="5">
         <v>46149.1693175</v>
@@ -8499,17 +8420,15 @@
         <v>46155.6016600463</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="5">
         <v>46246</v>
       </c>
@@ -8526,13 +8445,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8541,18 +8460,18 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B121" s="9">
         <v>46149.16932247685</v>
@@ -8562,17 +8481,15 @@
         <v>46155.601629756944</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="10"/>
       <c r="I121" s="9">
         <v>46246</v>
       </c>
@@ -8589,13 +8506,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8605,7 +8522,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46149.16932829861</v>
@@ -8615,17 +8532,15 @@
         <v>46155.60162688658</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46246</v>
       </c>
@@ -8642,13 +8557,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8658,7 +8573,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B123" s="9">
         <v>46155.56313421296</v>
@@ -8668,17 +8583,15 @@
         <v>46155.601624421295</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="10"/>
       <c r="I123" s="9">
         <v>46246</v>
       </c>
@@ -8695,13 +8608,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8711,7 +8624,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46155.5631459375</v>
@@ -8721,17 +8634,15 @@
         <v>46155.601620671296</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="5">
         <v>46246</v>
       </c>
@@ -8748,13 +8659,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8764,7 +8675,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B125" s="9">
         <v>46149.16933366898</v>
@@ -8774,16 +8685,16 @@
         <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8801,13 +8712,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8816,18 +8727,18 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B126" s="5">
         <v>46149.16933884259</v>
@@ -8837,16 +8748,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8862,13 +8773,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P126" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8878,7 +8789,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B127" s="9">
         <v>46149.16934681713</v>
@@ -8888,16 +8799,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8913,13 +8824,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8929,7 +8840,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B128" s="5">
         <v>46155.56323461806</v>
@@ -8939,16 +8850,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8964,13 +8875,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8980,7 +8891,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B129" s="9">
         <v>46155.563225370366</v>
@@ -8990,16 +8901,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -9015,13 +8926,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9031,7 +8942,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B130" s="5">
         <v>46149.1693534375</v>
@@ -9041,16 +8952,16 @@
         <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -9068,13 +8979,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -9083,18 +8994,18 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B131" s="9">
         <v>46149.16935909722</v>
@@ -9104,16 +9015,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9129,13 +9040,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9145,7 +9056,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B132" s="5">
         <v>46149.16936413194</v>
@@ -9155,16 +9066,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9180,13 +9091,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9196,7 +9107,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B133" s="9">
         <v>46155.56332277777</v>
@@ -9206,16 +9117,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9231,13 +9142,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9247,7 +9158,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B134" s="5">
         <v>46155.56333268518</v>
@@ -9257,16 +9168,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9282,13 +9193,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9298,7 +9209,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B135" s="9">
         <v>46149.16936914352</v>
@@ -9308,7 +9219,7 @@
         <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9332,7 +9243,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9345,7 +9256,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46149.169373136574</v>
@@ -9355,16 +9266,16 @@
         <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9382,13 +9293,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9397,18 +9308,18 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B137" s="9">
         <v>46149.169417349534</v>
@@ -9418,7 +9329,7 @@
         <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9445,13 +9356,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>
@@ -9460,13 +9371,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5362,7 +5362,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46212.17235166667</v>
+        <v>46219.16806675926</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>219</v>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46216.83960648148</v>
+        <v>46219.16806951389</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>188</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46216.839607754635</v>
+        <v>46219.16807071759</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>188</v>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46216.83960883102</v>
+        <v>46219.168137569446</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>188</v>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46216.83960983796</v>
+        <v>46219.16813913194</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>188</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46155.59934020833</v>
+        <v>46219.2083027662</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>233</v>
@@ -5681,8 +5681,8 @@
       <c r="R68" s="5">
         <v>46226</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>99</v>
+      <c r="S68" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -741,37 +741,37 @@
     <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
+    <t>1214596725492919</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596725514576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214739697907430</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214739697907431</t>
+  </si>
+  <si>
+    <t>1214596734023783</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596725492919</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596725514576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214739697907430</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214739697907431</t>
-  </si>
-  <si>
-    <t>1214596734023783</t>
-  </si>
-  <si>
-    <t>Armado</t>
   </si>
   <si>
     <t>1214596772418926</t>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46219.16806675926</v>
+        <v>46220.17670241898</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>219</v>
@@ -5406,8 +5406,8 @@
       <c r="R63" s="9">
         <v>46219</v>
       </c>
-      <c r="S63" s="12" t="s">
-        <v>223</v>
+      <c r="S63" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5458,10 +5458,10 @@
         <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5471,7 +5471,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5511,7 +5511,7 @@
         <v>219</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>188</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5564,7 +5564,7 @@
         <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>188</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5617,7 +5617,7 @@
         <v>219</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>188</v>
@@ -5630,7 +5630,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5640,7 +5640,7 @@
         <v>46219.2083027662</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5682,7 +5682,7 @@
         <v>46226</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5730,7 +5730,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>235</v>
@@ -5783,7 +5783,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>235</v>
@@ -5836,7 +5836,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>235</v>
@@ -5889,7 +5889,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>235</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46155.59937984953</v>
+        <v>46220.207858634254</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>241</v>
@@ -5956,8 +5956,8 @@
       <c r="R73" s="9">
         <v>46227</v>
       </c>
-      <c r="S73" s="7" t="s">
-        <v>99</v>
+      <c r="S73" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="372">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -291,6 +291,9 @@
     <t>propuesta nucleo rodete OT 4315</t>
   </si>
   <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4315</t>
   </si>
   <si>
@@ -519,6 +522,9 @@
     <t>Generacion OC Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214596772340045</t>
   </si>
   <si>
@@ -769,9 +775,6 @@
   </si>
   <si>
     <t>Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214596772418926</t>
@@ -2614,7 +2617,7 @@
         <v>46197.50268954861</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.502708472224</v>
+        <v>46223.59153822917</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2623,9 +2626,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I17" s="9">
         <v>46155</v>
       </c>
@@ -2648,7 +2653,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2668,7 +2673,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46149.168784837966</v>
@@ -2677,18 +2682,20 @@
         <v>46204.91285559028</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.56521946759</v>
+        <v>46223.59153387732</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I18" s="5">
         <v>46185</v>
       </c>
@@ -2708,10 +2715,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2731,7 +2738,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="9">
         <v>46149.168789351854</v>
@@ -2740,18 +2747,20 @@
         <v>46204.91289165509</v>
       </c>
       <c r="D19" s="9">
-        <v>46206.56539268518</v>
+        <v>46223.591530624995</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I19" s="9">
         <v>46185</v>
       </c>
@@ -2771,10 +2780,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2794,7 +2803,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46149.16879285879</v>
@@ -2803,18 +2812,20 @@
         <v>46204.91205277778</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.56555653935</v>
+        <v>46223.591527013894</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I20" s="5">
         <v>46185</v>
       </c>
@@ -2834,10 +2845,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2857,7 +2868,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="9">
         <v>46149.16879642361</v>
@@ -2866,18 +2877,20 @@
         <v>46204.911869143514</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.56578831018</v>
+        <v>46223.59152105324</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I21" s="9">
         <v>46185</v>
       </c>
@@ -2897,10 +2910,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2920,7 +2933,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46149.168676875</v>
@@ -2930,7 +2943,7 @@
         <v>46216.87167356482</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2954,7 +2967,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2964,12 +2977,12 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168800127314</v>
@@ -2981,16 +2994,16 @@
         <v>46212.66481476852</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -3008,13 +3021,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="9">
         <v>46157</v>
@@ -3034,7 +3047,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3046,16 +3059,16 @@
         <v>46212.66475459491</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3073,29 +3086,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3107,16 +3120,16 @@
         <v>46212.66478789352</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3134,29 +3147,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3168,16 +3181,16 @@
         <v>46212.66494965278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3195,13 +3208,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3221,7 +3234,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
@@ -3233,16 +3246,16 @@
         <v>46212.664871597226</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3260,29 +3273,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3294,16 +3307,16 @@
         <v>46212.664914918976</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3321,29 +3334,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
@@ -3355,16 +3368,16 @@
         <v>46216.87176959491</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3382,13 +3395,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="9">
         <v>46157</v>
@@ -3408,7 +3421,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3420,16 +3433,16 @@
         <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3447,29 +3460,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
@@ -3481,16 +3494,16 @@
         <v>46216.87164077546</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3508,29 +3521,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3542,16 +3555,16 @@
         <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3569,29 +3582,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3603,16 +3616,16 @@
         <v>46205.60771266204</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3630,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q33" s="9">
         <v>46189</v>
@@ -3656,7 +3669,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3668,16 +3681,16 @@
         <v>46205.60762148148</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3695,29 +3708,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3729,16 +3742,16 @@
         <v>46205.60768407407</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3756,29 +3769,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3790,16 +3803,16 @@
         <v>46205.608947719906</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3817,10 +3830,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3843,7 +3856,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3855,16 +3868,16 @@
         <v>46205.60888410879</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3882,13 +3895,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3898,7 +3911,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3910,16 +3923,16 @@
         <v>46205.60892006944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3937,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3953,7 +3966,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3962,19 +3975,19 @@
         <v>46205.843624166664</v>
       </c>
       <c r="D39" s="9">
-        <v>46205.84364175926</v>
+        <v>46223.2074775463</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -3992,10 +4005,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4006,8 +4019,8 @@
       <c r="R39" s="9">
         <v>46230</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>99</v>
+      <c r="S39" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4018,7 +4031,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4030,16 +4043,16 @@
         <v>46205.843509259255</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4057,13 +4070,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4073,7 +4086,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4085,16 +4098,16 @@
         <v>46205.84357975694</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4112,13 +4125,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4128,7 +4141,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4138,16 +4151,16 @@
         <v>46205.843587766205</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4165,10 +4178,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4181,7 +4194,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4193,16 +4206,16 @@
         <v>46211.19248402778</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4220,10 +4233,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4246,7 +4259,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4258,16 +4271,16 @@
         <v>46205.613227546295</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4285,13 +4298,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4301,7 +4314,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4313,16 +4326,16 @@
         <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4340,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4356,7 +4369,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4366,7 +4379,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4390,7 +4403,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4400,12 +4413,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4417,16 +4430,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4444,13 +4457,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4470,7 +4483,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4482,16 +4495,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4509,13 +4522,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4535,7 +4548,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4547,16 +4560,16 @@
         <v>46199.77907827546</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4572,13 +4585,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4587,7 +4600,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4598,7 +4611,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4608,16 +4621,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4635,10 +4648,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4650,18 +4663,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4671,16 +4684,16 @@
         <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4696,13 +4709,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4712,7 +4725,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4722,16 +4735,16 @@
         <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4747,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4763,7 +4776,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4773,16 +4786,16 @@
         <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4798,13 +4811,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4814,7 +4827,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4824,16 +4837,16 @@
         <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4849,13 +4862,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4865,7 +4878,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4877,7 +4890,7 @@
         <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4901,7 +4914,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4918,7 +4931,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4930,16 +4943,16 @@
         <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4957,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4983,7 +4996,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -4995,16 +5008,16 @@
         <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -5022,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5048,7 +5061,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5060,16 +5073,16 @@
         <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5087,13 +5100,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5113,7 +5126,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5125,16 +5138,16 @@
         <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5152,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5178,7 +5191,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5190,16 +5203,16 @@
         <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5217,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5243,7 +5256,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5255,16 +5268,16 @@
         <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5282,13 +5295,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>212</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5308,7 +5321,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5318,7 +5331,7 @@
         <v>46155.56887822917</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5342,7 +5355,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5355,7 +5368,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5365,16 +5378,16 @@
         <v>46220.17670241898</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5392,13 +5405,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5413,12 +5426,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5428,16 +5441,16 @@
         <v>46219.16806951389</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5455,13 +5468,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5471,7 +5484,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5481,16 +5494,16 @@
         <v>46219.16807071759</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5508,13 +5521,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5524,7 +5537,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5534,16 +5547,16 @@
         <v>46219.168137569446</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5561,13 +5574,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5577,7 +5590,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5587,16 +5600,16 @@
         <v>46219.16813913194</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5614,13 +5627,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5630,7 +5643,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5640,16 +5653,16 @@
         <v>46219.2083027662</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5667,13 +5680,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5682,18 +5695,18 @@
         <v>46226</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5703,16 +5716,16 @@
         <v>46199.779078356485</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5730,13 +5743,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5746,7 +5759,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5756,16 +5769,16 @@
         <v>46199.77907907407</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5783,13 +5796,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5799,7 +5812,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5809,16 +5822,16 @@
         <v>46199.77908222222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5836,13 +5849,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5852,7 +5865,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5862,16 +5875,16 @@
         <v>46199.7790828588</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5889,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5905,7 +5918,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5915,16 +5928,16 @@
         <v>46220.207858634254</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5942,13 +5955,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -5957,18 +5970,18 @@
         <v>46227</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -5978,16 +5991,16 @@
         <v>46199.77907962963</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -6005,13 +6018,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6021,7 +6034,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -6031,16 +6044,16 @@
         <v>46199.77908010417</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6058,13 +6071,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6074,7 +6087,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6084,16 +6097,16 @@
         <v>46199.779083437505</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6111,13 +6124,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6127,7 +6140,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6137,16 +6150,16 @@
         <v>46199.779083877314</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6164,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6180,7 +6193,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6190,7 +6203,7 @@
         <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6214,7 +6227,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6224,12 +6237,12 @@
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
       <c r="U78" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6241,16 +6254,16 @@
         <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6266,13 +6279,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6292,7 +6305,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6304,16 +6317,16 @@
         <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6331,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6357,7 +6370,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6369,16 +6382,16 @@
         <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6396,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6422,7 +6435,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6432,16 +6445,16 @@
         <v>46205.84359559028</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6459,13 +6472,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6474,18 +6487,18 @@
         <v>46231</v>
       </c>
       <c r="S82" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6495,7 +6508,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6519,7 +6532,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6532,25 +6545,27 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46155.60047521991</v>
+        <v>46223.592199652776</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I84" s="5">
         <v>46230</v>
       </c>
@@ -6567,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6582,36 +6597,38 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46149.16916685185</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46155.60002515046</v>
+        <v>46223.59164138889</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I85" s="9">
         <v>46230</v>
       </c>
@@ -6628,10 +6645,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6644,25 +6661,27 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46149.16917037037</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46155.60002232638</v>
+        <v>46223.591640729166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I86" s="5">
         <v>46230</v>
       </c>
@@ -6679,10 +6698,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6695,25 +6714,27 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46155.5624656713</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46155.60026604167</v>
+        <v>46223.59164002315</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I87" s="9">
         <v>46230</v>
       </c>
@@ -6730,13 +6751,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6746,25 +6767,27 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46155.562495266204</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46155.600359212964</v>
+        <v>46223.59163928241</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I88" s="5">
         <v>46230</v>
       </c>
@@ -6781,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6797,25 +6820,27 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46149.16917405093</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46213.50801929398</v>
+        <v>46223.59219898148</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I89" s="9">
         <v>46237</v>
       </c>
@@ -6832,13 +6857,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6847,18 +6872,18 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46149.169178321754</v>
@@ -6867,18 +6892,20 @@
         <v>46213.50800253473</v>
       </c>
       <c r="D90" s="5">
-        <v>46213.508005578704</v>
+        <v>46223.59174438658</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
         <v>46237</v>
@@ -6893,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6909,7 +6936,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46149.169183148144</v>
@@ -6918,18 +6945,20 @@
         <v>46213.50801122685</v>
       </c>
       <c r="D91" s="9">
-        <v>46213.508012962964</v>
+        <v>46223.591741261574</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
         <v>46237</v>
@@ -6944,13 +6973,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6960,25 +6989,27 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46155.56256662037</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46212.66505967593</v>
+        <v>46223.59173454861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46237</v>
@@ -6993,13 +7024,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7009,25 +7040,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
         <v>46155.56257849537</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46212.66506008102</v>
+        <v>46223.59173388889</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
         <v>46237</v>
@@ -7042,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7058,25 +7091,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46149.169187962965</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46213.50808509259</v>
+        <v>46223.59219834491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I94" s="5">
         <v>46238</v>
       </c>
@@ -7093,13 +7128,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7108,18 +7143,18 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
         <v>46149.1691919213</v>
@@ -7128,18 +7163,20 @@
         <v>46213.508068599534</v>
       </c>
       <c r="D95" s="9">
-        <v>46213.50807009259</v>
+        <v>46223.5918337037</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
         <v>46238</v>
@@ -7154,13 +7191,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7170,7 +7207,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46149.16919760416</v>
@@ -7179,18 +7216,20 @@
         <v>46213.50807769676</v>
       </c>
       <c r="D96" s="5">
-        <v>46213.50808212963</v>
+        <v>46223.591830219906</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
         <v>46238</v>
@@ -7205,13 +7244,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7221,25 +7260,27 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46155.562660428244</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46212.665048993054</v>
+        <v>46223.59182357639</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
         <v>46238</v>
@@ -7254,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7270,25 +7311,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46155.56267193287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46212.665049456016</v>
+        <v>46223.591822939816</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
         <v>46238</v>
@@ -7303,13 +7346,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7319,25 +7362,27 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="9">
         <v>46149.169203125</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46155.60094263889</v>
+        <v>46223.5921977199</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I99" s="9">
         <v>46239</v>
       </c>
@@ -7354,13 +7399,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7369,36 +7414,38 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46149.16920694444</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46216.87182809028</v>
+        <v>46223.59191454861</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46239</v>
@@ -7413,13 +7460,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7429,25 +7476,27 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
         <v>46149.16921202546</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46216.87182944444</v>
+        <v>46223.591913842596</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
         <v>46239</v>
@@ -7462,13 +7511,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7478,25 +7527,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46155.562741851856</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46216.87183001157</v>
+        <v>46223.59191307871</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
         <v>46239</v>
@@ -7511,13 +7562,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7527,25 +7578,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46155.562755046296</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46216.871830648146</v>
+        <v>46223.59191234954</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46239</v>
@@ -7560,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7576,25 +7629,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
         <v>46149.16921689815</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46155.60109780093</v>
+        <v>46223.59219704861</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I104" s="5">
         <v>46240</v>
       </c>
@@ -7611,13 +7666,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7626,36 +7681,38 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
         <v>46149.169220717595</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46155.60106565972</v>
+        <v>46223.59202306713</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I105" s="9">
         <v>46240</v>
       </c>
@@ -7672,13 +7729,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7688,25 +7745,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46149.16922577546</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46155.601062546295</v>
+        <v>46223.59202241898</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I106" s="5">
         <v>46240</v>
       </c>
@@ -7723,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7739,25 +7798,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
         <v>46155.56285743056</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46155.60105936343</v>
+        <v>46223.59202165509</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I107" s="9">
         <v>46240</v>
       </c>
@@ -7774,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7790,25 +7851,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46155.56284611111</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46155.60105565972</v>
+        <v>46223.59202096065</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I108" s="5">
         <v>46240</v>
       </c>
@@ -7825,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7841,25 +7904,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B109" s="9">
         <v>46149.169270370374</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46155.601273506945</v>
+        <v>46223.59219642361</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I109" s="9">
         <v>46244</v>
       </c>
@@ -7876,13 +7941,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7891,36 +7956,38 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46149.16928524306</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46155.60133046296</v>
+        <v>46223.592111550926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
         <v>46244</v>
@@ -7935,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7951,25 +8018,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
         <v>46149.16929128472</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46155.60132649305</v>
+        <v>46223.59211092592</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9">
         <v>46244</v>
@@ -7984,13 +8053,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8000,25 +8069,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46155.562937361115</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46155.60132342593</v>
+        <v>46223.59211032407</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
         <v>46244</v>
@@ -8033,13 +8104,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8049,25 +8120,27 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B113" s="9">
         <v>46155.56294952546</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46155.60131890046</v>
+        <v>46223.59210969908</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
         <v>46244</v>
@@ -8082,13 +8155,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8098,7 +8171,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46149.16929695602</v>
@@ -8108,7 +8181,7 @@
         <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8132,7 +8205,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8145,7 +8218,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B115" s="9">
         <v>46149.169301041664</v>
@@ -8155,16 +8228,16 @@
         <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8180,13 +8253,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8195,18 +8268,18 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46149.1693071412</v>
@@ -8216,16 +8289,16 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8241,13 +8314,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8257,7 +8330,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B117" s="9">
         <v>46149.16931233797</v>
@@ -8267,16 +8340,16 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8292,13 +8365,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8308,7 +8381,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
         <v>46155.56303070602</v>
@@ -8318,16 +8391,16 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8343,13 +8416,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8359,7 +8432,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B119" s="9">
         <v>46155.56306011574</v>
@@ -8369,16 +8442,16 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8394,13 +8467,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8410,25 +8483,27 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46149.1693175</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46155.6016600463</v>
+        <v>46223.59234582176</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I120" s="5">
         <v>46246</v>
       </c>
@@ -8445,13 +8520,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8460,36 +8535,38 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
         <v>46149.16932247685</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46155.601629756944</v>
+        <v>46223.592296180555</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I121" s="9">
         <v>46246</v>
       </c>
@@ -8506,13 +8583,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8522,25 +8599,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
         <v>46149.16932829861</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46155.60162688658</v>
+        <v>46223.5922953125</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I122" s="5">
         <v>46246</v>
       </c>
@@ -8557,13 +8636,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8573,25 +8652,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
         <v>46155.56313421296</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46155.601624421295</v>
+        <v>46223.592294675924</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I123" s="9">
         <v>46246</v>
       </c>
@@ -8608,13 +8689,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8624,25 +8705,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B124" s="5">
         <v>46155.5631459375</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46155.601620671296</v>
+        <v>46223.592294050926</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I124" s="5">
         <v>46246</v>
       </c>
@@ -8659,13 +8742,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8675,7 +8758,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B125" s="9">
         <v>46149.16933366898</v>
@@ -8685,16 +8768,16 @@
         <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8712,13 +8795,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8727,18 +8810,18 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B126" s="5">
         <v>46149.16933884259</v>
@@ -8748,16 +8831,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8773,13 +8856,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8789,7 +8872,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B127" s="9">
         <v>46149.16934681713</v>
@@ -8799,16 +8882,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8824,13 +8907,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8840,7 +8923,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B128" s="5">
         <v>46155.56323461806</v>
@@ -8850,16 +8933,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8875,13 +8958,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8891,7 +8974,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B129" s="9">
         <v>46155.563225370366</v>
@@ -8901,16 +8984,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -8926,13 +9009,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8942,7 +9025,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B130" s="5">
         <v>46149.1693534375</v>
@@ -8952,16 +9035,16 @@
         <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -8979,13 +9062,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -8994,18 +9077,18 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B131" s="9">
         <v>46149.16935909722</v>
@@ -9015,16 +9098,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9040,13 +9123,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9056,7 +9139,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B132" s="5">
         <v>46149.16936413194</v>
@@ -9066,16 +9149,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9091,13 +9174,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9107,7 +9190,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B133" s="9">
         <v>46155.56332277777</v>
@@ -9117,16 +9200,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9142,13 +9225,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9158,7 +9241,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B134" s="5">
         <v>46155.56333268518</v>
@@ -9168,16 +9251,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9193,13 +9276,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9209,7 +9292,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B135" s="9">
         <v>46149.16936914352</v>
@@ -9219,7 +9302,7 @@
         <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9243,7 +9326,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9256,7 +9339,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B136" s="5">
         <v>46149.169373136574</v>
@@ -9266,16 +9349,16 @@
         <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9293,13 +9376,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9308,18 +9391,18 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B137" s="9">
         <v>46149.169417349534</v>
@@ -9329,7 +9412,7 @@
         <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9356,13 +9439,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>
@@ -9371,13 +9454,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46205.84359559028</v>
+        <v>46224.19576207176</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>261</v>
@@ -6486,8 +6486,8 @@
       <c r="R82" s="5">
         <v>46231</v>
       </c>
-      <c r="S82" s="7" t="s">
-        <v>100</v>
+      <c r="S82" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46155.56887822917</v>
+        <v>46224.67388769676</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5373,9 +5373,11 @@
       <c r="B63" s="9">
         <v>46149.169042442125</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46224.67373001158</v>
+      </c>
       <c r="D63" s="9">
-        <v>46220.17670241898</v>
+        <v>46224.87838504629</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -5423,10 +5425,10 @@
         <v>33</v>
       </c>
       <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5436,9 +5438,11 @@
       <c r="B64" s="5">
         <v>46149.169049375</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46224.67369833333</v>
+      </c>
       <c r="D64" s="5">
-        <v>46219.16806951389</v>
+        <v>46224.673700625004</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>190</v>
@@ -5489,9 +5493,11 @@
       <c r="B65" s="9">
         <v>46149.16905616898</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46224.67370453704</v>
+      </c>
       <c r="D65" s="9">
-        <v>46219.16807071759</v>
+        <v>46224.67370611111</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>190</v>
@@ -5542,9 +5548,11 @@
       <c r="B66" s="5">
         <v>46155.562074166664</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46224.67371016204</v>
+      </c>
       <c r="D66" s="5">
-        <v>46219.168137569446</v>
+        <v>46224.67371170138</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>190</v>
@@ -5595,9 +5603,11 @@
       <c r="B67" s="9">
         <v>46155.562095416666</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46224.673715868055</v>
+      </c>
       <c r="D67" s="9">
-        <v>46219.16813913194</v>
+        <v>46224.67371741898</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>190</v>
@@ -5648,9 +5658,11 @@
       <c r="B68" s="5">
         <v>46149.169104699075</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46224.67387799769</v>
+      </c>
       <c r="D68" s="5">
-        <v>46219.2083027662</v>
+        <v>46224.673890763894</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5698,10 +5710,10 @@
         <v>150</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5711,9 +5723,11 @@
       <c r="B69" s="9">
         <v>46149.1691096412</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46224.6738443287</v>
+      </c>
       <c r="D69" s="9">
-        <v>46199.779078356485</v>
+        <v>46224.67384578704</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>190</v>
@@ -5764,9 +5778,11 @@
       <c r="B70" s="5">
         <v>46149.16911491899</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46224.673848425926</v>
+      </c>
       <c r="D70" s="5">
-        <v>46199.77907907407</v>
+        <v>46224.67385033565</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5817,9 +5833,11 @@
       <c r="B71" s="9">
         <v>46155.562225625</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9">
+        <v>46224.67385324074</v>
+      </c>
       <c r="D71" s="9">
-        <v>46199.77908222222</v>
+        <v>46224.67385497685</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -5870,9 +5888,11 @@
       <c r="B72" s="5">
         <v>46155.56224557871</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46224.67386333333</v>
+      </c>
       <c r="D72" s="5">
-        <v>46199.7790828588</v>
+        <v>46224.67386524305</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -5988,7 +6008,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46199.77907962963</v>
+        <v>46224.67385076389</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6041,7 +6061,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.77908010417</v>
+        <v>46224.67386304398</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6094,7 +6114,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46199.779083437505</v>
+        <v>46224.67386091435</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6147,7 +6167,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46199.779083877314</v>
+        <v>46224.67387116898</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5377,7 +5377,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46224.87838504629</v>
+        <v>46225.00960723379</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5377,7 +5377,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46225.00960723379</v>
+        <v>46225.5894531713</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="373">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -291,6 +291,9 @@
     <t>propuesta nucleo rodete OT 4315</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -744,7 +747,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -2629,7 +2632,7 @@
         <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="9">
         <v>46155</v>
@@ -2653,7 +2656,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="9">
         <v>46155</v>
@@ -2673,7 +2676,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46149.168784837966</v>
@@ -2685,7 +2688,7 @@
         <v>46223.59153387732</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2694,7 +2697,7 @@
         <v>73</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46185</v>
@@ -2715,10 +2718,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46185</v>
@@ -2738,7 +2741,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46149.168789351854</v>
@@ -2750,7 +2753,7 @@
         <v>46223.591530624995</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2759,7 +2762,7 @@
         <v>73</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="9">
         <v>46185</v>
@@ -2780,10 +2783,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46185</v>
@@ -2803,7 +2806,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46149.16879285879</v>
@@ -2815,7 +2818,7 @@
         <v>46223.591527013894</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2824,7 +2827,7 @@
         <v>73</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46185</v>
@@ -2845,10 +2848,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46185</v>
@@ -2868,7 +2871,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46149.16879642361</v>
@@ -2880,7 +2883,7 @@
         <v>46223.59152105324</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2889,7 +2892,7 @@
         <v>73</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" s="9">
         <v>46185</v>
@@ -2910,10 +2913,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46185</v>
@@ -2933,7 +2936,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46149.168676875</v>
@@ -2943,7 +2946,7 @@
         <v>46216.87167356482</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2967,7 +2970,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2977,12 +2980,12 @@
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
       <c r="U22" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46149.168800127314</v>
@@ -2994,16 +2997,16 @@
         <v>46212.66481476852</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46157</v>
@@ -3021,13 +3024,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="9">
         <v>46157</v>
@@ -3047,7 +3050,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46149.168804155095</v>
@@ -3059,16 +3062,16 @@
         <v>46212.66475459491</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3086,29 +3089,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46149.16880861111</v>
@@ -3120,16 +3123,16 @@
         <v>46212.66478789352</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46161</v>
@@ -3147,29 +3150,29 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46149.16881337963</v>
@@ -3181,16 +3184,16 @@
         <v>46212.66494965278</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3208,13 +3211,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3234,7 +3237,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46149.16881752315</v>
@@ -3246,16 +3249,16 @@
         <v>46212.664871597226</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46157</v>
@@ -3273,29 +3276,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46149.168821851854</v>
@@ -3307,16 +3310,16 @@
         <v>46212.664914918976</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46161</v>
@@ -3334,29 +3337,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46149.1688262963</v>
@@ -3368,16 +3371,16 @@
         <v>46216.87176959491</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46157</v>
@@ -3395,13 +3398,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="9">
         <v>46157</v>
@@ -3421,7 +3424,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46149.168830532406</v>
@@ -3433,16 +3436,16 @@
         <v>46199.75283171296</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46157</v>
@@ -3460,29 +3463,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46149.1688349537</v>
@@ -3494,16 +3497,16 @@
         <v>46216.87164077546</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46168</v>
@@ -3521,29 +3524,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46149.16884</v>
@@ -3555,16 +3558,16 @@
         <v>46199.752879155094</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46168</v>
@@ -3582,29 +3585,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46149.168844375</v>
@@ -3616,16 +3619,16 @@
         <v>46205.60771266204</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46189</v>
@@ -3643,13 +3646,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="9">
         <v>46189</v>
@@ -3669,7 +3672,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46149.16884893518</v>
@@ -3681,16 +3684,16 @@
         <v>46205.60762148148</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46189</v>
@@ -3708,29 +3711,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46149.16885364584</v>
@@ -3742,16 +3745,16 @@
         <v>46205.60768407407</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46191</v>
@@ -3769,29 +3772,29 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46149.1688584375</v>
@@ -3803,16 +3806,16 @@
         <v>46205.608947719906</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46189</v>
@@ -3830,10 +3833,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3856,7 +3859,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46149.16891136574</v>
@@ -3868,16 +3871,16 @@
         <v>46205.60888410879</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46189</v>
@@ -3895,13 +3898,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3911,7 +3914,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46149.168917256946</v>
@@ -3923,16 +3926,16 @@
         <v>46205.60892006944</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46191</v>
@@ -3950,13 +3953,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3966,7 +3969,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46149.16892260416</v>
@@ -3978,16 +3981,16 @@
         <v>46223.2074775463</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46189</v>
@@ -4005,10 +4008,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -4020,7 +4023,7 @@
         <v>46230</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4031,7 +4034,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4043,16 +4046,16 @@
         <v>46205.843509259255</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46189</v>
@@ -4070,13 +4073,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4086,7 +4089,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4098,16 +4101,16 @@
         <v>46205.84357975694</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46198</v>
@@ -4125,13 +4128,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4141,7 +4144,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4151,16 +4154,16 @@
         <v>46205.843587766205</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4178,10 +4181,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4194,7 +4197,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4206,16 +4209,16 @@
         <v>46211.19248402778</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46189</v>
@@ -4233,10 +4236,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4259,7 +4262,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4271,16 +4274,16 @@
         <v>46205.613227546295</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46189</v>
@@ -4298,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4326,16 +4329,16 @@
         <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46191</v>
@@ -4353,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4369,7 +4372,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4379,7 +4382,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4403,7 +4406,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4413,12 +4416,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4430,16 +4433,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4457,13 +4460,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4495,16 +4498,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4522,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4548,7 +4551,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4560,16 +4563,16 @@
         <v>46199.77907827546</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4585,13 +4588,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4600,7 +4603,7 @@
         <v>46153</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4611,7 +4614,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4621,16 +4624,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4648,10 +4651,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4663,18 +4666,18 @@
         <v>46241</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4684,16 +4687,16 @@
         <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4709,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4725,7 +4728,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4735,16 +4738,16 @@
         <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4760,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4776,7 +4779,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4786,16 +4789,16 @@
         <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4811,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4827,7 +4830,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4837,16 +4840,16 @@
         <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4862,13 +4865,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4878,7 +4881,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4890,7 +4893,7 @@
         <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4914,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4931,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4943,16 +4946,16 @@
         <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4970,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -5008,16 +5011,16 @@
         <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -5035,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5061,7 +5064,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5073,16 +5076,16 @@
         <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5100,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5138,16 +5141,16 @@
         <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5165,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5191,7 +5194,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5203,16 +5206,16 @@
         <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5256,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5268,16 +5271,16 @@
         <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5295,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5321,7 +5324,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5331,7 +5334,7 @@
         <v>46224.67388769676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5355,7 +5358,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5368,7 +5371,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5377,19 +5380,19 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46225.5894531713</v>
+        <v>46225.86188855324</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5407,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5433,7 +5436,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5445,16 +5448,16 @@
         <v>46224.673700625004</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5472,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5488,7 +5491,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5500,16 +5503,16 @@
         <v>46224.67370611111</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5527,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5555,16 +5558,16 @@
         <v>46224.67371170138</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5582,13 +5585,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5598,7 +5601,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5610,16 +5613,16 @@
         <v>46224.67371741898</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5637,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5653,7 +5656,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5665,16 +5668,16 @@
         <v>46224.673890763894</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5692,13 +5695,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5707,7 +5710,7 @@
         <v>46226</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5718,7 +5721,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5730,16 +5733,16 @@
         <v>46224.67384578704</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5757,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5773,7 +5776,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5785,16 +5788,16 @@
         <v>46224.67385033565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5812,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5828,7 +5831,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5840,16 +5843,16 @@
         <v>46224.67385497685</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5867,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5883,7 +5886,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5895,16 +5898,16 @@
         <v>46224.67386524305</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5922,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5938,7 +5941,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5948,16 +5951,16 @@
         <v>46220.207858634254</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5975,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -5990,18 +5993,18 @@
         <v>46227</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -6011,16 +6014,16 @@
         <v>46224.67385076389</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -6038,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6054,7 +6057,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -6064,16 +6067,16 @@
         <v>46224.67386304398</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6091,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6117,16 +6120,16 @@
         <v>46224.67386091435</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6144,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6160,7 +6163,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6170,16 +6173,16 @@
         <v>46224.67387116898</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6197,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6213,7 +6216,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6223,7 +6226,7 @@
         <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6247,7 +6250,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6257,12 +6260,12 @@
       <c r="S78" s="6"/>
       <c r="T78" s="6"/>
       <c r="U78" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6274,16 +6277,16 @@
         <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6299,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6337,16 +6340,16 @@
         <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6364,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6390,7 +6393,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6402,16 +6405,16 @@
         <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6429,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6455,7 +6458,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6465,16 +6468,16 @@
         <v>46224.19576207176</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6492,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6507,18 +6510,18 @@
         <v>46231</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6528,7 +6531,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6552,7 +6555,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6565,7 +6568,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
@@ -6575,7 +6578,7 @@
         <v>46223.592199652776</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6584,7 +6587,7 @@
         <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I84" s="5">
         <v>46230</v>
@@ -6602,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6617,18 +6620,18 @@
         <v>46234</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B85" s="9">
         <v>46149.16916685185</v>
@@ -6638,7 +6641,7 @@
         <v>46223.59164138889</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6647,7 +6650,7 @@
         <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I85" s="9">
         <v>46230</v>
@@ -6665,10 +6668,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6681,7 +6684,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
         <v>46149.16917037037</v>
@@ -6691,7 +6694,7 @@
         <v>46223.591640729166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6700,7 +6703,7 @@
         <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I86" s="5">
         <v>46230</v>
@@ -6718,10 +6721,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6734,7 +6737,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
         <v>46155.5624656713</v>
@@ -6744,7 +6747,7 @@
         <v>46223.59164002315</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6753,7 +6756,7 @@
         <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I87" s="9">
         <v>46230</v>
@@ -6771,13 +6774,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6787,7 +6790,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
         <v>46155.562495266204</v>
@@ -6797,7 +6800,7 @@
         <v>46223.59163928241</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6806,7 +6809,7 @@
         <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I88" s="5">
         <v>46230</v>
@@ -6824,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6840,7 +6843,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46149.16917405093</v>
@@ -6850,7 +6853,7 @@
         <v>46223.59219898148</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6859,7 +6862,7 @@
         <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I89" s="9">
         <v>46237</v>
@@ -6877,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6892,18 +6895,18 @@
         <v>46237</v>
       </c>
       <c r="S89" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46149.169178321754</v>
@@ -6915,7 +6918,7 @@
         <v>46223.59174438658</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6924,7 +6927,7 @@
         <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6940,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6956,7 +6959,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
         <v>46149.169183148144</v>
@@ -6968,7 +6971,7 @@
         <v>46223.591741261574</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6977,7 +6980,7 @@
         <v>73</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6993,13 +6996,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7009,7 +7012,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46155.56256662037</v>
@@ -7019,7 +7022,7 @@
         <v>46223.59173454861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7028,7 +7031,7 @@
         <v>73</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -7044,13 +7047,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7060,7 +7063,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B93" s="9">
         <v>46155.56257849537</v>
@@ -7070,7 +7073,7 @@
         <v>46223.59173388889</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7079,7 +7082,7 @@
         <v>73</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -7095,13 +7098,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7111,7 +7114,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B94" s="5">
         <v>46149.169187962965</v>
@@ -7121,7 +7124,7 @@
         <v>46223.59219834491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7130,7 +7133,7 @@
         <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I94" s="5">
         <v>46238</v>
@@ -7148,13 +7151,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7163,18 +7166,18 @@
         <v>46238</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B95" s="9">
         <v>46149.1691919213</v>
@@ -7186,7 +7189,7 @@
         <v>46223.5918337037</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7195,7 +7198,7 @@
         <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -7211,13 +7214,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7227,7 +7230,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
         <v>46149.16919760416</v>
@@ -7239,7 +7242,7 @@
         <v>46223.591830219906</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7248,7 +7251,7 @@
         <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7264,13 +7267,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7280,7 +7283,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="9">
         <v>46155.562660428244</v>
@@ -7290,7 +7293,7 @@
         <v>46223.59182357639</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7299,7 +7302,7 @@
         <v>73</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="9">
@@ -7315,13 +7318,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7331,7 +7334,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46155.56267193287</v>
@@ -7341,7 +7344,7 @@
         <v>46223.591822939816</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7350,7 +7353,7 @@
         <v>73</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7366,13 +7369,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7382,7 +7385,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B99" s="9">
         <v>46149.169203125</v>
@@ -7392,7 +7395,7 @@
         <v>46223.5921977199</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7401,7 +7404,7 @@
         <v>73</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I99" s="9">
         <v>46239</v>
@@ -7419,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7434,18 +7437,18 @@
         <v>46239</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B100" s="5">
         <v>46149.16920694444</v>
@@ -7455,7 +7458,7 @@
         <v>46223.59191454861</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7464,7 +7467,7 @@
         <v>73</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7480,13 +7483,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7496,7 +7499,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="9">
         <v>46149.16921202546</v>
@@ -7506,7 +7509,7 @@
         <v>46223.591913842596</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7515,7 +7518,7 @@
         <v>73</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7531,13 +7534,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7547,7 +7550,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46155.562741851856</v>
@@ -7557,7 +7560,7 @@
         <v>46223.59191307871</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7566,7 +7569,7 @@
         <v>73</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7582,13 +7585,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7598,7 +7601,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46155.562755046296</v>
@@ -7608,7 +7611,7 @@
         <v>46223.59191234954</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7617,7 +7620,7 @@
         <v>73</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7633,13 +7636,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7649,7 +7652,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46149.16921689815</v>
@@ -7659,7 +7662,7 @@
         <v>46223.59219704861</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7668,7 +7671,7 @@
         <v>73</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I104" s="5">
         <v>46240</v>
@@ -7686,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7701,18 +7704,18 @@
         <v>46240</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
         <v>46149.169220717595</v>
@@ -7722,7 +7725,7 @@
         <v>46223.59202306713</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7731,7 +7734,7 @@
         <v>73</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I105" s="9">
         <v>46240</v>
@@ -7749,13 +7752,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7765,7 +7768,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46149.16922577546</v>
@@ -7775,7 +7778,7 @@
         <v>46223.59202241898</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7784,7 +7787,7 @@
         <v>73</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I106" s="5">
         <v>46240</v>
@@ -7802,13 +7805,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7818,7 +7821,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B107" s="9">
         <v>46155.56285743056</v>
@@ -7828,7 +7831,7 @@
         <v>46223.59202165509</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7837,7 +7840,7 @@
         <v>73</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I107" s="9">
         <v>46240</v>
@@ -7855,13 +7858,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7871,7 +7874,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B108" s="5">
         <v>46155.56284611111</v>
@@ -7881,7 +7884,7 @@
         <v>46223.59202096065</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7890,7 +7893,7 @@
         <v>73</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I108" s="5">
         <v>46240</v>
@@ -7908,13 +7911,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7924,7 +7927,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B109" s="9">
         <v>46149.169270370374</v>
@@ -7934,7 +7937,7 @@
         <v>46223.59219642361</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7943,7 +7946,7 @@
         <v>73</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I109" s="9">
         <v>46244</v>
@@ -7961,13 +7964,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7976,18 +7979,18 @@
         <v>46244</v>
       </c>
       <c r="S109" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
         <v>46149.16928524306</v>
@@ -7997,7 +8000,7 @@
         <v>46223.592111550926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8006,7 +8009,7 @@
         <v>73</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I110" s="6"/>
       <c r="J110" s="5">
@@ -8022,13 +8025,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8038,7 +8041,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B111" s="9">
         <v>46149.16929128472</v>
@@ -8048,7 +8051,7 @@
         <v>46223.59211092592</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8057,7 +8060,7 @@
         <v>73</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I111" s="10"/>
       <c r="J111" s="9">
@@ -8073,13 +8076,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8089,7 +8092,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B112" s="5">
         <v>46155.562937361115</v>
@@ -8099,7 +8102,7 @@
         <v>46223.59211032407</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8108,7 +8111,7 @@
         <v>73</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8124,13 +8127,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8140,7 +8143,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B113" s="9">
         <v>46155.56294952546</v>
@@ -8150,7 +8153,7 @@
         <v>46223.59210969908</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8159,7 +8162,7 @@
         <v>73</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I113" s="10"/>
       <c r="J113" s="9">
@@ -8175,13 +8178,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8191,7 +8194,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46149.16929695602</v>
@@ -8201,7 +8204,7 @@
         <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8225,7 +8228,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8238,7 +8241,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B115" s="9">
         <v>46149.169301041664</v>
@@ -8248,16 +8251,16 @@
         <v>46155.60146953704</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8273,13 +8276,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8288,18 +8291,18 @@
         <v>46245</v>
       </c>
       <c r="S115" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
         <v>46149.1693071412</v>
@@ -8309,16 +8312,16 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8334,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8350,7 +8353,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B117" s="9">
         <v>46149.16931233797</v>
@@ -8360,16 +8363,16 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8385,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8401,7 +8404,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B118" s="5">
         <v>46155.56303070602</v>
@@ -8411,16 +8414,16 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8436,13 +8439,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8452,7 +8455,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B119" s="9">
         <v>46155.56306011574</v>
@@ -8462,16 +8465,16 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8487,13 +8490,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8503,7 +8506,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B120" s="5">
         <v>46149.1693175</v>
@@ -8513,7 +8516,7 @@
         <v>46223.59234582176</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8522,7 +8525,7 @@
         <v>73</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I120" s="5">
         <v>46246</v>
@@ -8540,13 +8543,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8555,18 +8558,18 @@
         <v>46246</v>
       </c>
       <c r="S120" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B121" s="9">
         <v>46149.16932247685</v>
@@ -8576,7 +8579,7 @@
         <v>46223.592296180555</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8585,7 +8588,7 @@
         <v>73</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I121" s="9">
         <v>46246</v>
@@ -8603,13 +8606,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8619,7 +8622,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B122" s="5">
         <v>46149.16932829861</v>
@@ -8629,7 +8632,7 @@
         <v>46223.5922953125</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8638,7 +8641,7 @@
         <v>73</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I122" s="5">
         <v>46246</v>
@@ -8656,13 +8659,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8672,7 +8675,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B123" s="9">
         <v>46155.56313421296</v>
@@ -8682,7 +8685,7 @@
         <v>46223.592294675924</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8691,7 +8694,7 @@
         <v>73</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I123" s="9">
         <v>46246</v>
@@ -8709,13 +8712,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8725,7 +8728,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B124" s="5">
         <v>46155.5631459375</v>
@@ -8735,7 +8738,7 @@
         <v>46223.592294050926</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8744,7 +8747,7 @@
         <v>73</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I124" s="5">
         <v>46246</v>
@@ -8762,13 +8765,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8778,7 +8781,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B125" s="9">
         <v>46149.16933366898</v>
@@ -8788,16 +8791,16 @@
         <v>46155.60192047454</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8815,13 +8818,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8830,18 +8833,18 @@
         <v>46247</v>
       </c>
       <c r="S125" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B126" s="5">
         <v>46149.16933884259</v>
@@ -8851,16 +8854,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8876,13 +8879,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8892,7 +8895,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B127" s="9">
         <v>46149.16934681713</v>
@@ -8902,16 +8905,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8927,13 +8930,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8943,7 +8946,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B128" s="5">
         <v>46155.56323461806</v>
@@ -8953,16 +8956,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8978,13 +8981,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8994,7 +8997,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B129" s="9">
         <v>46155.563225370366</v>
@@ -9004,16 +9007,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -9029,13 +9032,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9045,7 +9048,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B130" s="5">
         <v>46149.1693534375</v>
@@ -9055,16 +9058,16 @@
         <v>46155.60216496528</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -9082,13 +9085,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -9097,18 +9100,18 @@
         <v>46248</v>
       </c>
       <c r="S130" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B131" s="9">
         <v>46149.16935909722</v>
@@ -9118,16 +9121,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9143,13 +9146,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9159,7 +9162,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B132" s="5">
         <v>46149.16936413194</v>
@@ -9169,16 +9172,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9194,13 +9197,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9210,7 +9213,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B133" s="9">
         <v>46155.56332277777</v>
@@ -9220,16 +9223,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9245,13 +9248,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9261,7 +9264,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B134" s="5">
         <v>46155.56333268518</v>
@@ -9271,16 +9274,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9296,13 +9299,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9312,7 +9315,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B135" s="9">
         <v>46149.16936914352</v>
@@ -9322,7 +9325,7 @@
         <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9346,7 +9349,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9359,7 +9362,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B136" s="5">
         <v>46149.169373136574</v>
@@ -9369,16 +9372,16 @@
         <v>46155.602217824075</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9396,13 +9399,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9411,18 +9414,18 @@
         <v>46255</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B137" s="9">
         <v>46149.169417349534</v>
@@ -9432,7 +9435,7 @@
         <v>46196.86942971065</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9459,13 +9462,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>
@@ -9474,13 +9477,13 @@
         <v>46255</v>
       </c>
       <c r="S137" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46205.843587766205</v>
+        <v>46230.168406875004</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -5665,7 +5665,7 @@
         <v>46224.67387799769</v>
       </c>
       <c r="D68" s="5">
-        <v>46224.673890763894</v>
+        <v>46227.16954216435</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>235</v>
@@ -5709,8 +5709,8 @@
       <c r="R68" s="5">
         <v>46226</v>
       </c>
-      <c r="S68" s="12" t="s">
-        <v>151</v>
+      <c r="S68" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46220.207858634254</v>
+        <v>46228.16710329861</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>243</v>
@@ -5992,8 +5992,8 @@
       <c r="R73" s="9">
         <v>46227</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>151</v>
+      <c r="S73" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46224.67385076389</v>
+        <v>46227.16842824074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>191</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46224.67386304398</v>
+        <v>46227.16842944444</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>191</v>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46224.67386091435</v>
+        <v>46227.168525636574</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>191</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46224.67387116898</v>
+        <v>46227.168527118054</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>191</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46223.592199652776</v>
+        <v>46227.16939207176</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6619,8 +6619,8 @@
       <c r="R84" s="5">
         <v>46234</v>
       </c>
-      <c r="S84" s="7" t="s">
-        <v>101</v>
+      <c r="S84" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46223.59219898148</v>
+        <v>46230.19907855324</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>277</v>
@@ -6894,8 +6894,8 @@
       <c r="R89" s="9">
         <v>46237</v>
       </c>
-      <c r="S89" s="7" t="s">
-        <v>101</v>
+      <c r="S89" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -525,343 +525,343 @@
     <t>Generacion OC Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
   </si>
   <si>
+    <t>1214596772340045</t>
+  </si>
+  <si>
+    <t>Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472897</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4315</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa ,Fabricación Externa OT 4315,Control de calidad fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472912</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4315</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214596725472956</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472966</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>1214596725472981</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4315</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214563704105178</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214596624002438</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214596734094501</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
+  </si>
+  <si>
+    <t>check planos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214596734094526</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624006635</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105084</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105094</t>
+  </si>
+  <si>
+    <t>1214739697907509</t>
+  </si>
+  <si>
+    <t>1214739697907510</t>
+  </si>
+  <si>
+    <t>1214596734105104</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112602</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734114879</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596624027372</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624027387</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214596624027530</t>
+  </si>
+  <si>
+    <t>1214596624027545</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214596624027555</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1214596725492919</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596725514576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214739697907430</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214739697907431</t>
+  </si>
+  <si>
+    <t>1214596734023783</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214596772418926</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772419042</t>
+  </si>
+  <si>
+    <t>1214739697907432</t>
+  </si>
+  <si>
+    <t>1214739697907433</t>
+  </si>
+  <si>
+    <t>1214596772419062</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214596772420232</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Control de calidad Armado,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214596772420252</t>
+  </si>
+  <si>
+    <t>1214739697907434</t>
+  </si>
+  <si>
+    <t>OT3 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214739697907435</t>
+  </si>
+  <si>
+    <t>OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772422416</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214596772422426</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772422581</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772422601</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214596624060758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Revestimiento</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596772340045</t>
-  </si>
-  <si>
-    <t>Fabricación Externa OT 4315,Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472897</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4315</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa ,Fabricación Externa OT 4315,Control de calidad fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472912</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4315</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214596725472956</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Generación OC Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472966</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315,Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>1214596725472981</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4315</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4315,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214563704105178</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214596624002438</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214596734094501</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4315</t>
-  </si>
-  <si>
-    <t>check planos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214596734094526</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4315,propuesta Corte Laser OT 4315,Propuesta Corte plasma  OT 4315,Propuesta Mecanizado OT 4315,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624006635</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105084</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105094</t>
-  </si>
-  <si>
-    <t>1214739697907509</t>
-  </si>
-  <si>
-    <t>1214739697907510</t>
-  </si>
-  <si>
-    <t>1214596734105104</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112602</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734114879</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596624027372</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624027387</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214596624027530</t>
-  </si>
-  <si>
-    <t>1214596624027545</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214596624027555</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1214596725492919</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596725514576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214739697907430</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214739697907431</t>
-  </si>
-  <si>
-    <t>1214596734023783</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214596772418926</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772419042</t>
-  </si>
-  <si>
-    <t>1214739697907432</t>
-  </si>
-  <si>
-    <t>1214739697907433</t>
-  </si>
-  <si>
-    <t>1214596772419062</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214596772420232</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Control de calidad Armado,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214596772420252</t>
-  </si>
-  <si>
-    <t>1214739697907434</t>
-  </si>
-  <si>
-    <t>OT3 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214739697907435</t>
-  </si>
-  <si>
-    <t>OT4 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772422416</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214596772422426</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772422581</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772422601</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214596624060758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Revestimiento</t>
   </si>
   <si>
     <t>1214596772424812</t>
@@ -3978,7 +3978,7 @@
         <v>46205.843624166664</v>
       </c>
       <c r="D39" s="9">
-        <v>46223.2074775463</v>
+        <v>46231.20426721065</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -4022,8 +4022,8 @@
       <c r="R39" s="9">
         <v>46230</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>151</v>
+      <c r="S39" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46149.168932870365</v>
@@ -4079,7 +4079,7 @@
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46149.16893796297</v>
@@ -4101,7 +4101,7 @@
         <v>46205.84357975694</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4134,7 +4134,7 @@
         <v>88</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46149.16894290509</v>
@@ -4154,16 +4154,16 @@
         <v>46230.168406875004</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I42" s="5">
         <v>46227</v>
@@ -4184,7 +4184,7 @@
         <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46149.16894577546</v>
@@ -4209,7 +4209,7 @@
         <v>46211.19248402778</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4239,7 +4239,7 @@
         <v>90</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4262,7 +4262,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46149.16894971065</v>
@@ -4301,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46149.1689542824</v>
@@ -4329,7 +4329,7 @@
         <v>46205.61326564815</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4356,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46149.16868141203</v>
@@ -4382,7 +4382,7 @@
         <v>46199.77902613426</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4406,7 +4406,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46149.16895986111</v>
@@ -4433,16 +4433,16 @@
         <v>46197.71368634259</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46162</v>
@@ -4460,13 +4460,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46162</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46149.16896564815</v>
@@ -4498,16 +4498,16 @@
         <v>46199.779022372684</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46177</v>
@@ -4525,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46146</v>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46149.16897216435</v>
@@ -4569,10 +4569,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4588,13 +4588,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46184</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46149.16898688657</v>
@@ -4624,16 +4624,16 @@
         <v>46155.59844700231</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4651,10 +4651,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4687,16 +4687,16 @@
         <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="9">
@@ -4712,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4738,16 +4738,16 @@
         <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4763,13 +4763,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4789,16 +4789,16 @@
         <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="9">
@@ -4814,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4840,16 +4840,16 @@
         <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4865,13 +4865,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4893,7 +4893,7 @@
         <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4917,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4946,16 +4946,16 @@
         <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4973,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -5011,16 +5011,16 @@
         <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I57" s="9">
         <v>46204</v>
@@ -5038,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>206</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5076,16 +5076,16 @@
         <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5103,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5141,16 +5141,16 @@
         <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I59" s="9">
         <v>46204</v>
@@ -5168,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5206,16 +5206,16 @@
         <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5233,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5271,16 +5271,16 @@
         <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I61" s="9">
         <v>46213</v>
@@ -5298,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5334,7 +5334,7 @@
         <v>46224.67388769676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5358,7 +5358,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5380,19 +5380,19 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46225.86188855324</v>
+        <v>46231.56037025463</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5410,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5448,16 +5448,16 @@
         <v>46224.673700625004</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5475,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5503,16 +5503,16 @@
         <v>46224.67370611111</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5530,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5558,16 +5558,16 @@
         <v>46224.67371170138</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5585,13 +5585,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5613,16 +5613,16 @@
         <v>46224.67371741898</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5640,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5668,16 +5668,16 @@
         <v>46227.16954216435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5695,13 +5695,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5733,16 +5733,16 @@
         <v>46224.67384578704</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5760,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5788,16 +5788,16 @@
         <v>46224.67385033565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5815,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5843,16 +5843,16 @@
         <v>46224.67385497685</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5870,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5898,16 +5898,16 @@
         <v>46224.67386524305</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5925,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5951,16 +5951,16 @@
         <v>46228.16710329861</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I73" s="9">
         <v>46227</v>
@@ -5978,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -6014,16 +6014,16 @@
         <v>46227.16842824074</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I74" s="5">
         <v>46227</v>
@@ -6041,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -6067,16 +6067,16 @@
         <v>46227.16842944444</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I75" s="9">
         <v>46227</v>
@@ -6094,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6120,16 +6120,16 @@
         <v>46227.168525636574</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="I76" s="5">
         <v>46227</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6173,16 +6173,16 @@
         <v>46227.168527118054</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="I77" s="9">
         <v>46227</v>
@@ -6200,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6226,7 +6226,7 @@
         <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6250,7 +6250,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6277,16 +6277,16 @@
         <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6302,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6340,16 +6340,16 @@
         <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6367,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6405,16 +6405,16 @@
         <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6432,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6458,26 +6458,26 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46224.19576207176</v>
+        <v>46231.16799221065</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6495,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6510,7 +6510,7 @@
         <v>46231</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>46234</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6641,7 +6641,7 @@
         <v>46223.59164138889</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6694,7 +6694,7 @@
         <v>46223.591640729166</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6747,7 +6747,7 @@
         <v>46223.59164002315</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6777,7 +6777,7 @@
         <v>268</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>274</v>
@@ -6800,7 +6800,7 @@
         <v>46223.59163928241</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6830,7 +6830,7 @@
         <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>274</v>
@@ -6883,7 +6883,7 @@
         <v>265</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>265</v>
@@ -6895,7 +6895,7 @@
         <v>46237</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>46223.59174438658</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6971,7 +6971,7 @@
         <v>46223.591741261574</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7022,7 +7022,7 @@
         <v>46223.59173454861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7073,7 +7073,7 @@
         <v>46223.59173388889</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46223.59219834491</v>
+        <v>46231.1809171875</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7154,7 +7154,7 @@
         <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>265</v>
@@ -7165,8 +7165,8 @@
       <c r="R94" s="5">
         <v>46238</v>
       </c>
-      <c r="S94" s="7" t="s">
-        <v>101</v>
+      <c r="S94" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>46223.5918337037</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7242,7 +7242,7 @@
         <v>46223.591830219906</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7293,7 +7293,7 @@
         <v>46223.59182357639</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7344,7 +7344,7 @@
         <v>46223.591822939816</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7425,7 +7425,7 @@
         <v>265</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>265</v>
@@ -7458,7 +7458,7 @@
         <v>46223.59191454861</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7509,7 +7509,7 @@
         <v>46223.591913842596</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7560,7 +7560,7 @@
         <v>46223.59191307871</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7611,7 +7611,7 @@
         <v>46223.59191234954</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7692,7 +7692,7 @@
         <v>265</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>265</v>
@@ -7725,7 +7725,7 @@
         <v>46223.59202306713</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7755,7 +7755,7 @@
         <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>309</v>
@@ -7778,7 +7778,7 @@
         <v>46223.59202241898</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7808,7 +7808,7 @@
         <v>307</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>309</v>
@@ -7831,7 +7831,7 @@
         <v>46223.59202165509</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7861,7 +7861,7 @@
         <v>307</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>312</v>
@@ -7884,7 +7884,7 @@
         <v>46223.59202096065</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7914,7 +7914,7 @@
         <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>312</v>
@@ -7967,7 +7967,7 @@
         <v>265</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>316</v>
@@ -8000,7 +8000,7 @@
         <v>46223.592111550926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8028,7 +8028,7 @@
         <v>315</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>318</v>
@@ -8051,7 +8051,7 @@
         <v>46223.59211092592</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8079,7 +8079,7 @@
         <v>315</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>318</v>
@@ -8102,7 +8102,7 @@
         <v>46223.59211032407</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8130,7 +8130,7 @@
         <v>315</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>321</v>
@@ -8153,7 +8153,7 @@
         <v>46223.59210969908</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8181,7 +8181,7 @@
         <v>315</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>321</v>
@@ -8312,7 +8312,7 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8340,7 +8340,7 @@
         <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>332</v>
@@ -8363,7 +8363,7 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8391,7 +8391,7 @@
         <v>327</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>334</v>
@@ -8414,7 +8414,7 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8442,7 +8442,7 @@
         <v>327</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>334</v>
@@ -8465,7 +8465,7 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8493,7 +8493,7 @@
         <v>327</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>334</v>
@@ -8546,7 +8546,7 @@
         <v>324</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>324</v>
@@ -8579,7 +8579,7 @@
         <v>46223.592296180555</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8609,7 +8609,7 @@
         <v>338</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>340</v>
@@ -8632,7 +8632,7 @@
         <v>46223.5922953125</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8662,7 +8662,7 @@
         <v>338</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>340</v>
@@ -8685,7 +8685,7 @@
         <v>46223.592294675924</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8715,7 +8715,7 @@
         <v>338</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>343</v>
@@ -8738,7 +8738,7 @@
         <v>46223.592294050926</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8768,7 +8768,7 @@
         <v>338</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>345</v>
@@ -8797,10 +8797,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8854,16 +8854,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8882,7 +8882,7 @@
         <v>347</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>350</v>
@@ -8905,16 +8905,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8933,7 +8933,7 @@
         <v>347</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>352</v>
@@ -8956,16 +8956,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8984,7 +8984,7 @@
         <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>354</v>
@@ -9007,16 +9007,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -9035,7 +9035,7 @@
         <v>347</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>356</v>
@@ -9064,10 +9064,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -9121,16 +9121,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9149,7 +9149,7 @@
         <v>358</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>358</v>
@@ -9172,16 +9172,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9200,7 +9200,7 @@
         <v>358</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>358</v>
@@ -9223,16 +9223,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9251,7 +9251,7 @@
         <v>358</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>358</v>
@@ -9274,16 +9274,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9302,7 +9302,7 @@
         <v>358</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>358</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46231.56037025463</v>
+        <v>46231.653098090275</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -861,25 +861,25 @@
     <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Revestimiento</t>
   </si>
   <si>
+    <t>1214596772424812</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214596772424822</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa ,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596772424812</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214596772424822</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa ,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
     <t>1214596725524470</t>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46231.16799221065</v>
+        <v>46232.203200497686</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>261</v>
@@ -6509,8 +6509,8 @@
       <c r="R82" s="5">
         <v>46231</v>
       </c>
-      <c r="S82" s="12" t="s">
-        <v>263</v>
+      <c r="S82" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6531,7 +6531,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6555,7 +6555,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
@@ -6578,7 +6578,7 @@
         <v>46227.16939207176</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6605,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6620,7 +6620,7 @@
         <v>46234</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6668,7 +6668,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>271</v>
@@ -6721,7 +6721,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>271</v>
@@ -6774,7 +6774,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>190</v>
@@ -6827,7 +6827,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>190</v>
@@ -6880,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>212</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6895,7 +6895,7 @@
         <v>46237</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
@@ -7151,13 +7151,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7166,7 +7166,7 @@
         <v>46238</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46223.5921977199</v>
+        <v>46232.18355315972</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>296</v>
@@ -7422,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7436,8 +7436,8 @@
       <c r="R99" s="9">
         <v>46239</v>
       </c>
-      <c r="S99" s="7" t="s">
-        <v>101</v>
+      <c r="S99" s="12" t="s">
+        <v>269</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
@@ -7689,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>212</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7964,7 +7964,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>212</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46231.653098090275</v>
+        <v>46232.835988923616</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46223.59219704861</v>
+        <v>46233.18481633102</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>307</v>
@@ -7703,8 +7703,8 @@
       <c r="R104" s="5">
         <v>46240</v>
       </c>
-      <c r="S104" s="7" t="s">
-        <v>101</v>
+      <c r="S104" s="12" t="s">
+        <v>269</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46232.835988923616</v>
+        <v>46233.648261064816</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -639,6 +639,9 @@
     <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214596734105084</t>
   </si>
   <si>
@@ -877,9 +880,6 @@
   </si>
   <si>
     <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa ,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214596725524470</t>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46155.59844700231</v>
+        <v>46234.18331444444</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4665,8 +4665,8 @@
       <c r="R50" s="5">
         <v>46241</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>101</v>
+      <c r="S50" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4687,7 +4687,7 @@
         <v>46210.617212881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4715,10 +4715,10 @@
         <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4738,7 +4738,7 @@
         <v>46210.61721229166</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4766,10 +4766,10 @@
         <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4789,7 +4789,7 @@
         <v>46210.617211689816</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4817,10 +4817,10 @@
         <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4840,7 +4840,7 @@
         <v>46210.61721105324</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4868,10 +4868,10 @@
         <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4893,7 +4893,7 @@
         <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4917,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4946,16 +4946,16 @@
         <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4973,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -5011,7 +5011,7 @@
         <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5038,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5076,16 +5076,16 @@
         <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5103,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5141,7 +5141,7 @@
         <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5168,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5206,16 +5206,16 @@
         <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5233,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5271,7 +5271,7 @@
         <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5298,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5334,7 +5334,7 @@
         <v>46224.67388769676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5358,7 +5358,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5383,16 +5383,16 @@
         <v>46233.648261064816</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5410,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5448,16 +5448,16 @@
         <v>46224.673700625004</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5475,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5503,16 +5503,16 @@
         <v>46224.67370611111</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5530,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5558,16 +5558,16 @@
         <v>46224.67371170138</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5585,13 +5585,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5613,16 +5613,16 @@
         <v>46224.67371741898</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5640,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5668,16 +5668,16 @@
         <v>46227.16954216435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5695,13 +5695,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5733,16 +5733,16 @@
         <v>46224.67384578704</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5760,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5788,16 +5788,16 @@
         <v>46224.67385033565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5815,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5843,16 +5843,16 @@
         <v>46224.67385497685</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5870,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5898,16 +5898,16 @@
         <v>46224.67386524305</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5925,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5951,7 +5951,7 @@
         <v>46228.16710329861</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5978,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -6014,7 +6014,7 @@
         <v>46227.16842824074</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6041,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -6067,7 +6067,7 @@
         <v>46227.16842944444</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6094,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6120,7 +6120,7 @@
         <v>46227.168525636574</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6173,7 +6173,7 @@
         <v>46227.168527118054</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6200,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6226,7 +6226,7 @@
         <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6250,7 +6250,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6277,16 +6277,16 @@
         <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6302,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6340,16 +6340,16 @@
         <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6367,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6405,16 +6405,16 @@
         <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6432,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6468,16 +6468,16 @@
         <v>46232.203200497686</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6495,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6531,7 +6531,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6555,7 +6555,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6568,17 +6568,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46227.16939207176</v>
+        <v>46234.16939866898</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6605,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6620,7 +6620,7 @@
         <v>46234</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6638,10 +6638,10 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46223.59164138889</v>
+        <v>46234.16939539352</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6668,7 +6668,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>271</v>
@@ -6691,10 +6691,10 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46223.591640729166</v>
+        <v>46234.16939739583</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6721,7 +6721,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>271</v>
@@ -6744,10 +6744,10 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46223.59164002315</v>
+        <v>46234.16952005787</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6774,10 +6774,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>274</v>
@@ -6797,10 +6797,10 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46223.59163928241</v>
+        <v>46234.16952178241</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6827,10 +6827,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>274</v>
@@ -6880,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6895,7 +6895,7 @@
         <v>46237</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
@@ -6918,7 +6918,7 @@
         <v>46223.59174438658</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6971,7 +6971,7 @@
         <v>46223.591741261574</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7022,7 +7022,7 @@
         <v>46223.59173454861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7073,7 +7073,7 @@
         <v>46223.59173388889</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7151,13 +7151,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7166,7 +7166,7 @@
         <v>46238</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>46223.5918337037</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7242,7 +7242,7 @@
         <v>46223.591830219906</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7293,7 +7293,7 @@
         <v>46223.59182357639</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7344,7 +7344,7 @@
         <v>46223.591822939816</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7422,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7437,7 +7437,7 @@
         <v>46239</v>
       </c>
       <c r="S99" s="12" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
@@ -7458,7 +7458,7 @@
         <v>46223.59191454861</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7509,7 +7509,7 @@
         <v>46223.591913842596</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7560,7 +7560,7 @@
         <v>46223.59191307871</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7611,7 +7611,7 @@
         <v>46223.59191234954</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7689,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7704,7 +7704,7 @@
         <v>46240</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7725,7 +7725,7 @@
         <v>46223.59202306713</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7755,7 +7755,7 @@
         <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>309</v>
@@ -7778,7 +7778,7 @@
         <v>46223.59202241898</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7808,7 +7808,7 @@
         <v>307</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>309</v>
@@ -7831,7 +7831,7 @@
         <v>46223.59202165509</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7861,7 +7861,7 @@
         <v>307</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>312</v>
@@ -7884,7 +7884,7 @@
         <v>46223.59202096065</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7914,7 +7914,7 @@
         <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>312</v>
@@ -7964,10 +7964,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>316</v>
@@ -8000,7 +8000,7 @@
         <v>46223.592111550926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8028,7 +8028,7 @@
         <v>315</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>318</v>
@@ -8051,7 +8051,7 @@
         <v>46223.59211092592</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8079,7 +8079,7 @@
         <v>315</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>318</v>
@@ -8102,7 +8102,7 @@
         <v>46223.59211032407</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8130,7 +8130,7 @@
         <v>315</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>321</v>
@@ -8153,7 +8153,7 @@
         <v>46223.59210969908</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8181,7 +8181,7 @@
         <v>315</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>321</v>
@@ -8312,7 +8312,7 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8340,7 +8340,7 @@
         <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>332</v>
@@ -8363,7 +8363,7 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8391,7 +8391,7 @@
         <v>327</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>334</v>
@@ -8414,7 +8414,7 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8442,7 +8442,7 @@
         <v>327</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>334</v>
@@ -8465,7 +8465,7 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8493,7 +8493,7 @@
         <v>327</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>334</v>
@@ -8546,7 +8546,7 @@
         <v>324</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>324</v>
@@ -8579,7 +8579,7 @@
         <v>46223.592296180555</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8609,7 +8609,7 @@
         <v>338</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>340</v>
@@ -8632,7 +8632,7 @@
         <v>46223.5922953125</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8662,7 +8662,7 @@
         <v>338</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>340</v>
@@ -8685,7 +8685,7 @@
         <v>46223.592294675924</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8715,7 +8715,7 @@
         <v>338</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>343</v>
@@ -8738,7 +8738,7 @@
         <v>46223.592294050926</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8768,7 +8768,7 @@
         <v>338</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>345</v>
@@ -8797,10 +8797,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8854,16 +8854,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8882,7 +8882,7 @@
         <v>347</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>350</v>
@@ -8905,16 +8905,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8933,7 +8933,7 @@
         <v>347</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>352</v>
@@ -8956,16 +8956,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8984,7 +8984,7 @@
         <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>354</v>
@@ -9007,16 +9007,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -9035,7 +9035,7 @@
         <v>347</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>356</v>
@@ -9064,10 +9064,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -9121,16 +9121,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9149,7 +9149,7 @@
         <v>358</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>358</v>
@@ -9172,16 +9172,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9200,7 +9200,7 @@
         <v>358</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>358</v>
@@ -9223,16 +9223,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9251,7 +9251,7 @@
         <v>358</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>358</v>
@@ -9274,16 +9274,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9302,7 +9302,7 @@
         <v>358</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>358</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46234.16939866898</v>
+        <v>46235.20361111111</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6619,8 +6619,8 @@
       <c r="R84" s="5">
         <v>46234</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>189</v>
+      <c r="S84" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46235.20361111111</v>
+        <v>46237.537617152775</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6625,8 +6625,8 @@
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="11" t="s">
-        <v>102</v>
+      <c r="U84" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46230.19907855324</v>
+        <v>46237.53765103009</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>277</v>
@@ -6900,8 +6900,8 @@
       <c r="T89" s="10">
         <v>0</v>
       </c>
-      <c r="U89" s="11" t="s">
-        <v>102</v>
+      <c r="U89" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46223.59173454861</v>
+        <v>46237.16895704861</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>191</v>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46223.59173388889</v>
+        <v>46237.16895965278</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>191</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46231.1809171875</v>
+        <v>46237.537678356486</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7171,8 +7171,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="11" t="s">
-        <v>102</v>
+      <c r="U94" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46232.18355315972</v>
+        <v>46237.5377078125</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>296</v>
@@ -7442,8 +7442,8 @@
       <c r="T99" s="10">
         <v>0</v>
       </c>
-      <c r="U99" s="11" t="s">
-        <v>102</v>
+      <c r="U99" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46233.18481633102</v>
+        <v>46237.53772810185</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>307</v>
@@ -7709,8 +7709,8 @@
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="11" t="s">
-        <v>102</v>
+      <c r="U104" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46223.59219642361</v>
+        <v>46237.18984681713</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>315</v>
@@ -7978,8 +7978,8 @@
       <c r="R109" s="9">
         <v>46244</v>
       </c>
-      <c r="S109" s="7" t="s">
-        <v>101</v>
+      <c r="S109" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46223.59234582176</v>
+        <v>46237.53780239583</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8563,8 +8563,8 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="11" t="s">
-        <v>102</v>
+      <c r="U120" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -747,7 +747,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46233.648261064816</v>
+        <v>46237.57049912037</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46237.57049912037</v>
+        <v>46237.81015951389</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6850,7 +6850,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46237.53765103009</v>
+        <v>46238.20141277778</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>277</v>
@@ -6894,8 +6894,8 @@
       <c r="R89" s="9">
         <v>46237</v>
       </c>
-      <c r="S89" s="12" t="s">
-        <v>189</v>
+      <c r="S89" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T89" s="10">
         <v>0</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46237.537678356486</v>
+        <v>46238.168046226856</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46223.59182357639</v>
+        <v>46238.16811421297</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>191</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46223.591822939816</v>
+        <v>46238.16811594907</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>191</v>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46155.60146953704</v>
+        <v>46238.19851811342</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>327</v>
@@ -8290,8 +8290,8 @@
       <c r="R115" s="9">
         <v>46245</v>
       </c>
-      <c r="S115" s="7" t="s">
-        <v>101</v>
+      <c r="S115" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -747,7 +747,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46237.81015951389</v>
+        <v>46239.57424306713</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46238.168046226856</v>
+        <v>46239.170314664356</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7165,8 +7165,8 @@
       <c r="R94" s="5">
         <v>46238</v>
       </c>
-      <c r="S94" s="12" t="s">
-        <v>189</v>
+      <c r="S94" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46237.5377078125</v>
+        <v>46239.16801871528</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>296</v>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46223.59191454861</v>
+        <v>46239.16802082176</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>191</v>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46223.591913842596</v>
+        <v>46239.16802197917</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>191</v>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46223.59191307871</v>
+        <v>46239.1680906713</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>191</v>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46223.59191234954</v>
+        <v>46239.16809255787</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>191</v>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46237.53780239583</v>
+        <v>46239.18009083333</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8557,8 +8557,8 @@
       <c r="R120" s="5">
         <v>46246</v>
       </c>
-      <c r="S120" s="7" t="s">
-        <v>101</v>
+      <c r="S120" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -747,7 +747,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214596725492919</t>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46239.57424306713</v>
+        <v>46240.582704201384</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46239.16801871528</v>
+        <v>46240.170477685184</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>296</v>
@@ -7436,8 +7436,8 @@
       <c r="R99" s="9">
         <v>46239</v>
       </c>
-      <c r="S99" s="12" t="s">
-        <v>189</v>
+      <c r="S99" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T99" s="10">
         <v>0</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46237.53772810185</v>
+        <v>46240.16781454861</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>307</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46223.59202306713</v>
+        <v>46240.16781193287</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>191</v>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46223.59202241898</v>
+        <v>46240.16781346065</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>191</v>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46223.59202165509</v>
+        <v>46240.167892337966</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>191</v>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46223.59202096065</v>
+        <v>46240.16789085648</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>191</v>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46155.60192047454</v>
+        <v>46240.202886747684</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>347</v>
@@ -8832,8 +8832,8 @@
       <c r="R125" s="9">
         <v>46247</v>
       </c>
-      <c r="S125" s="7" t="s">
-        <v>101</v>
+      <c r="S125" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46234.18331444444</v>
+        <v>46241.168307569445</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46210.617212881945</v>
+        <v>46241.16831026621</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46210.61721229166</v>
+        <v>46241.16831137732</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46210.617211689816</v>
+        <v>46241.1683981713</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>191</v>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46210.61721105324</v>
+        <v>46241.1684000463</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46240.16781454861</v>
+        <v>46241.20550412037</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>307</v>
@@ -7703,8 +7703,8 @@
       <c r="R104" s="5">
         <v>46240</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>189</v>
+      <c r="S104" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46155.60216496528</v>
+        <v>46241.17305832176</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>358</v>
@@ -9099,8 +9099,8 @@
       <c r="R130" s="5">
         <v>46248</v>
       </c>
-      <c r="S130" s="7" t="s">
-        <v>101</v>
+      <c r="S130" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -639,388 +639,388 @@
     <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
+    <t>1214596734105084</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734105094</t>
+  </si>
+  <si>
+    <t>1214739697907509</t>
+  </si>
+  <si>
+    <t>1214739697907510</t>
+  </si>
+  <si>
+    <t>1214596734105104</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112602</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596734112622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596734114879</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214596624027372</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624027387</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214596624027530</t>
+  </si>
+  <si>
+    <t>1214596624027545</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214596624027555</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+  </si>
+  <si>
+    <t>1214596725492919</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596725514576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214739697907430</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214739697907431</t>
+  </si>
+  <si>
+    <t>1214596734023783</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214596772418926</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772419042</t>
+  </si>
+  <si>
+    <t>1214739697907432</t>
+  </si>
+  <si>
+    <t>1214739697907433</t>
+  </si>
+  <si>
+    <t>1214596772419062</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214596772420232</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Control de calidad Armado,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214596772420252</t>
+  </si>
+  <si>
+    <t>1214739697907434</t>
+  </si>
+  <si>
+    <t>OT3 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214739697907435</t>
+  </si>
+  <si>
+    <t>OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772422416</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214596772422426</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772422581</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772422601</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214596624060758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214596772424812</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214596772424822</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa ,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596725524470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214596725524485</t>
+  </si>
+  <si>
+    <t>1214739697907436</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214739697907437</t>
+  </si>
+  <si>
+    <t>1214596969874290</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214596969874305</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214596969874389</t>
+  </si>
+  <si>
+    <t>1214739697907438</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,OT3 4315 ZVN 1-9-63/2,check planos</t>
+  </si>
+  <si>
+    <t>1214739697907439</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,OT4 4315 ZVN 1-9-63/2,check planos</t>
+  </si>
+  <si>
+    <t>1214596969874409</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214596772441701</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1214596734152702</t>
+  </si>
+  <si>
+    <t>1214739697907440</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214739697907441</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,check planos,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214596734152727</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1214596734154011</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Montaje motor</t>
+  </si>
+  <si>
+    <t>1214596969875021</t>
+  </si>
+  <si>
+    <t>check planos,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214739697907442</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,check planos,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214739697907443</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>1214596969875041</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214596624084258</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624084278</t>
+  </si>
+  <si>
+    <t>1214739697907445</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214739697907444</t>
+  </si>
+  <si>
+    <t>1214596624029751</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596734105084</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734105094</t>
-  </si>
-  <si>
-    <t>1214739697907509</t>
-  </si>
-  <si>
-    <t>1214739697907510</t>
-  </si>
-  <si>
-    <t>1214596734105104</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112602</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596734112622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596734114879</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214596624027372</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624027387</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214596624027530</t>
-  </si>
-  <si>
-    <t>1214596624027545</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214596624027555</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
-  </si>
-  <si>
-    <t>1214596725492919</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596725514576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214739697907430</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado,Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214739697907431</t>
-  </si>
-  <si>
-    <t>1214596734023783</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214596772418926</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772419042</t>
-  </si>
-  <si>
-    <t>1214739697907432</t>
-  </si>
-  <si>
-    <t>1214739697907433</t>
-  </si>
-  <si>
-    <t>1214596772419062</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214596772420232</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Control de calidad Armado,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214596772420252</t>
-  </si>
-  <si>
-    <t>1214739697907434</t>
-  </si>
-  <si>
-    <t>OT3 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214739697907435</t>
-  </si>
-  <si>
-    <t>OT4 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772422416</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214596772422426</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772422581</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772422601</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214596624060758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214596772424812</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Rodete,RE-PINTADO,Montaje Alabe,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214596772424822</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa ,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596725524470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4315 ZVN 1-9-63/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214596725524485</t>
-  </si>
-  <si>
-    <t>1214739697907436</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214739697907437</t>
-  </si>
-  <si>
-    <t>1214596969874290</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214596969874305</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214596969874389</t>
-  </si>
-  <si>
-    <t>1214739697907438</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,OT3 4315 ZVN 1-9-63/2,check planos</t>
-  </si>
-  <si>
-    <t>1214739697907439</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,OT4 4315 ZVN 1-9-63/2,check planos</t>
-  </si>
-  <si>
-    <t>1214596969874409</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214596772441701</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1214596734152702</t>
-  </si>
-  <si>
-    <t>1214739697907440</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214739697907441</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,check planos,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214596734152727</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1214596734154011</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Montaje motor</t>
-  </si>
-  <si>
-    <t>1214596969875021</t>
-  </si>
-  <si>
-    <t>check planos,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214739697907442</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,check planos,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214739697907443</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>1214596969875041</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214596624084258</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624084278</t>
-  </si>
-  <si>
-    <t>1214739697907445</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214739697907444</t>
-  </si>
-  <si>
-    <t>1214596624029751</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
     <t>1214596772470213</t>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46241.168307569445</v>
+        <v>46242.18436197916</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4665,8 +4665,8 @@
       <c r="R50" s="5">
         <v>46241</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>189</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46149.168991412036</v>
@@ -4687,7 +4687,7 @@
         <v>46241.16831026621</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4715,10 +4715,10 @@
         <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46149.16900017361</v>
@@ -4738,7 +4738,7 @@
         <v>46241.16831137732</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4766,10 +4766,10 @@
         <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46155.577817384255</v>
@@ -4789,7 +4789,7 @@
         <v>46241.1683981713</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4817,10 +4817,10 @@
         <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46155.577829050926</v>
@@ -4840,7 +4840,7 @@
         <v>46241.1684000463</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4868,10 +4868,10 @@
         <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46149.1690050926</v>
@@ -4893,7 +4893,7 @@
         <v>46216.8396287963</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4917,7 +4917,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46149.16900940972</v>
@@ -4946,16 +4946,16 @@
         <v>46216.83970709491</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46202</v>
@@ -4973,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46202</v>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46149.16901516204</v>
@@ -5011,7 +5011,7 @@
         <v>46216.83978594907</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5038,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O57" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>206</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46174</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46149.16902107639</v>
@@ -5076,16 +5076,16 @@
         <v>46216.83981521991</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46202</v>
@@ -5103,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46202</v>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46149.16902621528</v>
@@ -5141,7 +5141,7 @@
         <v>46216.83984586806</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5168,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46174</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46149.1690303588</v>
@@ -5206,16 +5206,16 @@
         <v>46216.83987789352</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46211</v>
@@ -5233,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46211</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46149.16903488426</v>
@@ -5271,7 +5271,7 @@
         <v>46217.188729456015</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5298,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="9">
         <v>46213</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46149.1690391088</v>
@@ -5334,7 +5334,7 @@
         <v>46224.67388769676</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5358,7 +5358,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46149.169042442125</v>
@@ -5383,16 +5383,16 @@
         <v>46240.582704201384</v>
       </c>
       <c r="E63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="H63" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46217</v>
@@ -5410,13 +5410,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="9">
         <v>46217</v>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46149.169049375</v>
@@ -5448,16 +5448,16 @@
         <v>46224.673700625004</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46217</v>
@@ -5475,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46149.16905616898</v>
@@ -5503,16 +5503,16 @@
         <v>46224.67370611111</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46217</v>
@@ -5530,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46155.562074166664</v>
@@ -5558,16 +5558,16 @@
         <v>46224.67371170138</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46217</v>
@@ -5585,13 +5585,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
         <v>46155.562095416666</v>
@@ -5613,16 +5613,16 @@
         <v>46224.67371741898</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46217</v>
@@ -5640,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46149.169104699075</v>
@@ -5668,16 +5668,16 @@
         <v>46227.16954216435</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46220</v>
@@ -5695,13 +5695,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q68" s="5">
         <v>46220</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46149.1691096412</v>
@@ -5733,16 +5733,16 @@
         <v>46224.67384578704</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46220</v>
@@ -5760,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>237</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>238</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46149.16911491899</v>
@@ -5788,16 +5788,16 @@
         <v>46224.67385033565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5815,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46155.562225625</v>
@@ -5843,16 +5843,16 @@
         <v>46224.67385497685</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46220</v>
@@ -5870,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46155.56224557871</v>
@@ -5898,16 +5898,16 @@
         <v>46224.67386524305</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46220</v>
@@ -5925,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46149.169119768514</v>
@@ -5951,7 +5951,7 @@
         <v>46228.16710329861</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5978,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q73" s="9">
         <v>46227</v>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46149.16912365741</v>
@@ -6014,7 +6014,7 @@
         <v>46227.16842824074</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6041,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46149.16912908565</v>
@@ -6067,7 +6067,7 @@
         <v>46227.16842944444</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6094,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46155.56233189815</v>
@@ -6120,7 +6120,7 @@
         <v>46227.168525636574</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46155.562344351856</v>
@@ -6173,7 +6173,7 @@
         <v>46227.168527118054</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6200,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46149.16913412037</v>
@@ -6226,7 +6226,7 @@
         <v>46216.87183908565</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6250,7 +6250,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46149.16913708333</v>
@@ -6277,16 +6277,16 @@
         <v>46212.66505976852</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6302,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46181</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46149.16914224537</v>
@@ -6340,16 +6340,16 @@
         <v>46212.66506702546</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46164</v>
@@ -6367,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="5">
         <v>46164</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46149.16914733796</v>
@@ -6405,16 +6405,16 @@
         <v>46216.8718724537</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46197</v>
@@ -6432,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q81" s="9">
         <v>46197</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46149.16915236111</v>
@@ -6468,16 +6468,16 @@
         <v>46232.203200497686</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I82" s="5">
         <v>46231</v>
@@ -6495,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="5">
         <v>46231</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46149.16915732639</v>
@@ -6531,7 +6531,7 @@
         <v>46155.58270766203</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6555,7 +6555,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6568,7 +6568,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46149.16916049768</v>
@@ -6578,7 +6578,7 @@
         <v>46237.537617152775</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6605,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46230</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46149.16916685185</v>
@@ -6641,7 +6641,7 @@
         <v>46234.16939539352</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6668,10 +6668,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46149.16917037037</v>
@@ -6694,7 +6694,7 @@
         <v>46234.16939739583</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6721,10 +6721,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46155.5624656713</v>
@@ -6747,7 +6747,7 @@
         <v>46234.16952005787</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6774,13 +6774,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6790,7 +6790,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46155.562495266204</v>
@@ -6800,7 +6800,7 @@
         <v>46234.16952178241</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6827,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6843,7 +6843,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46149.16917405093</v>
@@ -6853,7 +6853,7 @@
         <v>46238.20141277778</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6880,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q89" s="9">
         <v>46237</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46149.169178321754</v>
@@ -6918,7 +6918,7 @@
         <v>46223.59174438658</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6943,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6959,7 +6959,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46149.169183148144</v>
@@ -6971,7 +6971,7 @@
         <v>46223.591741261574</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6996,13 +6996,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46155.56256662037</v>
@@ -7022,7 +7022,7 @@
         <v>46237.16895704861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7047,13 +7047,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
         <v>46155.56257849537</v>
@@ -7073,7 +7073,7 @@
         <v>46237.16895965278</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7098,13 +7098,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7114,7 +7114,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46149.169187962965</v>
@@ -7124,7 +7124,7 @@
         <v>46239.170314664356</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7151,13 +7151,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q94" s="5">
         <v>46238</v>
@@ -7177,7 +7177,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
         <v>46149.1691919213</v>
@@ -7189,7 +7189,7 @@
         <v>46223.5918337037</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7214,13 +7214,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7230,7 +7230,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46149.16919760416</v>
@@ -7242,7 +7242,7 @@
         <v>46223.591830219906</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7267,13 +7267,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7283,7 +7283,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46155.562660428244</v>
@@ -7293,7 +7293,7 @@
         <v>46238.16811421297</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7318,13 +7318,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7334,7 +7334,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46155.56267193287</v>
@@ -7344,7 +7344,7 @@
         <v>46238.16811594907</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7369,13 +7369,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B99" s="9">
         <v>46149.169203125</v>
@@ -7395,7 +7395,7 @@
         <v>46240.170477685184</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7422,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q99" s="9">
         <v>46239</v>
@@ -7448,7 +7448,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46149.16920694444</v>
@@ -7458,7 +7458,7 @@
         <v>46239.16802082176</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7483,13 +7483,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
         <v>46149.16921202546</v>
@@ -7509,7 +7509,7 @@
         <v>46239.16802197917</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7534,13 +7534,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7550,7 +7550,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46155.562741851856</v>
@@ -7560,7 +7560,7 @@
         <v>46239.1680906713</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7585,13 +7585,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46155.562755046296</v>
@@ -7611,7 +7611,7 @@
         <v>46239.16809255787</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7636,13 +7636,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7652,7 +7652,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
         <v>46149.16921689815</v>
@@ -7662,7 +7662,7 @@
         <v>46241.20550412037</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7689,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q104" s="5">
         <v>46240</v>
@@ -7715,7 +7715,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
         <v>46149.169220717595</v>
@@ -7725,7 +7725,7 @@
         <v>46240.16781193287</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7752,13 +7752,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46149.16922577546</v>
@@ -7778,7 +7778,7 @@
         <v>46240.16781346065</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7805,13 +7805,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7821,7 +7821,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
         <v>46155.56285743056</v>
@@ -7831,7 +7831,7 @@
         <v>46240.167892337966</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7858,13 +7858,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46155.56284611111</v>
@@ -7884,7 +7884,7 @@
         <v>46240.16789085648</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7911,13 +7911,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7927,7 +7927,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B109" s="9">
         <v>46149.169270370374</v>
@@ -7937,7 +7937,7 @@
         <v>46237.18984681713</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7964,13 +7964,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q109" s="9">
         <v>46244</v>
@@ -7979,7 +7979,7 @@
         <v>46244</v>
       </c>
       <c r="S109" s="12" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
@@ -8000,7 +8000,7 @@
         <v>46223.592111550926</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8025,10 +8025,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>318</v>
@@ -8051,7 +8051,7 @@
         <v>46223.59211092592</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8076,10 +8076,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>318</v>
@@ -8102,7 +8102,7 @@
         <v>46223.59211032407</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8127,10 +8127,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>321</v>
@@ -8153,7 +8153,7 @@
         <v>46223.59210969908</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8178,10 +8178,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>321</v>
@@ -8291,7 +8291,7 @@
         <v>46245</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
@@ -8312,7 +8312,7 @@
         <v>46155.60144278935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8340,7 +8340,7 @@
         <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>332</v>
@@ -8363,7 +8363,7 @@
         <v>46155.60143921296</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8391,7 +8391,7 @@
         <v>327</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>334</v>
@@ -8414,7 +8414,7 @@
         <v>46155.601436296296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8442,7 +8442,7 @@
         <v>327</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>334</v>
@@ -8465,7 +8465,7 @@
         <v>46155.60143193287</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8493,7 +8493,7 @@
         <v>327</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>334</v>
@@ -8546,7 +8546,7 @@
         <v>324</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>324</v>
@@ -8558,7 +8558,7 @@
         <v>46246</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
@@ -8579,7 +8579,7 @@
         <v>46223.592296180555</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8609,7 +8609,7 @@
         <v>338</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>340</v>
@@ -8632,7 +8632,7 @@
         <v>46223.5922953125</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8662,7 +8662,7 @@
         <v>338</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>340</v>
@@ -8685,7 +8685,7 @@
         <v>46223.592294675924</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8715,7 +8715,7 @@
         <v>338</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>343</v>
@@ -8738,7 +8738,7 @@
         <v>46223.592294050926</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8768,7 +8768,7 @@
         <v>338</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>345</v>
@@ -8797,10 +8797,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I125" s="9">
         <v>46247</v>
@@ -8833,7 +8833,7 @@
         <v>46247</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
@@ -8854,16 +8854,16 @@
         <v>46155.601853796295</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8882,7 +8882,7 @@
         <v>347</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>350</v>
@@ -8905,16 +8905,16 @@
         <v>46155.60185450231</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I127" s="10"/>
       <c r="J127" s="9">
@@ -8933,7 +8933,7 @@
         <v>347</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>352</v>
@@ -8956,16 +8956,16 @@
         <v>46155.60185530093</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -8984,7 +8984,7 @@
         <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>354</v>
@@ -9007,16 +9007,16 @@
         <v>46155.60185603009</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I129" s="10"/>
       <c r="J129" s="9">
@@ -9035,7 +9035,7 @@
         <v>347</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>356</v>
@@ -9064,10 +9064,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I130" s="5">
         <v>46248</v>
@@ -9100,7 +9100,7 @@
         <v>46248</v>
       </c>
       <c r="S130" s="12" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
@@ -9121,16 +9121,16 @@
         <v>46155.602132280095</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9149,7 +9149,7 @@
         <v>358</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>358</v>
@@ -9172,16 +9172,16 @@
         <v>46155.602128969906</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9200,7 +9200,7 @@
         <v>358</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>358</v>
@@ -9223,16 +9223,16 @@
         <v>46155.60212502315</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9251,7 +9251,7 @@
         <v>358</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>358</v>
@@ -9274,16 +9274,16 @@
         <v>46155.602120462965</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9302,7 +9302,7 @@
         <v>358</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>358</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46240.582704201384</v>
+        <v>46244.58203474537</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46237.18984681713</v>
+        <v>46244.16810444444</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>314</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46223.592111550926</v>
+        <v>46244.16810681713</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46223.59211092592</v>
+        <v>46244.16810809028</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46223.59211032407</v>
+        <v>46244.1681899074</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46223.59210969908</v>
+        <v>46244.16819121528</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46244.58203474537</v>
+        <v>46244.816473009254</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -1020,49 +1020,49 @@
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
+    <t>1214596772470213</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596772470228</t>
+  </si>
+  <si>
+    <t>1214739697907446</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214739697907447</t>
+  </si>
+  <si>
+    <t>1214596725560833</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Despacho,Embalaje,Coordinacion Entrega con Cliente,PACKING LIST</t>
+  </si>
+  <si>
+    <t>1214596725560843</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596772470213</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596772470228</t>
-  </si>
-  <si>
-    <t>1214739697907446</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214739697907447</t>
-  </si>
-  <si>
-    <t>1214596725560833</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Despacho,Embalaje,Coordinacion Entrega con Cliente,PACKING LIST</t>
-  </si>
-  <si>
-    <t>1214596725560843</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
     <t>1214596772479919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46244.816473009254</v>
+        <v>46244.91622328704</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46244.16810444444</v>
+        <v>46245.176255266204</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>314</v>
@@ -7978,8 +7978,8 @@
       <c r="R109" s="9">
         <v>46244</v>
       </c>
-      <c r="S109" s="12" t="s">
-        <v>316</v>
+      <c r="S109" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T109" s="10">
         <v>0</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46149.16928524306</v>
@@ -8031,7 +8031,7 @@
         <v>190</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
         <v>46149.16929128472</v>
@@ -8082,7 +8082,7 @@
         <v>190</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8092,7 +8092,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46155.562937361115</v>
@@ -8133,7 +8133,7 @@
         <v>190</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B113" s="9">
         <v>46155.56294952546</v>
@@ -8184,7 +8184,7 @@
         <v>190</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8194,7 +8194,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46149.16929695602</v>
@@ -8204,7 +8204,7 @@
         <v>46155.590775185185</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8228,7 +8228,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8241,26 +8241,26 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B115" s="9">
         <v>46149.169301041664</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46238.19851811342</v>
+        <v>46245.1676669213</v>
       </c>
       <c r="E115" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="F115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="10" t="s">
+      <c r="H115" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="I115" s="10"/>
       <c r="J115" s="9">
@@ -8276,13 +8276,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="9">
         <v>46245</v>
@@ -8291,7 +8291,7 @@
         <v>46245</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46155.60144278935</v>
+        <v>46245.16766902778</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8318,10 +8318,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8337,7 +8337,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>190</v>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46155.60143921296</v>
+        <v>46245.16767038194</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8369,10 +8369,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="I117" s="10"/>
       <c r="J117" s="9">
@@ -8388,7 +8388,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>190</v>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46155.601436296296</v>
+        <v>46245.167689699076</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8420,10 +8420,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8439,7 +8439,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>190</v>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46155.60143193287</v>
+        <v>46245.16769106482</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8471,10 +8471,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>329</v>
       </c>
       <c r="I119" s="10"/>
       <c r="J119" s="9">
@@ -8490,7 +8490,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>190</v>
@@ -8543,13 +8543,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q120" s="5">
         <v>46246</v>
@@ -8558,7 +8558,7 @@
         <v>46246</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
@@ -8818,13 +8818,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>348</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q125" s="9">
         <v>46247</v>
@@ -8833,7 +8833,7 @@
         <v>46247</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
@@ -9085,7 +9085,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>348</v>
@@ -9100,7 +9100,7 @@
         <v>46248</v>
       </c>
       <c r="S130" s="12" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1062,31 +1062,31 @@
     <t>RE-PINTADO,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
+    <t>1214596772479919</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214596772479934</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214739697907448</t>
+  </si>
+  <si>
+    <t>1214739697907449</t>
+  </si>
+  <si>
+    <t>1214596734185007</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596772479919</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214596772479934</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214739697907448</t>
-  </si>
-  <si>
-    <t>1214739697907449</t>
-  </si>
-  <si>
-    <t>1214596734185007</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
   </si>
   <si>
     <t>1214596734185022</t>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46245.1676669213</v>
+        <v>46246.18628197917</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>326</v>
@@ -8290,8 +8290,8 @@
       <c r="R115" s="9">
         <v>46245</v>
       </c>
-      <c r="S115" s="12" t="s">
-        <v>330</v>
+      <c r="S115" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T115" s="10">
         <v>0</v>
@@ -8302,7 +8302,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46149.1693071412</v>
@@ -8343,7 +8343,7 @@
         <v>190</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B117" s="9">
         <v>46149.16931233797</v>
@@ -8394,7 +8394,7 @@
         <v>190</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8404,7 +8404,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
         <v>46155.56303070602</v>
@@ -8445,7 +8445,7 @@
         <v>190</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8455,7 +8455,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B119" s="9">
         <v>46155.56306011574</v>
@@ -8496,7 +8496,7 @@
         <v>190</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8506,17 +8506,17 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46149.1693175</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46239.18009083333</v>
+        <v>46246.16808005787</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8558,7 +8558,7 @@
         <v>46246</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46223.592296180555</v>
+        <v>46246.16808239583</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8606,7 +8606,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>190</v>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46223.5922953125</v>
+        <v>46246.16808361111</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8659,7 +8659,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>190</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46223.592294675924</v>
+        <v>46246.16811077546</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8712,7 +8712,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>190</v>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46223.592294050926</v>
+        <v>46246.16811241898</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8765,7 +8765,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>190</v>
@@ -8833,7 +8833,7 @@
         <v>46247</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
@@ -9100,7 +9100,7 @@
         <v>46248</v>
       </c>
       <c r="S130" s="12" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1086,37 +1086,37 @@
     <t>Embalaje</t>
   </si>
   <si>
+    <t>1214596734185022</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596969889874</t>
+  </si>
+  <si>
+    <t>1214739697907450</t>
+  </si>
+  <si>
+    <t>Embalaje,OT3 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214739697907451</t>
+  </si>
+  <si>
+    <t>Embalaje,OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596969889889</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596734185022</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596969889874</t>
-  </si>
-  <si>
-    <t>1214739697907450</t>
-  </si>
-  <si>
-    <t>Embalaje,OT3 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214739697907451</t>
-  </si>
-  <si>
-    <t>Embalaje,OT4 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596969889889</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
     <t>1214596969899234</t>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46246.16808005787</v>
+        <v>46247.18316747685</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>337</v>
@@ -8557,8 +8557,8 @@
       <c r="R120" s="5">
         <v>46246</v>
       </c>
-      <c r="S120" s="12" t="s">
-        <v>338</v>
+      <c r="S120" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T120" s="6">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
         <v>46149.16932247685</v>
@@ -8612,7 +8612,7 @@
         <v>190</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8622,7 +8622,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
         <v>46149.16932829861</v>
@@ -8665,7 +8665,7 @@
         <v>190</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8675,7 +8675,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
         <v>46155.56313421296</v>
@@ -8718,7 +8718,7 @@
         <v>190</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B124" s="5">
         <v>46155.5631459375</v>
@@ -8771,7 +8771,7 @@
         <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8781,17 +8781,17 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B125" s="9">
         <v>46149.16933366898</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46240.202886747684</v>
+        <v>46247.16765732639</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8821,7 +8821,7 @@
         <v>323</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>323</v>
@@ -8833,7 +8833,7 @@
         <v>46247</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46155.601853796295</v>
+        <v>46247.16765993055</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8879,7 +8879,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>190</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46155.60185450231</v>
+        <v>46247.16766111111</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -8930,7 +8930,7 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>190</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46155.60185530093</v>
+        <v>46247.16771864583</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>249</v>
@@ -8981,7 +8981,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>190</v>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46155.60185603009</v>
+        <v>46247.16771729167</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>247</v>
@@ -9032,7 +9032,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>190</v>
@@ -9088,7 +9088,7 @@
         <v>323</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>359</v>
@@ -9100,7 +9100,7 @@
         <v>46248</v>
       </c>
       <c r="S130" s="12" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1116,40 +1116,40 @@
     <t>OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2,OT3 4315 ZVN 1-9-63/2,OT4 4315 ZVN 1-9-63/2</t>
   </si>
   <si>
+    <t>1214596969899234</t>
+  </si>
+  <si>
+    <t>OT 4315 ZVN 1-9-63/2,PACKING LIST,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1214596969899254</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT 4315 ZVN 1-9-63/2,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1214739697907453</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT4 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214739697907452</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT3 4315 ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1214596624118756</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Logistica:,Costos,Gestion</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596969899234</t>
-  </si>
-  <si>
-    <t>OT 4315 ZVN 1-9-63/2,PACKING LIST,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1214596969899254</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT 4315 ZVN 1-9-63/2,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1214739697907453</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT4 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214739697907452</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT3 4315 ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1214596624118756</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
     <t>1214596624118771</t>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46247.16765732639</v>
+        <v>46248.17570299769</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>346</v>
@@ -8832,8 +8832,8 @@
       <c r="R125" s="9">
         <v>46247</v>
       </c>
-      <c r="S125" s="12" t="s">
-        <v>348</v>
+      <c r="S125" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T125" s="10">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B126" s="5">
         <v>46149.16933884259</v>
@@ -8885,7 +8885,7 @@
         <v>190</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B127" s="9">
         <v>46149.16934681713</v>
@@ -8936,7 +8936,7 @@
         <v>190</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B128" s="5">
         <v>46155.56323461806</v>
@@ -8987,7 +8987,7 @@
         <v>190</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8997,7 +8997,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B129" s="9">
         <v>46155.563225370366</v>
@@ -9038,7 +9038,7 @@
         <v>190</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9048,17 +9048,17 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B130" s="5">
         <v>46149.1693534375</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46241.17305832176</v>
+        <v>46248.16844425926</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9091,7 +9091,7 @@
         <v>347</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q130" s="5">
         <v>46248</v>
@@ -9100,7 +9100,7 @@
         <v>46248</v>
       </c>
       <c r="S130" s="12" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46155.602132280095</v>
+        <v>46248.168446932876</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9146,13 +9146,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46155.602128969906</v>
+        <v>46248.168448055556</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9197,13 +9197,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46155.60212502315</v>
+        <v>46248.16855814814</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>247</v>
@@ -9248,13 +9248,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>247</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46155.602120462965</v>
+        <v>46248.16855982639</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>249</v>
@@ -9299,13 +9299,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>249</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46155.602217824075</v>
+        <v>46248.17726740741</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>368</v>
@@ -9402,7 +9402,7 @@
         <v>365</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>365</v>
@@ -9413,8 +9413,8 @@
       <c r="R136" s="5">
         <v>46255</v>
       </c>
-      <c r="S136" s="7" t="s">
-        <v>101</v>
+      <c r="S136" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46196.86942971065</v>
+        <v>46248.17727576389</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>372</v>
@@ -9465,7 +9465,7 @@
         <v>365</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>365</v>
@@ -9476,8 +9476,8 @@
       <c r="R137" s="9">
         <v>46255</v>
       </c>
-      <c r="S137" s="7" t="s">
-        <v>101</v>
+      <c r="S137" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -1149,40 +1149,40 @@
     <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
+    <t>1214596624118771</t>
+  </si>
+  <si>
+    <t>1214596725601397</t>
+  </si>
+  <si>
+    <t>1214739697907454</t>
+  </si>
+  <si>
+    <t>1214739697907455</t>
+  </si>
+  <si>
+    <t>1214596725601412</t>
+  </si>
+  <si>
+    <t>Cierre proyecto:</t>
+  </si>
+  <si>
+    <t>Costos,Gestion</t>
+  </si>
+  <si>
+    <t>1214596996028539</t>
+  </si>
+  <si>
+    <t>Gestion</t>
+  </si>
+  <si>
+    <t>Nicolás</t>
+  </si>
+  <si>
+    <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214596624118771</t>
-  </si>
-  <si>
-    <t>1214596725601397</t>
-  </si>
-  <si>
-    <t>1214739697907454</t>
-  </si>
-  <si>
-    <t>1214739697907455</t>
-  </si>
-  <si>
-    <t>1214596725601412</t>
-  </si>
-  <si>
-    <t>Cierre proyecto:</t>
-  </si>
-  <si>
-    <t>Costos,Gestion</t>
-  </si>
-  <si>
-    <t>1214596996028539</t>
-  </si>
-  <si>
-    <t>Gestion</t>
-  </si>
-  <si>
-    <t>Nicolás</t>
-  </si>
-  <si>
-    <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
     <t>1214596772411633</t>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46248.16844425926</v>
+        <v>46249.19191792824</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>357</v>
@@ -9099,8 +9099,8 @@
       <c r="R130" s="5">
         <v>46248</v>
       </c>
-      <c r="S130" s="12" t="s">
-        <v>359</v>
+      <c r="S130" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
@@ -9111,7 +9111,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B131" s="9">
         <v>46149.16935909722</v>
@@ -9162,7 +9162,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B132" s="5">
         <v>46149.16936413194</v>
@@ -9213,7 +9213,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B133" s="9">
         <v>46155.56332277777</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B134" s="5">
         <v>46155.56333268518</v>
@@ -9315,7 +9315,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B135" s="9">
         <v>46149.16936914352</v>
@@ -9325,7 +9325,7 @@
         <v>46155.60238891204</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9349,7 +9349,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B136" s="5">
         <v>46149.169373136574</v>
@@ -9372,16 +9372,16 @@
         <v>46248.17726740741</v>
       </c>
       <c r="E136" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G136" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="F136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G136" s="6" t="s">
+      <c r="H136" s="6" t="s">
         <v>369</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="I136" s="5">
         <v>46251</v>
@@ -9399,13 +9399,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>357</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q136" s="5">
         <v>46251</v>
@@ -9414,7 +9414,7 @@
         <v>46255</v>
       </c>
       <c r="S136" s="12" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
@@ -9462,13 +9462,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>357</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q137" s="9">
         <v>46251</v>
@@ -9477,7 +9477,7 @@
         <v>46255</v>
       </c>
       <c r="S137" s="12" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46244.91622328704</v>
+        <v>46252.55709054398</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5380,7 +5380,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46252.55709054398</v>
+        <v>46252.69803008102</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -9369,7 +9369,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46248.17726740741</v>
+        <v>46255.168166979165</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>367</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46248.17727576389</v>
+        <v>46255.16816436342</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>372</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="372">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -1180,9 +1180,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214596772411633</t>
@@ -9369,7 +9366,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46255.168166979165</v>
+        <v>46256.208017129626</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>367</v>
@@ -9413,8 +9410,8 @@
       <c r="R136" s="5">
         <v>46255</v>
       </c>
-      <c r="S136" s="12" t="s">
-        <v>370</v>
+      <c r="S136" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
@@ -9425,17 +9422,17 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B137" s="9">
         <v>46149.169417349534</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46255.16816436342</v>
+        <v>46256.20801716435</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9476,8 +9473,8 @@
       <c r="R137" s="9">
         <v>46255</v>
       </c>
-      <c r="S137" s="12" t="s">
-        <v>370</v>
+      <c r="S137" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -4374,9 +4374,11 @@
       <c r="B46" s="5">
         <v>46149.16868141203</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46258.57238159722</v>
+      </c>
       <c r="D46" s="5">
-        <v>46199.77902613426</v>
+        <v>46258.57239505787</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4411,9 +4413,11 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="12" t="s">
-        <v>92</v>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4616,9 +4620,11 @@
       <c r="B50" s="5">
         <v>46149.16898688657</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46258.57236372685</v>
+      </c>
       <c r="D50" s="5">
-        <v>46242.18436197916</v>
+        <v>46258.572388773144</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4666,10 +4672,10 @@
         <v>33</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5383,7 +5383,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46252.69803008102</v>
+        <v>46258.64931981482</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46238.20141277778</v>
+        <v>46260.57611892361</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>276</v>
@@ -6903,8 +6903,8 @@
       <c r="T89" s="10">
         <v>0</v>
       </c>
-      <c r="U89" s="12" t="s">
-        <v>92</v>
+      <c r="U89" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46239.170314664356</v>
+        <v>46260.576131643524</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>286</v>
@@ -7174,8 +7174,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
-        <v>92</v>
+      <c r="U94" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46241.20550412037</v>
+        <v>46260.5761935301</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>306</v>
@@ -7712,8 +7712,8 @@
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="12" t="s">
-        <v>92</v>
+      <c r="U104" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46245.176255266204</v>
+        <v>46260.57617069445</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>314</v>
@@ -7987,8 +7987,8 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="11" t="s">
-        <v>102</v>
+      <c r="U109" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46247.18316747685</v>
+        <v>46260.57624032407</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>337</v>
@@ -8566,8 +8566,8 @@
       <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="U120" s="12" t="s">
-        <v>92</v>
+      <c r="U120" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46248.17570299769</v>
+        <v>46260.576274074076</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>346</v>
@@ -8841,8 +8841,8 @@
       <c r="T125" s="10">
         <v>0</v>
       </c>
-      <c r="U125" s="11" t="s">
-        <v>102</v>
+      <c r="U125" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46249.19191792824</v>
+        <v>46260.57635934028</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>357</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="372">
   <si>
     <t>50001545 - XEMORTIZ MINERA FRISCO</t>
   </si>
@@ -4624,7 +4624,7 @@
         <v>46258.57236372685</v>
       </c>
       <c r="D50" s="5">
-        <v>46258.572388773144</v>
+        <v>46260.58278</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4674,8 +4674,8 @@
       <c r="T50" s="6">
         <v>1</v>
       </c>
-      <c r="U50" s="7" t="s">
-        <v>27</v>
+      <c r="U50" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4685,9 +4685,11 @@
       <c r="B51" s="9">
         <v>46149.168991412036</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46260.58275773148</v>
+      </c>
       <c r="D51" s="9">
-        <v>46241.16831026621</v>
+        <v>46260.582761770835</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4736,9 +4738,11 @@
       <c r="B52" s="5">
         <v>46149.16900017361</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46260.582758749995</v>
+      </c>
       <c r="D52" s="5">
-        <v>46241.16831137732</v>
+        <v>46260.5827622338</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4787,9 +4791,11 @@
       <c r="B53" s="9">
         <v>46155.577817384255</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46260.58275954861</v>
+      </c>
       <c r="D53" s="9">
-        <v>46241.1683981713</v>
+        <v>46260.58276263889</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -4838,9 +4844,11 @@
       <c r="B54" s="5">
         <v>46155.577829050926</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46260.582760254634</v>
+      </c>
       <c r="D54" s="5">
-        <v>46241.1684000463</v>
+        <v>46260.582763032406</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5334,7 +5342,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46224.67388769676</v>
+        <v>46260.57786643518</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5370,7 +5378,9 @@
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
       <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="U62" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
@@ -5949,9 +5959,11 @@
       <c r="B73" s="9">
         <v>46149.169119768514</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9">
+        <v>46260.57784618056</v>
+      </c>
       <c r="D73" s="9">
-        <v>46228.16710329861</v>
+        <v>46260.57785944444</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>242</v>
@@ -5999,10 +6011,10 @@
         <v>33</v>
       </c>
       <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6012,9 +6024,11 @@
       <c r="B74" s="5">
         <v>46149.16912365741</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46260.57780645833</v>
+      </c>
       <c r="D74" s="5">
-        <v>46227.16842824074</v>
+        <v>46260.57780840278</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -6065,9 +6079,11 @@
       <c r="B75" s="9">
         <v>46149.16912908565</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46260.57781854167</v>
+      </c>
       <c r="D75" s="9">
-        <v>46227.16842944444</v>
+        <v>46260.57782057871</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -6118,9 +6134,11 @@
       <c r="B76" s="5">
         <v>46155.56233189815</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46260.57782550926</v>
+      </c>
       <c r="D76" s="5">
-        <v>46227.168525636574</v>
+        <v>46260.57782712963</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6171,9 +6189,11 @@
       <c r="B77" s="9">
         <v>46155.562344351856</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="9">
+        <v>46260.5778320949</v>
+      </c>
       <c r="D77" s="9">
-        <v>46227.168527118054</v>
+        <v>46260.57783362269</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6224,9 +6244,11 @@
       <c r="B78" s="5">
         <v>46149.16913412037</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46260.58232613426</v>
+      </c>
       <c r="D78" s="5">
-        <v>46216.87183908565</v>
+        <v>46260.58233622686</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6261,9 +6283,11 @@
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
       <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="12" t="s">
-        <v>92</v>
+      <c r="T78" s="6">
+        <v>1</v>
+      </c>
+      <c r="U78" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6466,9 +6490,11 @@
       <c r="B82" s="5">
         <v>46149.16915236111</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46260.58231159722</v>
+      </c>
       <c r="D82" s="5">
-        <v>46232.203200497686</v>
+        <v>46260.5823260301</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>261</v>
@@ -6516,10 +6542,10 @@
         <v>33</v>
       </c>
       <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="12" t="s">
-        <v>92</v>
+        <v>1</v>
+      </c>
+      <c r="U82" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6531,7 +6557,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46155.58270766203</v>
+        <v>46260.58286214121</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>264</v>
@@ -6567,7 +6593,9 @@
       <c r="R83" s="10"/>
       <c r="S83" s="10"/>
       <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+      <c r="U83" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
@@ -6576,9 +6604,11 @@
       <c r="B84" s="5">
         <v>46149.16916049768</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46260.581344895836</v>
+      </c>
       <c r="D84" s="5">
-        <v>46237.537617152775</v>
+        <v>46260.58293175926</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6626,7 +6656,7 @@
         <v>33</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U84" s="7" t="s">
         <v>27</v>
@@ -6639,9 +6669,11 @@
       <c r="B85" s="9">
         <v>46149.16916685185</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46260.58126997685</v>
+      </c>
       <c r="D85" s="9">
-        <v>46234.16939539352</v>
+        <v>46260.58231699074</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6692,9 +6724,11 @@
       <c r="B86" s="5">
         <v>46149.16917037037</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46260.58133001157</v>
+      </c>
       <c r="D86" s="5">
-        <v>46234.16939739583</v>
+        <v>46260.58231762731</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6745,9 +6779,11 @@
       <c r="B87" s="9">
         <v>46155.5624656713</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="9">
+        <v>46260.57814078704</v>
+      </c>
       <c r="D87" s="9">
-        <v>46234.16952005787</v>
+        <v>46260.57814216435</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>247</v>
@@ -6798,9 +6834,11 @@
       <c r="B88" s="5">
         <v>46155.562495266204</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46260.57814827547</v>
+      </c>
       <c r="D88" s="5">
-        <v>46234.16952178241</v>
+        <v>46260.57814979166</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>249</v>
@@ -6851,9 +6889,11 @@
       <c r="B89" s="9">
         <v>46149.16917405093</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9">
+        <v>46260.582378935185</v>
+      </c>
       <c r="D89" s="9">
-        <v>46260.57611892361</v>
+        <v>46260.582932060184</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>276</v>
@@ -6901,7 +6941,7 @@
         <v>33</v>
       </c>
       <c r="T89" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U89" s="7" t="s">
         <v>27</v>
@@ -7020,9 +7060,11 @@
       <c r="B92" s="5">
         <v>46155.56256662037</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46260.582352349535</v>
+      </c>
       <c r="D92" s="5">
-        <v>46237.16895704861</v>
+        <v>46260.58235793981</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -7071,9 +7113,11 @@
       <c r="B93" s="9">
         <v>46155.56257849537</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46260.58236104167</v>
+      </c>
       <c r="D93" s="9">
-        <v>46237.16895965278</v>
+        <v>46260.582362430556</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -7122,9 +7166,11 @@
       <c r="B94" s="5">
         <v>46149.169187962965</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46260.582451145834</v>
+      </c>
       <c r="D94" s="5">
-        <v>46260.576131643524</v>
+        <v>46260.58293240741</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>286</v>
@@ -7172,7 +7218,7 @@
         <v>33</v>
       </c>
       <c r="T94" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U94" s="7" t="s">
         <v>27</v>
@@ -7291,9 +7337,11 @@
       <c r="B97" s="9">
         <v>46155.562660428244</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="9">
+        <v>46260.58243761574</v>
+      </c>
       <c r="D97" s="9">
-        <v>46238.16811421297</v>
+        <v>46260.58243894676</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7342,9 +7390,11 @@
       <c r="B98" s="5">
         <v>46155.56267193287</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46260.58243026621</v>
+      </c>
       <c r="D98" s="5">
-        <v>46238.16811594907</v>
+        <v>46260.5824315162</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7393,9 +7443,11 @@
       <c r="B99" s="9">
         <v>46149.169203125</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="9">
+        <v>46260.582532685185</v>
+      </c>
       <c r="D99" s="9">
-        <v>46240.170477685184</v>
+        <v>46260.5825537037</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>295</v>
@@ -7443,7 +7495,7 @@
         <v>33</v>
       </c>
       <c r="T99" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U99" s="7" t="s">
         <v>27</v>
@@ -7456,9 +7508,11 @@
       <c r="B100" s="5">
         <v>46149.16920694444</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46260.58251296297</v>
+      </c>
       <c r="D100" s="5">
-        <v>46239.16802082176</v>
+        <v>46260.582517118055</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7507,9 +7561,11 @@
       <c r="B101" s="9">
         <v>46149.16921202546</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="9">
+        <v>46260.582514016205</v>
+      </c>
       <c r="D101" s="9">
-        <v>46239.16802197917</v>
+        <v>46260.582517731484</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7558,9 +7614,11 @@
       <c r="B102" s="5">
         <v>46155.562741851856</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46260.58251478009</v>
+      </c>
       <c r="D102" s="5">
-        <v>46239.1680906713</v>
+        <v>46260.58251826389</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>190</v>
@@ -7609,9 +7667,11 @@
       <c r="B103" s="9">
         <v>46155.562755046296</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9">
+        <v>46260.582515462964</v>
+      </c>
       <c r="D103" s="9">
-        <v>46239.16809255787</v>
+        <v>46260.58251872685</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>190</v>
@@ -7660,9 +7720,11 @@
       <c r="B104" s="5">
         <v>46149.16921689815</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46260.58263561343</v>
+      </c>
       <c r="D104" s="5">
-        <v>46260.5761935301</v>
+        <v>46260.58293283565</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>306</v>
@@ -7710,7 +7772,7 @@
         <v>33</v>
       </c>
       <c r="T104" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U104" s="7" t="s">
         <v>27</v>
@@ -7723,9 +7785,11 @@
       <c r="B105" s="9">
         <v>46149.169220717595</v>
       </c>
-      <c r="C105" s="10"/>
+      <c r="C105" s="9">
+        <v>46260.58261738426</v>
+      </c>
       <c r="D105" s="9">
-        <v>46240.16781193287</v>
+        <v>46260.58262076389</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>190</v>
@@ -7776,9 +7840,11 @@
       <c r="B106" s="5">
         <v>46149.16922577546</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46260.58261824074</v>
+      </c>
       <c r="D106" s="5">
-        <v>46240.16781346065</v>
+        <v>46260.58262123843</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>190</v>
@@ -7829,9 +7895,11 @@
       <c r="B107" s="9">
         <v>46155.56285743056</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="9">
+        <v>46260.58261886574</v>
+      </c>
       <c r="D107" s="9">
-        <v>46240.167892337966</v>
+        <v>46260.582621678244</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>190</v>
@@ -7882,9 +7950,11 @@
       <c r="B108" s="5">
         <v>46155.56284611111</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46260.58261943287</v>
+      </c>
       <c r="D108" s="5">
-        <v>46240.16789085648</v>
+        <v>46260.58262208333</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7935,9 +8005,11 @@
       <c r="B109" s="9">
         <v>46149.169270370374</v>
       </c>
-      <c r="C109" s="10"/>
+      <c r="C109" s="9">
+        <v>46260.58284188657</v>
+      </c>
       <c r="D109" s="9">
-        <v>46260.57617069445</v>
+        <v>46260.58293314815</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>314</v>
@@ -7985,7 +8057,7 @@
         <v>33</v>
       </c>
       <c r="T109" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U109" s="7" t="s">
         <v>27</v>
@@ -7998,9 +8070,11 @@
       <c r="B110" s="5">
         <v>46149.16928524306</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46260.58282289351</v>
+      </c>
       <c r="D110" s="5">
-        <v>46244.16810681713</v>
+        <v>46260.58282577546</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -8049,9 +8123,11 @@
       <c r="B111" s="9">
         <v>46149.16929128472</v>
       </c>
-      <c r="C111" s="10"/>
+      <c r="C111" s="9">
+        <v>46260.582823599536</v>
+      </c>
       <c r="D111" s="9">
-        <v>46244.16810809028</v>
+        <v>46260.582826157406</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -8100,9 +8176,11 @@
       <c r="B112" s="5">
         <v>46155.562937361115</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46260.58282412037</v>
+      </c>
       <c r="D112" s="5">
-        <v>46244.1681899074</v>
+        <v>46260.58282649306</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8151,9 +8229,11 @@
       <c r="B113" s="9">
         <v>46155.56294952546</v>
       </c>
-      <c r="C113" s="10"/>
+      <c r="C113" s="9">
+        <v>46260.58282461806</v>
+      </c>
       <c r="D113" s="9">
-        <v>46244.16819121528</v>
+        <v>46260.582826770835</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8204,7 +8284,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46155.590775185185</v>
+        <v>46260.58701501157</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>323</v>
@@ -8251,7 +8331,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46246.18628197917</v>
+        <v>46260.5828516551</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>326</v>
@@ -8312,7 +8392,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46245.16766902778</v>
+        <v>46260.582835636575</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8363,7 +8443,7 @@
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46245.16767038194</v>
+        <v>46260.58283561343</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8414,7 +8494,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46245.167689699076</v>
+        <v>46260.58283261574</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8465,7 +8545,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46245.16769106482</v>
+        <v>46260.58283261574</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8514,9 +8594,11 @@
       <c r="B120" s="5">
         <v>46149.1693175</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46260.58651121528</v>
+      </c>
       <c r="D120" s="5">
-        <v>46260.57624032407</v>
+        <v>46260.587021643514</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>337</v>
@@ -8564,7 +8646,7 @@
         <v>33</v>
       </c>
       <c r="T120" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U120" s="7" t="s">
         <v>27</v>
@@ -8577,9 +8659,11 @@
       <c r="B121" s="9">
         <v>46149.16932247685</v>
       </c>
-      <c r="C121" s="10"/>
+      <c r="C121" s="9">
+        <v>46260.58662984954</v>
+      </c>
       <c r="D121" s="9">
-        <v>46246.16808239583</v>
+        <v>46260.58663115741</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8630,9 +8714,11 @@
       <c r="B122" s="5">
         <v>46149.16932829861</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46260.58667422454</v>
+      </c>
       <c r="D122" s="5">
-        <v>46246.16808361111</v>
+        <v>46260.586675555554</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8683,9 +8769,11 @@
       <c r="B123" s="9">
         <v>46155.56313421296</v>
       </c>
-      <c r="C123" s="10"/>
+      <c r="C123" s="9">
+        <v>46260.58672921296</v>
+      </c>
       <c r="D123" s="9">
-        <v>46246.16811077546</v>
+        <v>46260.58673065972</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8736,9 +8824,11 @@
       <c r="B124" s="5">
         <v>46155.5631459375</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46260.58678055556</v>
+      </c>
       <c r="D124" s="5">
-        <v>46246.16811241898</v>
+        <v>46260.58678203703</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8789,9 +8879,11 @@
       <c r="B125" s="9">
         <v>46149.16933366898</v>
       </c>
-      <c r="C125" s="10"/>
+      <c r="C125" s="9">
+        <v>46260.58700836806</v>
+      </c>
       <c r="D125" s="9">
-        <v>46260.576274074076</v>
+        <v>46260.58705417824</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>346</v>
@@ -8839,7 +8931,7 @@
         <v>33</v>
       </c>
       <c r="T125" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U125" s="7" t="s">
         <v>27</v>
@@ -8852,9 +8944,11 @@
       <c r="B126" s="5">
         <v>46149.16933884259</v>
       </c>
-      <c r="C126" s="6"/>
+      <c r="C126" s="5">
+        <v>46260.58698357639</v>
+      </c>
       <c r="D126" s="5">
-        <v>46247.16765993055</v>
+        <v>46260.58698681713</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8903,9 +8997,11 @@
       <c r="B127" s="9">
         <v>46149.16934681713</v>
       </c>
-      <c r="C127" s="10"/>
+      <c r="C127" s="9">
+        <v>46260.58698438657</v>
+      </c>
       <c r="D127" s="9">
-        <v>46247.16766111111</v>
+        <v>46260.58698740741</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -8954,9 +9050,11 @@
       <c r="B128" s="5">
         <v>46155.56323461806</v>
       </c>
-      <c r="C128" s="6"/>
+      <c r="C128" s="5">
+        <v>46260.58698504629</v>
+      </c>
       <c r="D128" s="5">
-        <v>46247.16771864583</v>
+        <v>46260.58698890047</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>249</v>
@@ -9005,9 +9103,11 @@
       <c r="B129" s="9">
         <v>46155.563225370366</v>
       </c>
-      <c r="C129" s="10"/>
+      <c r="C129" s="9">
+        <v>46260.58698559028</v>
+      </c>
       <c r="D129" s="9">
-        <v>46247.16771729167</v>
+        <v>46260.58699275463</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>247</v>
@@ -9121,7 +9221,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46248.168446932876</v>
+        <v>46260.586999340274</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9172,7 +9272,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46248.168448055556</v>
+        <v>46260.587002245375</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9223,7 +9323,7 @@
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46248.16855814814</v>
+        <v>46260.5870028125</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>247</v>
@@ -9274,7 +9374,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46248.16855982639</v>
+        <v>46260.58700177084</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>249</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5393,7 +5393,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46258.64931981482</v>
+        <v>46260.67955327546</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -744,7 +744,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4315 ZVN 1-9-63/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
     <t>1214596725492919</t>
@@ -5393,7 +5393,7 @@
         <v>46224.67373001158</v>
       </c>
       <c r="D63" s="9">
-        <v>46260.67955327546</v>
+        <v>46261.600822465276</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>

--- a/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
+++ b/data/50001545 - XEMORTIZ MINERA FRISCO.xlsx
@@ -2186,7 +2186,7 @@
         <v>46196.871632326394</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.87164857639</v>
+        <v>46264.11071415509</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
